--- a/KLR_Simple_Tracker.xlsx
+++ b/KLR_Simple_Tracker.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="92">
   <si>
     <t xml:space="preserve">MY TRADING RULES</t>
   </si>
@@ -97,7 +97,7 @@
     <t xml:space="preserve">Pairs</t>
   </si>
   <si>
-    <t xml:space="preserve">XAUUSD, EURUSD, GBPUSD, GER40, US500. Nothing else.</t>
+    <t xml:space="preserve">Main: XAUUSD, EURUSD, GBPUSD, GER40, US500. Extras: US100, BTCUSD. Nothing else.</t>
   </si>
   <si>
     <t xml:space="preserve">Never</t>
@@ -190,16 +190,28 @@
     <t xml:space="preserve">1 point = $1 per lot at many brokers. CHECK in MT5.</t>
   </si>
   <si>
+    <t xml:space="preserve">US100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extra. 1 point = $1 per lot at many brokers. CHECK in MT5.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Account</t>
   </si>
   <si>
+    <t xml:space="preserve">BTCUSD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extra. $1 move = $1 per lot (1 BTC contract). CHECK in MT5.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risk per trade ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.5% of starting balance. Change it on the Trade Log tab.)</t>
+  </si>
+  <si>
     <t xml:space="preserve">In MT5: right-click the pair &gt; Specification. Check the contract size; change the $ value if yours is different.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Risk per trade ($)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.5% of starting balance. Change it on the Trade Log tab.)</t>
   </si>
   <si>
     <t xml:space="preserve">TRADE LOG</t>
@@ -1120,7 +1132,7 @@
         <v>36</v>
       </c>
       <c r="B9" s="9" t="n">
-        <f aca="false">IFERROR(ROUND(ABS(B5-B6)/VLOOKUP(B4,$D$19:$F$23,2,FALSE()),1),"")</f>
+        <f aca="false">IFERROR(ROUND(ABS(B5-B6)/VLOOKUP(B4,$D$19:$F$25,2,FALSE()),1),"")</f>
         <v>30</v>
       </c>
     </row>
@@ -1138,7 +1150,7 @@
         <v>38</v>
       </c>
       <c r="B11" s="12" t="n">
-        <f aca="false">IFERROR(ROUNDDOWN(B10/(B9*VLOOKUP(B4,$D$19:$F$23,3,FALSE())),2),"")</f>
+        <f aca="false">IFERROR(ROUNDDOWN(B10/(B9*VLOOKUP(B4,$D$19:$F$25,3,FALSE())),2),"")</f>
         <v>0.16</v>
       </c>
       <c r="C11" s="4" t="s">
@@ -1159,7 +1171,7 @@
         <v>41</v>
       </c>
       <c r="B13" s="10" t="n">
-        <f aca="false">IFERROR(B11*B9*1.5*VLOOKUP(B4,$D$19:$F$23,3,FALSE()),"")</f>
+        <f aca="false">IFERROR(B11*B9*1.5*VLOOKUP(B4,$D$19:$F$25,3,FALSE()),"")</f>
         <v>72</v>
       </c>
     </row>
@@ -1257,17 +1269,40 @@
         <v>54</v>
       </c>
     </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D24" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="D25" s="19" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="19" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B26" s="10" t="n">
         <f aca="false">'Trade Log'!$M$2*'Trade Log'!$M$3</f>
@@ -1276,13 +1311,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="19" t="s">
-        <v>58</v>
+        <v>61</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B4" type="list">
-      <formula1>$D$19:$D$23</formula1>
+      <formula1>$D$19:$D$25</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -1319,12 +1357,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L2" s="11" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="M2" s="20" t="n">
         <v>10000</v>
@@ -1332,10 +1370,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="M3" s="21" t="n">
         <v>0.005</v>
@@ -1343,10 +1381,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="M4" s="22" t="n">
         <f aca="false">M2+SUM(J7:J206)</f>
@@ -1355,40 +1393,40 @@
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>31</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E6" s="16" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="J6" s="16" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="K6" s="16" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="L6" s="16" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7202,7 +7240,7 @@
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B7:B206" type="list">
-      <formula1>Calculator!$D$19:$D$23</formula1>
+      <formula1>Calculator!$D$19:$D$25</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K7:K206" type="list">
@@ -7225,7 +7263,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
@@ -7235,12 +7273,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="27" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B3" s="28" t="n">
         <f aca="false">COUNT('Trade Log'!I7:I206)</f>
@@ -7249,7 +7287,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="27" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B4" s="28" t="n">
         <f aca="false">COUNTIF('Trade Log'!H7:H206,"WIN")</f>
@@ -7258,7 +7296,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B5" s="28" t="n">
         <f aca="false">COUNTIF('Trade Log'!H7:H206,"LOSS")</f>
@@ -7267,7 +7305,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B6" s="29" t="n">
         <f aca="false">IFERROR(B4/B3,0)</f>
@@ -7276,7 +7314,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B7" s="30" t="n">
         <f aca="false">SUM('Trade Log'!I7:I206)</f>
@@ -7285,7 +7323,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B8" s="30" t="n">
         <f aca="false">IFERROR(B7/B3,0)</f>
@@ -7294,7 +7332,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B9" s="29" t="n">
         <f aca="false">IFERROR(COUNTIF('Trade Log'!K7:K206,"Yes")/B3,0)</f>
@@ -7303,7 +7341,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B10" s="31" t="n">
         <f aca="false">SUM('Trade Log'!J7:J206)</f>
@@ -7312,7 +7350,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B11" s="22" t="n">
         <f aca="false">'Trade Log'!M4</f>
@@ -7321,7 +7359,7 @@
     </row>
     <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="32" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7336,12 +7374,12 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="32" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7349,10 +7387,10 @@
         <v>31</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7417,6 +7455,32 @@
       </c>
       <c r="C24" s="24" t="n">
         <f aca="false">SUMIF('Trade Log'!B7:B206,A24,'Trade Log'!I7:I206)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" s="34" t="n">
+        <f aca="false">COUNTIFS('Trade Log'!B7:B206,A25,'Trade Log'!I7:I206,"&gt;-99")</f>
+        <v>0</v>
+      </c>
+      <c r="C25" s="24" t="n">
+        <f aca="false">SUMIF('Trade Log'!B7:B206,A25,'Trade Log'!I7:I206)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" s="34" t="n">
+        <f aca="false">COUNTIFS('Trade Log'!B7:B206,A26,'Trade Log'!I7:I206,"&gt;-99")</f>
+        <v>0</v>
+      </c>
+      <c r="C26" s="24" t="n">
+        <f aca="false">SUMIF('Trade Log'!B7:B206,A26,'Trade Log'!I7:I206)</f>
         <v>0</v>
       </c>
     </row>

--- a/KLR_Simple_Tracker.xlsx
+++ b/KLR_Simple_Tracker.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="95">
   <si>
     <t xml:space="preserve">MY TRADING RULES</t>
   </si>
@@ -136,7 +136,7 @@
     <t xml:space="preserve">Stop size (pips / points)</t>
   </si>
   <si>
-    <t xml:space="preserve">Money at risk ($)</t>
+    <t xml:space="preserve">Max risk allowed ($)</t>
   </si>
   <si>
     <t xml:space="preserve">LOT SIZE</t>
@@ -151,10 +151,16 @@
     <t xml:space="preserve">Profit if target hit ($)</t>
   </si>
   <si>
-    <t xml:space="preserve">If LOT SIZE shows 0.00, your stop is too big for your risk. Skip the trade.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAIR SETTINGS (check once in MT5)</t>
+    <t xml:space="preserve">Actual risk with this lot ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If LOT SIZE says SKIP, your stop is too big for the smallest lot. Skip the trade.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lots are rounded DOWN to what MT5 allows, so actual risk can be a bit under $50.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAIR SETTINGS (from your Deriv MT5 Standard account)</t>
   </si>
   <si>
     <t xml:space="preserve">1 pip / point =</t>
@@ -163,16 +169,22 @@
     <t xml:space="preserve">$ per pip, 1 lot</t>
   </si>
   <si>
-    <t xml:space="preserve">How to check</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gold: 0.10 move = $10 per lot (100 oz contract)</t>
+    <t xml:space="preserve">Min lot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lot step</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contract 100 oz: 0.10 move = $10 per lot</t>
   </si>
   <si>
     <t xml:space="preserve">EURUSD</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0001 move = $10 per lot</t>
+    <t xml:space="preserve">Contract 100,000: 0.0001 move = $10 per lot</t>
   </si>
   <si>
     <t xml:space="preserve">GBPUSD</t>
@@ -181,39 +193,39 @@
     <t xml:space="preserve">GER40</t>
   </si>
   <si>
-    <t xml:space="preserve">1 point = 1 EUR per lot at most brokers. CHECK in MT5.</t>
+    <t xml:space="preserve">Contract 1: 1 point = 1 EUR (about $1.15). If profit currency is USD, change to 1.00</t>
   </si>
   <si>
     <t xml:space="preserve">US500</t>
   </si>
   <si>
-    <t xml:space="preserve">1 point = $1 per lot at many brokers. CHECK in MT5.</t>
+    <t xml:space="preserve">Contract 1: 1 point = $1 per lot</t>
   </si>
   <si>
     <t xml:space="preserve">US100</t>
   </si>
   <si>
-    <t xml:space="preserve">Extra. 1 point = $1 per lot at many brokers. CHECK in MT5.</t>
+    <t xml:space="preserve">Extra. Contract 1: 1 point = $1 per lot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BTCUSD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extra. Contract 1 BTC: $1 move = $1 per lot</t>
   </si>
   <si>
     <t xml:space="preserve">Account</t>
   </si>
   <si>
-    <t xml:space="preserve">BTCUSD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extra. $1 move = $1 per lot (1 BTC contract). CHECK in MT5.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Risk per trade ($)</t>
   </si>
   <si>
+    <t xml:space="preserve">Checked on Deriv MT5 Standard, 8 Oct 2026. Your MT5 names: US Tech 100 = US100, US SP 500 = US500, Germany 40 = GER40.</t>
+  </si>
+  <si>
     <t xml:space="preserve">(0.5% of starting balance. Change it on the Trade Log tab.)</t>
   </si>
   <si>
-    <t xml:space="preserve">In MT5: right-click the pair &gt; Specification. Check the contract size; change the $ value if yours is different.</t>
-  </si>
-  <si>
     <t xml:space="preserve">TRADE LOG</t>
   </si>
   <si>
@@ -257,9 +269,6 @@
   </si>
   <si>
     <t xml:space="preserve">Followed all rules?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notes</t>
   </si>
   <si>
     <t xml:space="preserve">HOW AM I DOING?</t>
@@ -404,16 +413,16 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="9"/>
+      <color rgb="FF595959"/>
       <name val="Arial Nova"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF595959"/>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial Nova"/>
       <family val="0"/>
       <charset val="1"/>
@@ -510,7 +519,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -571,11 +580,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -587,8 +600,8 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="168" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="170" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1073,7 +1086,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -1081,7 +1094,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1132,7 +1146,7 @@
         <v>36</v>
       </c>
       <c r="B9" s="9" t="n">
-        <f aca="false">IFERROR(ROUND(ABS(B5-B6)/VLOOKUP(B4,$D$19:$F$25,2,FALSE()),1),"")</f>
+        <f aca="false">IFERROR(ROUND(ABS(B5-B6)/VLOOKUP(B4,$D$19:$H$25,2,FALSE()),1),"")</f>
         <v>30</v>
       </c>
     </row>
@@ -1141,7 +1155,7 @@
         <v>37</v>
       </c>
       <c r="B10" s="10" t="n">
-        <f aca="false">B26</f>
+        <f aca="false">B27</f>
         <v>50</v>
       </c>
     </row>
@@ -1150,7 +1164,7 @@
         <v>38</v>
       </c>
       <c r="B11" s="12" t="n">
-        <f aca="false">IFERROR(ROUNDDOWN(B10/(B9*VLOOKUP(B4,$D$19:$F$25,3,FALSE())),2),"")</f>
+        <f aca="false">IFERROR(IF(B10/(B9*VLOOKUP(B4,$D$19:$H$25,3,FALSE()))&lt;VLOOKUP(B4,$D$19:$H$25,4,FALSE()),"SKIP",ROUNDDOWN(B10/(B9*VLOOKUP(B4,$D$19:$H$25,3,FALSE()))/VLOOKUP(B4,$D$19:$H$25,5,FALSE())+0.000001,0)*VLOOKUP(B4,$D$19:$H$25,5,FALSE())),"")</f>
         <v>0.16</v>
       </c>
       <c r="C11" s="4" t="s">
@@ -1171,150 +1185,212 @@
         <v>41</v>
       </c>
       <c r="B13" s="10" t="n">
-        <f aca="false">IFERROR(B11*B9*1.5*VLOOKUP(B4,$D$19:$F$25,3,FALSE()),"")</f>
+        <f aca="false">IFERROR(B11*B9*1.5*VLOOKUP(B4,$D$19:$H$25,3,FALSE()),"")</f>
         <v>72</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
         <v>42</v>
       </c>
+      <c r="B14" s="10" t="n">
+        <f aca="false">IFERROR(B11*B9*VLOOKUP(B4,$D$19:$H$25,3,FALSE()),"")</f>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="14" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D17" s="15" t="s">
-        <v>43</v>
+      <c r="A17" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="E18" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="F18" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="G18" s="16" t="s">
+      <c r="E18" s="17" t="s">
         <v>46</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="H18" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I18" s="17" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D19" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E19" s="17" t="n">
+      <c r="E19" s="18" t="n">
         <v>0.1</v>
       </c>
-      <c r="F19" s="18" t="n">
+      <c r="F19" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="G19" s="19" t="s">
-        <v>47</v>
+      <c r="G19" s="20" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H19" s="20" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I19" s="15" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D20" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E20" s="17" t="n">
+        <v>52</v>
+      </c>
+      <c r="E20" s="18" t="n">
         <v>0.0001</v>
       </c>
-      <c r="F20" s="18" t="n">
+      <c r="F20" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="G20" s="19" t="s">
-        <v>49</v>
+      <c r="G20" s="20" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H20" s="20" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I20" s="15" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D21" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="E21" s="17" t="n">
+        <v>54</v>
+      </c>
+      <c r="E21" s="18" t="n">
         <v>0.0001</v>
       </c>
-      <c r="F21" s="18" t="n">
+      <c r="F21" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="G21" s="19" t="s">
-        <v>49</v>
+      <c r="G21" s="20" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H21" s="20" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I21" s="15" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D22" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="E22" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="E22" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F22" s="18" t="n">
+      <c r="F22" s="19" t="n">
         <v>1.15</v>
       </c>
-      <c r="G22" s="19" t="s">
-        <v>52</v>
+      <c r="G22" s="20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H22" s="20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I22" s="15" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D23" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E23" s="17" t="n">
+        <v>57</v>
+      </c>
+      <c r="E23" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F23" s="18" t="n">
+      <c r="F23" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="19" t="s">
-        <v>54</v>
+      <c r="G23" s="20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H23" s="20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I23" s="15" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D24" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="E24" s="17" t="n">
+        <v>59</v>
+      </c>
+      <c r="E24" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="18" t="n">
+      <c r="F24" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="19" t="s">
-        <v>56</v>
+      <c r="G24" s="20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H24" s="20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="15" t="s">
-        <v>57</v>
-      </c>
       <c r="D25" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E25" s="17" t="n">
+        <v>61</v>
+      </c>
+      <c r="E25" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="18" t="n">
+      <c r="F25" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="19" t="s">
-        <v>59</v>
+      <c r="G25" s="20" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H25" s="20" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I25" s="15" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B26" s="10" t="n">
+      <c r="A26" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B27" s="10" t="n">
         <f aca="false">'Trade Log'!$M$2*'Trade Log'!$M$3</f>
         <v>50</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="D27" s="19" t="s">
-        <v>62</v>
+      <c r="D27" s="15" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="15" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1357,80 +1433,80 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L2" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="M2" s="20" t="n">
+        <v>68</v>
+      </c>
+      <c r="M2" s="21" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="M3" s="21" t="n">
+        <v>70</v>
+      </c>
+      <c r="M3" s="22" t="n">
         <v>0.005</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="M4" s="22" t="n">
+        <v>72</v>
+      </c>
+      <c r="M4" s="23" t="n">
         <f aca="false">M2+SUM(J7:J206)</f>
         <v>10000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="B6" s="16" t="s">
+      <c r="A6" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="E6" s="16" t="s">
+      <c r="C6" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="G6" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="H6" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="I6" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="J6" s="16" t="s">
+      <c r="F6" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="K6" s="16" t="s">
+      <c r="G6" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="L6" s="16" t="s">
+      <c r="H6" s="17" t="s">
         <v>78</v>
       </c>
+      <c r="I6" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="K6" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="L6" s="17" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="23"/>
+      <c r="A7" s="24"/>
       <c r="B7" s="6"/>
       <c r="C7" s="8" t="str">
         <f aca="false">IF(OR(D7="",E7="",D7=E7),"",IF(E7&lt;D7,"BUY","SELL"))</f>
@@ -1447,19 +1523,19 @@
         <f aca="false">IF(I7="","",IF(I7&gt;0,"WIN",IF(I7&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I7" s="24" t="str">
+      <c r="I7" s="25" t="str">
         <f aca="false">IF(OR(G7="",C7=""),"",ROUND((G7-D7)/(D7-E7),2))</f>
         <v/>
       </c>
-      <c r="J7" s="25" t="str">
+      <c r="J7" s="26" t="str">
         <f aca="false">IF(I7="","",ROUND(I7*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K7" s="6"/>
-      <c r="L7" s="26"/>
+      <c r="L7" s="27"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="23"/>
+      <c r="A8" s="24"/>
       <c r="B8" s="6"/>
       <c r="C8" s="8" t="str">
         <f aca="false">IF(OR(D8="",E8="",D8=E8),"",IF(E8&lt;D8,"BUY","SELL"))</f>
@@ -1476,19 +1552,19 @@
         <f aca="false">IF(I8="","",IF(I8&gt;0,"WIN",IF(I8&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I8" s="24" t="str">
+      <c r="I8" s="25" t="str">
         <f aca="false">IF(OR(G8="",C8=""),"",ROUND((G8-D8)/(D8-E8),2))</f>
         <v/>
       </c>
-      <c r="J8" s="25" t="str">
+      <c r="J8" s="26" t="str">
         <f aca="false">IF(I8="","",ROUND(I8*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K8" s="6"/>
-      <c r="L8" s="26"/>
+      <c r="L8" s="27"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="23"/>
+      <c r="A9" s="24"/>
       <c r="B9" s="6"/>
       <c r="C9" s="8" t="str">
         <f aca="false">IF(OR(D9="",E9="",D9=E9),"",IF(E9&lt;D9,"BUY","SELL"))</f>
@@ -1505,19 +1581,19 @@
         <f aca="false">IF(I9="","",IF(I9&gt;0,"WIN",IF(I9&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I9" s="24" t="str">
+      <c r="I9" s="25" t="str">
         <f aca="false">IF(OR(G9="",C9=""),"",ROUND((G9-D9)/(D9-E9),2))</f>
         <v/>
       </c>
-      <c r="J9" s="25" t="str">
+      <c r="J9" s="26" t="str">
         <f aca="false">IF(I9="","",ROUND(I9*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K9" s="6"/>
-      <c r="L9" s="26"/>
+      <c r="L9" s="27"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="23"/>
+      <c r="A10" s="24"/>
       <c r="B10" s="6"/>
       <c r="C10" s="8" t="str">
         <f aca="false">IF(OR(D10="",E10="",D10=E10),"",IF(E10&lt;D10,"BUY","SELL"))</f>
@@ -1534,19 +1610,19 @@
         <f aca="false">IF(I10="","",IF(I10&gt;0,"WIN",IF(I10&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I10" s="24" t="str">
+      <c r="I10" s="25" t="str">
         <f aca="false">IF(OR(G10="",C10=""),"",ROUND((G10-D10)/(D10-E10),2))</f>
         <v/>
       </c>
-      <c r="J10" s="25" t="str">
+      <c r="J10" s="26" t="str">
         <f aca="false">IF(I10="","",ROUND(I10*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K10" s="6"/>
-      <c r="L10" s="26"/>
+      <c r="L10" s="27"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="23"/>
+      <c r="A11" s="24"/>
       <c r="B11" s="6"/>
       <c r="C11" s="8" t="str">
         <f aca="false">IF(OR(D11="",E11="",D11=E11),"",IF(E11&lt;D11,"BUY","SELL"))</f>
@@ -1563,19 +1639,19 @@
         <f aca="false">IF(I11="","",IF(I11&gt;0,"WIN",IF(I11&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I11" s="24" t="str">
+      <c r="I11" s="25" t="str">
         <f aca="false">IF(OR(G11="",C11=""),"",ROUND((G11-D11)/(D11-E11),2))</f>
         <v/>
       </c>
-      <c r="J11" s="25" t="str">
+      <c r="J11" s="26" t="str">
         <f aca="false">IF(I11="","",ROUND(I11*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K11" s="6"/>
-      <c r="L11" s="26"/>
+      <c r="L11" s="27"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="23"/>
+      <c r="A12" s="24"/>
       <c r="B12" s="6"/>
       <c r="C12" s="8" t="str">
         <f aca="false">IF(OR(D12="",E12="",D12=E12),"",IF(E12&lt;D12,"BUY","SELL"))</f>
@@ -1592,19 +1668,19 @@
         <f aca="false">IF(I12="","",IF(I12&gt;0,"WIN",IF(I12&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I12" s="24" t="str">
+      <c r="I12" s="25" t="str">
         <f aca="false">IF(OR(G12="",C12=""),"",ROUND((G12-D12)/(D12-E12),2))</f>
         <v/>
       </c>
-      <c r="J12" s="25" t="str">
+      <c r="J12" s="26" t="str">
         <f aca="false">IF(I12="","",ROUND(I12*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K12" s="6"/>
-      <c r="L12" s="26"/>
+      <c r="L12" s="27"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="23"/>
+      <c r="A13" s="24"/>
       <c r="B13" s="6"/>
       <c r="C13" s="8" t="str">
         <f aca="false">IF(OR(D13="",E13="",D13=E13),"",IF(E13&lt;D13,"BUY","SELL"))</f>
@@ -1621,19 +1697,19 @@
         <f aca="false">IF(I13="","",IF(I13&gt;0,"WIN",IF(I13&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I13" s="24" t="str">
+      <c r="I13" s="25" t="str">
         <f aca="false">IF(OR(G13="",C13=""),"",ROUND((G13-D13)/(D13-E13),2))</f>
         <v/>
       </c>
-      <c r="J13" s="25" t="str">
+      <c r="J13" s="26" t="str">
         <f aca="false">IF(I13="","",ROUND(I13*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K13" s="6"/>
-      <c r="L13" s="26"/>
+      <c r="L13" s="27"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="23"/>
+      <c r="A14" s="24"/>
       <c r="B14" s="6"/>
       <c r="C14" s="8" t="str">
         <f aca="false">IF(OR(D14="",E14="",D14=E14),"",IF(E14&lt;D14,"BUY","SELL"))</f>
@@ -1650,19 +1726,19 @@
         <f aca="false">IF(I14="","",IF(I14&gt;0,"WIN",IF(I14&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I14" s="24" t="str">
+      <c r="I14" s="25" t="str">
         <f aca="false">IF(OR(G14="",C14=""),"",ROUND((G14-D14)/(D14-E14),2))</f>
         <v/>
       </c>
-      <c r="J14" s="25" t="str">
+      <c r="J14" s="26" t="str">
         <f aca="false">IF(I14="","",ROUND(I14*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K14" s="6"/>
-      <c r="L14" s="26"/>
+      <c r="L14" s="27"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="23"/>
+      <c r="A15" s="24"/>
       <c r="B15" s="6"/>
       <c r="C15" s="8" t="str">
         <f aca="false">IF(OR(D15="",E15="",D15=E15),"",IF(E15&lt;D15,"BUY","SELL"))</f>
@@ -1679,19 +1755,19 @@
         <f aca="false">IF(I15="","",IF(I15&gt;0,"WIN",IF(I15&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I15" s="24" t="str">
+      <c r="I15" s="25" t="str">
         <f aca="false">IF(OR(G15="",C15=""),"",ROUND((G15-D15)/(D15-E15),2))</f>
         <v/>
       </c>
-      <c r="J15" s="25" t="str">
+      <c r="J15" s="26" t="str">
         <f aca="false">IF(I15="","",ROUND(I15*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K15" s="6"/>
-      <c r="L15" s="26"/>
+      <c r="L15" s="27"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="23"/>
+      <c r="A16" s="24"/>
       <c r="B16" s="6"/>
       <c r="C16" s="8" t="str">
         <f aca="false">IF(OR(D16="",E16="",D16=E16),"",IF(E16&lt;D16,"BUY","SELL"))</f>
@@ -1708,19 +1784,19 @@
         <f aca="false">IF(I16="","",IF(I16&gt;0,"WIN",IF(I16&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I16" s="24" t="str">
+      <c r="I16" s="25" t="str">
         <f aca="false">IF(OR(G16="",C16=""),"",ROUND((G16-D16)/(D16-E16),2))</f>
         <v/>
       </c>
-      <c r="J16" s="25" t="str">
+      <c r="J16" s="26" t="str">
         <f aca="false">IF(I16="","",ROUND(I16*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K16" s="6"/>
-      <c r="L16" s="26"/>
+      <c r="L16" s="27"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="23"/>
+      <c r="A17" s="24"/>
       <c r="B17" s="6"/>
       <c r="C17" s="8" t="str">
         <f aca="false">IF(OR(D17="",E17="",D17=E17),"",IF(E17&lt;D17,"BUY","SELL"))</f>
@@ -1737,19 +1813,19 @@
         <f aca="false">IF(I17="","",IF(I17&gt;0,"WIN",IF(I17&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I17" s="24" t="str">
+      <c r="I17" s="25" t="str">
         <f aca="false">IF(OR(G17="",C17=""),"",ROUND((G17-D17)/(D17-E17),2))</f>
         <v/>
       </c>
-      <c r="J17" s="25" t="str">
+      <c r="J17" s="26" t="str">
         <f aca="false">IF(I17="","",ROUND(I17*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K17" s="6"/>
-      <c r="L17" s="26"/>
+      <c r="L17" s="27"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="23"/>
+      <c r="A18" s="24"/>
       <c r="B18" s="6"/>
       <c r="C18" s="8" t="str">
         <f aca="false">IF(OR(D18="",E18="",D18=E18),"",IF(E18&lt;D18,"BUY","SELL"))</f>
@@ -1766,19 +1842,19 @@
         <f aca="false">IF(I18="","",IF(I18&gt;0,"WIN",IF(I18&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I18" s="24" t="str">
+      <c r="I18" s="25" t="str">
         <f aca="false">IF(OR(G18="",C18=""),"",ROUND((G18-D18)/(D18-E18),2))</f>
         <v/>
       </c>
-      <c r="J18" s="25" t="str">
+      <c r="J18" s="26" t="str">
         <f aca="false">IF(I18="","",ROUND(I18*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K18" s="6"/>
-      <c r="L18" s="26"/>
+      <c r="L18" s="27"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="23"/>
+      <c r="A19" s="24"/>
       <c r="B19" s="6"/>
       <c r="C19" s="8" t="str">
         <f aca="false">IF(OR(D19="",E19="",D19=E19),"",IF(E19&lt;D19,"BUY","SELL"))</f>
@@ -1795,19 +1871,19 @@
         <f aca="false">IF(I19="","",IF(I19&gt;0,"WIN",IF(I19&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I19" s="24" t="str">
+      <c r="I19" s="25" t="str">
         <f aca="false">IF(OR(G19="",C19=""),"",ROUND((G19-D19)/(D19-E19),2))</f>
         <v/>
       </c>
-      <c r="J19" s="25" t="str">
+      <c r="J19" s="26" t="str">
         <f aca="false">IF(I19="","",ROUND(I19*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K19" s="6"/>
-      <c r="L19" s="26"/>
+      <c r="L19" s="27"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="23"/>
+      <c r="A20" s="24"/>
       <c r="B20" s="6"/>
       <c r="C20" s="8" t="str">
         <f aca="false">IF(OR(D20="",E20="",D20=E20),"",IF(E20&lt;D20,"BUY","SELL"))</f>
@@ -1824,19 +1900,19 @@
         <f aca="false">IF(I20="","",IF(I20&gt;0,"WIN",IF(I20&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I20" s="24" t="str">
+      <c r="I20" s="25" t="str">
         <f aca="false">IF(OR(G20="",C20=""),"",ROUND((G20-D20)/(D20-E20),2))</f>
         <v/>
       </c>
-      <c r="J20" s="25" t="str">
+      <c r="J20" s="26" t="str">
         <f aca="false">IF(I20="","",ROUND(I20*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K20" s="6"/>
-      <c r="L20" s="26"/>
+      <c r="L20" s="27"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="23"/>
+      <c r="A21" s="24"/>
       <c r="B21" s="6"/>
       <c r="C21" s="8" t="str">
         <f aca="false">IF(OR(D21="",E21="",D21=E21),"",IF(E21&lt;D21,"BUY","SELL"))</f>
@@ -1853,19 +1929,19 @@
         <f aca="false">IF(I21="","",IF(I21&gt;0,"WIN",IF(I21&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I21" s="24" t="str">
+      <c r="I21" s="25" t="str">
         <f aca="false">IF(OR(G21="",C21=""),"",ROUND((G21-D21)/(D21-E21),2))</f>
         <v/>
       </c>
-      <c r="J21" s="25" t="str">
+      <c r="J21" s="26" t="str">
         <f aca="false">IF(I21="","",ROUND(I21*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K21" s="6"/>
-      <c r="L21" s="26"/>
+      <c r="L21" s="27"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="23"/>
+      <c r="A22" s="24"/>
       <c r="B22" s="6"/>
       <c r="C22" s="8" t="str">
         <f aca="false">IF(OR(D22="",E22="",D22=E22),"",IF(E22&lt;D22,"BUY","SELL"))</f>
@@ -1882,19 +1958,19 @@
         <f aca="false">IF(I22="","",IF(I22&gt;0,"WIN",IF(I22&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I22" s="24" t="str">
+      <c r="I22" s="25" t="str">
         <f aca="false">IF(OR(G22="",C22=""),"",ROUND((G22-D22)/(D22-E22),2))</f>
         <v/>
       </c>
-      <c r="J22" s="25" t="str">
+      <c r="J22" s="26" t="str">
         <f aca="false">IF(I22="","",ROUND(I22*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K22" s="6"/>
-      <c r="L22" s="26"/>
+      <c r="L22" s="27"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="23"/>
+      <c r="A23" s="24"/>
       <c r="B23" s="6"/>
       <c r="C23" s="8" t="str">
         <f aca="false">IF(OR(D23="",E23="",D23=E23),"",IF(E23&lt;D23,"BUY","SELL"))</f>
@@ -1911,19 +1987,19 @@
         <f aca="false">IF(I23="","",IF(I23&gt;0,"WIN",IF(I23&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I23" s="24" t="str">
+      <c r="I23" s="25" t="str">
         <f aca="false">IF(OR(G23="",C23=""),"",ROUND((G23-D23)/(D23-E23),2))</f>
         <v/>
       </c>
-      <c r="J23" s="25" t="str">
+      <c r="J23" s="26" t="str">
         <f aca="false">IF(I23="","",ROUND(I23*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K23" s="6"/>
-      <c r="L23" s="26"/>
+      <c r="L23" s="27"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="23"/>
+      <c r="A24" s="24"/>
       <c r="B24" s="6"/>
       <c r="C24" s="8" t="str">
         <f aca="false">IF(OR(D24="",E24="",D24=E24),"",IF(E24&lt;D24,"BUY","SELL"))</f>
@@ -1940,19 +2016,19 @@
         <f aca="false">IF(I24="","",IF(I24&gt;0,"WIN",IF(I24&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I24" s="24" t="str">
+      <c r="I24" s="25" t="str">
         <f aca="false">IF(OR(G24="",C24=""),"",ROUND((G24-D24)/(D24-E24),2))</f>
         <v/>
       </c>
-      <c r="J24" s="25" t="str">
+      <c r="J24" s="26" t="str">
         <f aca="false">IF(I24="","",ROUND(I24*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K24" s="6"/>
-      <c r="L24" s="26"/>
+      <c r="L24" s="27"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="23"/>
+      <c r="A25" s="24"/>
       <c r="B25" s="6"/>
       <c r="C25" s="8" t="str">
         <f aca="false">IF(OR(D25="",E25="",D25=E25),"",IF(E25&lt;D25,"BUY","SELL"))</f>
@@ -1969,19 +2045,19 @@
         <f aca="false">IF(I25="","",IF(I25&gt;0,"WIN",IF(I25&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I25" s="24" t="str">
+      <c r="I25" s="25" t="str">
         <f aca="false">IF(OR(G25="",C25=""),"",ROUND((G25-D25)/(D25-E25),2))</f>
         <v/>
       </c>
-      <c r="J25" s="25" t="str">
+      <c r="J25" s="26" t="str">
         <f aca="false">IF(I25="","",ROUND(I25*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K25" s="6"/>
-      <c r="L25" s="26"/>
+      <c r="L25" s="27"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="23"/>
+      <c r="A26" s="24"/>
       <c r="B26" s="6"/>
       <c r="C26" s="8" t="str">
         <f aca="false">IF(OR(D26="",E26="",D26=E26),"",IF(E26&lt;D26,"BUY","SELL"))</f>
@@ -1998,19 +2074,19 @@
         <f aca="false">IF(I26="","",IF(I26&gt;0,"WIN",IF(I26&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I26" s="24" t="str">
+      <c r="I26" s="25" t="str">
         <f aca="false">IF(OR(G26="",C26=""),"",ROUND((G26-D26)/(D26-E26),2))</f>
         <v/>
       </c>
-      <c r="J26" s="25" t="str">
+      <c r="J26" s="26" t="str">
         <f aca="false">IF(I26="","",ROUND(I26*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K26" s="6"/>
-      <c r="L26" s="26"/>
+      <c r="L26" s="27"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="23"/>
+      <c r="A27" s="24"/>
       <c r="B27" s="6"/>
       <c r="C27" s="8" t="str">
         <f aca="false">IF(OR(D27="",E27="",D27=E27),"",IF(E27&lt;D27,"BUY","SELL"))</f>
@@ -2027,19 +2103,19 @@
         <f aca="false">IF(I27="","",IF(I27&gt;0,"WIN",IF(I27&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I27" s="24" t="str">
+      <c r="I27" s="25" t="str">
         <f aca="false">IF(OR(G27="",C27=""),"",ROUND((G27-D27)/(D27-E27),2))</f>
         <v/>
       </c>
-      <c r="J27" s="25" t="str">
+      <c r="J27" s="26" t="str">
         <f aca="false">IF(I27="","",ROUND(I27*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K27" s="6"/>
-      <c r="L27" s="26"/>
+      <c r="L27" s="27"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="23"/>
+      <c r="A28" s="24"/>
       <c r="B28" s="6"/>
       <c r="C28" s="8" t="str">
         <f aca="false">IF(OR(D28="",E28="",D28=E28),"",IF(E28&lt;D28,"BUY","SELL"))</f>
@@ -2056,19 +2132,19 @@
         <f aca="false">IF(I28="","",IF(I28&gt;0,"WIN",IF(I28&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I28" s="24" t="str">
+      <c r="I28" s="25" t="str">
         <f aca="false">IF(OR(G28="",C28=""),"",ROUND((G28-D28)/(D28-E28),2))</f>
         <v/>
       </c>
-      <c r="J28" s="25" t="str">
+      <c r="J28" s="26" t="str">
         <f aca="false">IF(I28="","",ROUND(I28*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K28" s="6"/>
-      <c r="L28" s="26"/>
+      <c r="L28" s="27"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="23"/>
+      <c r="A29" s="24"/>
       <c r="B29" s="6"/>
       <c r="C29" s="8" t="str">
         <f aca="false">IF(OR(D29="",E29="",D29=E29),"",IF(E29&lt;D29,"BUY","SELL"))</f>
@@ -2085,19 +2161,19 @@
         <f aca="false">IF(I29="","",IF(I29&gt;0,"WIN",IF(I29&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I29" s="24" t="str">
+      <c r="I29" s="25" t="str">
         <f aca="false">IF(OR(G29="",C29=""),"",ROUND((G29-D29)/(D29-E29),2))</f>
         <v/>
       </c>
-      <c r="J29" s="25" t="str">
+      <c r="J29" s="26" t="str">
         <f aca="false">IF(I29="","",ROUND(I29*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K29" s="6"/>
-      <c r="L29" s="26"/>
+      <c r="L29" s="27"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="23"/>
+      <c r="A30" s="24"/>
       <c r="B30" s="6"/>
       <c r="C30" s="8" t="str">
         <f aca="false">IF(OR(D30="",E30="",D30=E30),"",IF(E30&lt;D30,"BUY","SELL"))</f>
@@ -2114,19 +2190,19 @@
         <f aca="false">IF(I30="","",IF(I30&gt;0,"WIN",IF(I30&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I30" s="24" t="str">
+      <c r="I30" s="25" t="str">
         <f aca="false">IF(OR(G30="",C30=""),"",ROUND((G30-D30)/(D30-E30),2))</f>
         <v/>
       </c>
-      <c r="J30" s="25" t="str">
+      <c r="J30" s="26" t="str">
         <f aca="false">IF(I30="","",ROUND(I30*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K30" s="6"/>
-      <c r="L30" s="26"/>
+      <c r="L30" s="27"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="23"/>
+      <c r="A31" s="24"/>
       <c r="B31" s="6"/>
       <c r="C31" s="8" t="str">
         <f aca="false">IF(OR(D31="",E31="",D31=E31),"",IF(E31&lt;D31,"BUY","SELL"))</f>
@@ -2143,19 +2219,19 @@
         <f aca="false">IF(I31="","",IF(I31&gt;0,"WIN",IF(I31&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I31" s="24" t="str">
+      <c r="I31" s="25" t="str">
         <f aca="false">IF(OR(G31="",C31=""),"",ROUND((G31-D31)/(D31-E31),2))</f>
         <v/>
       </c>
-      <c r="J31" s="25" t="str">
+      <c r="J31" s="26" t="str">
         <f aca="false">IF(I31="","",ROUND(I31*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K31" s="6"/>
-      <c r="L31" s="26"/>
+      <c r="L31" s="27"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="23"/>
+      <c r="A32" s="24"/>
       <c r="B32" s="6"/>
       <c r="C32" s="8" t="str">
         <f aca="false">IF(OR(D32="",E32="",D32=E32),"",IF(E32&lt;D32,"BUY","SELL"))</f>
@@ -2172,19 +2248,19 @@
         <f aca="false">IF(I32="","",IF(I32&gt;0,"WIN",IF(I32&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I32" s="24" t="str">
+      <c r="I32" s="25" t="str">
         <f aca="false">IF(OR(G32="",C32=""),"",ROUND((G32-D32)/(D32-E32),2))</f>
         <v/>
       </c>
-      <c r="J32" s="25" t="str">
+      <c r="J32" s="26" t="str">
         <f aca="false">IF(I32="","",ROUND(I32*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K32" s="6"/>
-      <c r="L32" s="26"/>
+      <c r="L32" s="27"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="23"/>
+      <c r="A33" s="24"/>
       <c r="B33" s="6"/>
       <c r="C33" s="8" t="str">
         <f aca="false">IF(OR(D33="",E33="",D33=E33),"",IF(E33&lt;D33,"BUY","SELL"))</f>
@@ -2201,19 +2277,19 @@
         <f aca="false">IF(I33="","",IF(I33&gt;0,"WIN",IF(I33&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I33" s="24" t="str">
+      <c r="I33" s="25" t="str">
         <f aca="false">IF(OR(G33="",C33=""),"",ROUND((G33-D33)/(D33-E33),2))</f>
         <v/>
       </c>
-      <c r="J33" s="25" t="str">
+      <c r="J33" s="26" t="str">
         <f aca="false">IF(I33="","",ROUND(I33*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K33" s="6"/>
-      <c r="L33" s="26"/>
+      <c r="L33" s="27"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="23"/>
+      <c r="A34" s="24"/>
       <c r="B34" s="6"/>
       <c r="C34" s="8" t="str">
         <f aca="false">IF(OR(D34="",E34="",D34=E34),"",IF(E34&lt;D34,"BUY","SELL"))</f>
@@ -2230,19 +2306,19 @@
         <f aca="false">IF(I34="","",IF(I34&gt;0,"WIN",IF(I34&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I34" s="24" t="str">
+      <c r="I34" s="25" t="str">
         <f aca="false">IF(OR(G34="",C34=""),"",ROUND((G34-D34)/(D34-E34),2))</f>
         <v/>
       </c>
-      <c r="J34" s="25" t="str">
+      <c r="J34" s="26" t="str">
         <f aca="false">IF(I34="","",ROUND(I34*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K34" s="6"/>
-      <c r="L34" s="26"/>
+      <c r="L34" s="27"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="23"/>
+      <c r="A35" s="24"/>
       <c r="B35" s="6"/>
       <c r="C35" s="8" t="str">
         <f aca="false">IF(OR(D35="",E35="",D35=E35),"",IF(E35&lt;D35,"BUY","SELL"))</f>
@@ -2259,19 +2335,19 @@
         <f aca="false">IF(I35="","",IF(I35&gt;0,"WIN",IF(I35&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I35" s="24" t="str">
+      <c r="I35" s="25" t="str">
         <f aca="false">IF(OR(G35="",C35=""),"",ROUND((G35-D35)/(D35-E35),2))</f>
         <v/>
       </c>
-      <c r="J35" s="25" t="str">
+      <c r="J35" s="26" t="str">
         <f aca="false">IF(I35="","",ROUND(I35*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K35" s="6"/>
-      <c r="L35" s="26"/>
+      <c r="L35" s="27"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="23"/>
+      <c r="A36" s="24"/>
       <c r="B36" s="6"/>
       <c r="C36" s="8" t="str">
         <f aca="false">IF(OR(D36="",E36="",D36=E36),"",IF(E36&lt;D36,"BUY","SELL"))</f>
@@ -2288,19 +2364,19 @@
         <f aca="false">IF(I36="","",IF(I36&gt;0,"WIN",IF(I36&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I36" s="24" t="str">
+      <c r="I36" s="25" t="str">
         <f aca="false">IF(OR(G36="",C36=""),"",ROUND((G36-D36)/(D36-E36),2))</f>
         <v/>
       </c>
-      <c r="J36" s="25" t="str">
+      <c r="J36" s="26" t="str">
         <f aca="false">IF(I36="","",ROUND(I36*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K36" s="6"/>
-      <c r="L36" s="26"/>
+      <c r="L36" s="27"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="23"/>
+      <c r="A37" s="24"/>
       <c r="B37" s="6"/>
       <c r="C37" s="8" t="str">
         <f aca="false">IF(OR(D37="",E37="",D37=E37),"",IF(E37&lt;D37,"BUY","SELL"))</f>
@@ -2317,19 +2393,19 @@
         <f aca="false">IF(I37="","",IF(I37&gt;0,"WIN",IF(I37&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I37" s="24" t="str">
+      <c r="I37" s="25" t="str">
         <f aca="false">IF(OR(G37="",C37=""),"",ROUND((G37-D37)/(D37-E37),2))</f>
         <v/>
       </c>
-      <c r="J37" s="25" t="str">
+      <c r="J37" s="26" t="str">
         <f aca="false">IF(I37="","",ROUND(I37*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K37" s="6"/>
-      <c r="L37" s="26"/>
+      <c r="L37" s="27"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="23"/>
+      <c r="A38" s="24"/>
       <c r="B38" s="6"/>
       <c r="C38" s="8" t="str">
         <f aca="false">IF(OR(D38="",E38="",D38=E38),"",IF(E38&lt;D38,"BUY","SELL"))</f>
@@ -2346,19 +2422,19 @@
         <f aca="false">IF(I38="","",IF(I38&gt;0,"WIN",IF(I38&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I38" s="24" t="str">
+      <c r="I38" s="25" t="str">
         <f aca="false">IF(OR(G38="",C38=""),"",ROUND((G38-D38)/(D38-E38),2))</f>
         <v/>
       </c>
-      <c r="J38" s="25" t="str">
+      <c r="J38" s="26" t="str">
         <f aca="false">IF(I38="","",ROUND(I38*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K38" s="6"/>
-      <c r="L38" s="26"/>
+      <c r="L38" s="27"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="23"/>
+      <c r="A39" s="24"/>
       <c r="B39" s="6"/>
       <c r="C39" s="8" t="str">
         <f aca="false">IF(OR(D39="",E39="",D39=E39),"",IF(E39&lt;D39,"BUY","SELL"))</f>
@@ -2375,19 +2451,19 @@
         <f aca="false">IF(I39="","",IF(I39&gt;0,"WIN",IF(I39&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I39" s="24" t="str">
+      <c r="I39" s="25" t="str">
         <f aca="false">IF(OR(G39="",C39=""),"",ROUND((G39-D39)/(D39-E39),2))</f>
         <v/>
       </c>
-      <c r="J39" s="25" t="str">
+      <c r="J39" s="26" t="str">
         <f aca="false">IF(I39="","",ROUND(I39*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K39" s="6"/>
-      <c r="L39" s="26"/>
+      <c r="L39" s="27"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="23"/>
+      <c r="A40" s="24"/>
       <c r="B40" s="6"/>
       <c r="C40" s="8" t="str">
         <f aca="false">IF(OR(D40="",E40="",D40=E40),"",IF(E40&lt;D40,"BUY","SELL"))</f>
@@ -2404,19 +2480,19 @@
         <f aca="false">IF(I40="","",IF(I40&gt;0,"WIN",IF(I40&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I40" s="24" t="str">
+      <c r="I40" s="25" t="str">
         <f aca="false">IF(OR(G40="",C40=""),"",ROUND((G40-D40)/(D40-E40),2))</f>
         <v/>
       </c>
-      <c r="J40" s="25" t="str">
+      <c r="J40" s="26" t="str">
         <f aca="false">IF(I40="","",ROUND(I40*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K40" s="6"/>
-      <c r="L40" s="26"/>
+      <c r="L40" s="27"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="23"/>
+      <c r="A41" s="24"/>
       <c r="B41" s="6"/>
       <c r="C41" s="8" t="str">
         <f aca="false">IF(OR(D41="",E41="",D41=E41),"",IF(E41&lt;D41,"BUY","SELL"))</f>
@@ -2433,19 +2509,19 @@
         <f aca="false">IF(I41="","",IF(I41&gt;0,"WIN",IF(I41&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I41" s="24" t="str">
+      <c r="I41" s="25" t="str">
         <f aca="false">IF(OR(G41="",C41=""),"",ROUND((G41-D41)/(D41-E41),2))</f>
         <v/>
       </c>
-      <c r="J41" s="25" t="str">
+      <c r="J41" s="26" t="str">
         <f aca="false">IF(I41="","",ROUND(I41*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K41" s="6"/>
-      <c r="L41" s="26"/>
+      <c r="L41" s="27"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="23"/>
+      <c r="A42" s="24"/>
       <c r="B42" s="6"/>
       <c r="C42" s="8" t="str">
         <f aca="false">IF(OR(D42="",E42="",D42=E42),"",IF(E42&lt;D42,"BUY","SELL"))</f>
@@ -2462,19 +2538,19 @@
         <f aca="false">IF(I42="","",IF(I42&gt;0,"WIN",IF(I42&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I42" s="24" t="str">
+      <c r="I42" s="25" t="str">
         <f aca="false">IF(OR(G42="",C42=""),"",ROUND((G42-D42)/(D42-E42),2))</f>
         <v/>
       </c>
-      <c r="J42" s="25" t="str">
+      <c r="J42" s="26" t="str">
         <f aca="false">IF(I42="","",ROUND(I42*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K42" s="6"/>
-      <c r="L42" s="26"/>
+      <c r="L42" s="27"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="23"/>
+      <c r="A43" s="24"/>
       <c r="B43" s="6"/>
       <c r="C43" s="8" t="str">
         <f aca="false">IF(OR(D43="",E43="",D43=E43),"",IF(E43&lt;D43,"BUY","SELL"))</f>
@@ -2491,19 +2567,19 @@
         <f aca="false">IF(I43="","",IF(I43&gt;0,"WIN",IF(I43&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I43" s="24" t="str">
+      <c r="I43" s="25" t="str">
         <f aca="false">IF(OR(G43="",C43=""),"",ROUND((G43-D43)/(D43-E43),2))</f>
         <v/>
       </c>
-      <c r="J43" s="25" t="str">
+      <c r="J43" s="26" t="str">
         <f aca="false">IF(I43="","",ROUND(I43*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K43" s="6"/>
-      <c r="L43" s="26"/>
+      <c r="L43" s="27"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="23"/>
+      <c r="A44" s="24"/>
       <c r="B44" s="6"/>
       <c r="C44" s="8" t="str">
         <f aca="false">IF(OR(D44="",E44="",D44=E44),"",IF(E44&lt;D44,"BUY","SELL"))</f>
@@ -2520,19 +2596,19 @@
         <f aca="false">IF(I44="","",IF(I44&gt;0,"WIN",IF(I44&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I44" s="24" t="str">
+      <c r="I44" s="25" t="str">
         <f aca="false">IF(OR(G44="",C44=""),"",ROUND((G44-D44)/(D44-E44),2))</f>
         <v/>
       </c>
-      <c r="J44" s="25" t="str">
+      <c r="J44" s="26" t="str">
         <f aca="false">IF(I44="","",ROUND(I44*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K44" s="6"/>
-      <c r="L44" s="26"/>
+      <c r="L44" s="27"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="23"/>
+      <c r="A45" s="24"/>
       <c r="B45" s="6"/>
       <c r="C45" s="8" t="str">
         <f aca="false">IF(OR(D45="",E45="",D45=E45),"",IF(E45&lt;D45,"BUY","SELL"))</f>
@@ -2549,19 +2625,19 @@
         <f aca="false">IF(I45="","",IF(I45&gt;0,"WIN",IF(I45&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I45" s="24" t="str">
+      <c r="I45" s="25" t="str">
         <f aca="false">IF(OR(G45="",C45=""),"",ROUND((G45-D45)/(D45-E45),2))</f>
         <v/>
       </c>
-      <c r="J45" s="25" t="str">
+      <c r="J45" s="26" t="str">
         <f aca="false">IF(I45="","",ROUND(I45*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K45" s="6"/>
-      <c r="L45" s="26"/>
+      <c r="L45" s="27"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="23"/>
+      <c r="A46" s="24"/>
       <c r="B46" s="6"/>
       <c r="C46" s="8" t="str">
         <f aca="false">IF(OR(D46="",E46="",D46=E46),"",IF(E46&lt;D46,"BUY","SELL"))</f>
@@ -2578,19 +2654,19 @@
         <f aca="false">IF(I46="","",IF(I46&gt;0,"WIN",IF(I46&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I46" s="24" t="str">
+      <c r="I46" s="25" t="str">
         <f aca="false">IF(OR(G46="",C46=""),"",ROUND((G46-D46)/(D46-E46),2))</f>
         <v/>
       </c>
-      <c r="J46" s="25" t="str">
+      <c r="J46" s="26" t="str">
         <f aca="false">IF(I46="","",ROUND(I46*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K46" s="6"/>
-      <c r="L46" s="26"/>
+      <c r="L46" s="27"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="23"/>
+      <c r="A47" s="24"/>
       <c r="B47" s="6"/>
       <c r="C47" s="8" t="str">
         <f aca="false">IF(OR(D47="",E47="",D47=E47),"",IF(E47&lt;D47,"BUY","SELL"))</f>
@@ -2607,19 +2683,19 @@
         <f aca="false">IF(I47="","",IF(I47&gt;0,"WIN",IF(I47&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I47" s="24" t="str">
+      <c r="I47" s="25" t="str">
         <f aca="false">IF(OR(G47="",C47=""),"",ROUND((G47-D47)/(D47-E47),2))</f>
         <v/>
       </c>
-      <c r="J47" s="25" t="str">
+      <c r="J47" s="26" t="str">
         <f aca="false">IF(I47="","",ROUND(I47*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K47" s="6"/>
-      <c r="L47" s="26"/>
+      <c r="L47" s="27"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="23"/>
+      <c r="A48" s="24"/>
       <c r="B48" s="6"/>
       <c r="C48" s="8" t="str">
         <f aca="false">IF(OR(D48="",E48="",D48=E48),"",IF(E48&lt;D48,"BUY","SELL"))</f>
@@ -2636,19 +2712,19 @@
         <f aca="false">IF(I48="","",IF(I48&gt;0,"WIN",IF(I48&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I48" s="24" t="str">
+      <c r="I48" s="25" t="str">
         <f aca="false">IF(OR(G48="",C48=""),"",ROUND((G48-D48)/(D48-E48),2))</f>
         <v/>
       </c>
-      <c r="J48" s="25" t="str">
+      <c r="J48" s="26" t="str">
         <f aca="false">IF(I48="","",ROUND(I48*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K48" s="6"/>
-      <c r="L48" s="26"/>
+      <c r="L48" s="27"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="23"/>
+      <c r="A49" s="24"/>
       <c r="B49" s="6"/>
       <c r="C49" s="8" t="str">
         <f aca="false">IF(OR(D49="",E49="",D49=E49),"",IF(E49&lt;D49,"BUY","SELL"))</f>
@@ -2665,19 +2741,19 @@
         <f aca="false">IF(I49="","",IF(I49&gt;0,"WIN",IF(I49&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I49" s="24" t="str">
+      <c r="I49" s="25" t="str">
         <f aca="false">IF(OR(G49="",C49=""),"",ROUND((G49-D49)/(D49-E49),2))</f>
         <v/>
       </c>
-      <c r="J49" s="25" t="str">
+      <c r="J49" s="26" t="str">
         <f aca="false">IF(I49="","",ROUND(I49*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K49" s="6"/>
-      <c r="L49" s="26"/>
+      <c r="L49" s="27"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="23"/>
+      <c r="A50" s="24"/>
       <c r="B50" s="6"/>
       <c r="C50" s="8" t="str">
         <f aca="false">IF(OR(D50="",E50="",D50=E50),"",IF(E50&lt;D50,"BUY","SELL"))</f>
@@ -2694,19 +2770,19 @@
         <f aca="false">IF(I50="","",IF(I50&gt;0,"WIN",IF(I50&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I50" s="24" t="str">
+      <c r="I50" s="25" t="str">
         <f aca="false">IF(OR(G50="",C50=""),"",ROUND((G50-D50)/(D50-E50),2))</f>
         <v/>
       </c>
-      <c r="J50" s="25" t="str">
+      <c r="J50" s="26" t="str">
         <f aca="false">IF(I50="","",ROUND(I50*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K50" s="6"/>
-      <c r="L50" s="26"/>
+      <c r="L50" s="27"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="23"/>
+      <c r="A51" s="24"/>
       <c r="B51" s="6"/>
       <c r="C51" s="8" t="str">
         <f aca="false">IF(OR(D51="",E51="",D51=E51),"",IF(E51&lt;D51,"BUY","SELL"))</f>
@@ -2723,19 +2799,19 @@
         <f aca="false">IF(I51="","",IF(I51&gt;0,"WIN",IF(I51&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I51" s="24" t="str">
+      <c r="I51" s="25" t="str">
         <f aca="false">IF(OR(G51="",C51=""),"",ROUND((G51-D51)/(D51-E51),2))</f>
         <v/>
       </c>
-      <c r="J51" s="25" t="str">
+      <c r="J51" s="26" t="str">
         <f aca="false">IF(I51="","",ROUND(I51*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K51" s="6"/>
-      <c r="L51" s="26"/>
+      <c r="L51" s="27"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="23"/>
+      <c r="A52" s="24"/>
       <c r="B52" s="6"/>
       <c r="C52" s="8" t="str">
         <f aca="false">IF(OR(D52="",E52="",D52=E52),"",IF(E52&lt;D52,"BUY","SELL"))</f>
@@ -2752,19 +2828,19 @@
         <f aca="false">IF(I52="","",IF(I52&gt;0,"WIN",IF(I52&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I52" s="24" t="str">
+      <c r="I52" s="25" t="str">
         <f aca="false">IF(OR(G52="",C52=""),"",ROUND((G52-D52)/(D52-E52),2))</f>
         <v/>
       </c>
-      <c r="J52" s="25" t="str">
+      <c r="J52" s="26" t="str">
         <f aca="false">IF(I52="","",ROUND(I52*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K52" s="6"/>
-      <c r="L52" s="26"/>
+      <c r="L52" s="27"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="23"/>
+      <c r="A53" s="24"/>
       <c r="B53" s="6"/>
       <c r="C53" s="8" t="str">
         <f aca="false">IF(OR(D53="",E53="",D53=E53),"",IF(E53&lt;D53,"BUY","SELL"))</f>
@@ -2781,19 +2857,19 @@
         <f aca="false">IF(I53="","",IF(I53&gt;0,"WIN",IF(I53&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I53" s="24" t="str">
+      <c r="I53" s="25" t="str">
         <f aca="false">IF(OR(G53="",C53=""),"",ROUND((G53-D53)/(D53-E53),2))</f>
         <v/>
       </c>
-      <c r="J53" s="25" t="str">
+      <c r="J53" s="26" t="str">
         <f aca="false">IF(I53="","",ROUND(I53*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K53" s="6"/>
-      <c r="L53" s="26"/>
+      <c r="L53" s="27"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="23"/>
+      <c r="A54" s="24"/>
       <c r="B54" s="6"/>
       <c r="C54" s="8" t="str">
         <f aca="false">IF(OR(D54="",E54="",D54=E54),"",IF(E54&lt;D54,"BUY","SELL"))</f>
@@ -2810,19 +2886,19 @@
         <f aca="false">IF(I54="","",IF(I54&gt;0,"WIN",IF(I54&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I54" s="24" t="str">
+      <c r="I54" s="25" t="str">
         <f aca="false">IF(OR(G54="",C54=""),"",ROUND((G54-D54)/(D54-E54),2))</f>
         <v/>
       </c>
-      <c r="J54" s="25" t="str">
+      <c r="J54" s="26" t="str">
         <f aca="false">IF(I54="","",ROUND(I54*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K54" s="6"/>
-      <c r="L54" s="26"/>
+      <c r="L54" s="27"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="23"/>
+      <c r="A55" s="24"/>
       <c r="B55" s="6"/>
       <c r="C55" s="8" t="str">
         <f aca="false">IF(OR(D55="",E55="",D55=E55),"",IF(E55&lt;D55,"BUY","SELL"))</f>
@@ -2839,19 +2915,19 @@
         <f aca="false">IF(I55="","",IF(I55&gt;0,"WIN",IF(I55&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I55" s="24" t="str">
+      <c r="I55" s="25" t="str">
         <f aca="false">IF(OR(G55="",C55=""),"",ROUND((G55-D55)/(D55-E55),2))</f>
         <v/>
       </c>
-      <c r="J55" s="25" t="str">
+      <c r="J55" s="26" t="str">
         <f aca="false">IF(I55="","",ROUND(I55*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K55" s="6"/>
-      <c r="L55" s="26"/>
+      <c r="L55" s="27"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="23"/>
+      <c r="A56" s="24"/>
       <c r="B56" s="6"/>
       <c r="C56" s="8" t="str">
         <f aca="false">IF(OR(D56="",E56="",D56=E56),"",IF(E56&lt;D56,"BUY","SELL"))</f>
@@ -2868,19 +2944,19 @@
         <f aca="false">IF(I56="","",IF(I56&gt;0,"WIN",IF(I56&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I56" s="24" t="str">
+      <c r="I56" s="25" t="str">
         <f aca="false">IF(OR(G56="",C56=""),"",ROUND((G56-D56)/(D56-E56),2))</f>
         <v/>
       </c>
-      <c r="J56" s="25" t="str">
+      <c r="J56" s="26" t="str">
         <f aca="false">IF(I56="","",ROUND(I56*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K56" s="6"/>
-      <c r="L56" s="26"/>
+      <c r="L56" s="27"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="23"/>
+      <c r="A57" s="24"/>
       <c r="B57" s="6"/>
       <c r="C57" s="8" t="str">
         <f aca="false">IF(OR(D57="",E57="",D57=E57),"",IF(E57&lt;D57,"BUY","SELL"))</f>
@@ -2897,19 +2973,19 @@
         <f aca="false">IF(I57="","",IF(I57&gt;0,"WIN",IF(I57&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I57" s="24" t="str">
+      <c r="I57" s="25" t="str">
         <f aca="false">IF(OR(G57="",C57=""),"",ROUND((G57-D57)/(D57-E57),2))</f>
         <v/>
       </c>
-      <c r="J57" s="25" t="str">
+      <c r="J57" s="26" t="str">
         <f aca="false">IF(I57="","",ROUND(I57*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K57" s="6"/>
-      <c r="L57" s="26"/>
+      <c r="L57" s="27"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="23"/>
+      <c r="A58" s="24"/>
       <c r="B58" s="6"/>
       <c r="C58" s="8" t="str">
         <f aca="false">IF(OR(D58="",E58="",D58=E58),"",IF(E58&lt;D58,"BUY","SELL"))</f>
@@ -2926,19 +3002,19 @@
         <f aca="false">IF(I58="","",IF(I58&gt;0,"WIN",IF(I58&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I58" s="24" t="str">
+      <c r="I58" s="25" t="str">
         <f aca="false">IF(OR(G58="",C58=""),"",ROUND((G58-D58)/(D58-E58),2))</f>
         <v/>
       </c>
-      <c r="J58" s="25" t="str">
+      <c r="J58" s="26" t="str">
         <f aca="false">IF(I58="","",ROUND(I58*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K58" s="6"/>
-      <c r="L58" s="26"/>
+      <c r="L58" s="27"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="23"/>
+      <c r="A59" s="24"/>
       <c r="B59" s="6"/>
       <c r="C59" s="8" t="str">
         <f aca="false">IF(OR(D59="",E59="",D59=E59),"",IF(E59&lt;D59,"BUY","SELL"))</f>
@@ -2955,19 +3031,19 @@
         <f aca="false">IF(I59="","",IF(I59&gt;0,"WIN",IF(I59&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I59" s="24" t="str">
+      <c r="I59" s="25" t="str">
         <f aca="false">IF(OR(G59="",C59=""),"",ROUND((G59-D59)/(D59-E59),2))</f>
         <v/>
       </c>
-      <c r="J59" s="25" t="str">
+      <c r="J59" s="26" t="str">
         <f aca="false">IF(I59="","",ROUND(I59*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K59" s="6"/>
-      <c r="L59" s="26"/>
+      <c r="L59" s="27"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="23"/>
+      <c r="A60" s="24"/>
       <c r="B60" s="6"/>
       <c r="C60" s="8" t="str">
         <f aca="false">IF(OR(D60="",E60="",D60=E60),"",IF(E60&lt;D60,"BUY","SELL"))</f>
@@ -2984,19 +3060,19 @@
         <f aca="false">IF(I60="","",IF(I60&gt;0,"WIN",IF(I60&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I60" s="24" t="str">
+      <c r="I60" s="25" t="str">
         <f aca="false">IF(OR(G60="",C60=""),"",ROUND((G60-D60)/(D60-E60),2))</f>
         <v/>
       </c>
-      <c r="J60" s="25" t="str">
+      <c r="J60" s="26" t="str">
         <f aca="false">IF(I60="","",ROUND(I60*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K60" s="6"/>
-      <c r="L60" s="26"/>
+      <c r="L60" s="27"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="23"/>
+      <c r="A61" s="24"/>
       <c r="B61" s="6"/>
       <c r="C61" s="8" t="str">
         <f aca="false">IF(OR(D61="",E61="",D61=E61),"",IF(E61&lt;D61,"BUY","SELL"))</f>
@@ -3013,19 +3089,19 @@
         <f aca="false">IF(I61="","",IF(I61&gt;0,"WIN",IF(I61&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I61" s="24" t="str">
+      <c r="I61" s="25" t="str">
         <f aca="false">IF(OR(G61="",C61=""),"",ROUND((G61-D61)/(D61-E61),2))</f>
         <v/>
       </c>
-      <c r="J61" s="25" t="str">
+      <c r="J61" s="26" t="str">
         <f aca="false">IF(I61="","",ROUND(I61*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K61" s="6"/>
-      <c r="L61" s="26"/>
+      <c r="L61" s="27"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="23"/>
+      <c r="A62" s="24"/>
       <c r="B62" s="6"/>
       <c r="C62" s="8" t="str">
         <f aca="false">IF(OR(D62="",E62="",D62=E62),"",IF(E62&lt;D62,"BUY","SELL"))</f>
@@ -3042,19 +3118,19 @@
         <f aca="false">IF(I62="","",IF(I62&gt;0,"WIN",IF(I62&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I62" s="24" t="str">
+      <c r="I62" s="25" t="str">
         <f aca="false">IF(OR(G62="",C62=""),"",ROUND((G62-D62)/(D62-E62),2))</f>
         <v/>
       </c>
-      <c r="J62" s="25" t="str">
+      <c r="J62" s="26" t="str">
         <f aca="false">IF(I62="","",ROUND(I62*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K62" s="6"/>
-      <c r="L62" s="26"/>
+      <c r="L62" s="27"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="23"/>
+      <c r="A63" s="24"/>
       <c r="B63" s="6"/>
       <c r="C63" s="8" t="str">
         <f aca="false">IF(OR(D63="",E63="",D63=E63),"",IF(E63&lt;D63,"BUY","SELL"))</f>
@@ -3071,19 +3147,19 @@
         <f aca="false">IF(I63="","",IF(I63&gt;0,"WIN",IF(I63&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I63" s="24" t="str">
+      <c r="I63" s="25" t="str">
         <f aca="false">IF(OR(G63="",C63=""),"",ROUND((G63-D63)/(D63-E63),2))</f>
         <v/>
       </c>
-      <c r="J63" s="25" t="str">
+      <c r="J63" s="26" t="str">
         <f aca="false">IF(I63="","",ROUND(I63*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K63" s="6"/>
-      <c r="L63" s="26"/>
+      <c r="L63" s="27"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="23"/>
+      <c r="A64" s="24"/>
       <c r="B64" s="6"/>
       <c r="C64" s="8" t="str">
         <f aca="false">IF(OR(D64="",E64="",D64=E64),"",IF(E64&lt;D64,"BUY","SELL"))</f>
@@ -3100,19 +3176,19 @@
         <f aca="false">IF(I64="","",IF(I64&gt;0,"WIN",IF(I64&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I64" s="24" t="str">
+      <c r="I64" s="25" t="str">
         <f aca="false">IF(OR(G64="",C64=""),"",ROUND((G64-D64)/(D64-E64),2))</f>
         <v/>
       </c>
-      <c r="J64" s="25" t="str">
+      <c r="J64" s="26" t="str">
         <f aca="false">IF(I64="","",ROUND(I64*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K64" s="6"/>
-      <c r="L64" s="26"/>
+      <c r="L64" s="27"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="23"/>
+      <c r="A65" s="24"/>
       <c r="B65" s="6"/>
       <c r="C65" s="8" t="str">
         <f aca="false">IF(OR(D65="",E65="",D65=E65),"",IF(E65&lt;D65,"BUY","SELL"))</f>
@@ -3129,19 +3205,19 @@
         <f aca="false">IF(I65="","",IF(I65&gt;0,"WIN",IF(I65&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I65" s="24" t="str">
+      <c r="I65" s="25" t="str">
         <f aca="false">IF(OR(G65="",C65=""),"",ROUND((G65-D65)/(D65-E65),2))</f>
         <v/>
       </c>
-      <c r="J65" s="25" t="str">
+      <c r="J65" s="26" t="str">
         <f aca="false">IF(I65="","",ROUND(I65*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K65" s="6"/>
-      <c r="L65" s="26"/>
+      <c r="L65" s="27"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="23"/>
+      <c r="A66" s="24"/>
       <c r="B66" s="6"/>
       <c r="C66" s="8" t="str">
         <f aca="false">IF(OR(D66="",E66="",D66=E66),"",IF(E66&lt;D66,"BUY","SELL"))</f>
@@ -3158,19 +3234,19 @@
         <f aca="false">IF(I66="","",IF(I66&gt;0,"WIN",IF(I66&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I66" s="24" t="str">
+      <c r="I66" s="25" t="str">
         <f aca="false">IF(OR(G66="",C66=""),"",ROUND((G66-D66)/(D66-E66),2))</f>
         <v/>
       </c>
-      <c r="J66" s="25" t="str">
+      <c r="J66" s="26" t="str">
         <f aca="false">IF(I66="","",ROUND(I66*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K66" s="6"/>
-      <c r="L66" s="26"/>
+      <c r="L66" s="27"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="23"/>
+      <c r="A67" s="24"/>
       <c r="B67" s="6"/>
       <c r="C67" s="8" t="str">
         <f aca="false">IF(OR(D67="",E67="",D67=E67),"",IF(E67&lt;D67,"BUY","SELL"))</f>
@@ -3187,19 +3263,19 @@
         <f aca="false">IF(I67="","",IF(I67&gt;0,"WIN",IF(I67&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I67" s="24" t="str">
+      <c r="I67" s="25" t="str">
         <f aca="false">IF(OR(G67="",C67=""),"",ROUND((G67-D67)/(D67-E67),2))</f>
         <v/>
       </c>
-      <c r="J67" s="25" t="str">
+      <c r="J67" s="26" t="str">
         <f aca="false">IF(I67="","",ROUND(I67*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K67" s="6"/>
-      <c r="L67" s="26"/>
+      <c r="L67" s="27"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="23"/>
+      <c r="A68" s="24"/>
       <c r="B68" s="6"/>
       <c r="C68" s="8" t="str">
         <f aca="false">IF(OR(D68="",E68="",D68=E68),"",IF(E68&lt;D68,"BUY","SELL"))</f>
@@ -3216,19 +3292,19 @@
         <f aca="false">IF(I68="","",IF(I68&gt;0,"WIN",IF(I68&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I68" s="24" t="str">
+      <c r="I68" s="25" t="str">
         <f aca="false">IF(OR(G68="",C68=""),"",ROUND((G68-D68)/(D68-E68),2))</f>
         <v/>
       </c>
-      <c r="J68" s="25" t="str">
+      <c r="J68" s="26" t="str">
         <f aca="false">IF(I68="","",ROUND(I68*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K68" s="6"/>
-      <c r="L68" s="26"/>
+      <c r="L68" s="27"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="23"/>
+      <c r="A69" s="24"/>
       <c r="B69" s="6"/>
       <c r="C69" s="8" t="str">
         <f aca="false">IF(OR(D69="",E69="",D69=E69),"",IF(E69&lt;D69,"BUY","SELL"))</f>
@@ -3245,19 +3321,19 @@
         <f aca="false">IF(I69="","",IF(I69&gt;0,"WIN",IF(I69&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I69" s="24" t="str">
+      <c r="I69" s="25" t="str">
         <f aca="false">IF(OR(G69="",C69=""),"",ROUND((G69-D69)/(D69-E69),2))</f>
         <v/>
       </c>
-      <c r="J69" s="25" t="str">
+      <c r="J69" s="26" t="str">
         <f aca="false">IF(I69="","",ROUND(I69*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K69" s="6"/>
-      <c r="L69" s="26"/>
+      <c r="L69" s="27"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="23"/>
+      <c r="A70" s="24"/>
       <c r="B70" s="6"/>
       <c r="C70" s="8" t="str">
         <f aca="false">IF(OR(D70="",E70="",D70=E70),"",IF(E70&lt;D70,"BUY","SELL"))</f>
@@ -3274,19 +3350,19 @@
         <f aca="false">IF(I70="","",IF(I70&gt;0,"WIN",IF(I70&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I70" s="24" t="str">
+      <c r="I70" s="25" t="str">
         <f aca="false">IF(OR(G70="",C70=""),"",ROUND((G70-D70)/(D70-E70),2))</f>
         <v/>
       </c>
-      <c r="J70" s="25" t="str">
+      <c r="J70" s="26" t="str">
         <f aca="false">IF(I70="","",ROUND(I70*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K70" s="6"/>
-      <c r="L70" s="26"/>
+      <c r="L70" s="27"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="23"/>
+      <c r="A71" s="24"/>
       <c r="B71" s="6"/>
       <c r="C71" s="8" t="str">
         <f aca="false">IF(OR(D71="",E71="",D71=E71),"",IF(E71&lt;D71,"BUY","SELL"))</f>
@@ -3303,19 +3379,19 @@
         <f aca="false">IF(I71="","",IF(I71&gt;0,"WIN",IF(I71&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I71" s="24" t="str">
+      <c r="I71" s="25" t="str">
         <f aca="false">IF(OR(G71="",C71=""),"",ROUND((G71-D71)/(D71-E71),2))</f>
         <v/>
       </c>
-      <c r="J71" s="25" t="str">
+      <c r="J71" s="26" t="str">
         <f aca="false">IF(I71="","",ROUND(I71*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K71" s="6"/>
-      <c r="L71" s="26"/>
+      <c r="L71" s="27"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="23"/>
+      <c r="A72" s="24"/>
       <c r="B72" s="6"/>
       <c r="C72" s="8" t="str">
         <f aca="false">IF(OR(D72="",E72="",D72=E72),"",IF(E72&lt;D72,"BUY","SELL"))</f>
@@ -3332,19 +3408,19 @@
         <f aca="false">IF(I72="","",IF(I72&gt;0,"WIN",IF(I72&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I72" s="24" t="str">
+      <c r="I72" s="25" t="str">
         <f aca="false">IF(OR(G72="",C72=""),"",ROUND((G72-D72)/(D72-E72),2))</f>
         <v/>
       </c>
-      <c r="J72" s="25" t="str">
+      <c r="J72" s="26" t="str">
         <f aca="false">IF(I72="","",ROUND(I72*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K72" s="6"/>
-      <c r="L72" s="26"/>
+      <c r="L72" s="27"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="23"/>
+      <c r="A73" s="24"/>
       <c r="B73" s="6"/>
       <c r="C73" s="8" t="str">
         <f aca="false">IF(OR(D73="",E73="",D73=E73),"",IF(E73&lt;D73,"BUY","SELL"))</f>
@@ -3361,19 +3437,19 @@
         <f aca="false">IF(I73="","",IF(I73&gt;0,"WIN",IF(I73&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I73" s="24" t="str">
+      <c r="I73" s="25" t="str">
         <f aca="false">IF(OR(G73="",C73=""),"",ROUND((G73-D73)/(D73-E73),2))</f>
         <v/>
       </c>
-      <c r="J73" s="25" t="str">
+      <c r="J73" s="26" t="str">
         <f aca="false">IF(I73="","",ROUND(I73*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K73" s="6"/>
-      <c r="L73" s="26"/>
+      <c r="L73" s="27"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="23"/>
+      <c r="A74" s="24"/>
       <c r="B74" s="6"/>
       <c r="C74" s="8" t="str">
         <f aca="false">IF(OR(D74="",E74="",D74=E74),"",IF(E74&lt;D74,"BUY","SELL"))</f>
@@ -3390,19 +3466,19 @@
         <f aca="false">IF(I74="","",IF(I74&gt;0,"WIN",IF(I74&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I74" s="24" t="str">
+      <c r="I74" s="25" t="str">
         <f aca="false">IF(OR(G74="",C74=""),"",ROUND((G74-D74)/(D74-E74),2))</f>
         <v/>
       </c>
-      <c r="J74" s="25" t="str">
+      <c r="J74" s="26" t="str">
         <f aca="false">IF(I74="","",ROUND(I74*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K74" s="6"/>
-      <c r="L74" s="26"/>
+      <c r="L74" s="27"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="23"/>
+      <c r="A75" s="24"/>
       <c r="B75" s="6"/>
       <c r="C75" s="8" t="str">
         <f aca="false">IF(OR(D75="",E75="",D75=E75),"",IF(E75&lt;D75,"BUY","SELL"))</f>
@@ -3419,19 +3495,19 @@
         <f aca="false">IF(I75="","",IF(I75&gt;0,"WIN",IF(I75&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I75" s="24" t="str">
+      <c r="I75" s="25" t="str">
         <f aca="false">IF(OR(G75="",C75=""),"",ROUND((G75-D75)/(D75-E75),2))</f>
         <v/>
       </c>
-      <c r="J75" s="25" t="str">
+      <c r="J75" s="26" t="str">
         <f aca="false">IF(I75="","",ROUND(I75*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K75" s="6"/>
-      <c r="L75" s="26"/>
+      <c r="L75" s="27"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="23"/>
+      <c r="A76" s="24"/>
       <c r="B76" s="6"/>
       <c r="C76" s="8" t="str">
         <f aca="false">IF(OR(D76="",E76="",D76=E76),"",IF(E76&lt;D76,"BUY","SELL"))</f>
@@ -3448,19 +3524,19 @@
         <f aca="false">IF(I76="","",IF(I76&gt;0,"WIN",IF(I76&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I76" s="24" t="str">
+      <c r="I76" s="25" t="str">
         <f aca="false">IF(OR(G76="",C76=""),"",ROUND((G76-D76)/(D76-E76),2))</f>
         <v/>
       </c>
-      <c r="J76" s="25" t="str">
+      <c r="J76" s="26" t="str">
         <f aca="false">IF(I76="","",ROUND(I76*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K76" s="6"/>
-      <c r="L76" s="26"/>
+      <c r="L76" s="27"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="23"/>
+      <c r="A77" s="24"/>
       <c r="B77" s="6"/>
       <c r="C77" s="8" t="str">
         <f aca="false">IF(OR(D77="",E77="",D77=E77),"",IF(E77&lt;D77,"BUY","SELL"))</f>
@@ -3477,19 +3553,19 @@
         <f aca="false">IF(I77="","",IF(I77&gt;0,"WIN",IF(I77&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I77" s="24" t="str">
+      <c r="I77" s="25" t="str">
         <f aca="false">IF(OR(G77="",C77=""),"",ROUND((G77-D77)/(D77-E77),2))</f>
         <v/>
       </c>
-      <c r="J77" s="25" t="str">
+      <c r="J77" s="26" t="str">
         <f aca="false">IF(I77="","",ROUND(I77*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K77" s="6"/>
-      <c r="L77" s="26"/>
+      <c r="L77" s="27"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="23"/>
+      <c r="A78" s="24"/>
       <c r="B78" s="6"/>
       <c r="C78" s="8" t="str">
         <f aca="false">IF(OR(D78="",E78="",D78=E78),"",IF(E78&lt;D78,"BUY","SELL"))</f>
@@ -3506,19 +3582,19 @@
         <f aca="false">IF(I78="","",IF(I78&gt;0,"WIN",IF(I78&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I78" s="24" t="str">
+      <c r="I78" s="25" t="str">
         <f aca="false">IF(OR(G78="",C78=""),"",ROUND((G78-D78)/(D78-E78),2))</f>
         <v/>
       </c>
-      <c r="J78" s="25" t="str">
+      <c r="J78" s="26" t="str">
         <f aca="false">IF(I78="","",ROUND(I78*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K78" s="6"/>
-      <c r="L78" s="26"/>
+      <c r="L78" s="27"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="23"/>
+      <c r="A79" s="24"/>
       <c r="B79" s="6"/>
       <c r="C79" s="8" t="str">
         <f aca="false">IF(OR(D79="",E79="",D79=E79),"",IF(E79&lt;D79,"BUY","SELL"))</f>
@@ -3535,19 +3611,19 @@
         <f aca="false">IF(I79="","",IF(I79&gt;0,"WIN",IF(I79&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I79" s="24" t="str">
+      <c r="I79" s="25" t="str">
         <f aca="false">IF(OR(G79="",C79=""),"",ROUND((G79-D79)/(D79-E79),2))</f>
         <v/>
       </c>
-      <c r="J79" s="25" t="str">
+      <c r="J79" s="26" t="str">
         <f aca="false">IF(I79="","",ROUND(I79*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K79" s="6"/>
-      <c r="L79" s="26"/>
+      <c r="L79" s="27"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="23"/>
+      <c r="A80" s="24"/>
       <c r="B80" s="6"/>
       <c r="C80" s="8" t="str">
         <f aca="false">IF(OR(D80="",E80="",D80=E80),"",IF(E80&lt;D80,"BUY","SELL"))</f>
@@ -3564,19 +3640,19 @@
         <f aca="false">IF(I80="","",IF(I80&gt;0,"WIN",IF(I80&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I80" s="24" t="str">
+      <c r="I80" s="25" t="str">
         <f aca="false">IF(OR(G80="",C80=""),"",ROUND((G80-D80)/(D80-E80),2))</f>
         <v/>
       </c>
-      <c r="J80" s="25" t="str">
+      <c r="J80" s="26" t="str">
         <f aca="false">IF(I80="","",ROUND(I80*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K80" s="6"/>
-      <c r="L80" s="26"/>
+      <c r="L80" s="27"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="23"/>
+      <c r="A81" s="24"/>
       <c r="B81" s="6"/>
       <c r="C81" s="8" t="str">
         <f aca="false">IF(OR(D81="",E81="",D81=E81),"",IF(E81&lt;D81,"BUY","SELL"))</f>
@@ -3593,19 +3669,19 @@
         <f aca="false">IF(I81="","",IF(I81&gt;0,"WIN",IF(I81&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I81" s="24" t="str">
+      <c r="I81" s="25" t="str">
         <f aca="false">IF(OR(G81="",C81=""),"",ROUND((G81-D81)/(D81-E81),2))</f>
         <v/>
       </c>
-      <c r="J81" s="25" t="str">
+      <c r="J81" s="26" t="str">
         <f aca="false">IF(I81="","",ROUND(I81*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K81" s="6"/>
-      <c r="L81" s="26"/>
+      <c r="L81" s="27"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="23"/>
+      <c r="A82" s="24"/>
       <c r="B82" s="6"/>
       <c r="C82" s="8" t="str">
         <f aca="false">IF(OR(D82="",E82="",D82=E82),"",IF(E82&lt;D82,"BUY","SELL"))</f>
@@ -3622,19 +3698,19 @@
         <f aca="false">IF(I82="","",IF(I82&gt;0,"WIN",IF(I82&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I82" s="24" t="str">
+      <c r="I82" s="25" t="str">
         <f aca="false">IF(OR(G82="",C82=""),"",ROUND((G82-D82)/(D82-E82),2))</f>
         <v/>
       </c>
-      <c r="J82" s="25" t="str">
+      <c r="J82" s="26" t="str">
         <f aca="false">IF(I82="","",ROUND(I82*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K82" s="6"/>
-      <c r="L82" s="26"/>
+      <c r="L82" s="27"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="23"/>
+      <c r="A83" s="24"/>
       <c r="B83" s="6"/>
       <c r="C83" s="8" t="str">
         <f aca="false">IF(OR(D83="",E83="",D83=E83),"",IF(E83&lt;D83,"BUY","SELL"))</f>
@@ -3651,19 +3727,19 @@
         <f aca="false">IF(I83="","",IF(I83&gt;0,"WIN",IF(I83&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I83" s="24" t="str">
+      <c r="I83" s="25" t="str">
         <f aca="false">IF(OR(G83="",C83=""),"",ROUND((G83-D83)/(D83-E83),2))</f>
         <v/>
       </c>
-      <c r="J83" s="25" t="str">
+      <c r="J83" s="26" t="str">
         <f aca="false">IF(I83="","",ROUND(I83*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K83" s="6"/>
-      <c r="L83" s="26"/>
+      <c r="L83" s="27"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="23"/>
+      <c r="A84" s="24"/>
       <c r="B84" s="6"/>
       <c r="C84" s="8" t="str">
         <f aca="false">IF(OR(D84="",E84="",D84=E84),"",IF(E84&lt;D84,"BUY","SELL"))</f>
@@ -3680,19 +3756,19 @@
         <f aca="false">IF(I84="","",IF(I84&gt;0,"WIN",IF(I84&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I84" s="24" t="str">
+      <c r="I84" s="25" t="str">
         <f aca="false">IF(OR(G84="",C84=""),"",ROUND((G84-D84)/(D84-E84),2))</f>
         <v/>
       </c>
-      <c r="J84" s="25" t="str">
+      <c r="J84" s="26" t="str">
         <f aca="false">IF(I84="","",ROUND(I84*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K84" s="6"/>
-      <c r="L84" s="26"/>
+      <c r="L84" s="27"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="23"/>
+      <c r="A85" s="24"/>
       <c r="B85" s="6"/>
       <c r="C85" s="8" t="str">
         <f aca="false">IF(OR(D85="",E85="",D85=E85),"",IF(E85&lt;D85,"BUY","SELL"))</f>
@@ -3709,19 +3785,19 @@
         <f aca="false">IF(I85="","",IF(I85&gt;0,"WIN",IF(I85&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I85" s="24" t="str">
+      <c r="I85" s="25" t="str">
         <f aca="false">IF(OR(G85="",C85=""),"",ROUND((G85-D85)/(D85-E85),2))</f>
         <v/>
       </c>
-      <c r="J85" s="25" t="str">
+      <c r="J85" s="26" t="str">
         <f aca="false">IF(I85="","",ROUND(I85*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K85" s="6"/>
-      <c r="L85" s="26"/>
+      <c r="L85" s="27"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="23"/>
+      <c r="A86" s="24"/>
       <c r="B86" s="6"/>
       <c r="C86" s="8" t="str">
         <f aca="false">IF(OR(D86="",E86="",D86=E86),"",IF(E86&lt;D86,"BUY","SELL"))</f>
@@ -3738,19 +3814,19 @@
         <f aca="false">IF(I86="","",IF(I86&gt;0,"WIN",IF(I86&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I86" s="24" t="str">
+      <c r="I86" s="25" t="str">
         <f aca="false">IF(OR(G86="",C86=""),"",ROUND((G86-D86)/(D86-E86),2))</f>
         <v/>
       </c>
-      <c r="J86" s="25" t="str">
+      <c r="J86" s="26" t="str">
         <f aca="false">IF(I86="","",ROUND(I86*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K86" s="6"/>
-      <c r="L86" s="26"/>
+      <c r="L86" s="27"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="23"/>
+      <c r="A87" s="24"/>
       <c r="B87" s="6"/>
       <c r="C87" s="8" t="str">
         <f aca="false">IF(OR(D87="",E87="",D87=E87),"",IF(E87&lt;D87,"BUY","SELL"))</f>
@@ -3767,19 +3843,19 @@
         <f aca="false">IF(I87="","",IF(I87&gt;0,"WIN",IF(I87&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I87" s="24" t="str">
+      <c r="I87" s="25" t="str">
         <f aca="false">IF(OR(G87="",C87=""),"",ROUND((G87-D87)/(D87-E87),2))</f>
         <v/>
       </c>
-      <c r="J87" s="25" t="str">
+      <c r="J87" s="26" t="str">
         <f aca="false">IF(I87="","",ROUND(I87*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K87" s="6"/>
-      <c r="L87" s="26"/>
+      <c r="L87" s="27"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="23"/>
+      <c r="A88" s="24"/>
       <c r="B88" s="6"/>
       <c r="C88" s="8" t="str">
         <f aca="false">IF(OR(D88="",E88="",D88=E88),"",IF(E88&lt;D88,"BUY","SELL"))</f>
@@ -3796,19 +3872,19 @@
         <f aca="false">IF(I88="","",IF(I88&gt;0,"WIN",IF(I88&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I88" s="24" t="str">
+      <c r="I88" s="25" t="str">
         <f aca="false">IF(OR(G88="",C88=""),"",ROUND((G88-D88)/(D88-E88),2))</f>
         <v/>
       </c>
-      <c r="J88" s="25" t="str">
+      <c r="J88" s="26" t="str">
         <f aca="false">IF(I88="","",ROUND(I88*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K88" s="6"/>
-      <c r="L88" s="26"/>
+      <c r="L88" s="27"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="23"/>
+      <c r="A89" s="24"/>
       <c r="B89" s="6"/>
       <c r="C89" s="8" t="str">
         <f aca="false">IF(OR(D89="",E89="",D89=E89),"",IF(E89&lt;D89,"BUY","SELL"))</f>
@@ -3825,19 +3901,19 @@
         <f aca="false">IF(I89="","",IF(I89&gt;0,"WIN",IF(I89&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I89" s="24" t="str">
+      <c r="I89" s="25" t="str">
         <f aca="false">IF(OR(G89="",C89=""),"",ROUND((G89-D89)/(D89-E89),2))</f>
         <v/>
       </c>
-      <c r="J89" s="25" t="str">
+      <c r="J89" s="26" t="str">
         <f aca="false">IF(I89="","",ROUND(I89*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K89" s="6"/>
-      <c r="L89" s="26"/>
+      <c r="L89" s="27"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="23"/>
+      <c r="A90" s="24"/>
       <c r="B90" s="6"/>
       <c r="C90" s="8" t="str">
         <f aca="false">IF(OR(D90="",E90="",D90=E90),"",IF(E90&lt;D90,"BUY","SELL"))</f>
@@ -3854,19 +3930,19 @@
         <f aca="false">IF(I90="","",IF(I90&gt;0,"WIN",IF(I90&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I90" s="24" t="str">
+      <c r="I90" s="25" t="str">
         <f aca="false">IF(OR(G90="",C90=""),"",ROUND((G90-D90)/(D90-E90),2))</f>
         <v/>
       </c>
-      <c r="J90" s="25" t="str">
+      <c r="J90" s="26" t="str">
         <f aca="false">IF(I90="","",ROUND(I90*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K90" s="6"/>
-      <c r="L90" s="26"/>
+      <c r="L90" s="27"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="23"/>
+      <c r="A91" s="24"/>
       <c r="B91" s="6"/>
       <c r="C91" s="8" t="str">
         <f aca="false">IF(OR(D91="",E91="",D91=E91),"",IF(E91&lt;D91,"BUY","SELL"))</f>
@@ -3883,19 +3959,19 @@
         <f aca="false">IF(I91="","",IF(I91&gt;0,"WIN",IF(I91&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I91" s="24" t="str">
+      <c r="I91" s="25" t="str">
         <f aca="false">IF(OR(G91="",C91=""),"",ROUND((G91-D91)/(D91-E91),2))</f>
         <v/>
       </c>
-      <c r="J91" s="25" t="str">
+      <c r="J91" s="26" t="str">
         <f aca="false">IF(I91="","",ROUND(I91*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K91" s="6"/>
-      <c r="L91" s="26"/>
+      <c r="L91" s="27"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="23"/>
+      <c r="A92" s="24"/>
       <c r="B92" s="6"/>
       <c r="C92" s="8" t="str">
         <f aca="false">IF(OR(D92="",E92="",D92=E92),"",IF(E92&lt;D92,"BUY","SELL"))</f>
@@ -3912,19 +3988,19 @@
         <f aca="false">IF(I92="","",IF(I92&gt;0,"WIN",IF(I92&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I92" s="24" t="str">
+      <c r="I92" s="25" t="str">
         <f aca="false">IF(OR(G92="",C92=""),"",ROUND((G92-D92)/(D92-E92),2))</f>
         <v/>
       </c>
-      <c r="J92" s="25" t="str">
+      <c r="J92" s="26" t="str">
         <f aca="false">IF(I92="","",ROUND(I92*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K92" s="6"/>
-      <c r="L92" s="26"/>
+      <c r="L92" s="27"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="23"/>
+      <c r="A93" s="24"/>
       <c r="B93" s="6"/>
       <c r="C93" s="8" t="str">
         <f aca="false">IF(OR(D93="",E93="",D93=E93),"",IF(E93&lt;D93,"BUY","SELL"))</f>
@@ -3941,19 +4017,19 @@
         <f aca="false">IF(I93="","",IF(I93&gt;0,"WIN",IF(I93&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I93" s="24" t="str">
+      <c r="I93" s="25" t="str">
         <f aca="false">IF(OR(G93="",C93=""),"",ROUND((G93-D93)/(D93-E93),2))</f>
         <v/>
       </c>
-      <c r="J93" s="25" t="str">
+      <c r="J93" s="26" t="str">
         <f aca="false">IF(I93="","",ROUND(I93*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K93" s="6"/>
-      <c r="L93" s="26"/>
+      <c r="L93" s="27"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="23"/>
+      <c r="A94" s="24"/>
       <c r="B94" s="6"/>
       <c r="C94" s="8" t="str">
         <f aca="false">IF(OR(D94="",E94="",D94=E94),"",IF(E94&lt;D94,"BUY","SELL"))</f>
@@ -3970,19 +4046,19 @@
         <f aca="false">IF(I94="","",IF(I94&gt;0,"WIN",IF(I94&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I94" s="24" t="str">
+      <c r="I94" s="25" t="str">
         <f aca="false">IF(OR(G94="",C94=""),"",ROUND((G94-D94)/(D94-E94),2))</f>
         <v/>
       </c>
-      <c r="J94" s="25" t="str">
+      <c r="J94" s="26" t="str">
         <f aca="false">IF(I94="","",ROUND(I94*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K94" s="6"/>
-      <c r="L94" s="26"/>
+      <c r="L94" s="27"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="23"/>
+      <c r="A95" s="24"/>
       <c r="B95" s="6"/>
       <c r="C95" s="8" t="str">
         <f aca="false">IF(OR(D95="",E95="",D95=E95),"",IF(E95&lt;D95,"BUY","SELL"))</f>
@@ -3999,19 +4075,19 @@
         <f aca="false">IF(I95="","",IF(I95&gt;0,"WIN",IF(I95&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I95" s="24" t="str">
+      <c r="I95" s="25" t="str">
         <f aca="false">IF(OR(G95="",C95=""),"",ROUND((G95-D95)/(D95-E95),2))</f>
         <v/>
       </c>
-      <c r="J95" s="25" t="str">
+      <c r="J95" s="26" t="str">
         <f aca="false">IF(I95="","",ROUND(I95*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K95" s="6"/>
-      <c r="L95" s="26"/>
+      <c r="L95" s="27"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="23"/>
+      <c r="A96" s="24"/>
       <c r="B96" s="6"/>
       <c r="C96" s="8" t="str">
         <f aca="false">IF(OR(D96="",E96="",D96=E96),"",IF(E96&lt;D96,"BUY","SELL"))</f>
@@ -4028,19 +4104,19 @@
         <f aca="false">IF(I96="","",IF(I96&gt;0,"WIN",IF(I96&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I96" s="24" t="str">
+      <c r="I96" s="25" t="str">
         <f aca="false">IF(OR(G96="",C96=""),"",ROUND((G96-D96)/(D96-E96),2))</f>
         <v/>
       </c>
-      <c r="J96" s="25" t="str">
+      <c r="J96" s="26" t="str">
         <f aca="false">IF(I96="","",ROUND(I96*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K96" s="6"/>
-      <c r="L96" s="26"/>
+      <c r="L96" s="27"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="23"/>
+      <c r="A97" s="24"/>
       <c r="B97" s="6"/>
       <c r="C97" s="8" t="str">
         <f aca="false">IF(OR(D97="",E97="",D97=E97),"",IF(E97&lt;D97,"BUY","SELL"))</f>
@@ -4057,19 +4133,19 @@
         <f aca="false">IF(I97="","",IF(I97&gt;0,"WIN",IF(I97&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I97" s="24" t="str">
+      <c r="I97" s="25" t="str">
         <f aca="false">IF(OR(G97="",C97=""),"",ROUND((G97-D97)/(D97-E97),2))</f>
         <v/>
       </c>
-      <c r="J97" s="25" t="str">
+      <c r="J97" s="26" t="str">
         <f aca="false">IF(I97="","",ROUND(I97*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K97" s="6"/>
-      <c r="L97" s="26"/>
+      <c r="L97" s="27"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="23"/>
+      <c r="A98" s="24"/>
       <c r="B98" s="6"/>
       <c r="C98" s="8" t="str">
         <f aca="false">IF(OR(D98="",E98="",D98=E98),"",IF(E98&lt;D98,"BUY","SELL"))</f>
@@ -4086,19 +4162,19 @@
         <f aca="false">IF(I98="","",IF(I98&gt;0,"WIN",IF(I98&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I98" s="24" t="str">
+      <c r="I98" s="25" t="str">
         <f aca="false">IF(OR(G98="",C98=""),"",ROUND((G98-D98)/(D98-E98),2))</f>
         <v/>
       </c>
-      <c r="J98" s="25" t="str">
+      <c r="J98" s="26" t="str">
         <f aca="false">IF(I98="","",ROUND(I98*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K98" s="6"/>
-      <c r="L98" s="26"/>
+      <c r="L98" s="27"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="23"/>
+      <c r="A99" s="24"/>
       <c r="B99" s="6"/>
       <c r="C99" s="8" t="str">
         <f aca="false">IF(OR(D99="",E99="",D99=E99),"",IF(E99&lt;D99,"BUY","SELL"))</f>
@@ -4115,19 +4191,19 @@
         <f aca="false">IF(I99="","",IF(I99&gt;0,"WIN",IF(I99&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I99" s="24" t="str">
+      <c r="I99" s="25" t="str">
         <f aca="false">IF(OR(G99="",C99=""),"",ROUND((G99-D99)/(D99-E99),2))</f>
         <v/>
       </c>
-      <c r="J99" s="25" t="str">
+      <c r="J99" s="26" t="str">
         <f aca="false">IF(I99="","",ROUND(I99*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K99" s="6"/>
-      <c r="L99" s="26"/>
+      <c r="L99" s="27"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="23"/>
+      <c r="A100" s="24"/>
       <c r="B100" s="6"/>
       <c r="C100" s="8" t="str">
         <f aca="false">IF(OR(D100="",E100="",D100=E100),"",IF(E100&lt;D100,"BUY","SELL"))</f>
@@ -4144,19 +4220,19 @@
         <f aca="false">IF(I100="","",IF(I100&gt;0,"WIN",IF(I100&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I100" s="24" t="str">
+      <c r="I100" s="25" t="str">
         <f aca="false">IF(OR(G100="",C100=""),"",ROUND((G100-D100)/(D100-E100),2))</f>
         <v/>
       </c>
-      <c r="J100" s="25" t="str">
+      <c r="J100" s="26" t="str">
         <f aca="false">IF(I100="","",ROUND(I100*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K100" s="6"/>
-      <c r="L100" s="26"/>
+      <c r="L100" s="27"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="23"/>
+      <c r="A101" s="24"/>
       <c r="B101" s="6"/>
       <c r="C101" s="8" t="str">
         <f aca="false">IF(OR(D101="",E101="",D101=E101),"",IF(E101&lt;D101,"BUY","SELL"))</f>
@@ -4173,19 +4249,19 @@
         <f aca="false">IF(I101="","",IF(I101&gt;0,"WIN",IF(I101&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I101" s="24" t="str">
+      <c r="I101" s="25" t="str">
         <f aca="false">IF(OR(G101="",C101=""),"",ROUND((G101-D101)/(D101-E101),2))</f>
         <v/>
       </c>
-      <c r="J101" s="25" t="str">
+      <c r="J101" s="26" t="str">
         <f aca="false">IF(I101="","",ROUND(I101*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K101" s="6"/>
-      <c r="L101" s="26"/>
+      <c r="L101" s="27"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="23"/>
+      <c r="A102" s="24"/>
       <c r="B102" s="6"/>
       <c r="C102" s="8" t="str">
         <f aca="false">IF(OR(D102="",E102="",D102=E102),"",IF(E102&lt;D102,"BUY","SELL"))</f>
@@ -4202,19 +4278,19 @@
         <f aca="false">IF(I102="","",IF(I102&gt;0,"WIN",IF(I102&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I102" s="24" t="str">
+      <c r="I102" s="25" t="str">
         <f aca="false">IF(OR(G102="",C102=""),"",ROUND((G102-D102)/(D102-E102),2))</f>
         <v/>
       </c>
-      <c r="J102" s="25" t="str">
+      <c r="J102" s="26" t="str">
         <f aca="false">IF(I102="","",ROUND(I102*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K102" s="6"/>
-      <c r="L102" s="26"/>
+      <c r="L102" s="27"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="23"/>
+      <c r="A103" s="24"/>
       <c r="B103" s="6"/>
       <c r="C103" s="8" t="str">
         <f aca="false">IF(OR(D103="",E103="",D103=E103),"",IF(E103&lt;D103,"BUY","SELL"))</f>
@@ -4231,19 +4307,19 @@
         <f aca="false">IF(I103="","",IF(I103&gt;0,"WIN",IF(I103&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I103" s="24" t="str">
+      <c r="I103" s="25" t="str">
         <f aca="false">IF(OR(G103="",C103=""),"",ROUND((G103-D103)/(D103-E103),2))</f>
         <v/>
       </c>
-      <c r="J103" s="25" t="str">
+      <c r="J103" s="26" t="str">
         <f aca="false">IF(I103="","",ROUND(I103*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K103" s="6"/>
-      <c r="L103" s="26"/>
+      <c r="L103" s="27"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="23"/>
+      <c r="A104" s="24"/>
       <c r="B104" s="6"/>
       <c r="C104" s="8" t="str">
         <f aca="false">IF(OR(D104="",E104="",D104=E104),"",IF(E104&lt;D104,"BUY","SELL"))</f>
@@ -4260,19 +4336,19 @@
         <f aca="false">IF(I104="","",IF(I104&gt;0,"WIN",IF(I104&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I104" s="24" t="str">
+      <c r="I104" s="25" t="str">
         <f aca="false">IF(OR(G104="",C104=""),"",ROUND((G104-D104)/(D104-E104),2))</f>
         <v/>
       </c>
-      <c r="J104" s="25" t="str">
+      <c r="J104" s="26" t="str">
         <f aca="false">IF(I104="","",ROUND(I104*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K104" s="6"/>
-      <c r="L104" s="26"/>
+      <c r="L104" s="27"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="23"/>
+      <c r="A105" s="24"/>
       <c r="B105" s="6"/>
       <c r="C105" s="8" t="str">
         <f aca="false">IF(OR(D105="",E105="",D105=E105),"",IF(E105&lt;D105,"BUY","SELL"))</f>
@@ -4289,19 +4365,19 @@
         <f aca="false">IF(I105="","",IF(I105&gt;0,"WIN",IF(I105&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I105" s="24" t="str">
+      <c r="I105" s="25" t="str">
         <f aca="false">IF(OR(G105="",C105=""),"",ROUND((G105-D105)/(D105-E105),2))</f>
         <v/>
       </c>
-      <c r="J105" s="25" t="str">
+      <c r="J105" s="26" t="str">
         <f aca="false">IF(I105="","",ROUND(I105*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K105" s="6"/>
-      <c r="L105" s="26"/>
+      <c r="L105" s="27"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="23"/>
+      <c r="A106" s="24"/>
       <c r="B106" s="6"/>
       <c r="C106" s="8" t="str">
         <f aca="false">IF(OR(D106="",E106="",D106=E106),"",IF(E106&lt;D106,"BUY","SELL"))</f>
@@ -4318,19 +4394,19 @@
         <f aca="false">IF(I106="","",IF(I106&gt;0,"WIN",IF(I106&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I106" s="24" t="str">
+      <c r="I106" s="25" t="str">
         <f aca="false">IF(OR(G106="",C106=""),"",ROUND((G106-D106)/(D106-E106),2))</f>
         <v/>
       </c>
-      <c r="J106" s="25" t="str">
+      <c r="J106" s="26" t="str">
         <f aca="false">IF(I106="","",ROUND(I106*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K106" s="6"/>
-      <c r="L106" s="26"/>
+      <c r="L106" s="27"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="23"/>
+      <c r="A107" s="24"/>
       <c r="B107" s="6"/>
       <c r="C107" s="8" t="str">
         <f aca="false">IF(OR(D107="",E107="",D107=E107),"",IF(E107&lt;D107,"BUY","SELL"))</f>
@@ -4347,19 +4423,19 @@
         <f aca="false">IF(I107="","",IF(I107&gt;0,"WIN",IF(I107&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I107" s="24" t="str">
+      <c r="I107" s="25" t="str">
         <f aca="false">IF(OR(G107="",C107=""),"",ROUND((G107-D107)/(D107-E107),2))</f>
         <v/>
       </c>
-      <c r="J107" s="25" t="str">
+      <c r="J107" s="26" t="str">
         <f aca="false">IF(I107="","",ROUND(I107*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K107" s="6"/>
-      <c r="L107" s="26"/>
+      <c r="L107" s="27"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="23"/>
+      <c r="A108" s="24"/>
       <c r="B108" s="6"/>
       <c r="C108" s="8" t="str">
         <f aca="false">IF(OR(D108="",E108="",D108=E108),"",IF(E108&lt;D108,"BUY","SELL"))</f>
@@ -4376,19 +4452,19 @@
         <f aca="false">IF(I108="","",IF(I108&gt;0,"WIN",IF(I108&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I108" s="24" t="str">
+      <c r="I108" s="25" t="str">
         <f aca="false">IF(OR(G108="",C108=""),"",ROUND((G108-D108)/(D108-E108),2))</f>
         <v/>
       </c>
-      <c r="J108" s="25" t="str">
+      <c r="J108" s="26" t="str">
         <f aca="false">IF(I108="","",ROUND(I108*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K108" s="6"/>
-      <c r="L108" s="26"/>
+      <c r="L108" s="27"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="23"/>
+      <c r="A109" s="24"/>
       <c r="B109" s="6"/>
       <c r="C109" s="8" t="str">
         <f aca="false">IF(OR(D109="",E109="",D109=E109),"",IF(E109&lt;D109,"BUY","SELL"))</f>
@@ -4405,19 +4481,19 @@
         <f aca="false">IF(I109="","",IF(I109&gt;0,"WIN",IF(I109&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I109" s="24" t="str">
+      <c r="I109" s="25" t="str">
         <f aca="false">IF(OR(G109="",C109=""),"",ROUND((G109-D109)/(D109-E109),2))</f>
         <v/>
       </c>
-      <c r="J109" s="25" t="str">
+      <c r="J109" s="26" t="str">
         <f aca="false">IF(I109="","",ROUND(I109*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K109" s="6"/>
-      <c r="L109" s="26"/>
+      <c r="L109" s="27"/>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="23"/>
+      <c r="A110" s="24"/>
       <c r="B110" s="6"/>
       <c r="C110" s="8" t="str">
         <f aca="false">IF(OR(D110="",E110="",D110=E110),"",IF(E110&lt;D110,"BUY","SELL"))</f>
@@ -4434,19 +4510,19 @@
         <f aca="false">IF(I110="","",IF(I110&gt;0,"WIN",IF(I110&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I110" s="24" t="str">
+      <c r="I110" s="25" t="str">
         <f aca="false">IF(OR(G110="",C110=""),"",ROUND((G110-D110)/(D110-E110),2))</f>
         <v/>
       </c>
-      <c r="J110" s="25" t="str">
+      <c r="J110" s="26" t="str">
         <f aca="false">IF(I110="","",ROUND(I110*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K110" s="6"/>
-      <c r="L110" s="26"/>
+      <c r="L110" s="27"/>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="23"/>
+      <c r="A111" s="24"/>
       <c r="B111" s="6"/>
       <c r="C111" s="8" t="str">
         <f aca="false">IF(OR(D111="",E111="",D111=E111),"",IF(E111&lt;D111,"BUY","SELL"))</f>
@@ -4463,19 +4539,19 @@
         <f aca="false">IF(I111="","",IF(I111&gt;0,"WIN",IF(I111&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I111" s="24" t="str">
+      <c r="I111" s="25" t="str">
         <f aca="false">IF(OR(G111="",C111=""),"",ROUND((G111-D111)/(D111-E111),2))</f>
         <v/>
       </c>
-      <c r="J111" s="25" t="str">
+      <c r="J111" s="26" t="str">
         <f aca="false">IF(I111="","",ROUND(I111*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K111" s="6"/>
-      <c r="L111" s="26"/>
+      <c r="L111" s="27"/>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="23"/>
+      <c r="A112" s="24"/>
       <c r="B112" s="6"/>
       <c r="C112" s="8" t="str">
         <f aca="false">IF(OR(D112="",E112="",D112=E112),"",IF(E112&lt;D112,"BUY","SELL"))</f>
@@ -4492,19 +4568,19 @@
         <f aca="false">IF(I112="","",IF(I112&gt;0,"WIN",IF(I112&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I112" s="24" t="str">
+      <c r="I112" s="25" t="str">
         <f aca="false">IF(OR(G112="",C112=""),"",ROUND((G112-D112)/(D112-E112),2))</f>
         <v/>
       </c>
-      <c r="J112" s="25" t="str">
+      <c r="J112" s="26" t="str">
         <f aca="false">IF(I112="","",ROUND(I112*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K112" s="6"/>
-      <c r="L112" s="26"/>
+      <c r="L112" s="27"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="23"/>
+      <c r="A113" s="24"/>
       <c r="B113" s="6"/>
       <c r="C113" s="8" t="str">
         <f aca="false">IF(OR(D113="",E113="",D113=E113),"",IF(E113&lt;D113,"BUY","SELL"))</f>
@@ -4521,19 +4597,19 @@
         <f aca="false">IF(I113="","",IF(I113&gt;0,"WIN",IF(I113&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I113" s="24" t="str">
+      <c r="I113" s="25" t="str">
         <f aca="false">IF(OR(G113="",C113=""),"",ROUND((G113-D113)/(D113-E113),2))</f>
         <v/>
       </c>
-      <c r="J113" s="25" t="str">
+      <c r="J113" s="26" t="str">
         <f aca="false">IF(I113="","",ROUND(I113*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K113" s="6"/>
-      <c r="L113" s="26"/>
+      <c r="L113" s="27"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="23"/>
+      <c r="A114" s="24"/>
       <c r="B114" s="6"/>
       <c r="C114" s="8" t="str">
         <f aca="false">IF(OR(D114="",E114="",D114=E114),"",IF(E114&lt;D114,"BUY","SELL"))</f>
@@ -4550,19 +4626,19 @@
         <f aca="false">IF(I114="","",IF(I114&gt;0,"WIN",IF(I114&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I114" s="24" t="str">
+      <c r="I114" s="25" t="str">
         <f aca="false">IF(OR(G114="",C114=""),"",ROUND((G114-D114)/(D114-E114),2))</f>
         <v/>
       </c>
-      <c r="J114" s="25" t="str">
+      <c r="J114" s="26" t="str">
         <f aca="false">IF(I114="","",ROUND(I114*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K114" s="6"/>
-      <c r="L114" s="26"/>
+      <c r="L114" s="27"/>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="23"/>
+      <c r="A115" s="24"/>
       <c r="B115" s="6"/>
       <c r="C115" s="8" t="str">
         <f aca="false">IF(OR(D115="",E115="",D115=E115),"",IF(E115&lt;D115,"BUY","SELL"))</f>
@@ -4579,19 +4655,19 @@
         <f aca="false">IF(I115="","",IF(I115&gt;0,"WIN",IF(I115&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I115" s="24" t="str">
+      <c r="I115" s="25" t="str">
         <f aca="false">IF(OR(G115="",C115=""),"",ROUND((G115-D115)/(D115-E115),2))</f>
         <v/>
       </c>
-      <c r="J115" s="25" t="str">
+      <c r="J115" s="26" t="str">
         <f aca="false">IF(I115="","",ROUND(I115*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K115" s="6"/>
-      <c r="L115" s="26"/>
+      <c r="L115" s="27"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="23"/>
+      <c r="A116" s="24"/>
       <c r="B116" s="6"/>
       <c r="C116" s="8" t="str">
         <f aca="false">IF(OR(D116="",E116="",D116=E116),"",IF(E116&lt;D116,"BUY","SELL"))</f>
@@ -4608,19 +4684,19 @@
         <f aca="false">IF(I116="","",IF(I116&gt;0,"WIN",IF(I116&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I116" s="24" t="str">
+      <c r="I116" s="25" t="str">
         <f aca="false">IF(OR(G116="",C116=""),"",ROUND((G116-D116)/(D116-E116),2))</f>
         <v/>
       </c>
-      <c r="J116" s="25" t="str">
+      <c r="J116" s="26" t="str">
         <f aca="false">IF(I116="","",ROUND(I116*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K116" s="6"/>
-      <c r="L116" s="26"/>
+      <c r="L116" s="27"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="23"/>
+      <c r="A117" s="24"/>
       <c r="B117" s="6"/>
       <c r="C117" s="8" t="str">
         <f aca="false">IF(OR(D117="",E117="",D117=E117),"",IF(E117&lt;D117,"BUY","SELL"))</f>
@@ -4637,19 +4713,19 @@
         <f aca="false">IF(I117="","",IF(I117&gt;0,"WIN",IF(I117&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I117" s="24" t="str">
+      <c r="I117" s="25" t="str">
         <f aca="false">IF(OR(G117="",C117=""),"",ROUND((G117-D117)/(D117-E117),2))</f>
         <v/>
       </c>
-      <c r="J117" s="25" t="str">
+      <c r="J117" s="26" t="str">
         <f aca="false">IF(I117="","",ROUND(I117*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K117" s="6"/>
-      <c r="L117" s="26"/>
+      <c r="L117" s="27"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="23"/>
+      <c r="A118" s="24"/>
       <c r="B118" s="6"/>
       <c r="C118" s="8" t="str">
         <f aca="false">IF(OR(D118="",E118="",D118=E118),"",IF(E118&lt;D118,"BUY","SELL"))</f>
@@ -4666,19 +4742,19 @@
         <f aca="false">IF(I118="","",IF(I118&gt;0,"WIN",IF(I118&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I118" s="24" t="str">
+      <c r="I118" s="25" t="str">
         <f aca="false">IF(OR(G118="",C118=""),"",ROUND((G118-D118)/(D118-E118),2))</f>
         <v/>
       </c>
-      <c r="J118" s="25" t="str">
+      <c r="J118" s="26" t="str">
         <f aca="false">IF(I118="","",ROUND(I118*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K118" s="6"/>
-      <c r="L118" s="26"/>
+      <c r="L118" s="27"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="23"/>
+      <c r="A119" s="24"/>
       <c r="B119" s="6"/>
       <c r="C119" s="8" t="str">
         <f aca="false">IF(OR(D119="",E119="",D119=E119),"",IF(E119&lt;D119,"BUY","SELL"))</f>
@@ -4695,19 +4771,19 @@
         <f aca="false">IF(I119="","",IF(I119&gt;0,"WIN",IF(I119&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I119" s="24" t="str">
+      <c r="I119" s="25" t="str">
         <f aca="false">IF(OR(G119="",C119=""),"",ROUND((G119-D119)/(D119-E119),2))</f>
         <v/>
       </c>
-      <c r="J119" s="25" t="str">
+      <c r="J119" s="26" t="str">
         <f aca="false">IF(I119="","",ROUND(I119*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K119" s="6"/>
-      <c r="L119" s="26"/>
+      <c r="L119" s="27"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="23"/>
+      <c r="A120" s="24"/>
       <c r="B120" s="6"/>
       <c r="C120" s="8" t="str">
         <f aca="false">IF(OR(D120="",E120="",D120=E120),"",IF(E120&lt;D120,"BUY","SELL"))</f>
@@ -4724,19 +4800,19 @@
         <f aca="false">IF(I120="","",IF(I120&gt;0,"WIN",IF(I120&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I120" s="24" t="str">
+      <c r="I120" s="25" t="str">
         <f aca="false">IF(OR(G120="",C120=""),"",ROUND((G120-D120)/(D120-E120),2))</f>
         <v/>
       </c>
-      <c r="J120" s="25" t="str">
+      <c r="J120" s="26" t="str">
         <f aca="false">IF(I120="","",ROUND(I120*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K120" s="6"/>
-      <c r="L120" s="26"/>
+      <c r="L120" s="27"/>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="23"/>
+      <c r="A121" s="24"/>
       <c r="B121" s="6"/>
       <c r="C121" s="8" t="str">
         <f aca="false">IF(OR(D121="",E121="",D121=E121),"",IF(E121&lt;D121,"BUY","SELL"))</f>
@@ -4753,19 +4829,19 @@
         <f aca="false">IF(I121="","",IF(I121&gt;0,"WIN",IF(I121&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I121" s="24" t="str">
+      <c r="I121" s="25" t="str">
         <f aca="false">IF(OR(G121="",C121=""),"",ROUND((G121-D121)/(D121-E121),2))</f>
         <v/>
       </c>
-      <c r="J121" s="25" t="str">
+      <c r="J121" s="26" t="str">
         <f aca="false">IF(I121="","",ROUND(I121*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K121" s="6"/>
-      <c r="L121" s="26"/>
+      <c r="L121" s="27"/>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="23"/>
+      <c r="A122" s="24"/>
       <c r="B122" s="6"/>
       <c r="C122" s="8" t="str">
         <f aca="false">IF(OR(D122="",E122="",D122=E122),"",IF(E122&lt;D122,"BUY","SELL"))</f>
@@ -4782,19 +4858,19 @@
         <f aca="false">IF(I122="","",IF(I122&gt;0,"WIN",IF(I122&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I122" s="24" t="str">
+      <c r="I122" s="25" t="str">
         <f aca="false">IF(OR(G122="",C122=""),"",ROUND((G122-D122)/(D122-E122),2))</f>
         <v/>
       </c>
-      <c r="J122" s="25" t="str">
+      <c r="J122" s="26" t="str">
         <f aca="false">IF(I122="","",ROUND(I122*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K122" s="6"/>
-      <c r="L122" s="26"/>
+      <c r="L122" s="27"/>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="23"/>
+      <c r="A123" s="24"/>
       <c r="B123" s="6"/>
       <c r="C123" s="8" t="str">
         <f aca="false">IF(OR(D123="",E123="",D123=E123),"",IF(E123&lt;D123,"BUY","SELL"))</f>
@@ -4811,19 +4887,19 @@
         <f aca="false">IF(I123="","",IF(I123&gt;0,"WIN",IF(I123&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I123" s="24" t="str">
+      <c r="I123" s="25" t="str">
         <f aca="false">IF(OR(G123="",C123=""),"",ROUND((G123-D123)/(D123-E123),2))</f>
         <v/>
       </c>
-      <c r="J123" s="25" t="str">
+      <c r="J123" s="26" t="str">
         <f aca="false">IF(I123="","",ROUND(I123*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K123" s="6"/>
-      <c r="L123" s="26"/>
+      <c r="L123" s="27"/>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="23"/>
+      <c r="A124" s="24"/>
       <c r="B124" s="6"/>
       <c r="C124" s="8" t="str">
         <f aca="false">IF(OR(D124="",E124="",D124=E124),"",IF(E124&lt;D124,"BUY","SELL"))</f>
@@ -4840,19 +4916,19 @@
         <f aca="false">IF(I124="","",IF(I124&gt;0,"WIN",IF(I124&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I124" s="24" t="str">
+      <c r="I124" s="25" t="str">
         <f aca="false">IF(OR(G124="",C124=""),"",ROUND((G124-D124)/(D124-E124),2))</f>
         <v/>
       </c>
-      <c r="J124" s="25" t="str">
+      <c r="J124" s="26" t="str">
         <f aca="false">IF(I124="","",ROUND(I124*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K124" s="6"/>
-      <c r="L124" s="26"/>
+      <c r="L124" s="27"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="23"/>
+      <c r="A125" s="24"/>
       <c r="B125" s="6"/>
       <c r="C125" s="8" t="str">
         <f aca="false">IF(OR(D125="",E125="",D125=E125),"",IF(E125&lt;D125,"BUY","SELL"))</f>
@@ -4869,19 +4945,19 @@
         <f aca="false">IF(I125="","",IF(I125&gt;0,"WIN",IF(I125&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I125" s="24" t="str">
+      <c r="I125" s="25" t="str">
         <f aca="false">IF(OR(G125="",C125=""),"",ROUND((G125-D125)/(D125-E125),2))</f>
         <v/>
       </c>
-      <c r="J125" s="25" t="str">
+      <c r="J125" s="26" t="str">
         <f aca="false">IF(I125="","",ROUND(I125*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K125" s="6"/>
-      <c r="L125" s="26"/>
+      <c r="L125" s="27"/>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="23"/>
+      <c r="A126" s="24"/>
       <c r="B126" s="6"/>
       <c r="C126" s="8" t="str">
         <f aca="false">IF(OR(D126="",E126="",D126=E126),"",IF(E126&lt;D126,"BUY","SELL"))</f>
@@ -4898,19 +4974,19 @@
         <f aca="false">IF(I126="","",IF(I126&gt;0,"WIN",IF(I126&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I126" s="24" t="str">
+      <c r="I126" s="25" t="str">
         <f aca="false">IF(OR(G126="",C126=""),"",ROUND((G126-D126)/(D126-E126),2))</f>
         <v/>
       </c>
-      <c r="J126" s="25" t="str">
+      <c r="J126" s="26" t="str">
         <f aca="false">IF(I126="","",ROUND(I126*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K126" s="6"/>
-      <c r="L126" s="26"/>
+      <c r="L126" s="27"/>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="23"/>
+      <c r="A127" s="24"/>
       <c r="B127" s="6"/>
       <c r="C127" s="8" t="str">
         <f aca="false">IF(OR(D127="",E127="",D127=E127),"",IF(E127&lt;D127,"BUY","SELL"))</f>
@@ -4927,19 +5003,19 @@
         <f aca="false">IF(I127="","",IF(I127&gt;0,"WIN",IF(I127&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I127" s="24" t="str">
+      <c r="I127" s="25" t="str">
         <f aca="false">IF(OR(G127="",C127=""),"",ROUND((G127-D127)/(D127-E127),2))</f>
         <v/>
       </c>
-      <c r="J127" s="25" t="str">
+      <c r="J127" s="26" t="str">
         <f aca="false">IF(I127="","",ROUND(I127*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K127" s="6"/>
-      <c r="L127" s="26"/>
+      <c r="L127" s="27"/>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="23"/>
+      <c r="A128" s="24"/>
       <c r="B128" s="6"/>
       <c r="C128" s="8" t="str">
         <f aca="false">IF(OR(D128="",E128="",D128=E128),"",IF(E128&lt;D128,"BUY","SELL"))</f>
@@ -4956,19 +5032,19 @@
         <f aca="false">IF(I128="","",IF(I128&gt;0,"WIN",IF(I128&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I128" s="24" t="str">
+      <c r="I128" s="25" t="str">
         <f aca="false">IF(OR(G128="",C128=""),"",ROUND((G128-D128)/(D128-E128),2))</f>
         <v/>
       </c>
-      <c r="J128" s="25" t="str">
+      <c r="J128" s="26" t="str">
         <f aca="false">IF(I128="","",ROUND(I128*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K128" s="6"/>
-      <c r="L128" s="26"/>
+      <c r="L128" s="27"/>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="23"/>
+      <c r="A129" s="24"/>
       <c r="B129" s="6"/>
       <c r="C129" s="8" t="str">
         <f aca="false">IF(OR(D129="",E129="",D129=E129),"",IF(E129&lt;D129,"BUY","SELL"))</f>
@@ -4985,19 +5061,19 @@
         <f aca="false">IF(I129="","",IF(I129&gt;0,"WIN",IF(I129&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I129" s="24" t="str">
+      <c r="I129" s="25" t="str">
         <f aca="false">IF(OR(G129="",C129=""),"",ROUND((G129-D129)/(D129-E129),2))</f>
         <v/>
       </c>
-      <c r="J129" s="25" t="str">
+      <c r="J129" s="26" t="str">
         <f aca="false">IF(I129="","",ROUND(I129*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K129" s="6"/>
-      <c r="L129" s="26"/>
+      <c r="L129" s="27"/>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="23"/>
+      <c r="A130" s="24"/>
       <c r="B130" s="6"/>
       <c r="C130" s="8" t="str">
         <f aca="false">IF(OR(D130="",E130="",D130=E130),"",IF(E130&lt;D130,"BUY","SELL"))</f>
@@ -5014,19 +5090,19 @@
         <f aca="false">IF(I130="","",IF(I130&gt;0,"WIN",IF(I130&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I130" s="24" t="str">
+      <c r="I130" s="25" t="str">
         <f aca="false">IF(OR(G130="",C130=""),"",ROUND((G130-D130)/(D130-E130),2))</f>
         <v/>
       </c>
-      <c r="J130" s="25" t="str">
+      <c r="J130" s="26" t="str">
         <f aca="false">IF(I130="","",ROUND(I130*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K130" s="6"/>
-      <c r="L130" s="26"/>
+      <c r="L130" s="27"/>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="23"/>
+      <c r="A131" s="24"/>
       <c r="B131" s="6"/>
       <c r="C131" s="8" t="str">
         <f aca="false">IF(OR(D131="",E131="",D131=E131),"",IF(E131&lt;D131,"BUY","SELL"))</f>
@@ -5043,19 +5119,19 @@
         <f aca="false">IF(I131="","",IF(I131&gt;0,"WIN",IF(I131&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I131" s="24" t="str">
+      <c r="I131" s="25" t="str">
         <f aca="false">IF(OR(G131="",C131=""),"",ROUND((G131-D131)/(D131-E131),2))</f>
         <v/>
       </c>
-      <c r="J131" s="25" t="str">
+      <c r="J131" s="26" t="str">
         <f aca="false">IF(I131="","",ROUND(I131*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K131" s="6"/>
-      <c r="L131" s="26"/>
+      <c r="L131" s="27"/>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="23"/>
+      <c r="A132" s="24"/>
       <c r="B132" s="6"/>
       <c r="C132" s="8" t="str">
         <f aca="false">IF(OR(D132="",E132="",D132=E132),"",IF(E132&lt;D132,"BUY","SELL"))</f>
@@ -5072,19 +5148,19 @@
         <f aca="false">IF(I132="","",IF(I132&gt;0,"WIN",IF(I132&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I132" s="24" t="str">
+      <c r="I132" s="25" t="str">
         <f aca="false">IF(OR(G132="",C132=""),"",ROUND((G132-D132)/(D132-E132),2))</f>
         <v/>
       </c>
-      <c r="J132" s="25" t="str">
+      <c r="J132" s="26" t="str">
         <f aca="false">IF(I132="","",ROUND(I132*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K132" s="6"/>
-      <c r="L132" s="26"/>
+      <c r="L132" s="27"/>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="23"/>
+      <c r="A133" s="24"/>
       <c r="B133" s="6"/>
       <c r="C133" s="8" t="str">
         <f aca="false">IF(OR(D133="",E133="",D133=E133),"",IF(E133&lt;D133,"BUY","SELL"))</f>
@@ -5101,19 +5177,19 @@
         <f aca="false">IF(I133="","",IF(I133&gt;0,"WIN",IF(I133&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I133" s="24" t="str">
+      <c r="I133" s="25" t="str">
         <f aca="false">IF(OR(G133="",C133=""),"",ROUND((G133-D133)/(D133-E133),2))</f>
         <v/>
       </c>
-      <c r="J133" s="25" t="str">
+      <c r="J133" s="26" t="str">
         <f aca="false">IF(I133="","",ROUND(I133*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K133" s="6"/>
-      <c r="L133" s="26"/>
+      <c r="L133" s="27"/>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="23"/>
+      <c r="A134" s="24"/>
       <c r="B134" s="6"/>
       <c r="C134" s="8" t="str">
         <f aca="false">IF(OR(D134="",E134="",D134=E134),"",IF(E134&lt;D134,"BUY","SELL"))</f>
@@ -5130,19 +5206,19 @@
         <f aca="false">IF(I134="","",IF(I134&gt;0,"WIN",IF(I134&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I134" s="24" t="str">
+      <c r="I134" s="25" t="str">
         <f aca="false">IF(OR(G134="",C134=""),"",ROUND((G134-D134)/(D134-E134),2))</f>
         <v/>
       </c>
-      <c r="J134" s="25" t="str">
+      <c r="J134" s="26" t="str">
         <f aca="false">IF(I134="","",ROUND(I134*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K134" s="6"/>
-      <c r="L134" s="26"/>
+      <c r="L134" s="27"/>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="23"/>
+      <c r="A135" s="24"/>
       <c r="B135" s="6"/>
       <c r="C135" s="8" t="str">
         <f aca="false">IF(OR(D135="",E135="",D135=E135),"",IF(E135&lt;D135,"BUY","SELL"))</f>
@@ -5159,19 +5235,19 @@
         <f aca="false">IF(I135="","",IF(I135&gt;0,"WIN",IF(I135&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I135" s="24" t="str">
+      <c r="I135" s="25" t="str">
         <f aca="false">IF(OR(G135="",C135=""),"",ROUND((G135-D135)/(D135-E135),2))</f>
         <v/>
       </c>
-      <c r="J135" s="25" t="str">
+      <c r="J135" s="26" t="str">
         <f aca="false">IF(I135="","",ROUND(I135*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K135" s="6"/>
-      <c r="L135" s="26"/>
+      <c r="L135" s="27"/>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="23"/>
+      <c r="A136" s="24"/>
       <c r="B136" s="6"/>
       <c r="C136" s="8" t="str">
         <f aca="false">IF(OR(D136="",E136="",D136=E136),"",IF(E136&lt;D136,"BUY","SELL"))</f>
@@ -5188,19 +5264,19 @@
         <f aca="false">IF(I136="","",IF(I136&gt;0,"WIN",IF(I136&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I136" s="24" t="str">
+      <c r="I136" s="25" t="str">
         <f aca="false">IF(OR(G136="",C136=""),"",ROUND((G136-D136)/(D136-E136),2))</f>
         <v/>
       </c>
-      <c r="J136" s="25" t="str">
+      <c r="J136" s="26" t="str">
         <f aca="false">IF(I136="","",ROUND(I136*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K136" s="6"/>
-      <c r="L136" s="26"/>
+      <c r="L136" s="27"/>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="23"/>
+      <c r="A137" s="24"/>
       <c r="B137" s="6"/>
       <c r="C137" s="8" t="str">
         <f aca="false">IF(OR(D137="",E137="",D137=E137),"",IF(E137&lt;D137,"BUY","SELL"))</f>
@@ -5217,19 +5293,19 @@
         <f aca="false">IF(I137="","",IF(I137&gt;0,"WIN",IF(I137&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I137" s="24" t="str">
+      <c r="I137" s="25" t="str">
         <f aca="false">IF(OR(G137="",C137=""),"",ROUND((G137-D137)/(D137-E137),2))</f>
         <v/>
       </c>
-      <c r="J137" s="25" t="str">
+      <c r="J137" s="26" t="str">
         <f aca="false">IF(I137="","",ROUND(I137*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K137" s="6"/>
-      <c r="L137" s="26"/>
+      <c r="L137" s="27"/>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="23"/>
+      <c r="A138" s="24"/>
       <c r="B138" s="6"/>
       <c r="C138" s="8" t="str">
         <f aca="false">IF(OR(D138="",E138="",D138=E138),"",IF(E138&lt;D138,"BUY","SELL"))</f>
@@ -5246,19 +5322,19 @@
         <f aca="false">IF(I138="","",IF(I138&gt;0,"WIN",IF(I138&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I138" s="24" t="str">
+      <c r="I138" s="25" t="str">
         <f aca="false">IF(OR(G138="",C138=""),"",ROUND((G138-D138)/(D138-E138),2))</f>
         <v/>
       </c>
-      <c r="J138" s="25" t="str">
+      <c r="J138" s="26" t="str">
         <f aca="false">IF(I138="","",ROUND(I138*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K138" s="6"/>
-      <c r="L138" s="26"/>
+      <c r="L138" s="27"/>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="23"/>
+      <c r="A139" s="24"/>
       <c r="B139" s="6"/>
       <c r="C139" s="8" t="str">
         <f aca="false">IF(OR(D139="",E139="",D139=E139),"",IF(E139&lt;D139,"BUY","SELL"))</f>
@@ -5275,19 +5351,19 @@
         <f aca="false">IF(I139="","",IF(I139&gt;0,"WIN",IF(I139&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I139" s="24" t="str">
+      <c r="I139" s="25" t="str">
         <f aca="false">IF(OR(G139="",C139=""),"",ROUND((G139-D139)/(D139-E139),2))</f>
         <v/>
       </c>
-      <c r="J139" s="25" t="str">
+      <c r="J139" s="26" t="str">
         <f aca="false">IF(I139="","",ROUND(I139*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K139" s="6"/>
-      <c r="L139" s="26"/>
+      <c r="L139" s="27"/>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="23"/>
+      <c r="A140" s="24"/>
       <c r="B140" s="6"/>
       <c r="C140" s="8" t="str">
         <f aca="false">IF(OR(D140="",E140="",D140=E140),"",IF(E140&lt;D140,"BUY","SELL"))</f>
@@ -5304,19 +5380,19 @@
         <f aca="false">IF(I140="","",IF(I140&gt;0,"WIN",IF(I140&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I140" s="24" t="str">
+      <c r="I140" s="25" t="str">
         <f aca="false">IF(OR(G140="",C140=""),"",ROUND((G140-D140)/(D140-E140),2))</f>
         <v/>
       </c>
-      <c r="J140" s="25" t="str">
+      <c r="J140" s="26" t="str">
         <f aca="false">IF(I140="","",ROUND(I140*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K140" s="6"/>
-      <c r="L140" s="26"/>
+      <c r="L140" s="27"/>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="23"/>
+      <c r="A141" s="24"/>
       <c r="B141" s="6"/>
       <c r="C141" s="8" t="str">
         <f aca="false">IF(OR(D141="",E141="",D141=E141),"",IF(E141&lt;D141,"BUY","SELL"))</f>
@@ -5333,19 +5409,19 @@
         <f aca="false">IF(I141="","",IF(I141&gt;0,"WIN",IF(I141&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I141" s="24" t="str">
+      <c r="I141" s="25" t="str">
         <f aca="false">IF(OR(G141="",C141=""),"",ROUND((G141-D141)/(D141-E141),2))</f>
         <v/>
       </c>
-      <c r="J141" s="25" t="str">
+      <c r="J141" s="26" t="str">
         <f aca="false">IF(I141="","",ROUND(I141*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K141" s="6"/>
-      <c r="L141" s="26"/>
+      <c r="L141" s="27"/>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="23"/>
+      <c r="A142" s="24"/>
       <c r="B142" s="6"/>
       <c r="C142" s="8" t="str">
         <f aca="false">IF(OR(D142="",E142="",D142=E142),"",IF(E142&lt;D142,"BUY","SELL"))</f>
@@ -5362,19 +5438,19 @@
         <f aca="false">IF(I142="","",IF(I142&gt;0,"WIN",IF(I142&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I142" s="24" t="str">
+      <c r="I142" s="25" t="str">
         <f aca="false">IF(OR(G142="",C142=""),"",ROUND((G142-D142)/(D142-E142),2))</f>
         <v/>
       </c>
-      <c r="J142" s="25" t="str">
+      <c r="J142" s="26" t="str">
         <f aca="false">IF(I142="","",ROUND(I142*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K142" s="6"/>
-      <c r="L142" s="26"/>
+      <c r="L142" s="27"/>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="23"/>
+      <c r="A143" s="24"/>
       <c r="B143" s="6"/>
       <c r="C143" s="8" t="str">
         <f aca="false">IF(OR(D143="",E143="",D143=E143),"",IF(E143&lt;D143,"BUY","SELL"))</f>
@@ -5391,19 +5467,19 @@
         <f aca="false">IF(I143="","",IF(I143&gt;0,"WIN",IF(I143&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I143" s="24" t="str">
+      <c r="I143" s="25" t="str">
         <f aca="false">IF(OR(G143="",C143=""),"",ROUND((G143-D143)/(D143-E143),2))</f>
         <v/>
       </c>
-      <c r="J143" s="25" t="str">
+      <c r="J143" s="26" t="str">
         <f aca="false">IF(I143="","",ROUND(I143*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K143" s="6"/>
-      <c r="L143" s="26"/>
+      <c r="L143" s="27"/>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="23"/>
+      <c r="A144" s="24"/>
       <c r="B144" s="6"/>
       <c r="C144" s="8" t="str">
         <f aca="false">IF(OR(D144="",E144="",D144=E144),"",IF(E144&lt;D144,"BUY","SELL"))</f>
@@ -5420,19 +5496,19 @@
         <f aca="false">IF(I144="","",IF(I144&gt;0,"WIN",IF(I144&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I144" s="24" t="str">
+      <c r="I144" s="25" t="str">
         <f aca="false">IF(OR(G144="",C144=""),"",ROUND((G144-D144)/(D144-E144),2))</f>
         <v/>
       </c>
-      <c r="J144" s="25" t="str">
+      <c r="J144" s="26" t="str">
         <f aca="false">IF(I144="","",ROUND(I144*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K144" s="6"/>
-      <c r="L144" s="26"/>
+      <c r="L144" s="27"/>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="23"/>
+      <c r="A145" s="24"/>
       <c r="B145" s="6"/>
       <c r="C145" s="8" t="str">
         <f aca="false">IF(OR(D145="",E145="",D145=E145),"",IF(E145&lt;D145,"BUY","SELL"))</f>
@@ -5449,19 +5525,19 @@
         <f aca="false">IF(I145="","",IF(I145&gt;0,"WIN",IF(I145&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I145" s="24" t="str">
+      <c r="I145" s="25" t="str">
         <f aca="false">IF(OR(G145="",C145=""),"",ROUND((G145-D145)/(D145-E145),2))</f>
         <v/>
       </c>
-      <c r="J145" s="25" t="str">
+      <c r="J145" s="26" t="str">
         <f aca="false">IF(I145="","",ROUND(I145*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K145" s="6"/>
-      <c r="L145" s="26"/>
+      <c r="L145" s="27"/>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="23"/>
+      <c r="A146" s="24"/>
       <c r="B146" s="6"/>
       <c r="C146" s="8" t="str">
         <f aca="false">IF(OR(D146="",E146="",D146=E146),"",IF(E146&lt;D146,"BUY","SELL"))</f>
@@ -5478,19 +5554,19 @@
         <f aca="false">IF(I146="","",IF(I146&gt;0,"WIN",IF(I146&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I146" s="24" t="str">
+      <c r="I146" s="25" t="str">
         <f aca="false">IF(OR(G146="",C146=""),"",ROUND((G146-D146)/(D146-E146),2))</f>
         <v/>
       </c>
-      <c r="J146" s="25" t="str">
+      <c r="J146" s="26" t="str">
         <f aca="false">IF(I146="","",ROUND(I146*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K146" s="6"/>
-      <c r="L146" s="26"/>
+      <c r="L146" s="27"/>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="23"/>
+      <c r="A147" s="24"/>
       <c r="B147" s="6"/>
       <c r="C147" s="8" t="str">
         <f aca="false">IF(OR(D147="",E147="",D147=E147),"",IF(E147&lt;D147,"BUY","SELL"))</f>
@@ -5507,19 +5583,19 @@
         <f aca="false">IF(I147="","",IF(I147&gt;0,"WIN",IF(I147&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I147" s="24" t="str">
+      <c r="I147" s="25" t="str">
         <f aca="false">IF(OR(G147="",C147=""),"",ROUND((G147-D147)/(D147-E147),2))</f>
         <v/>
       </c>
-      <c r="J147" s="25" t="str">
+      <c r="J147" s="26" t="str">
         <f aca="false">IF(I147="","",ROUND(I147*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K147" s="6"/>
-      <c r="L147" s="26"/>
+      <c r="L147" s="27"/>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="23"/>
+      <c r="A148" s="24"/>
       <c r="B148" s="6"/>
       <c r="C148" s="8" t="str">
         <f aca="false">IF(OR(D148="",E148="",D148=E148),"",IF(E148&lt;D148,"BUY","SELL"))</f>
@@ -5536,19 +5612,19 @@
         <f aca="false">IF(I148="","",IF(I148&gt;0,"WIN",IF(I148&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I148" s="24" t="str">
+      <c r="I148" s="25" t="str">
         <f aca="false">IF(OR(G148="",C148=""),"",ROUND((G148-D148)/(D148-E148),2))</f>
         <v/>
       </c>
-      <c r="J148" s="25" t="str">
+      <c r="J148" s="26" t="str">
         <f aca="false">IF(I148="","",ROUND(I148*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K148" s="6"/>
-      <c r="L148" s="26"/>
+      <c r="L148" s="27"/>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="23"/>
+      <c r="A149" s="24"/>
       <c r="B149" s="6"/>
       <c r="C149" s="8" t="str">
         <f aca="false">IF(OR(D149="",E149="",D149=E149),"",IF(E149&lt;D149,"BUY","SELL"))</f>
@@ -5565,19 +5641,19 @@
         <f aca="false">IF(I149="","",IF(I149&gt;0,"WIN",IF(I149&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I149" s="24" t="str">
+      <c r="I149" s="25" t="str">
         <f aca="false">IF(OR(G149="",C149=""),"",ROUND((G149-D149)/(D149-E149),2))</f>
         <v/>
       </c>
-      <c r="J149" s="25" t="str">
+      <c r="J149" s="26" t="str">
         <f aca="false">IF(I149="","",ROUND(I149*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K149" s="6"/>
-      <c r="L149" s="26"/>
+      <c r="L149" s="27"/>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="23"/>
+      <c r="A150" s="24"/>
       <c r="B150" s="6"/>
       <c r="C150" s="8" t="str">
         <f aca="false">IF(OR(D150="",E150="",D150=E150),"",IF(E150&lt;D150,"BUY","SELL"))</f>
@@ -5594,19 +5670,19 @@
         <f aca="false">IF(I150="","",IF(I150&gt;0,"WIN",IF(I150&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I150" s="24" t="str">
+      <c r="I150" s="25" t="str">
         <f aca="false">IF(OR(G150="",C150=""),"",ROUND((G150-D150)/(D150-E150),2))</f>
         <v/>
       </c>
-      <c r="J150" s="25" t="str">
+      <c r="J150" s="26" t="str">
         <f aca="false">IF(I150="","",ROUND(I150*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K150" s="6"/>
-      <c r="L150" s="26"/>
+      <c r="L150" s="27"/>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="23"/>
+      <c r="A151" s="24"/>
       <c r="B151" s="6"/>
       <c r="C151" s="8" t="str">
         <f aca="false">IF(OR(D151="",E151="",D151=E151),"",IF(E151&lt;D151,"BUY","SELL"))</f>
@@ -5623,19 +5699,19 @@
         <f aca="false">IF(I151="","",IF(I151&gt;0,"WIN",IF(I151&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I151" s="24" t="str">
+      <c r="I151" s="25" t="str">
         <f aca="false">IF(OR(G151="",C151=""),"",ROUND((G151-D151)/(D151-E151),2))</f>
         <v/>
       </c>
-      <c r="J151" s="25" t="str">
+      <c r="J151" s="26" t="str">
         <f aca="false">IF(I151="","",ROUND(I151*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K151" s="6"/>
-      <c r="L151" s="26"/>
+      <c r="L151" s="27"/>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="23"/>
+      <c r="A152" s="24"/>
       <c r="B152" s="6"/>
       <c r="C152" s="8" t="str">
         <f aca="false">IF(OR(D152="",E152="",D152=E152),"",IF(E152&lt;D152,"BUY","SELL"))</f>
@@ -5652,19 +5728,19 @@
         <f aca="false">IF(I152="","",IF(I152&gt;0,"WIN",IF(I152&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I152" s="24" t="str">
+      <c r="I152" s="25" t="str">
         <f aca="false">IF(OR(G152="",C152=""),"",ROUND((G152-D152)/(D152-E152),2))</f>
         <v/>
       </c>
-      <c r="J152" s="25" t="str">
+      <c r="J152" s="26" t="str">
         <f aca="false">IF(I152="","",ROUND(I152*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K152" s="6"/>
-      <c r="L152" s="26"/>
+      <c r="L152" s="27"/>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="23"/>
+      <c r="A153" s="24"/>
       <c r="B153" s="6"/>
       <c r="C153" s="8" t="str">
         <f aca="false">IF(OR(D153="",E153="",D153=E153),"",IF(E153&lt;D153,"BUY","SELL"))</f>
@@ -5681,19 +5757,19 @@
         <f aca="false">IF(I153="","",IF(I153&gt;0,"WIN",IF(I153&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I153" s="24" t="str">
+      <c r="I153" s="25" t="str">
         <f aca="false">IF(OR(G153="",C153=""),"",ROUND((G153-D153)/(D153-E153),2))</f>
         <v/>
       </c>
-      <c r="J153" s="25" t="str">
+      <c r="J153" s="26" t="str">
         <f aca="false">IF(I153="","",ROUND(I153*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K153" s="6"/>
-      <c r="L153" s="26"/>
+      <c r="L153" s="27"/>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="23"/>
+      <c r="A154" s="24"/>
       <c r="B154" s="6"/>
       <c r="C154" s="8" t="str">
         <f aca="false">IF(OR(D154="",E154="",D154=E154),"",IF(E154&lt;D154,"BUY","SELL"))</f>
@@ -5710,19 +5786,19 @@
         <f aca="false">IF(I154="","",IF(I154&gt;0,"WIN",IF(I154&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I154" s="24" t="str">
+      <c r="I154" s="25" t="str">
         <f aca="false">IF(OR(G154="",C154=""),"",ROUND((G154-D154)/(D154-E154),2))</f>
         <v/>
       </c>
-      <c r="J154" s="25" t="str">
+      <c r="J154" s="26" t="str">
         <f aca="false">IF(I154="","",ROUND(I154*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K154" s="6"/>
-      <c r="L154" s="26"/>
+      <c r="L154" s="27"/>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="23"/>
+      <c r="A155" s="24"/>
       <c r="B155" s="6"/>
       <c r="C155" s="8" t="str">
         <f aca="false">IF(OR(D155="",E155="",D155=E155),"",IF(E155&lt;D155,"BUY","SELL"))</f>
@@ -5739,19 +5815,19 @@
         <f aca="false">IF(I155="","",IF(I155&gt;0,"WIN",IF(I155&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I155" s="24" t="str">
+      <c r="I155" s="25" t="str">
         <f aca="false">IF(OR(G155="",C155=""),"",ROUND((G155-D155)/(D155-E155),2))</f>
         <v/>
       </c>
-      <c r="J155" s="25" t="str">
+      <c r="J155" s="26" t="str">
         <f aca="false">IF(I155="","",ROUND(I155*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K155" s="6"/>
-      <c r="L155" s="26"/>
+      <c r="L155" s="27"/>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="23"/>
+      <c r="A156" s="24"/>
       <c r="B156" s="6"/>
       <c r="C156" s="8" t="str">
         <f aca="false">IF(OR(D156="",E156="",D156=E156),"",IF(E156&lt;D156,"BUY","SELL"))</f>
@@ -5768,19 +5844,19 @@
         <f aca="false">IF(I156="","",IF(I156&gt;0,"WIN",IF(I156&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I156" s="24" t="str">
+      <c r="I156" s="25" t="str">
         <f aca="false">IF(OR(G156="",C156=""),"",ROUND((G156-D156)/(D156-E156),2))</f>
         <v/>
       </c>
-      <c r="J156" s="25" t="str">
+      <c r="J156" s="26" t="str">
         <f aca="false">IF(I156="","",ROUND(I156*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K156" s="6"/>
-      <c r="L156" s="26"/>
+      <c r="L156" s="27"/>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="23"/>
+      <c r="A157" s="24"/>
       <c r="B157" s="6"/>
       <c r="C157" s="8" t="str">
         <f aca="false">IF(OR(D157="",E157="",D157=E157),"",IF(E157&lt;D157,"BUY","SELL"))</f>
@@ -5797,19 +5873,19 @@
         <f aca="false">IF(I157="","",IF(I157&gt;0,"WIN",IF(I157&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I157" s="24" t="str">
+      <c r="I157" s="25" t="str">
         <f aca="false">IF(OR(G157="",C157=""),"",ROUND((G157-D157)/(D157-E157),2))</f>
         <v/>
       </c>
-      <c r="J157" s="25" t="str">
+      <c r="J157" s="26" t="str">
         <f aca="false">IF(I157="","",ROUND(I157*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K157" s="6"/>
-      <c r="L157" s="26"/>
+      <c r="L157" s="27"/>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="23"/>
+      <c r="A158" s="24"/>
       <c r="B158" s="6"/>
       <c r="C158" s="8" t="str">
         <f aca="false">IF(OR(D158="",E158="",D158=E158),"",IF(E158&lt;D158,"BUY","SELL"))</f>
@@ -5826,19 +5902,19 @@
         <f aca="false">IF(I158="","",IF(I158&gt;0,"WIN",IF(I158&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I158" s="24" t="str">
+      <c r="I158" s="25" t="str">
         <f aca="false">IF(OR(G158="",C158=""),"",ROUND((G158-D158)/(D158-E158),2))</f>
         <v/>
       </c>
-      <c r="J158" s="25" t="str">
+      <c r="J158" s="26" t="str">
         <f aca="false">IF(I158="","",ROUND(I158*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K158" s="6"/>
-      <c r="L158" s="26"/>
+      <c r="L158" s="27"/>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="23"/>
+      <c r="A159" s="24"/>
       <c r="B159" s="6"/>
       <c r="C159" s="8" t="str">
         <f aca="false">IF(OR(D159="",E159="",D159=E159),"",IF(E159&lt;D159,"BUY","SELL"))</f>
@@ -5855,19 +5931,19 @@
         <f aca="false">IF(I159="","",IF(I159&gt;0,"WIN",IF(I159&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I159" s="24" t="str">
+      <c r="I159" s="25" t="str">
         <f aca="false">IF(OR(G159="",C159=""),"",ROUND((G159-D159)/(D159-E159),2))</f>
         <v/>
       </c>
-      <c r="J159" s="25" t="str">
+      <c r="J159" s="26" t="str">
         <f aca="false">IF(I159="","",ROUND(I159*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K159" s="6"/>
-      <c r="L159" s="26"/>
+      <c r="L159" s="27"/>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="23"/>
+      <c r="A160" s="24"/>
       <c r="B160" s="6"/>
       <c r="C160" s="8" t="str">
         <f aca="false">IF(OR(D160="",E160="",D160=E160),"",IF(E160&lt;D160,"BUY","SELL"))</f>
@@ -5884,19 +5960,19 @@
         <f aca="false">IF(I160="","",IF(I160&gt;0,"WIN",IF(I160&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I160" s="24" t="str">
+      <c r="I160" s="25" t="str">
         <f aca="false">IF(OR(G160="",C160=""),"",ROUND((G160-D160)/(D160-E160),2))</f>
         <v/>
       </c>
-      <c r="J160" s="25" t="str">
+      <c r="J160" s="26" t="str">
         <f aca="false">IF(I160="","",ROUND(I160*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K160" s="6"/>
-      <c r="L160" s="26"/>
+      <c r="L160" s="27"/>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="23"/>
+      <c r="A161" s="24"/>
       <c r="B161" s="6"/>
       <c r="C161" s="8" t="str">
         <f aca="false">IF(OR(D161="",E161="",D161=E161),"",IF(E161&lt;D161,"BUY","SELL"))</f>
@@ -5913,19 +5989,19 @@
         <f aca="false">IF(I161="","",IF(I161&gt;0,"WIN",IF(I161&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I161" s="24" t="str">
+      <c r="I161" s="25" t="str">
         <f aca="false">IF(OR(G161="",C161=""),"",ROUND((G161-D161)/(D161-E161),2))</f>
         <v/>
       </c>
-      <c r="J161" s="25" t="str">
+      <c r="J161" s="26" t="str">
         <f aca="false">IF(I161="","",ROUND(I161*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K161" s="6"/>
-      <c r="L161" s="26"/>
+      <c r="L161" s="27"/>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="23"/>
+      <c r="A162" s="24"/>
       <c r="B162" s="6"/>
       <c r="C162" s="8" t="str">
         <f aca="false">IF(OR(D162="",E162="",D162=E162),"",IF(E162&lt;D162,"BUY","SELL"))</f>
@@ -5942,19 +6018,19 @@
         <f aca="false">IF(I162="","",IF(I162&gt;0,"WIN",IF(I162&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I162" s="24" t="str">
+      <c r="I162" s="25" t="str">
         <f aca="false">IF(OR(G162="",C162=""),"",ROUND((G162-D162)/(D162-E162),2))</f>
         <v/>
       </c>
-      <c r="J162" s="25" t="str">
+      <c r="J162" s="26" t="str">
         <f aca="false">IF(I162="","",ROUND(I162*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K162" s="6"/>
-      <c r="L162" s="26"/>
+      <c r="L162" s="27"/>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="23"/>
+      <c r="A163" s="24"/>
       <c r="B163" s="6"/>
       <c r="C163" s="8" t="str">
         <f aca="false">IF(OR(D163="",E163="",D163=E163),"",IF(E163&lt;D163,"BUY","SELL"))</f>
@@ -5971,19 +6047,19 @@
         <f aca="false">IF(I163="","",IF(I163&gt;0,"WIN",IF(I163&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I163" s="24" t="str">
+      <c r="I163" s="25" t="str">
         <f aca="false">IF(OR(G163="",C163=""),"",ROUND((G163-D163)/(D163-E163),2))</f>
         <v/>
       </c>
-      <c r="J163" s="25" t="str">
+      <c r="J163" s="26" t="str">
         <f aca="false">IF(I163="","",ROUND(I163*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K163" s="6"/>
-      <c r="L163" s="26"/>
+      <c r="L163" s="27"/>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="23"/>
+      <c r="A164" s="24"/>
       <c r="B164" s="6"/>
       <c r="C164" s="8" t="str">
         <f aca="false">IF(OR(D164="",E164="",D164=E164),"",IF(E164&lt;D164,"BUY","SELL"))</f>
@@ -6000,19 +6076,19 @@
         <f aca="false">IF(I164="","",IF(I164&gt;0,"WIN",IF(I164&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I164" s="24" t="str">
+      <c r="I164" s="25" t="str">
         <f aca="false">IF(OR(G164="",C164=""),"",ROUND((G164-D164)/(D164-E164),2))</f>
         <v/>
       </c>
-      <c r="J164" s="25" t="str">
+      <c r="J164" s="26" t="str">
         <f aca="false">IF(I164="","",ROUND(I164*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K164" s="6"/>
-      <c r="L164" s="26"/>
+      <c r="L164" s="27"/>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="23"/>
+      <c r="A165" s="24"/>
       <c r="B165" s="6"/>
       <c r="C165" s="8" t="str">
         <f aca="false">IF(OR(D165="",E165="",D165=E165),"",IF(E165&lt;D165,"BUY","SELL"))</f>
@@ -6029,19 +6105,19 @@
         <f aca="false">IF(I165="","",IF(I165&gt;0,"WIN",IF(I165&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I165" s="24" t="str">
+      <c r="I165" s="25" t="str">
         <f aca="false">IF(OR(G165="",C165=""),"",ROUND((G165-D165)/(D165-E165),2))</f>
         <v/>
       </c>
-      <c r="J165" s="25" t="str">
+      <c r="J165" s="26" t="str">
         <f aca="false">IF(I165="","",ROUND(I165*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K165" s="6"/>
-      <c r="L165" s="26"/>
+      <c r="L165" s="27"/>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="23"/>
+      <c r="A166" s="24"/>
       <c r="B166" s="6"/>
       <c r="C166" s="8" t="str">
         <f aca="false">IF(OR(D166="",E166="",D166=E166),"",IF(E166&lt;D166,"BUY","SELL"))</f>
@@ -6058,19 +6134,19 @@
         <f aca="false">IF(I166="","",IF(I166&gt;0,"WIN",IF(I166&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I166" s="24" t="str">
+      <c r="I166" s="25" t="str">
         <f aca="false">IF(OR(G166="",C166=""),"",ROUND((G166-D166)/(D166-E166),2))</f>
         <v/>
       </c>
-      <c r="J166" s="25" t="str">
+      <c r="J166" s="26" t="str">
         <f aca="false">IF(I166="","",ROUND(I166*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K166" s="6"/>
-      <c r="L166" s="26"/>
+      <c r="L166" s="27"/>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="23"/>
+      <c r="A167" s="24"/>
       <c r="B167" s="6"/>
       <c r="C167" s="8" t="str">
         <f aca="false">IF(OR(D167="",E167="",D167=E167),"",IF(E167&lt;D167,"BUY","SELL"))</f>
@@ -6087,19 +6163,19 @@
         <f aca="false">IF(I167="","",IF(I167&gt;0,"WIN",IF(I167&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I167" s="24" t="str">
+      <c r="I167" s="25" t="str">
         <f aca="false">IF(OR(G167="",C167=""),"",ROUND((G167-D167)/(D167-E167),2))</f>
         <v/>
       </c>
-      <c r="J167" s="25" t="str">
+      <c r="J167" s="26" t="str">
         <f aca="false">IF(I167="","",ROUND(I167*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K167" s="6"/>
-      <c r="L167" s="26"/>
+      <c r="L167" s="27"/>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="23"/>
+      <c r="A168" s="24"/>
       <c r="B168" s="6"/>
       <c r="C168" s="8" t="str">
         <f aca="false">IF(OR(D168="",E168="",D168=E168),"",IF(E168&lt;D168,"BUY","SELL"))</f>
@@ -6116,19 +6192,19 @@
         <f aca="false">IF(I168="","",IF(I168&gt;0,"WIN",IF(I168&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I168" s="24" t="str">
+      <c r="I168" s="25" t="str">
         <f aca="false">IF(OR(G168="",C168=""),"",ROUND((G168-D168)/(D168-E168),2))</f>
         <v/>
       </c>
-      <c r="J168" s="25" t="str">
+      <c r="J168" s="26" t="str">
         <f aca="false">IF(I168="","",ROUND(I168*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K168" s="6"/>
-      <c r="L168" s="26"/>
+      <c r="L168" s="27"/>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="23"/>
+      <c r="A169" s="24"/>
       <c r="B169" s="6"/>
       <c r="C169" s="8" t="str">
         <f aca="false">IF(OR(D169="",E169="",D169=E169),"",IF(E169&lt;D169,"BUY","SELL"))</f>
@@ -6145,19 +6221,19 @@
         <f aca="false">IF(I169="","",IF(I169&gt;0,"WIN",IF(I169&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I169" s="24" t="str">
+      <c r="I169" s="25" t="str">
         <f aca="false">IF(OR(G169="",C169=""),"",ROUND((G169-D169)/(D169-E169),2))</f>
         <v/>
       </c>
-      <c r="J169" s="25" t="str">
+      <c r="J169" s="26" t="str">
         <f aca="false">IF(I169="","",ROUND(I169*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K169" s="6"/>
-      <c r="L169" s="26"/>
+      <c r="L169" s="27"/>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="23"/>
+      <c r="A170" s="24"/>
       <c r="B170" s="6"/>
       <c r="C170" s="8" t="str">
         <f aca="false">IF(OR(D170="",E170="",D170=E170),"",IF(E170&lt;D170,"BUY","SELL"))</f>
@@ -6174,19 +6250,19 @@
         <f aca="false">IF(I170="","",IF(I170&gt;0,"WIN",IF(I170&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I170" s="24" t="str">
+      <c r="I170" s="25" t="str">
         <f aca="false">IF(OR(G170="",C170=""),"",ROUND((G170-D170)/(D170-E170),2))</f>
         <v/>
       </c>
-      <c r="J170" s="25" t="str">
+      <c r="J170" s="26" t="str">
         <f aca="false">IF(I170="","",ROUND(I170*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K170" s="6"/>
-      <c r="L170" s="26"/>
+      <c r="L170" s="27"/>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="23"/>
+      <c r="A171" s="24"/>
       <c r="B171" s="6"/>
       <c r="C171" s="8" t="str">
         <f aca="false">IF(OR(D171="",E171="",D171=E171),"",IF(E171&lt;D171,"BUY","SELL"))</f>
@@ -6203,19 +6279,19 @@
         <f aca="false">IF(I171="","",IF(I171&gt;0,"WIN",IF(I171&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I171" s="24" t="str">
+      <c r="I171" s="25" t="str">
         <f aca="false">IF(OR(G171="",C171=""),"",ROUND((G171-D171)/(D171-E171),2))</f>
         <v/>
       </c>
-      <c r="J171" s="25" t="str">
+      <c r="J171" s="26" t="str">
         <f aca="false">IF(I171="","",ROUND(I171*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K171" s="6"/>
-      <c r="L171" s="26"/>
+      <c r="L171" s="27"/>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="23"/>
+      <c r="A172" s="24"/>
       <c r="B172" s="6"/>
       <c r="C172" s="8" t="str">
         <f aca="false">IF(OR(D172="",E172="",D172=E172),"",IF(E172&lt;D172,"BUY","SELL"))</f>
@@ -6232,19 +6308,19 @@
         <f aca="false">IF(I172="","",IF(I172&gt;0,"WIN",IF(I172&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I172" s="24" t="str">
+      <c r="I172" s="25" t="str">
         <f aca="false">IF(OR(G172="",C172=""),"",ROUND((G172-D172)/(D172-E172),2))</f>
         <v/>
       </c>
-      <c r="J172" s="25" t="str">
+      <c r="J172" s="26" t="str">
         <f aca="false">IF(I172="","",ROUND(I172*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K172" s="6"/>
-      <c r="L172" s="26"/>
+      <c r="L172" s="27"/>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="23"/>
+      <c r="A173" s="24"/>
       <c r="B173" s="6"/>
       <c r="C173" s="8" t="str">
         <f aca="false">IF(OR(D173="",E173="",D173=E173),"",IF(E173&lt;D173,"BUY","SELL"))</f>
@@ -6261,19 +6337,19 @@
         <f aca="false">IF(I173="","",IF(I173&gt;0,"WIN",IF(I173&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I173" s="24" t="str">
+      <c r="I173" s="25" t="str">
         <f aca="false">IF(OR(G173="",C173=""),"",ROUND((G173-D173)/(D173-E173),2))</f>
         <v/>
       </c>
-      <c r="J173" s="25" t="str">
+      <c r="J173" s="26" t="str">
         <f aca="false">IF(I173="","",ROUND(I173*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K173" s="6"/>
-      <c r="L173" s="26"/>
+      <c r="L173" s="27"/>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="23"/>
+      <c r="A174" s="24"/>
       <c r="B174" s="6"/>
       <c r="C174" s="8" t="str">
         <f aca="false">IF(OR(D174="",E174="",D174=E174),"",IF(E174&lt;D174,"BUY","SELL"))</f>
@@ -6290,19 +6366,19 @@
         <f aca="false">IF(I174="","",IF(I174&gt;0,"WIN",IF(I174&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I174" s="24" t="str">
+      <c r="I174" s="25" t="str">
         <f aca="false">IF(OR(G174="",C174=""),"",ROUND((G174-D174)/(D174-E174),2))</f>
         <v/>
       </c>
-      <c r="J174" s="25" t="str">
+      <c r="J174" s="26" t="str">
         <f aca="false">IF(I174="","",ROUND(I174*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K174" s="6"/>
-      <c r="L174" s="26"/>
+      <c r="L174" s="27"/>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="23"/>
+      <c r="A175" s="24"/>
       <c r="B175" s="6"/>
       <c r="C175" s="8" t="str">
         <f aca="false">IF(OR(D175="",E175="",D175=E175),"",IF(E175&lt;D175,"BUY","SELL"))</f>
@@ -6319,19 +6395,19 @@
         <f aca="false">IF(I175="","",IF(I175&gt;0,"WIN",IF(I175&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I175" s="24" t="str">
+      <c r="I175" s="25" t="str">
         <f aca="false">IF(OR(G175="",C175=""),"",ROUND((G175-D175)/(D175-E175),2))</f>
         <v/>
       </c>
-      <c r="J175" s="25" t="str">
+      <c r="J175" s="26" t="str">
         <f aca="false">IF(I175="","",ROUND(I175*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K175" s="6"/>
-      <c r="L175" s="26"/>
+      <c r="L175" s="27"/>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="23"/>
+      <c r="A176" s="24"/>
       <c r="B176" s="6"/>
       <c r="C176" s="8" t="str">
         <f aca="false">IF(OR(D176="",E176="",D176=E176),"",IF(E176&lt;D176,"BUY","SELL"))</f>
@@ -6348,19 +6424,19 @@
         <f aca="false">IF(I176="","",IF(I176&gt;0,"WIN",IF(I176&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I176" s="24" t="str">
+      <c r="I176" s="25" t="str">
         <f aca="false">IF(OR(G176="",C176=""),"",ROUND((G176-D176)/(D176-E176),2))</f>
         <v/>
       </c>
-      <c r="J176" s="25" t="str">
+      <c r="J176" s="26" t="str">
         <f aca="false">IF(I176="","",ROUND(I176*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K176" s="6"/>
-      <c r="L176" s="26"/>
+      <c r="L176" s="27"/>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="23"/>
+      <c r="A177" s="24"/>
       <c r="B177" s="6"/>
       <c r="C177" s="8" t="str">
         <f aca="false">IF(OR(D177="",E177="",D177=E177),"",IF(E177&lt;D177,"BUY","SELL"))</f>
@@ -6377,19 +6453,19 @@
         <f aca="false">IF(I177="","",IF(I177&gt;0,"WIN",IF(I177&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I177" s="24" t="str">
+      <c r="I177" s="25" t="str">
         <f aca="false">IF(OR(G177="",C177=""),"",ROUND((G177-D177)/(D177-E177),2))</f>
         <v/>
       </c>
-      <c r="J177" s="25" t="str">
+      <c r="J177" s="26" t="str">
         <f aca="false">IF(I177="","",ROUND(I177*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K177" s="6"/>
-      <c r="L177" s="26"/>
+      <c r="L177" s="27"/>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="23"/>
+      <c r="A178" s="24"/>
       <c r="B178" s="6"/>
       <c r="C178" s="8" t="str">
         <f aca="false">IF(OR(D178="",E178="",D178=E178),"",IF(E178&lt;D178,"BUY","SELL"))</f>
@@ -6406,19 +6482,19 @@
         <f aca="false">IF(I178="","",IF(I178&gt;0,"WIN",IF(I178&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I178" s="24" t="str">
+      <c r="I178" s="25" t="str">
         <f aca="false">IF(OR(G178="",C178=""),"",ROUND((G178-D178)/(D178-E178),2))</f>
         <v/>
       </c>
-      <c r="J178" s="25" t="str">
+      <c r="J178" s="26" t="str">
         <f aca="false">IF(I178="","",ROUND(I178*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K178" s="6"/>
-      <c r="L178" s="26"/>
+      <c r="L178" s="27"/>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="23"/>
+      <c r="A179" s="24"/>
       <c r="B179" s="6"/>
       <c r="C179" s="8" t="str">
         <f aca="false">IF(OR(D179="",E179="",D179=E179),"",IF(E179&lt;D179,"BUY","SELL"))</f>
@@ -6435,19 +6511,19 @@
         <f aca="false">IF(I179="","",IF(I179&gt;0,"WIN",IF(I179&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I179" s="24" t="str">
+      <c r="I179" s="25" t="str">
         <f aca="false">IF(OR(G179="",C179=""),"",ROUND((G179-D179)/(D179-E179),2))</f>
         <v/>
       </c>
-      <c r="J179" s="25" t="str">
+      <c r="J179" s="26" t="str">
         <f aca="false">IF(I179="","",ROUND(I179*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K179" s="6"/>
-      <c r="L179" s="26"/>
+      <c r="L179" s="27"/>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="23"/>
+      <c r="A180" s="24"/>
       <c r="B180" s="6"/>
       <c r="C180" s="8" t="str">
         <f aca="false">IF(OR(D180="",E180="",D180=E180),"",IF(E180&lt;D180,"BUY","SELL"))</f>
@@ -6464,19 +6540,19 @@
         <f aca="false">IF(I180="","",IF(I180&gt;0,"WIN",IF(I180&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I180" s="24" t="str">
+      <c r="I180" s="25" t="str">
         <f aca="false">IF(OR(G180="",C180=""),"",ROUND((G180-D180)/(D180-E180),2))</f>
         <v/>
       </c>
-      <c r="J180" s="25" t="str">
+      <c r="J180" s="26" t="str">
         <f aca="false">IF(I180="","",ROUND(I180*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K180" s="6"/>
-      <c r="L180" s="26"/>
+      <c r="L180" s="27"/>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="23"/>
+      <c r="A181" s="24"/>
       <c r="B181" s="6"/>
       <c r="C181" s="8" t="str">
         <f aca="false">IF(OR(D181="",E181="",D181=E181),"",IF(E181&lt;D181,"BUY","SELL"))</f>
@@ -6493,19 +6569,19 @@
         <f aca="false">IF(I181="","",IF(I181&gt;0,"WIN",IF(I181&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I181" s="24" t="str">
+      <c r="I181" s="25" t="str">
         <f aca="false">IF(OR(G181="",C181=""),"",ROUND((G181-D181)/(D181-E181),2))</f>
         <v/>
       </c>
-      <c r="J181" s="25" t="str">
+      <c r="J181" s="26" t="str">
         <f aca="false">IF(I181="","",ROUND(I181*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K181" s="6"/>
-      <c r="L181" s="26"/>
+      <c r="L181" s="27"/>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="23"/>
+      <c r="A182" s="24"/>
       <c r="B182" s="6"/>
       <c r="C182" s="8" t="str">
         <f aca="false">IF(OR(D182="",E182="",D182=E182),"",IF(E182&lt;D182,"BUY","SELL"))</f>
@@ -6522,19 +6598,19 @@
         <f aca="false">IF(I182="","",IF(I182&gt;0,"WIN",IF(I182&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I182" s="24" t="str">
+      <c r="I182" s="25" t="str">
         <f aca="false">IF(OR(G182="",C182=""),"",ROUND((G182-D182)/(D182-E182),2))</f>
         <v/>
       </c>
-      <c r="J182" s="25" t="str">
+      <c r="J182" s="26" t="str">
         <f aca="false">IF(I182="","",ROUND(I182*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K182" s="6"/>
-      <c r="L182" s="26"/>
+      <c r="L182" s="27"/>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="23"/>
+      <c r="A183" s="24"/>
       <c r="B183" s="6"/>
       <c r="C183" s="8" t="str">
         <f aca="false">IF(OR(D183="",E183="",D183=E183),"",IF(E183&lt;D183,"BUY","SELL"))</f>
@@ -6551,19 +6627,19 @@
         <f aca="false">IF(I183="","",IF(I183&gt;0,"WIN",IF(I183&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I183" s="24" t="str">
+      <c r="I183" s="25" t="str">
         <f aca="false">IF(OR(G183="",C183=""),"",ROUND((G183-D183)/(D183-E183),2))</f>
         <v/>
       </c>
-      <c r="J183" s="25" t="str">
+      <c r="J183" s="26" t="str">
         <f aca="false">IF(I183="","",ROUND(I183*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K183" s="6"/>
-      <c r="L183" s="26"/>
+      <c r="L183" s="27"/>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="23"/>
+      <c r="A184" s="24"/>
       <c r="B184" s="6"/>
       <c r="C184" s="8" t="str">
         <f aca="false">IF(OR(D184="",E184="",D184=E184),"",IF(E184&lt;D184,"BUY","SELL"))</f>
@@ -6580,19 +6656,19 @@
         <f aca="false">IF(I184="","",IF(I184&gt;0,"WIN",IF(I184&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I184" s="24" t="str">
+      <c r="I184" s="25" t="str">
         <f aca="false">IF(OR(G184="",C184=""),"",ROUND((G184-D184)/(D184-E184),2))</f>
         <v/>
       </c>
-      <c r="J184" s="25" t="str">
+      <c r="J184" s="26" t="str">
         <f aca="false">IF(I184="","",ROUND(I184*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K184" s="6"/>
-      <c r="L184" s="26"/>
+      <c r="L184" s="27"/>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="23"/>
+      <c r="A185" s="24"/>
       <c r="B185" s="6"/>
       <c r="C185" s="8" t="str">
         <f aca="false">IF(OR(D185="",E185="",D185=E185),"",IF(E185&lt;D185,"BUY","SELL"))</f>
@@ -6609,19 +6685,19 @@
         <f aca="false">IF(I185="","",IF(I185&gt;0,"WIN",IF(I185&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I185" s="24" t="str">
+      <c r="I185" s="25" t="str">
         <f aca="false">IF(OR(G185="",C185=""),"",ROUND((G185-D185)/(D185-E185),2))</f>
         <v/>
       </c>
-      <c r="J185" s="25" t="str">
+      <c r="J185" s="26" t="str">
         <f aca="false">IF(I185="","",ROUND(I185*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K185" s="6"/>
-      <c r="L185" s="26"/>
+      <c r="L185" s="27"/>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="23"/>
+      <c r="A186" s="24"/>
       <c r="B186" s="6"/>
       <c r="C186" s="8" t="str">
         <f aca="false">IF(OR(D186="",E186="",D186=E186),"",IF(E186&lt;D186,"BUY","SELL"))</f>
@@ -6638,19 +6714,19 @@
         <f aca="false">IF(I186="","",IF(I186&gt;0,"WIN",IF(I186&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I186" s="24" t="str">
+      <c r="I186" s="25" t="str">
         <f aca="false">IF(OR(G186="",C186=""),"",ROUND((G186-D186)/(D186-E186),2))</f>
         <v/>
       </c>
-      <c r="J186" s="25" t="str">
+      <c r="J186" s="26" t="str">
         <f aca="false">IF(I186="","",ROUND(I186*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K186" s="6"/>
-      <c r="L186" s="26"/>
+      <c r="L186" s="27"/>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="23"/>
+      <c r="A187" s="24"/>
       <c r="B187" s="6"/>
       <c r="C187" s="8" t="str">
         <f aca="false">IF(OR(D187="",E187="",D187=E187),"",IF(E187&lt;D187,"BUY","SELL"))</f>
@@ -6667,19 +6743,19 @@
         <f aca="false">IF(I187="","",IF(I187&gt;0,"WIN",IF(I187&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I187" s="24" t="str">
+      <c r="I187" s="25" t="str">
         <f aca="false">IF(OR(G187="",C187=""),"",ROUND((G187-D187)/(D187-E187),2))</f>
         <v/>
       </c>
-      <c r="J187" s="25" t="str">
+      <c r="J187" s="26" t="str">
         <f aca="false">IF(I187="","",ROUND(I187*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K187" s="6"/>
-      <c r="L187" s="26"/>
+      <c r="L187" s="27"/>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="23"/>
+      <c r="A188" s="24"/>
       <c r="B188" s="6"/>
       <c r="C188" s="8" t="str">
         <f aca="false">IF(OR(D188="",E188="",D188=E188),"",IF(E188&lt;D188,"BUY","SELL"))</f>
@@ -6696,19 +6772,19 @@
         <f aca="false">IF(I188="","",IF(I188&gt;0,"WIN",IF(I188&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I188" s="24" t="str">
+      <c r="I188" s="25" t="str">
         <f aca="false">IF(OR(G188="",C188=""),"",ROUND((G188-D188)/(D188-E188),2))</f>
         <v/>
       </c>
-      <c r="J188" s="25" t="str">
+      <c r="J188" s="26" t="str">
         <f aca="false">IF(I188="","",ROUND(I188*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K188" s="6"/>
-      <c r="L188" s="26"/>
+      <c r="L188" s="27"/>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="23"/>
+      <c r="A189" s="24"/>
       <c r="B189" s="6"/>
       <c r="C189" s="8" t="str">
         <f aca="false">IF(OR(D189="",E189="",D189=E189),"",IF(E189&lt;D189,"BUY","SELL"))</f>
@@ -6725,19 +6801,19 @@
         <f aca="false">IF(I189="","",IF(I189&gt;0,"WIN",IF(I189&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I189" s="24" t="str">
+      <c r="I189" s="25" t="str">
         <f aca="false">IF(OR(G189="",C189=""),"",ROUND((G189-D189)/(D189-E189),2))</f>
         <v/>
       </c>
-      <c r="J189" s="25" t="str">
+      <c r="J189" s="26" t="str">
         <f aca="false">IF(I189="","",ROUND(I189*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K189" s="6"/>
-      <c r="L189" s="26"/>
+      <c r="L189" s="27"/>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="23"/>
+      <c r="A190" s="24"/>
       <c r="B190" s="6"/>
       <c r="C190" s="8" t="str">
         <f aca="false">IF(OR(D190="",E190="",D190=E190),"",IF(E190&lt;D190,"BUY","SELL"))</f>
@@ -6754,19 +6830,19 @@
         <f aca="false">IF(I190="","",IF(I190&gt;0,"WIN",IF(I190&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I190" s="24" t="str">
+      <c r="I190" s="25" t="str">
         <f aca="false">IF(OR(G190="",C190=""),"",ROUND((G190-D190)/(D190-E190),2))</f>
         <v/>
       </c>
-      <c r="J190" s="25" t="str">
+      <c r="J190" s="26" t="str">
         <f aca="false">IF(I190="","",ROUND(I190*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K190" s="6"/>
-      <c r="L190" s="26"/>
+      <c r="L190" s="27"/>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="23"/>
+      <c r="A191" s="24"/>
       <c r="B191" s="6"/>
       <c r="C191" s="8" t="str">
         <f aca="false">IF(OR(D191="",E191="",D191=E191),"",IF(E191&lt;D191,"BUY","SELL"))</f>
@@ -6783,19 +6859,19 @@
         <f aca="false">IF(I191="","",IF(I191&gt;0,"WIN",IF(I191&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I191" s="24" t="str">
+      <c r="I191" s="25" t="str">
         <f aca="false">IF(OR(G191="",C191=""),"",ROUND((G191-D191)/(D191-E191),2))</f>
         <v/>
       </c>
-      <c r="J191" s="25" t="str">
+      <c r="J191" s="26" t="str">
         <f aca="false">IF(I191="","",ROUND(I191*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K191" s="6"/>
-      <c r="L191" s="26"/>
+      <c r="L191" s="27"/>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="23"/>
+      <c r="A192" s="24"/>
       <c r="B192" s="6"/>
       <c r="C192" s="8" t="str">
         <f aca="false">IF(OR(D192="",E192="",D192=E192),"",IF(E192&lt;D192,"BUY","SELL"))</f>
@@ -6812,19 +6888,19 @@
         <f aca="false">IF(I192="","",IF(I192&gt;0,"WIN",IF(I192&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I192" s="24" t="str">
+      <c r="I192" s="25" t="str">
         <f aca="false">IF(OR(G192="",C192=""),"",ROUND((G192-D192)/(D192-E192),2))</f>
         <v/>
       </c>
-      <c r="J192" s="25" t="str">
+      <c r="J192" s="26" t="str">
         <f aca="false">IF(I192="","",ROUND(I192*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K192" s="6"/>
-      <c r="L192" s="26"/>
+      <c r="L192" s="27"/>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="23"/>
+      <c r="A193" s="24"/>
       <c r="B193" s="6"/>
       <c r="C193" s="8" t="str">
         <f aca="false">IF(OR(D193="",E193="",D193=E193),"",IF(E193&lt;D193,"BUY","SELL"))</f>
@@ -6841,19 +6917,19 @@
         <f aca="false">IF(I193="","",IF(I193&gt;0,"WIN",IF(I193&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I193" s="24" t="str">
+      <c r="I193" s="25" t="str">
         <f aca="false">IF(OR(G193="",C193=""),"",ROUND((G193-D193)/(D193-E193),2))</f>
         <v/>
       </c>
-      <c r="J193" s="25" t="str">
+      <c r="J193" s="26" t="str">
         <f aca="false">IF(I193="","",ROUND(I193*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K193" s="6"/>
-      <c r="L193" s="26"/>
+      <c r="L193" s="27"/>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="23"/>
+      <c r="A194" s="24"/>
       <c r="B194" s="6"/>
       <c r="C194" s="8" t="str">
         <f aca="false">IF(OR(D194="",E194="",D194=E194),"",IF(E194&lt;D194,"BUY","SELL"))</f>
@@ -6870,19 +6946,19 @@
         <f aca="false">IF(I194="","",IF(I194&gt;0,"WIN",IF(I194&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I194" s="24" t="str">
+      <c r="I194" s="25" t="str">
         <f aca="false">IF(OR(G194="",C194=""),"",ROUND((G194-D194)/(D194-E194),2))</f>
         <v/>
       </c>
-      <c r="J194" s="25" t="str">
+      <c r="J194" s="26" t="str">
         <f aca="false">IF(I194="","",ROUND(I194*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K194" s="6"/>
-      <c r="L194" s="26"/>
+      <c r="L194" s="27"/>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="23"/>
+      <c r="A195" s="24"/>
       <c r="B195" s="6"/>
       <c r="C195" s="8" t="str">
         <f aca="false">IF(OR(D195="",E195="",D195=E195),"",IF(E195&lt;D195,"BUY","SELL"))</f>
@@ -6899,19 +6975,19 @@
         <f aca="false">IF(I195="","",IF(I195&gt;0,"WIN",IF(I195&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I195" s="24" t="str">
+      <c r="I195" s="25" t="str">
         <f aca="false">IF(OR(G195="",C195=""),"",ROUND((G195-D195)/(D195-E195),2))</f>
         <v/>
       </c>
-      <c r="J195" s="25" t="str">
+      <c r="J195" s="26" t="str">
         <f aca="false">IF(I195="","",ROUND(I195*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K195" s="6"/>
-      <c r="L195" s="26"/>
+      <c r="L195" s="27"/>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="23"/>
+      <c r="A196" s="24"/>
       <c r="B196" s="6"/>
       <c r="C196" s="8" t="str">
         <f aca="false">IF(OR(D196="",E196="",D196=E196),"",IF(E196&lt;D196,"BUY","SELL"))</f>
@@ -6928,19 +7004,19 @@
         <f aca="false">IF(I196="","",IF(I196&gt;0,"WIN",IF(I196&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I196" s="24" t="str">
+      <c r="I196" s="25" t="str">
         <f aca="false">IF(OR(G196="",C196=""),"",ROUND((G196-D196)/(D196-E196),2))</f>
         <v/>
       </c>
-      <c r="J196" s="25" t="str">
+      <c r="J196" s="26" t="str">
         <f aca="false">IF(I196="","",ROUND(I196*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K196" s="6"/>
-      <c r="L196" s="26"/>
+      <c r="L196" s="27"/>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="23"/>
+      <c r="A197" s="24"/>
       <c r="B197" s="6"/>
       <c r="C197" s="8" t="str">
         <f aca="false">IF(OR(D197="",E197="",D197=E197),"",IF(E197&lt;D197,"BUY","SELL"))</f>
@@ -6957,19 +7033,19 @@
         <f aca="false">IF(I197="","",IF(I197&gt;0,"WIN",IF(I197&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I197" s="24" t="str">
+      <c r="I197" s="25" t="str">
         <f aca="false">IF(OR(G197="",C197=""),"",ROUND((G197-D197)/(D197-E197),2))</f>
         <v/>
       </c>
-      <c r="J197" s="25" t="str">
+      <c r="J197" s="26" t="str">
         <f aca="false">IF(I197="","",ROUND(I197*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K197" s="6"/>
-      <c r="L197" s="26"/>
+      <c r="L197" s="27"/>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="23"/>
+      <c r="A198" s="24"/>
       <c r="B198" s="6"/>
       <c r="C198" s="8" t="str">
         <f aca="false">IF(OR(D198="",E198="",D198=E198),"",IF(E198&lt;D198,"BUY","SELL"))</f>
@@ -6986,19 +7062,19 @@
         <f aca="false">IF(I198="","",IF(I198&gt;0,"WIN",IF(I198&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I198" s="24" t="str">
+      <c r="I198" s="25" t="str">
         <f aca="false">IF(OR(G198="",C198=""),"",ROUND((G198-D198)/(D198-E198),2))</f>
         <v/>
       </c>
-      <c r="J198" s="25" t="str">
+      <c r="J198" s="26" t="str">
         <f aca="false">IF(I198="","",ROUND(I198*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K198" s="6"/>
-      <c r="L198" s="26"/>
+      <c r="L198" s="27"/>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="23"/>
+      <c r="A199" s="24"/>
       <c r="B199" s="6"/>
       <c r="C199" s="8" t="str">
         <f aca="false">IF(OR(D199="",E199="",D199=E199),"",IF(E199&lt;D199,"BUY","SELL"))</f>
@@ -7015,19 +7091,19 @@
         <f aca="false">IF(I199="","",IF(I199&gt;0,"WIN",IF(I199&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I199" s="24" t="str">
+      <c r="I199" s="25" t="str">
         <f aca="false">IF(OR(G199="",C199=""),"",ROUND((G199-D199)/(D199-E199),2))</f>
         <v/>
       </c>
-      <c r="J199" s="25" t="str">
+      <c r="J199" s="26" t="str">
         <f aca="false">IF(I199="","",ROUND(I199*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K199" s="6"/>
-      <c r="L199" s="26"/>
+      <c r="L199" s="27"/>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="23"/>
+      <c r="A200" s="24"/>
       <c r="B200" s="6"/>
       <c r="C200" s="8" t="str">
         <f aca="false">IF(OR(D200="",E200="",D200=E200),"",IF(E200&lt;D200,"BUY","SELL"))</f>
@@ -7044,19 +7120,19 @@
         <f aca="false">IF(I200="","",IF(I200&gt;0,"WIN",IF(I200&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I200" s="24" t="str">
+      <c r="I200" s="25" t="str">
         <f aca="false">IF(OR(G200="",C200=""),"",ROUND((G200-D200)/(D200-E200),2))</f>
         <v/>
       </c>
-      <c r="J200" s="25" t="str">
+      <c r="J200" s="26" t="str">
         <f aca="false">IF(I200="","",ROUND(I200*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K200" s="6"/>
-      <c r="L200" s="26"/>
+      <c r="L200" s="27"/>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="23"/>
+      <c r="A201" s="24"/>
       <c r="B201" s="6"/>
       <c r="C201" s="8" t="str">
         <f aca="false">IF(OR(D201="",E201="",D201=E201),"",IF(E201&lt;D201,"BUY","SELL"))</f>
@@ -7073,19 +7149,19 @@
         <f aca="false">IF(I201="","",IF(I201&gt;0,"WIN",IF(I201&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I201" s="24" t="str">
+      <c r="I201" s="25" t="str">
         <f aca="false">IF(OR(G201="",C201=""),"",ROUND((G201-D201)/(D201-E201),2))</f>
         <v/>
       </c>
-      <c r="J201" s="25" t="str">
+      <c r="J201" s="26" t="str">
         <f aca="false">IF(I201="","",ROUND(I201*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K201" s="6"/>
-      <c r="L201" s="26"/>
+      <c r="L201" s="27"/>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="23"/>
+      <c r="A202" s="24"/>
       <c r="B202" s="6"/>
       <c r="C202" s="8" t="str">
         <f aca="false">IF(OR(D202="",E202="",D202=E202),"",IF(E202&lt;D202,"BUY","SELL"))</f>
@@ -7102,19 +7178,19 @@
         <f aca="false">IF(I202="","",IF(I202&gt;0,"WIN",IF(I202&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I202" s="24" t="str">
+      <c r="I202" s="25" t="str">
         <f aca="false">IF(OR(G202="",C202=""),"",ROUND((G202-D202)/(D202-E202),2))</f>
         <v/>
       </c>
-      <c r="J202" s="25" t="str">
+      <c r="J202" s="26" t="str">
         <f aca="false">IF(I202="","",ROUND(I202*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K202" s="6"/>
-      <c r="L202" s="26"/>
+      <c r="L202" s="27"/>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="23"/>
+      <c r="A203" s="24"/>
       <c r="B203" s="6"/>
       <c r="C203" s="8" t="str">
         <f aca="false">IF(OR(D203="",E203="",D203=E203),"",IF(E203&lt;D203,"BUY","SELL"))</f>
@@ -7131,19 +7207,19 @@
         <f aca="false">IF(I203="","",IF(I203&gt;0,"WIN",IF(I203&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I203" s="24" t="str">
+      <c r="I203" s="25" t="str">
         <f aca="false">IF(OR(G203="",C203=""),"",ROUND((G203-D203)/(D203-E203),2))</f>
         <v/>
       </c>
-      <c r="J203" s="25" t="str">
+      <c r="J203" s="26" t="str">
         <f aca="false">IF(I203="","",ROUND(I203*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K203" s="6"/>
-      <c r="L203" s="26"/>
+      <c r="L203" s="27"/>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="23"/>
+      <c r="A204" s="24"/>
       <c r="B204" s="6"/>
       <c r="C204" s="8" t="str">
         <f aca="false">IF(OR(D204="",E204="",D204=E204),"",IF(E204&lt;D204,"BUY","SELL"))</f>
@@ -7160,19 +7236,19 @@
         <f aca="false">IF(I204="","",IF(I204&gt;0,"WIN",IF(I204&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I204" s="24" t="str">
+      <c r="I204" s="25" t="str">
         <f aca="false">IF(OR(G204="",C204=""),"",ROUND((G204-D204)/(D204-E204),2))</f>
         <v/>
       </c>
-      <c r="J204" s="25" t="str">
+      <c r="J204" s="26" t="str">
         <f aca="false">IF(I204="","",ROUND(I204*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K204" s="6"/>
-      <c r="L204" s="26"/>
+      <c r="L204" s="27"/>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="23"/>
+      <c r="A205" s="24"/>
       <c r="B205" s="6"/>
       <c r="C205" s="8" t="str">
         <f aca="false">IF(OR(D205="",E205="",D205=E205),"",IF(E205&lt;D205,"BUY","SELL"))</f>
@@ -7189,19 +7265,19 @@
         <f aca="false">IF(I205="","",IF(I205&gt;0,"WIN",IF(I205&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I205" s="24" t="str">
+      <c r="I205" s="25" t="str">
         <f aca="false">IF(OR(G205="",C205=""),"",ROUND((G205-D205)/(D205-E205),2))</f>
         <v/>
       </c>
-      <c r="J205" s="25" t="str">
+      <c r="J205" s="26" t="str">
         <f aca="false">IF(I205="","",ROUND(I205*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K205" s="6"/>
-      <c r="L205" s="26"/>
+      <c r="L205" s="27"/>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="23"/>
+      <c r="A206" s="24"/>
       <c r="B206" s="6"/>
       <c r="C206" s="8" t="str">
         <f aca="false">IF(OR(D206="",E206="",D206=E206),"",IF(E206&lt;D206,"BUY","SELL"))</f>
@@ -7218,16 +7294,16 @@
         <f aca="false">IF(I206="","",IF(I206&gt;0,"WIN",IF(I206&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I206" s="24" t="str">
+      <c r="I206" s="25" t="str">
         <f aca="false">IF(OR(G206="",C206=""),"",ROUND((G206-D206)/(D206-E206),2))</f>
         <v/>
       </c>
-      <c r="J206" s="25" t="str">
+      <c r="J206" s="26" t="str">
         <f aca="false">IF(I206="","",ROUND(I206*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K206" s="6"/>
-      <c r="L206" s="26"/>
+      <c r="L206" s="27"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H7:H206">
@@ -7273,213 +7349,213 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="B3" s="28" t="n">
+      <c r="A3" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" s="29" t="n">
         <f aca="false">COUNT('Trade Log'!I7:I206)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="B4" s="28" t="n">
+      <c r="A4" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="29" t="n">
         <f aca="false">COUNTIF('Trade Log'!H7:H206,"WIN")</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="B5" s="28" t="n">
+      <c r="A5" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="B5" s="29" t="n">
         <f aca="false">COUNTIF('Trade Log'!H7:H206,"LOSS")</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="B6" s="29" t="n">
+      <c r="A6" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="B6" s="30" t="n">
         <f aca="false">IFERROR(B4/B3,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="B7" s="30" t="n">
+      <c r="A7" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="B7" s="31" t="n">
         <f aca="false">SUM('Trade Log'!I7:I206)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="27" t="s">
-        <v>85</v>
-      </c>
-      <c r="B8" s="30" t="n">
+      <c r="A8" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="31" t="n">
         <f aca="false">IFERROR(B7/B3,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="27" t="s">
-        <v>86</v>
-      </c>
-      <c r="B9" s="29" t="n">
+      <c r="A9" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="30" t="n">
         <f aca="false">IFERROR(COUNTIF('Trade Log'!K7:K206,"Yes")/B3,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="27" t="s">
-        <v>87</v>
-      </c>
-      <c r="B10" s="31" t="n">
+      <c r="A10" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" s="32" t="n">
         <f aca="false">SUM('Trade Log'!J7:J206)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="27" t="s">
-        <v>68</v>
-      </c>
-      <c r="B11" s="22" t="n">
+      <c r="A11" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" s="23" t="n">
         <f aca="false">'Trade Log'!M4</f>
         <v>10000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="32" t="s">
-        <v>88</v>
+      <c r="A13" s="33" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="33" t="str">
+      <c r="A14" s="34" t="str">
         <f aca="false">IF(B3&lt;50,"Not enough trades yet: "&amp;B3&amp;" of 50. Keep going.",IF(B9&lt;0.9,"You broke the rules too often. The results don't count yet.",IF(B8&gt;=0.15,"Looks promising. Keep going to 100 trades to be sure.",IF(B8&lt;=0,"Not working as it is. Stop and review.","Too close to call. Keep going to 100 trades."))))</f>
         <v>Not enough trades yet: 0 of 50. Keep going.</v>
       </c>
-      <c r="B14" s="33"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
-        <v>89</v>
+      <c r="A15" s="15" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="32" t="s">
-        <v>90</v>
+      <c r="A18" s="33" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="16" t="s">
+      <c r="A19" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>84</v>
+      <c r="B19" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="34" t="n">
+      <c r="B20" s="35" t="n">
         <f aca="false">COUNTIFS('Trade Log'!B7:B206,A20,'Trade Log'!I7:I206,"&gt;-99")</f>
         <v>0</v>
       </c>
-      <c r="C20" s="24" t="n">
+      <c r="C20" s="25" t="n">
         <f aca="false">SUMIF('Trade Log'!B7:B206,A20,'Trade Log'!I7:I206)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B21" s="34" t="n">
+        <v>52</v>
+      </c>
+      <c r="B21" s="35" t="n">
         <f aca="false">COUNTIFS('Trade Log'!B7:B206,A21,'Trade Log'!I7:I206,"&gt;-99")</f>
         <v>0</v>
       </c>
-      <c r="C21" s="24" t="n">
+      <c r="C21" s="25" t="n">
         <f aca="false">SUMIF('Trade Log'!B7:B206,A21,'Trade Log'!I7:I206)</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="B22" s="34" t="n">
+        <v>54</v>
+      </c>
+      <c r="B22" s="35" t="n">
         <f aca="false">COUNTIFS('Trade Log'!B7:B206,A22,'Trade Log'!I7:I206,"&gt;-99")</f>
         <v>0</v>
       </c>
-      <c r="C22" s="24" t="n">
+      <c r="C22" s="25" t="n">
         <f aca="false">SUMIF('Trade Log'!B7:B206,A22,'Trade Log'!I7:I206)</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B23" s="34" t="n">
+        <v>55</v>
+      </c>
+      <c r="B23" s="35" t="n">
         <f aca="false">COUNTIFS('Trade Log'!B7:B206,A23,'Trade Log'!I7:I206,"&gt;-99")</f>
         <v>0</v>
       </c>
-      <c r="C23" s="24" t="n">
+      <c r="C23" s="25" t="n">
         <f aca="false">SUMIF('Trade Log'!B7:B206,A23,'Trade Log'!I7:I206)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B24" s="34" t="n">
+        <v>57</v>
+      </c>
+      <c r="B24" s="35" t="n">
         <f aca="false">COUNTIFS('Trade Log'!B7:B206,A24,'Trade Log'!I7:I206,"&gt;-99")</f>
         <v>0</v>
       </c>
-      <c r="C24" s="24" t="n">
+      <c r="C24" s="25" t="n">
         <f aca="false">SUMIF('Trade Log'!B7:B206,A24,'Trade Log'!I7:I206)</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B25" s="34" t="n">
+        <v>59</v>
+      </c>
+      <c r="B25" s="35" t="n">
         <f aca="false">COUNTIFS('Trade Log'!B7:B206,A25,'Trade Log'!I7:I206,"&gt;-99")</f>
         <v>0</v>
       </c>
-      <c r="C25" s="24" t="n">
+      <c r="C25" s="25" t="n">
         <f aca="false">SUMIF('Trade Log'!B7:B206,A25,'Trade Log'!I7:I206)</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B26" s="34" t="n">
+        <v>61</v>
+      </c>
+      <c r="B26" s="35" t="n">
         <f aca="false">COUNTIFS('Trade Log'!B7:B206,A26,'Trade Log'!I7:I206,"&gt;-99")</f>
         <v>0</v>
       </c>
-      <c r="C26" s="24" t="n">
+      <c r="C26" s="25" t="n">
         <f aca="false">SUMIF('Trade Log'!B7:B206,A26,'Trade Log'!I7:I206)</f>
         <v>0</v>
       </c>

--- a/KLR_Simple_Tracker.xlsx
+++ b/KLR_Simple_Tracker.xlsx
@@ -193,7 +193,7 @@
     <t xml:space="preserve">GER40</t>
   </si>
   <si>
-    <t xml:space="preserve">Contract 1: 1 point = 1 EUR (about $1.15). If profit currency is USD, change to 1.00</t>
+    <t xml:space="preserve">Paid in EUR: 1 point = 1 EUR. Set this to the current EURUSD price (update weekly)</t>
   </si>
   <si>
     <t xml:space="preserve">US500</t>

--- a/KLR_Simple_Tracker.xlsx
+++ b/KLR_Simple_Tracker.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="96">
   <si>
     <t xml:space="preserve">MY TRADING RULES</t>
   </si>
@@ -49,13 +49,19 @@
     <t xml:space="preserve">Step 2</t>
   </si>
   <si>
-    <t xml:space="preserve">On the 1-minute chart, price stops going up (or down) and starts turning.</t>
+    <t xml:space="preserve">On the 1-minute chart, mark the last swing of that run (last higher low if it ran up, last lower high if it ran down).</t>
   </si>
   <si>
     <t xml:space="preserve">Step 3</t>
   </si>
   <si>
-    <t xml:space="preserve">One strong candle in the new direction. Enter when price breaks that candle.</t>
+    <t xml:space="preserve">CHoCH: wait for a candle to CLOSE beyond that swing point.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Market order as soon as that CHoCH candle closes. No waiting for a retest.</t>
   </si>
   <si>
     <t xml:space="preserve">Stop</t>
@@ -248,9 +254,6 @@
   </si>
   <si>
     <t xml:space="preserve">Buy / Sell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entry</t>
   </si>
   <si>
     <t xml:space="preserve">Target (auto)</t>
@@ -946,7 +949,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
@@ -1068,6 +1071,14 @@
       </c>
       <c r="B16" s="3" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1100,25 +1111,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B5" s="7" t="n">
         <v>2650</v>
@@ -1126,7 +1137,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B6" s="7" t="n">
         <v>2647</v>
@@ -1134,7 +1145,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B8" s="8" t="str">
         <f aca="false">IF(OR(B5="",B6="",B5=B6),"",IF(B6&lt;B5,"BUY","SELL"))</f>
@@ -1143,7 +1154,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B9" s="9" t="n">
         <f aca="false">IFERROR(ROUND(ABS(B5-B6)/VLOOKUP(B4,$D$19:$H$25,2,FALSE()),1),"")</f>
@@ -1152,7 +1163,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B10" s="10" t="n">
         <f aca="false">B27</f>
@@ -1161,19 +1172,19 @@
     </row>
     <row r="11" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B11" s="12" t="n">
         <f aca="false">IFERROR(IF(B10/(B9*VLOOKUP(B4,$D$19:$H$25,3,FALSE()))&lt;VLOOKUP(B4,$D$19:$H$25,4,FALSE()),"SKIP",ROUNDDOWN(B10/(B9*VLOOKUP(B4,$D$19:$H$25,3,FALSE()))/VLOOKUP(B4,$D$19:$H$25,5,FALSE())+0.000001,0)*VLOOKUP(B4,$D$19:$H$25,5,FALSE())),"")</f>
         <v>0.16</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B12" s="13" t="n">
         <f aca="false">IF(B8="","",IF(B8="BUY",B5+1.5*(B5-B6),B5-1.5*(B6-B5)))</f>
@@ -1182,7 +1193,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B13" s="10" t="n">
         <f aca="false">IFERROR(B11*B9*1.5*VLOOKUP(B4,$D$19:$H$25,3,FALSE()),"")</f>
@@ -1191,7 +1202,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B14" s="10" t="n">
         <f aca="false">IFERROR(B11*B9*VLOOKUP(B4,$D$19:$H$25,3,FALSE()),"")</f>
@@ -1200,40 +1211,40 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D18" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H18" s="17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I18" s="17" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D19" s="8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E19" s="18" t="n">
         <v>0.1</v>
@@ -1248,12 +1259,12 @@
         <v>0.01</v>
       </c>
       <c r="I19" s="15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D20" s="8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E20" s="18" t="n">
         <v>0.0001</v>
@@ -1268,12 +1279,12 @@
         <v>0.01</v>
       </c>
       <c r="I20" s="15" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D21" s="8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E21" s="18" t="n">
         <v>0.0001</v>
@@ -1288,12 +1299,12 @@
         <v>0.01</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D22" s="8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E22" s="18" t="n">
         <v>1</v>
@@ -1308,12 +1319,12 @@
         <v>0.1</v>
       </c>
       <c r="I22" s="15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D23" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E23" s="18" t="n">
         <v>1</v>
@@ -1328,12 +1339,12 @@
         <v>0.1</v>
       </c>
       <c r="I23" s="15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D24" s="8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E24" s="18" t="n">
         <v>1</v>
@@ -1348,12 +1359,12 @@
         <v>0.1</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D25" s="8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E25" s="18" t="n">
         <v>1</v>
@@ -1368,29 +1379,29 @@
         <v>0.01</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="16" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B27" s="10" t="n">
         <f aca="false">'Trade Log'!$M$2*'Trade Log'!$M$3</f>
         <v>50</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1433,12 +1444,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L2" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M2" s="21" t="n">
         <v>10000</v>
@@ -1446,10 +1457,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M3" s="22" t="n">
         <v>0.005</v>
@@ -1457,10 +1468,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M4" s="23" t="n">
         <f aca="false">M2+SUM(J7:J206)</f>
@@ -1469,40 +1480,40 @@
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>75</v>
+        <v>11</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J6" s="17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K6" s="17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L6" s="17" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7349,12 +7360,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="28" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B3" s="29" t="n">
         <f aca="false">COUNT('Trade Log'!I7:I206)</f>
@@ -7363,7 +7374,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="28" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B4" s="29" t="n">
         <f aca="false">COUNTIF('Trade Log'!H7:H206,"WIN")</f>
@@ -7372,7 +7383,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="28" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B5" s="29" t="n">
         <f aca="false">COUNTIF('Trade Log'!H7:H206,"LOSS")</f>
@@ -7381,7 +7392,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="28" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B6" s="30" t="n">
         <f aca="false">IFERROR(B4/B3,0)</f>
@@ -7390,7 +7401,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B7" s="31" t="n">
         <f aca="false">SUM('Trade Log'!I7:I206)</f>
@@ -7399,7 +7410,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="28" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B8" s="31" t="n">
         <f aca="false">IFERROR(B7/B3,0)</f>
@@ -7408,7 +7419,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="28" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B9" s="30" t="n">
         <f aca="false">IFERROR(COUNTIF('Trade Log'!K7:K206,"Yes")/B3,0)</f>
@@ -7417,7 +7428,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="28" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B10" s="32" t="n">
         <f aca="false">SUM('Trade Log'!J7:J206)</f>
@@ -7426,7 +7437,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="28" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B11" s="23" t="n">
         <f aca="false">'Trade Log'!M4</f>
@@ -7435,7 +7446,7 @@
     </row>
     <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="33" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7450,28 +7461,28 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="33" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B20" s="35" t="n">
         <f aca="false">COUNTIFS('Trade Log'!B7:B206,A20,'Trade Log'!I7:I206,"&gt;-99")</f>
@@ -7484,7 +7495,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B21" s="35" t="n">
         <f aca="false">COUNTIFS('Trade Log'!B7:B206,A21,'Trade Log'!I7:I206,"&gt;-99")</f>
@@ -7497,7 +7508,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B22" s="35" t="n">
         <f aca="false">COUNTIFS('Trade Log'!B7:B206,A22,'Trade Log'!I7:I206,"&gt;-99")</f>
@@ -7510,7 +7521,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B23" s="35" t="n">
         <f aca="false">COUNTIFS('Trade Log'!B7:B206,A23,'Trade Log'!I7:I206,"&gt;-99")</f>
@@ -7523,7 +7534,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B24" s="35" t="n">
         <f aca="false">COUNTIFS('Trade Log'!B7:B206,A24,'Trade Log'!I7:I206,"&gt;-99")</f>
@@ -7536,7 +7547,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B25" s="35" t="n">
         <f aca="false">COUNTIFS('Trade Log'!B7:B206,A25,'Trade Log'!I7:I206,"&gt;-99")</f>
@@ -7549,7 +7560,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B26" s="35" t="n">
         <f aca="false">COUNTIFS('Trade Log'!B7:B206,A26,'Trade Log'!I7:I206,"&gt;-99")</f>

--- a/KLR_Simple_Tracker.xlsx
+++ b/KLR_Simple_Tracker.xlsx
@@ -10,8 +10,9 @@
   <sheets>
     <sheet name="Rules" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Calculator" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Trade Log" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Summary" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Compare" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Trade Log" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Summary" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="108">
   <si>
     <t xml:space="preserve">MY TRADING RULES</t>
   </si>
@@ -112,10 +113,16 @@
     <t xml:space="preserve">Move my stop further away. Trade without the 3 steps. Trade outside my times.</t>
   </si>
   <si>
-    <t xml:space="preserve">Goal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log 50 demo trades with these rules. Then the Summary tab tells me if it works.</t>
+    <t xml:space="preserve">9–16 Oct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Watch only, no trades. Each time price hits a zone, note what each entry method did (Compare tab).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From 19 Oct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demo trades with the CHoCH entry. Log 50 trades, then the Summary tab tells me if it works.</t>
   </si>
   <si>
     <t xml:space="preserve">LOT SIZE CALCULATOR</t>
@@ -232,6 +239,42 @@
     <t xml:space="preserve">(0.5% of starting balance. Change it on the Trade Log tab.)</t>
   </si>
   <si>
+    <t xml:space="preserve">WATCH WEEK: WHICH ENTRY WORKS BEST?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9–16 Oct, no trades. Each time price hits a zone, write what happened with each method. Same stop for all (past the run). Target = 1.5R.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rejection candle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engulfing candle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHoCH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hit target</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hit stop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Win rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Best method = highest Total R. With only one week of setups, treat it as a hint, not proof.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date / Pair</t>
+  </si>
+  <si>
     <t xml:space="preserve">TRADE LOG</t>
   </si>
   <si>
@@ -284,12 +327,6 @@
   </si>
   <si>
     <t xml:space="preserve">Losses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Win rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total R</t>
   </si>
   <si>
     <t xml:space="preserve">Average R per trade</t>
@@ -317,20 +354,21 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="13">
+  <numFmts count="14">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00###"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="168" formatCode="0.00"/>
     <numFmt numFmtId="169" formatCode="0.####"/>
-    <numFmt numFmtId="170" formatCode="\$#,##0"/>
-    <numFmt numFmtId="171" formatCode="0.0%"/>
-    <numFmt numFmtId="172" formatCode="dd\-mmm\-yy"/>
-    <numFmt numFmtId="173" formatCode="0.00;\-0.00;0.00"/>
-    <numFmt numFmtId="174" formatCode="\$#,##0.00;&quot;-$&quot;#,##0.00"/>
-    <numFmt numFmtId="175" formatCode="0"/>
-    <numFmt numFmtId="176" formatCode="0%"/>
+    <numFmt numFmtId="170" formatCode="0"/>
+    <numFmt numFmtId="171" formatCode="0%"/>
+    <numFmt numFmtId="172" formatCode="0.0;\-0.0;0.0"/>
+    <numFmt numFmtId="173" formatCode="\$#,##0"/>
+    <numFmt numFmtId="174" formatCode="0.0%"/>
+    <numFmt numFmtId="175" formatCode="dd\-mmm\-yy"/>
+    <numFmt numFmtId="176" formatCode="0.00;\-0.00;0.00"/>
+    <numFmt numFmtId="177" formatCode="\$#,##0.00;&quot;-$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="16">
     <font>
@@ -522,7 +560,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="40">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -607,11 +645,35 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -619,27 +681,27 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="175" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -647,11 +709,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="174" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -661,10 +719,6 @@
     </xf>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -949,7 +1003,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
@@ -1079,6 +1133,14 @@
       </c>
       <c r="B17" s="3" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1111,25 +1173,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B5" s="7" t="n">
         <v>2650</v>
@@ -1137,7 +1199,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B6" s="7" t="n">
         <v>2647</v>
@@ -1145,7 +1207,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B8" s="8" t="str">
         <f aca="false">IF(OR(B5="",B6="",B5=B6),"",IF(B6&lt;B5,"BUY","SELL"))</f>
@@ -1154,7 +1216,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B9" s="9" t="n">
         <f aca="false">IFERROR(ROUND(ABS(B5-B6)/VLOOKUP(B4,$D$19:$H$25,2,FALSE()),1),"")</f>
@@ -1163,7 +1225,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B10" s="10" t="n">
         <f aca="false">B27</f>
@@ -1172,19 +1234,19 @@
     </row>
     <row r="11" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B11" s="12" t="n">
         <f aca="false">IFERROR(IF(B10/(B9*VLOOKUP(B4,$D$19:$H$25,3,FALSE()))&lt;VLOOKUP(B4,$D$19:$H$25,4,FALSE()),"SKIP",ROUNDDOWN(B10/(B9*VLOOKUP(B4,$D$19:$H$25,3,FALSE()))/VLOOKUP(B4,$D$19:$H$25,5,FALSE())+0.000001,0)*VLOOKUP(B4,$D$19:$H$25,5,FALSE())),"")</f>
         <v>0.16</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B12" s="13" t="n">
         <f aca="false">IF(B8="","",IF(B8="BUY",B5+1.5*(B5-B6),B5-1.5*(B6-B5)))</f>
@@ -1193,7 +1255,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B13" s="10" t="n">
         <f aca="false">IFERROR(B11*B9*1.5*VLOOKUP(B4,$D$19:$H$25,3,FALSE()),"")</f>
@@ -1202,7 +1264,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B14" s="10" t="n">
         <f aca="false">IFERROR(B11*B9*VLOOKUP(B4,$D$19:$H$25,3,FALSE()),"")</f>
@@ -1211,40 +1273,40 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D18" s="17" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H18" s="17" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I18" s="17" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D19" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E19" s="18" t="n">
         <v>0.1</v>
@@ -1259,12 +1321,12 @@
         <v>0.01</v>
       </c>
       <c r="I19" s="15" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D20" s="8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E20" s="18" t="n">
         <v>0.0001</v>
@@ -1279,12 +1341,12 @@
         <v>0.01</v>
       </c>
       <c r="I20" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D21" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E21" s="18" t="n">
         <v>0.0001</v>
@@ -1299,12 +1361,12 @@
         <v>0.01</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D22" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E22" s="18" t="n">
         <v>1</v>
@@ -1319,12 +1381,12 @@
         <v>0.1</v>
       </c>
       <c r="I22" s="15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D23" s="8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E23" s="18" t="n">
         <v>1</v>
@@ -1339,12 +1401,12 @@
         <v>0.1</v>
       </c>
       <c r="I23" s="15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D24" s="8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E24" s="18" t="n">
         <v>1</v>
@@ -1359,12 +1421,12 @@
         <v>0.1</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D25" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E25" s="18" t="n">
         <v>1</v>
@@ -1379,29 +1441,29 @@
         <v>0.01</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="16" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B27" s="10" t="n">
         <f aca="false">'Trade Log'!$M$2*'Trade Log'!$M$3</f>
         <v>50</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1426,6 +1488,875 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:F112"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="40"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" s="22" t="n">
+        <f aca="false">COUNTIF(B13:B112,"Target")+COUNTIF(B13:B112,"Stop")</f>
+        <v>0</v>
+      </c>
+      <c r="C5" s="22" t="n">
+        <f aca="false">COUNTIF(C13:C112,"Target")+COUNTIF(C13:C112,"Stop")</f>
+        <v>0</v>
+      </c>
+      <c r="D5" s="22" t="n">
+        <f aca="false">COUNTIF(D13:D112,"Target")+COUNTIF(D13:D112,"Stop")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" s="22" t="n">
+        <f aca="false">COUNTIF(B13:B112,"Target")</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="22" t="n">
+        <f aca="false">COUNTIF(C13:C112,"Target")</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="22" t="n">
+        <f aca="false">COUNTIF(D13:D112,"Target")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" s="22" t="n">
+        <f aca="false">COUNTIF(B13:B112,"Stop")</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="22" t="n">
+        <f aca="false">COUNTIF(C13:C112,"Stop")</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="22" t="n">
+        <f aca="false">COUNTIF(D13:D112,"Stop")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="23" t="n">
+        <f aca="false">IFERROR(B6/B5,0)</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="23" t="n">
+        <f aca="false">IFERROR(C6/C5,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="23" t="n">
+        <f aca="false">IFERROR(D6/D5,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9" s="24" t="n">
+        <f aca="false">B6*1.5-B7</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="24" t="n">
+        <f aca="false">C6*1.5-C7</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="24" t="n">
+        <f aca="false">D6*1.5-D7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="15" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="F12" s="25"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="26"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="26"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="26"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="26"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="26"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="26"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="26"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="26"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="26"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="26"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="26"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="26"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="26"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="26"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="26"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="26"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="6"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="26"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="26"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="26"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="26"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="6"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="26"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="6"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="26"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="6"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="26"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="6"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="26"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="26"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="6"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="26"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="26"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="26"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="26"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="6"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="26"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="26"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="6"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="26"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="6"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="26"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="6"/>
+      <c r="B46" s="6"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="26"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="6"/>
+      <c r="B47" s="6"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="26"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="6"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="26"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="6"/>
+      <c r="B49" s="6"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="26"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="6"/>
+      <c r="B50" s="6"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="26"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="6"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="26"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="6"/>
+      <c r="B52" s="6"/>
+      <c r="C52" s="6"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="26"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="6"/>
+      <c r="B53" s="6"/>
+      <c r="C53" s="6"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="26"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="6"/>
+      <c r="B54" s="6"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="26"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="6"/>
+      <c r="B55" s="6"/>
+      <c r="C55" s="6"/>
+      <c r="D55" s="6"/>
+      <c r="E55" s="26"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="6"/>
+      <c r="B56" s="6"/>
+      <c r="C56" s="6"/>
+      <c r="D56" s="6"/>
+      <c r="E56" s="26"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="6"/>
+      <c r="B57" s="6"/>
+      <c r="C57" s="6"/>
+      <c r="D57" s="6"/>
+      <c r="E57" s="26"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="6"/>
+      <c r="B58" s="6"/>
+      <c r="C58" s="6"/>
+      <c r="D58" s="6"/>
+      <c r="E58" s="26"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="6"/>
+      <c r="B59" s="6"/>
+      <c r="C59" s="6"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="26"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="6"/>
+      <c r="B60" s="6"/>
+      <c r="C60" s="6"/>
+      <c r="D60" s="6"/>
+      <c r="E60" s="26"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="6"/>
+      <c r="B61" s="6"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="6"/>
+      <c r="E61" s="26"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="6"/>
+      <c r="B62" s="6"/>
+      <c r="C62" s="6"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="26"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="6"/>
+      <c r="B63" s="6"/>
+      <c r="C63" s="6"/>
+      <c r="D63" s="6"/>
+      <c r="E63" s="26"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="6"/>
+      <c r="B64" s="6"/>
+      <c r="C64" s="6"/>
+      <c r="D64" s="6"/>
+      <c r="E64" s="26"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="6"/>
+      <c r="B65" s="6"/>
+      <c r="C65" s="6"/>
+      <c r="D65" s="6"/>
+      <c r="E65" s="26"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="6"/>
+      <c r="B66" s="6"/>
+      <c r="C66" s="6"/>
+      <c r="D66" s="6"/>
+      <c r="E66" s="26"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="6"/>
+      <c r="B67" s="6"/>
+      <c r="C67" s="6"/>
+      <c r="D67" s="6"/>
+      <c r="E67" s="26"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="6"/>
+      <c r="B68" s="6"/>
+      <c r="C68" s="6"/>
+      <c r="D68" s="6"/>
+      <c r="E68" s="26"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="6"/>
+      <c r="B69" s="6"/>
+      <c r="C69" s="6"/>
+      <c r="D69" s="6"/>
+      <c r="E69" s="26"/>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="6"/>
+      <c r="B70" s="6"/>
+      <c r="C70" s="6"/>
+      <c r="D70" s="6"/>
+      <c r="E70" s="26"/>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="6"/>
+      <c r="B71" s="6"/>
+      <c r="C71" s="6"/>
+      <c r="D71" s="6"/>
+      <c r="E71" s="26"/>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="6"/>
+      <c r="B72" s="6"/>
+      <c r="C72" s="6"/>
+      <c r="D72" s="6"/>
+      <c r="E72" s="26"/>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="6"/>
+      <c r="B73" s="6"/>
+      <c r="C73" s="6"/>
+      <c r="D73" s="6"/>
+      <c r="E73" s="26"/>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="6"/>
+      <c r="B74" s="6"/>
+      <c r="C74" s="6"/>
+      <c r="D74" s="6"/>
+      <c r="E74" s="26"/>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="6"/>
+      <c r="B75" s="6"/>
+      <c r="C75" s="6"/>
+      <c r="D75" s="6"/>
+      <c r="E75" s="26"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="6"/>
+      <c r="B76" s="6"/>
+      <c r="C76" s="6"/>
+      <c r="D76" s="6"/>
+      <c r="E76" s="26"/>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="6"/>
+      <c r="B77" s="6"/>
+      <c r="C77" s="6"/>
+      <c r="D77" s="6"/>
+      <c r="E77" s="26"/>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="6"/>
+      <c r="B78" s="6"/>
+      <c r="C78" s="6"/>
+      <c r="D78" s="6"/>
+      <c r="E78" s="26"/>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="6"/>
+      <c r="B79" s="6"/>
+      <c r="C79" s="6"/>
+      <c r="D79" s="6"/>
+      <c r="E79" s="26"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="6"/>
+      <c r="B80" s="6"/>
+      <c r="C80" s="6"/>
+      <c r="D80" s="6"/>
+      <c r="E80" s="26"/>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="6"/>
+      <c r="B81" s="6"/>
+      <c r="C81" s="6"/>
+      <c r="D81" s="6"/>
+      <c r="E81" s="26"/>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="6"/>
+      <c r="B82" s="6"/>
+      <c r="C82" s="6"/>
+      <c r="D82" s="6"/>
+      <c r="E82" s="26"/>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="6"/>
+      <c r="B83" s="6"/>
+      <c r="C83" s="6"/>
+      <c r="D83" s="6"/>
+      <c r="E83" s="26"/>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="6"/>
+      <c r="B84" s="6"/>
+      <c r="C84" s="6"/>
+      <c r="D84" s="6"/>
+      <c r="E84" s="26"/>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="6"/>
+      <c r="B85" s="6"/>
+      <c r="C85" s="6"/>
+      <c r="D85" s="6"/>
+      <c r="E85" s="26"/>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="6"/>
+      <c r="B86" s="6"/>
+      <c r="C86" s="6"/>
+      <c r="D86" s="6"/>
+      <c r="E86" s="26"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="6"/>
+      <c r="B87" s="6"/>
+      <c r="C87" s="6"/>
+      <c r="D87" s="6"/>
+      <c r="E87" s="26"/>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="6"/>
+      <c r="B88" s="6"/>
+      <c r="C88" s="6"/>
+      <c r="D88" s="6"/>
+      <c r="E88" s="26"/>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="6"/>
+      <c r="B89" s="6"/>
+      <c r="C89" s="6"/>
+      <c r="D89" s="6"/>
+      <c r="E89" s="26"/>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="6"/>
+      <c r="B90" s="6"/>
+      <c r="C90" s="6"/>
+      <c r="D90" s="6"/>
+      <c r="E90" s="26"/>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="6"/>
+      <c r="B91" s="6"/>
+      <c r="C91" s="6"/>
+      <c r="D91" s="6"/>
+      <c r="E91" s="26"/>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="6"/>
+      <c r="B92" s="6"/>
+      <c r="C92" s="6"/>
+      <c r="D92" s="6"/>
+      <c r="E92" s="26"/>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="6"/>
+      <c r="B93" s="6"/>
+      <c r="C93" s="6"/>
+      <c r="D93" s="6"/>
+      <c r="E93" s="26"/>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="6"/>
+      <c r="B94" s="6"/>
+      <c r="C94" s="6"/>
+      <c r="D94" s="6"/>
+      <c r="E94" s="26"/>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="6"/>
+      <c r="B95" s="6"/>
+      <c r="C95" s="6"/>
+      <c r="D95" s="6"/>
+      <c r="E95" s="26"/>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="6"/>
+      <c r="B96" s="6"/>
+      <c r="C96" s="6"/>
+      <c r="D96" s="6"/>
+      <c r="E96" s="26"/>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="6"/>
+      <c r="B97" s="6"/>
+      <c r="C97" s="6"/>
+      <c r="D97" s="6"/>
+      <c r="E97" s="26"/>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="6"/>
+      <c r="B98" s="6"/>
+      <c r="C98" s="6"/>
+      <c r="D98" s="6"/>
+      <c r="E98" s="26"/>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="6"/>
+      <c r="B99" s="6"/>
+      <c r="C99" s="6"/>
+      <c r="D99" s="6"/>
+      <c r="E99" s="26"/>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="6"/>
+      <c r="B100" s="6"/>
+      <c r="C100" s="6"/>
+      <c r="D100" s="6"/>
+      <c r="E100" s="26"/>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="6"/>
+      <c r="B101" s="6"/>
+      <c r="C101" s="6"/>
+      <c r="D101" s="6"/>
+      <c r="E101" s="26"/>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="6"/>
+      <c r="B102" s="6"/>
+      <c r="C102" s="6"/>
+      <c r="D102" s="6"/>
+      <c r="E102" s="26"/>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="6"/>
+      <c r="B103" s="6"/>
+      <c r="C103" s="6"/>
+      <c r="D103" s="6"/>
+      <c r="E103" s="26"/>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="6"/>
+      <c r="B104" s="6"/>
+      <c r="C104" s="6"/>
+      <c r="D104" s="6"/>
+      <c r="E104" s="26"/>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="6"/>
+      <c r="B105" s="6"/>
+      <c r="C105" s="6"/>
+      <c r="D105" s="6"/>
+      <c r="E105" s="26"/>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="6"/>
+      <c r="B106" s="6"/>
+      <c r="C106" s="6"/>
+      <c r="D106" s="6"/>
+      <c r="E106" s="26"/>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="6"/>
+      <c r="B107" s="6"/>
+      <c r="C107" s="6"/>
+      <c r="D107" s="6"/>
+      <c r="E107" s="26"/>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="6"/>
+      <c r="B108" s="6"/>
+      <c r="C108" s="6"/>
+      <c r="D108" s="6"/>
+      <c r="E108" s="26"/>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="6"/>
+      <c r="B109" s="6"/>
+      <c r="C109" s="6"/>
+      <c r="D109" s="6"/>
+      <c r="E109" s="26"/>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="6"/>
+      <c r="B110" s="6"/>
+      <c r="C110" s="6"/>
+      <c r="D110" s="6"/>
+      <c r="E110" s="26"/>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="6"/>
+      <c r="B111" s="6"/>
+      <c r="C111" s="6"/>
+      <c r="D111" s="6"/>
+      <c r="E111" s="26"/>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="6"/>
+      <c r="B112" s="6"/>
+      <c r="C112" s="6"/>
+      <c r="D112" s="6"/>
+      <c r="E112" s="26"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B13:D112">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>"Target"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>"Stop"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B13:D112" type="list">
+      <formula1>"Target,Stop,No signal"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:M206"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -1444,49 +2375,49 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L2" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="M2" s="21" t="n">
+        <v>84</v>
+      </c>
+      <c r="M2" s="27" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="M3" s="22" t="n">
+        <v>86</v>
+      </c>
+      <c r="M3" s="28" t="n">
         <v>0.005</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="M4" s="23" t="n">
+        <v>88</v>
+      </c>
+      <c r="M4" s="29" t="n">
         <f aca="false">M2+SUM(J7:J206)</f>
         <v>10000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>11</v>
@@ -1495,29 +2426,29 @@
         <v>13</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="J6" s="17" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K6" s="17" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="L6" s="17" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="24"/>
+      <c r="A7" s="30"/>
       <c r="B7" s="6"/>
       <c r="C7" s="8" t="str">
         <f aca="false">IF(OR(D7="",E7="",D7=E7),"",IF(E7&lt;D7,"BUY","SELL"))</f>
@@ -1534,19 +2465,19 @@
         <f aca="false">IF(I7="","",IF(I7&gt;0,"WIN",IF(I7&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I7" s="25" t="str">
+      <c r="I7" s="31" t="str">
         <f aca="false">IF(OR(G7="",C7=""),"",ROUND((G7-D7)/(D7-E7),2))</f>
         <v/>
       </c>
-      <c r="J7" s="26" t="str">
+      <c r="J7" s="32" t="str">
         <f aca="false">IF(I7="","",ROUND(I7*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K7" s="6"/>
-      <c r="L7" s="27"/>
+      <c r="L7" s="26"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="24"/>
+      <c r="A8" s="30"/>
       <c r="B8" s="6"/>
       <c r="C8" s="8" t="str">
         <f aca="false">IF(OR(D8="",E8="",D8=E8),"",IF(E8&lt;D8,"BUY","SELL"))</f>
@@ -1563,19 +2494,19 @@
         <f aca="false">IF(I8="","",IF(I8&gt;0,"WIN",IF(I8&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I8" s="25" t="str">
+      <c r="I8" s="31" t="str">
         <f aca="false">IF(OR(G8="",C8=""),"",ROUND((G8-D8)/(D8-E8),2))</f>
         <v/>
       </c>
-      <c r="J8" s="26" t="str">
+      <c r="J8" s="32" t="str">
         <f aca="false">IF(I8="","",ROUND(I8*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K8" s="6"/>
-      <c r="L8" s="27"/>
+      <c r="L8" s="26"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="24"/>
+      <c r="A9" s="30"/>
       <c r="B9" s="6"/>
       <c r="C9" s="8" t="str">
         <f aca="false">IF(OR(D9="",E9="",D9=E9),"",IF(E9&lt;D9,"BUY","SELL"))</f>
@@ -1592,19 +2523,19 @@
         <f aca="false">IF(I9="","",IF(I9&gt;0,"WIN",IF(I9&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I9" s="25" t="str">
+      <c r="I9" s="31" t="str">
         <f aca="false">IF(OR(G9="",C9=""),"",ROUND((G9-D9)/(D9-E9),2))</f>
         <v/>
       </c>
-      <c r="J9" s="26" t="str">
+      <c r="J9" s="32" t="str">
         <f aca="false">IF(I9="","",ROUND(I9*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K9" s="6"/>
-      <c r="L9" s="27"/>
+      <c r="L9" s="26"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="24"/>
+      <c r="A10" s="30"/>
       <c r="B10" s="6"/>
       <c r="C10" s="8" t="str">
         <f aca="false">IF(OR(D10="",E10="",D10=E10),"",IF(E10&lt;D10,"BUY","SELL"))</f>
@@ -1621,19 +2552,19 @@
         <f aca="false">IF(I10="","",IF(I10&gt;0,"WIN",IF(I10&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I10" s="25" t="str">
+      <c r="I10" s="31" t="str">
         <f aca="false">IF(OR(G10="",C10=""),"",ROUND((G10-D10)/(D10-E10),2))</f>
         <v/>
       </c>
-      <c r="J10" s="26" t="str">
+      <c r="J10" s="32" t="str">
         <f aca="false">IF(I10="","",ROUND(I10*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K10" s="6"/>
-      <c r="L10" s="27"/>
+      <c r="L10" s="26"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="24"/>
+      <c r="A11" s="30"/>
       <c r="B11" s="6"/>
       <c r="C11" s="8" t="str">
         <f aca="false">IF(OR(D11="",E11="",D11=E11),"",IF(E11&lt;D11,"BUY","SELL"))</f>
@@ -1650,19 +2581,19 @@
         <f aca="false">IF(I11="","",IF(I11&gt;0,"WIN",IF(I11&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I11" s="25" t="str">
+      <c r="I11" s="31" t="str">
         <f aca="false">IF(OR(G11="",C11=""),"",ROUND((G11-D11)/(D11-E11),2))</f>
         <v/>
       </c>
-      <c r="J11" s="26" t="str">
+      <c r="J11" s="32" t="str">
         <f aca="false">IF(I11="","",ROUND(I11*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K11" s="6"/>
-      <c r="L11" s="27"/>
+      <c r="L11" s="26"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="24"/>
+      <c r="A12" s="30"/>
       <c r="B12" s="6"/>
       <c r="C12" s="8" t="str">
         <f aca="false">IF(OR(D12="",E12="",D12=E12),"",IF(E12&lt;D12,"BUY","SELL"))</f>
@@ -1679,19 +2610,19 @@
         <f aca="false">IF(I12="","",IF(I12&gt;0,"WIN",IF(I12&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I12" s="25" t="str">
+      <c r="I12" s="31" t="str">
         <f aca="false">IF(OR(G12="",C12=""),"",ROUND((G12-D12)/(D12-E12),2))</f>
         <v/>
       </c>
-      <c r="J12" s="26" t="str">
+      <c r="J12" s="32" t="str">
         <f aca="false">IF(I12="","",ROUND(I12*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K12" s="6"/>
-      <c r="L12" s="27"/>
+      <c r="L12" s="26"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="24"/>
+      <c r="A13" s="30"/>
       <c r="B13" s="6"/>
       <c r="C13" s="8" t="str">
         <f aca="false">IF(OR(D13="",E13="",D13=E13),"",IF(E13&lt;D13,"BUY","SELL"))</f>
@@ -1708,19 +2639,19 @@
         <f aca="false">IF(I13="","",IF(I13&gt;0,"WIN",IF(I13&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I13" s="25" t="str">
+      <c r="I13" s="31" t="str">
         <f aca="false">IF(OR(G13="",C13=""),"",ROUND((G13-D13)/(D13-E13),2))</f>
         <v/>
       </c>
-      <c r="J13" s="26" t="str">
+      <c r="J13" s="32" t="str">
         <f aca="false">IF(I13="","",ROUND(I13*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K13" s="6"/>
-      <c r="L13" s="27"/>
+      <c r="L13" s="26"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="24"/>
+      <c r="A14" s="30"/>
       <c r="B14" s="6"/>
       <c r="C14" s="8" t="str">
         <f aca="false">IF(OR(D14="",E14="",D14=E14),"",IF(E14&lt;D14,"BUY","SELL"))</f>
@@ -1737,19 +2668,19 @@
         <f aca="false">IF(I14="","",IF(I14&gt;0,"WIN",IF(I14&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I14" s="25" t="str">
+      <c r="I14" s="31" t="str">
         <f aca="false">IF(OR(G14="",C14=""),"",ROUND((G14-D14)/(D14-E14),2))</f>
         <v/>
       </c>
-      <c r="J14" s="26" t="str">
+      <c r="J14" s="32" t="str">
         <f aca="false">IF(I14="","",ROUND(I14*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K14" s="6"/>
-      <c r="L14" s="27"/>
+      <c r="L14" s="26"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="24"/>
+      <c r="A15" s="30"/>
       <c r="B15" s="6"/>
       <c r="C15" s="8" t="str">
         <f aca="false">IF(OR(D15="",E15="",D15=E15),"",IF(E15&lt;D15,"BUY","SELL"))</f>
@@ -1766,19 +2697,19 @@
         <f aca="false">IF(I15="","",IF(I15&gt;0,"WIN",IF(I15&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I15" s="25" t="str">
+      <c r="I15" s="31" t="str">
         <f aca="false">IF(OR(G15="",C15=""),"",ROUND((G15-D15)/(D15-E15),2))</f>
         <v/>
       </c>
-      <c r="J15" s="26" t="str">
+      <c r="J15" s="32" t="str">
         <f aca="false">IF(I15="","",ROUND(I15*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K15" s="6"/>
-      <c r="L15" s="27"/>
+      <c r="L15" s="26"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="24"/>
+      <c r="A16" s="30"/>
       <c r="B16" s="6"/>
       <c r="C16" s="8" t="str">
         <f aca="false">IF(OR(D16="",E16="",D16=E16),"",IF(E16&lt;D16,"BUY","SELL"))</f>
@@ -1795,19 +2726,19 @@
         <f aca="false">IF(I16="","",IF(I16&gt;0,"WIN",IF(I16&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I16" s="25" t="str">
+      <c r="I16" s="31" t="str">
         <f aca="false">IF(OR(G16="",C16=""),"",ROUND((G16-D16)/(D16-E16),2))</f>
         <v/>
       </c>
-      <c r="J16" s="26" t="str">
+      <c r="J16" s="32" t="str">
         <f aca="false">IF(I16="","",ROUND(I16*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K16" s="6"/>
-      <c r="L16" s="27"/>
+      <c r="L16" s="26"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="24"/>
+      <c r="A17" s="30"/>
       <c r="B17" s="6"/>
       <c r="C17" s="8" t="str">
         <f aca="false">IF(OR(D17="",E17="",D17=E17),"",IF(E17&lt;D17,"BUY","SELL"))</f>
@@ -1824,19 +2755,19 @@
         <f aca="false">IF(I17="","",IF(I17&gt;0,"WIN",IF(I17&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I17" s="25" t="str">
+      <c r="I17" s="31" t="str">
         <f aca="false">IF(OR(G17="",C17=""),"",ROUND((G17-D17)/(D17-E17),2))</f>
         <v/>
       </c>
-      <c r="J17" s="26" t="str">
+      <c r="J17" s="32" t="str">
         <f aca="false">IF(I17="","",ROUND(I17*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K17" s="6"/>
-      <c r="L17" s="27"/>
+      <c r="L17" s="26"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="24"/>
+      <c r="A18" s="30"/>
       <c r="B18" s="6"/>
       <c r="C18" s="8" t="str">
         <f aca="false">IF(OR(D18="",E18="",D18=E18),"",IF(E18&lt;D18,"BUY","SELL"))</f>
@@ -1853,19 +2784,19 @@
         <f aca="false">IF(I18="","",IF(I18&gt;0,"WIN",IF(I18&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I18" s="25" t="str">
+      <c r="I18" s="31" t="str">
         <f aca="false">IF(OR(G18="",C18=""),"",ROUND((G18-D18)/(D18-E18),2))</f>
         <v/>
       </c>
-      <c r="J18" s="26" t="str">
+      <c r="J18" s="32" t="str">
         <f aca="false">IF(I18="","",ROUND(I18*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K18" s="6"/>
-      <c r="L18" s="27"/>
+      <c r="L18" s="26"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="24"/>
+      <c r="A19" s="30"/>
       <c r="B19" s="6"/>
       <c r="C19" s="8" t="str">
         <f aca="false">IF(OR(D19="",E19="",D19=E19),"",IF(E19&lt;D19,"BUY","SELL"))</f>
@@ -1882,19 +2813,19 @@
         <f aca="false">IF(I19="","",IF(I19&gt;0,"WIN",IF(I19&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I19" s="25" t="str">
+      <c r="I19" s="31" t="str">
         <f aca="false">IF(OR(G19="",C19=""),"",ROUND((G19-D19)/(D19-E19),2))</f>
         <v/>
       </c>
-      <c r="J19" s="26" t="str">
+      <c r="J19" s="32" t="str">
         <f aca="false">IF(I19="","",ROUND(I19*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K19" s="6"/>
-      <c r="L19" s="27"/>
+      <c r="L19" s="26"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="24"/>
+      <c r="A20" s="30"/>
       <c r="B20" s="6"/>
       <c r="C20" s="8" t="str">
         <f aca="false">IF(OR(D20="",E20="",D20=E20),"",IF(E20&lt;D20,"BUY","SELL"))</f>
@@ -1911,19 +2842,19 @@
         <f aca="false">IF(I20="","",IF(I20&gt;0,"WIN",IF(I20&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I20" s="25" t="str">
+      <c r="I20" s="31" t="str">
         <f aca="false">IF(OR(G20="",C20=""),"",ROUND((G20-D20)/(D20-E20),2))</f>
         <v/>
       </c>
-      <c r="J20" s="26" t="str">
+      <c r="J20" s="32" t="str">
         <f aca="false">IF(I20="","",ROUND(I20*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K20" s="6"/>
-      <c r="L20" s="27"/>
+      <c r="L20" s="26"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="24"/>
+      <c r="A21" s="30"/>
       <c r="B21" s="6"/>
       <c r="C21" s="8" t="str">
         <f aca="false">IF(OR(D21="",E21="",D21=E21),"",IF(E21&lt;D21,"BUY","SELL"))</f>
@@ -1940,19 +2871,19 @@
         <f aca="false">IF(I21="","",IF(I21&gt;0,"WIN",IF(I21&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I21" s="25" t="str">
+      <c r="I21" s="31" t="str">
         <f aca="false">IF(OR(G21="",C21=""),"",ROUND((G21-D21)/(D21-E21),2))</f>
         <v/>
       </c>
-      <c r="J21" s="26" t="str">
+      <c r="J21" s="32" t="str">
         <f aca="false">IF(I21="","",ROUND(I21*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K21" s="6"/>
-      <c r="L21" s="27"/>
+      <c r="L21" s="26"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="24"/>
+      <c r="A22" s="30"/>
       <c r="B22" s="6"/>
       <c r="C22" s="8" t="str">
         <f aca="false">IF(OR(D22="",E22="",D22=E22),"",IF(E22&lt;D22,"BUY","SELL"))</f>
@@ -1969,19 +2900,19 @@
         <f aca="false">IF(I22="","",IF(I22&gt;0,"WIN",IF(I22&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I22" s="25" t="str">
+      <c r="I22" s="31" t="str">
         <f aca="false">IF(OR(G22="",C22=""),"",ROUND((G22-D22)/(D22-E22),2))</f>
         <v/>
       </c>
-      <c r="J22" s="26" t="str">
+      <c r="J22" s="32" t="str">
         <f aca="false">IF(I22="","",ROUND(I22*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K22" s="6"/>
-      <c r="L22" s="27"/>
+      <c r="L22" s="26"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="24"/>
+      <c r="A23" s="30"/>
       <c r="B23" s="6"/>
       <c r="C23" s="8" t="str">
         <f aca="false">IF(OR(D23="",E23="",D23=E23),"",IF(E23&lt;D23,"BUY","SELL"))</f>
@@ -1998,19 +2929,19 @@
         <f aca="false">IF(I23="","",IF(I23&gt;0,"WIN",IF(I23&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I23" s="25" t="str">
+      <c r="I23" s="31" t="str">
         <f aca="false">IF(OR(G23="",C23=""),"",ROUND((G23-D23)/(D23-E23),2))</f>
         <v/>
       </c>
-      <c r="J23" s="26" t="str">
+      <c r="J23" s="32" t="str">
         <f aca="false">IF(I23="","",ROUND(I23*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K23" s="6"/>
-      <c r="L23" s="27"/>
+      <c r="L23" s="26"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="24"/>
+      <c r="A24" s="30"/>
       <c r="B24" s="6"/>
       <c r="C24" s="8" t="str">
         <f aca="false">IF(OR(D24="",E24="",D24=E24),"",IF(E24&lt;D24,"BUY","SELL"))</f>
@@ -2027,19 +2958,19 @@
         <f aca="false">IF(I24="","",IF(I24&gt;0,"WIN",IF(I24&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I24" s="25" t="str">
+      <c r="I24" s="31" t="str">
         <f aca="false">IF(OR(G24="",C24=""),"",ROUND((G24-D24)/(D24-E24),2))</f>
         <v/>
       </c>
-      <c r="J24" s="26" t="str">
+      <c r="J24" s="32" t="str">
         <f aca="false">IF(I24="","",ROUND(I24*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K24" s="6"/>
-      <c r="L24" s="27"/>
+      <c r="L24" s="26"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="24"/>
+      <c r="A25" s="30"/>
       <c r="B25" s="6"/>
       <c r="C25" s="8" t="str">
         <f aca="false">IF(OR(D25="",E25="",D25=E25),"",IF(E25&lt;D25,"BUY","SELL"))</f>
@@ -2056,19 +2987,19 @@
         <f aca="false">IF(I25="","",IF(I25&gt;0,"WIN",IF(I25&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I25" s="25" t="str">
+      <c r="I25" s="31" t="str">
         <f aca="false">IF(OR(G25="",C25=""),"",ROUND((G25-D25)/(D25-E25),2))</f>
         <v/>
       </c>
-      <c r="J25" s="26" t="str">
+      <c r="J25" s="32" t="str">
         <f aca="false">IF(I25="","",ROUND(I25*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K25" s="6"/>
-      <c r="L25" s="27"/>
+      <c r="L25" s="26"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="24"/>
+      <c r="A26" s="30"/>
       <c r="B26" s="6"/>
       <c r="C26" s="8" t="str">
         <f aca="false">IF(OR(D26="",E26="",D26=E26),"",IF(E26&lt;D26,"BUY","SELL"))</f>
@@ -2085,19 +3016,19 @@
         <f aca="false">IF(I26="","",IF(I26&gt;0,"WIN",IF(I26&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I26" s="25" t="str">
+      <c r="I26" s="31" t="str">
         <f aca="false">IF(OR(G26="",C26=""),"",ROUND((G26-D26)/(D26-E26),2))</f>
         <v/>
       </c>
-      <c r="J26" s="26" t="str">
+      <c r="J26" s="32" t="str">
         <f aca="false">IF(I26="","",ROUND(I26*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K26" s="6"/>
-      <c r="L26" s="27"/>
+      <c r="L26" s="26"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="24"/>
+      <c r="A27" s="30"/>
       <c r="B27" s="6"/>
       <c r="C27" s="8" t="str">
         <f aca="false">IF(OR(D27="",E27="",D27=E27),"",IF(E27&lt;D27,"BUY","SELL"))</f>
@@ -2114,19 +3045,19 @@
         <f aca="false">IF(I27="","",IF(I27&gt;0,"WIN",IF(I27&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I27" s="25" t="str">
+      <c r="I27" s="31" t="str">
         <f aca="false">IF(OR(G27="",C27=""),"",ROUND((G27-D27)/(D27-E27),2))</f>
         <v/>
       </c>
-      <c r="J27" s="26" t="str">
+      <c r="J27" s="32" t="str">
         <f aca="false">IF(I27="","",ROUND(I27*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K27" s="6"/>
-      <c r="L27" s="27"/>
+      <c r="L27" s="26"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="24"/>
+      <c r="A28" s="30"/>
       <c r="B28" s="6"/>
       <c r="C28" s="8" t="str">
         <f aca="false">IF(OR(D28="",E28="",D28=E28),"",IF(E28&lt;D28,"BUY","SELL"))</f>
@@ -2143,19 +3074,19 @@
         <f aca="false">IF(I28="","",IF(I28&gt;0,"WIN",IF(I28&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I28" s="25" t="str">
+      <c r="I28" s="31" t="str">
         <f aca="false">IF(OR(G28="",C28=""),"",ROUND((G28-D28)/(D28-E28),2))</f>
         <v/>
       </c>
-      <c r="J28" s="26" t="str">
+      <c r="J28" s="32" t="str">
         <f aca="false">IF(I28="","",ROUND(I28*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K28" s="6"/>
-      <c r="L28" s="27"/>
+      <c r="L28" s="26"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="24"/>
+      <c r="A29" s="30"/>
       <c r="B29" s="6"/>
       <c r="C29" s="8" t="str">
         <f aca="false">IF(OR(D29="",E29="",D29=E29),"",IF(E29&lt;D29,"BUY","SELL"))</f>
@@ -2172,19 +3103,19 @@
         <f aca="false">IF(I29="","",IF(I29&gt;0,"WIN",IF(I29&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I29" s="25" t="str">
+      <c r="I29" s="31" t="str">
         <f aca="false">IF(OR(G29="",C29=""),"",ROUND((G29-D29)/(D29-E29),2))</f>
         <v/>
       </c>
-      <c r="J29" s="26" t="str">
+      <c r="J29" s="32" t="str">
         <f aca="false">IF(I29="","",ROUND(I29*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K29" s="6"/>
-      <c r="L29" s="27"/>
+      <c r="L29" s="26"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="24"/>
+      <c r="A30" s="30"/>
       <c r="B30" s="6"/>
       <c r="C30" s="8" t="str">
         <f aca="false">IF(OR(D30="",E30="",D30=E30),"",IF(E30&lt;D30,"BUY","SELL"))</f>
@@ -2201,19 +3132,19 @@
         <f aca="false">IF(I30="","",IF(I30&gt;0,"WIN",IF(I30&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I30" s="25" t="str">
+      <c r="I30" s="31" t="str">
         <f aca="false">IF(OR(G30="",C30=""),"",ROUND((G30-D30)/(D30-E30),2))</f>
         <v/>
       </c>
-      <c r="J30" s="26" t="str">
+      <c r="J30" s="32" t="str">
         <f aca="false">IF(I30="","",ROUND(I30*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K30" s="6"/>
-      <c r="L30" s="27"/>
+      <c r="L30" s="26"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="24"/>
+      <c r="A31" s="30"/>
       <c r="B31" s="6"/>
       <c r="C31" s="8" t="str">
         <f aca="false">IF(OR(D31="",E31="",D31=E31),"",IF(E31&lt;D31,"BUY","SELL"))</f>
@@ -2230,19 +3161,19 @@
         <f aca="false">IF(I31="","",IF(I31&gt;0,"WIN",IF(I31&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I31" s="25" t="str">
+      <c r="I31" s="31" t="str">
         <f aca="false">IF(OR(G31="",C31=""),"",ROUND((G31-D31)/(D31-E31),2))</f>
         <v/>
       </c>
-      <c r="J31" s="26" t="str">
+      <c r="J31" s="32" t="str">
         <f aca="false">IF(I31="","",ROUND(I31*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K31" s="6"/>
-      <c r="L31" s="27"/>
+      <c r="L31" s="26"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="24"/>
+      <c r="A32" s="30"/>
       <c r="B32" s="6"/>
       <c r="C32" s="8" t="str">
         <f aca="false">IF(OR(D32="",E32="",D32=E32),"",IF(E32&lt;D32,"BUY","SELL"))</f>
@@ -2259,19 +3190,19 @@
         <f aca="false">IF(I32="","",IF(I32&gt;0,"WIN",IF(I32&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I32" s="25" t="str">
+      <c r="I32" s="31" t="str">
         <f aca="false">IF(OR(G32="",C32=""),"",ROUND((G32-D32)/(D32-E32),2))</f>
         <v/>
       </c>
-      <c r="J32" s="26" t="str">
+      <c r="J32" s="32" t="str">
         <f aca="false">IF(I32="","",ROUND(I32*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K32" s="6"/>
-      <c r="L32" s="27"/>
+      <c r="L32" s="26"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="24"/>
+      <c r="A33" s="30"/>
       <c r="B33" s="6"/>
       <c r="C33" s="8" t="str">
         <f aca="false">IF(OR(D33="",E33="",D33=E33),"",IF(E33&lt;D33,"BUY","SELL"))</f>
@@ -2288,19 +3219,19 @@
         <f aca="false">IF(I33="","",IF(I33&gt;0,"WIN",IF(I33&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I33" s="25" t="str">
+      <c r="I33" s="31" t="str">
         <f aca="false">IF(OR(G33="",C33=""),"",ROUND((G33-D33)/(D33-E33),2))</f>
         <v/>
       </c>
-      <c r="J33" s="26" t="str">
+      <c r="J33" s="32" t="str">
         <f aca="false">IF(I33="","",ROUND(I33*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K33" s="6"/>
-      <c r="L33" s="27"/>
+      <c r="L33" s="26"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="24"/>
+      <c r="A34" s="30"/>
       <c r="B34" s="6"/>
       <c r="C34" s="8" t="str">
         <f aca="false">IF(OR(D34="",E34="",D34=E34),"",IF(E34&lt;D34,"BUY","SELL"))</f>
@@ -2317,19 +3248,19 @@
         <f aca="false">IF(I34="","",IF(I34&gt;0,"WIN",IF(I34&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I34" s="25" t="str">
+      <c r="I34" s="31" t="str">
         <f aca="false">IF(OR(G34="",C34=""),"",ROUND((G34-D34)/(D34-E34),2))</f>
         <v/>
       </c>
-      <c r="J34" s="26" t="str">
+      <c r="J34" s="32" t="str">
         <f aca="false">IF(I34="","",ROUND(I34*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K34" s="6"/>
-      <c r="L34" s="27"/>
+      <c r="L34" s="26"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="24"/>
+      <c r="A35" s="30"/>
       <c r="B35" s="6"/>
       <c r="C35" s="8" t="str">
         <f aca="false">IF(OR(D35="",E35="",D35=E35),"",IF(E35&lt;D35,"BUY","SELL"))</f>
@@ -2346,19 +3277,19 @@
         <f aca="false">IF(I35="","",IF(I35&gt;0,"WIN",IF(I35&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I35" s="25" t="str">
+      <c r="I35" s="31" t="str">
         <f aca="false">IF(OR(G35="",C35=""),"",ROUND((G35-D35)/(D35-E35),2))</f>
         <v/>
       </c>
-      <c r="J35" s="26" t="str">
+      <c r="J35" s="32" t="str">
         <f aca="false">IF(I35="","",ROUND(I35*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K35" s="6"/>
-      <c r="L35" s="27"/>
+      <c r="L35" s="26"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="24"/>
+      <c r="A36" s="30"/>
       <c r="B36" s="6"/>
       <c r="C36" s="8" t="str">
         <f aca="false">IF(OR(D36="",E36="",D36=E36),"",IF(E36&lt;D36,"BUY","SELL"))</f>
@@ -2375,19 +3306,19 @@
         <f aca="false">IF(I36="","",IF(I36&gt;0,"WIN",IF(I36&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I36" s="25" t="str">
+      <c r="I36" s="31" t="str">
         <f aca="false">IF(OR(G36="",C36=""),"",ROUND((G36-D36)/(D36-E36),2))</f>
         <v/>
       </c>
-      <c r="J36" s="26" t="str">
+      <c r="J36" s="32" t="str">
         <f aca="false">IF(I36="","",ROUND(I36*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K36" s="6"/>
-      <c r="L36" s="27"/>
+      <c r="L36" s="26"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="24"/>
+      <c r="A37" s="30"/>
       <c r="B37" s="6"/>
       <c r="C37" s="8" t="str">
         <f aca="false">IF(OR(D37="",E37="",D37=E37),"",IF(E37&lt;D37,"BUY","SELL"))</f>
@@ -2404,19 +3335,19 @@
         <f aca="false">IF(I37="","",IF(I37&gt;0,"WIN",IF(I37&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I37" s="25" t="str">
+      <c r="I37" s="31" t="str">
         <f aca="false">IF(OR(G37="",C37=""),"",ROUND((G37-D37)/(D37-E37),2))</f>
         <v/>
       </c>
-      <c r="J37" s="26" t="str">
+      <c r="J37" s="32" t="str">
         <f aca="false">IF(I37="","",ROUND(I37*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K37" s="6"/>
-      <c r="L37" s="27"/>
+      <c r="L37" s="26"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="24"/>
+      <c r="A38" s="30"/>
       <c r="B38" s="6"/>
       <c r="C38" s="8" t="str">
         <f aca="false">IF(OR(D38="",E38="",D38=E38),"",IF(E38&lt;D38,"BUY","SELL"))</f>
@@ -2433,19 +3364,19 @@
         <f aca="false">IF(I38="","",IF(I38&gt;0,"WIN",IF(I38&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I38" s="25" t="str">
+      <c r="I38" s="31" t="str">
         <f aca="false">IF(OR(G38="",C38=""),"",ROUND((G38-D38)/(D38-E38),2))</f>
         <v/>
       </c>
-      <c r="J38" s="26" t="str">
+      <c r="J38" s="32" t="str">
         <f aca="false">IF(I38="","",ROUND(I38*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K38" s="6"/>
-      <c r="L38" s="27"/>
+      <c r="L38" s="26"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="24"/>
+      <c r="A39" s="30"/>
       <c r="B39" s="6"/>
       <c r="C39" s="8" t="str">
         <f aca="false">IF(OR(D39="",E39="",D39=E39),"",IF(E39&lt;D39,"BUY","SELL"))</f>
@@ -2462,19 +3393,19 @@
         <f aca="false">IF(I39="","",IF(I39&gt;0,"WIN",IF(I39&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I39" s="25" t="str">
+      <c r="I39" s="31" t="str">
         <f aca="false">IF(OR(G39="",C39=""),"",ROUND((G39-D39)/(D39-E39),2))</f>
         <v/>
       </c>
-      <c r="J39" s="26" t="str">
+      <c r="J39" s="32" t="str">
         <f aca="false">IF(I39="","",ROUND(I39*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K39" s="6"/>
-      <c r="L39" s="27"/>
+      <c r="L39" s="26"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="24"/>
+      <c r="A40" s="30"/>
       <c r="B40" s="6"/>
       <c r="C40" s="8" t="str">
         <f aca="false">IF(OR(D40="",E40="",D40=E40),"",IF(E40&lt;D40,"BUY","SELL"))</f>
@@ -2491,19 +3422,19 @@
         <f aca="false">IF(I40="","",IF(I40&gt;0,"WIN",IF(I40&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I40" s="25" t="str">
+      <c r="I40" s="31" t="str">
         <f aca="false">IF(OR(G40="",C40=""),"",ROUND((G40-D40)/(D40-E40),2))</f>
         <v/>
       </c>
-      <c r="J40" s="26" t="str">
+      <c r="J40" s="32" t="str">
         <f aca="false">IF(I40="","",ROUND(I40*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K40" s="6"/>
-      <c r="L40" s="27"/>
+      <c r="L40" s="26"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="24"/>
+      <c r="A41" s="30"/>
       <c r="B41" s="6"/>
       <c r="C41" s="8" t="str">
         <f aca="false">IF(OR(D41="",E41="",D41=E41),"",IF(E41&lt;D41,"BUY","SELL"))</f>
@@ -2520,19 +3451,19 @@
         <f aca="false">IF(I41="","",IF(I41&gt;0,"WIN",IF(I41&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I41" s="25" t="str">
+      <c r="I41" s="31" t="str">
         <f aca="false">IF(OR(G41="",C41=""),"",ROUND((G41-D41)/(D41-E41),2))</f>
         <v/>
       </c>
-      <c r="J41" s="26" t="str">
+      <c r="J41" s="32" t="str">
         <f aca="false">IF(I41="","",ROUND(I41*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K41" s="6"/>
-      <c r="L41" s="27"/>
+      <c r="L41" s="26"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="24"/>
+      <c r="A42" s="30"/>
       <c r="B42" s="6"/>
       <c r="C42" s="8" t="str">
         <f aca="false">IF(OR(D42="",E42="",D42=E42),"",IF(E42&lt;D42,"BUY","SELL"))</f>
@@ -2549,19 +3480,19 @@
         <f aca="false">IF(I42="","",IF(I42&gt;0,"WIN",IF(I42&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I42" s="25" t="str">
+      <c r="I42" s="31" t="str">
         <f aca="false">IF(OR(G42="",C42=""),"",ROUND((G42-D42)/(D42-E42),2))</f>
         <v/>
       </c>
-      <c r="J42" s="26" t="str">
+      <c r="J42" s="32" t="str">
         <f aca="false">IF(I42="","",ROUND(I42*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K42" s="6"/>
-      <c r="L42" s="27"/>
+      <c r="L42" s="26"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="24"/>
+      <c r="A43" s="30"/>
       <c r="B43" s="6"/>
       <c r="C43" s="8" t="str">
         <f aca="false">IF(OR(D43="",E43="",D43=E43),"",IF(E43&lt;D43,"BUY","SELL"))</f>
@@ -2578,19 +3509,19 @@
         <f aca="false">IF(I43="","",IF(I43&gt;0,"WIN",IF(I43&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I43" s="25" t="str">
+      <c r="I43" s="31" t="str">
         <f aca="false">IF(OR(G43="",C43=""),"",ROUND((G43-D43)/(D43-E43),2))</f>
         <v/>
       </c>
-      <c r="J43" s="26" t="str">
+      <c r="J43" s="32" t="str">
         <f aca="false">IF(I43="","",ROUND(I43*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K43" s="6"/>
-      <c r="L43" s="27"/>
+      <c r="L43" s="26"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="24"/>
+      <c r="A44" s="30"/>
       <c r="B44" s="6"/>
       <c r="C44" s="8" t="str">
         <f aca="false">IF(OR(D44="",E44="",D44=E44),"",IF(E44&lt;D44,"BUY","SELL"))</f>
@@ -2607,19 +3538,19 @@
         <f aca="false">IF(I44="","",IF(I44&gt;0,"WIN",IF(I44&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I44" s="25" t="str">
+      <c r="I44" s="31" t="str">
         <f aca="false">IF(OR(G44="",C44=""),"",ROUND((G44-D44)/(D44-E44),2))</f>
         <v/>
       </c>
-      <c r="J44" s="26" t="str">
+      <c r="J44" s="32" t="str">
         <f aca="false">IF(I44="","",ROUND(I44*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K44" s="6"/>
-      <c r="L44" s="27"/>
+      <c r="L44" s="26"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="24"/>
+      <c r="A45" s="30"/>
       <c r="B45" s="6"/>
       <c r="C45" s="8" t="str">
         <f aca="false">IF(OR(D45="",E45="",D45=E45),"",IF(E45&lt;D45,"BUY","SELL"))</f>
@@ -2636,19 +3567,19 @@
         <f aca="false">IF(I45="","",IF(I45&gt;0,"WIN",IF(I45&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I45" s="25" t="str">
+      <c r="I45" s="31" t="str">
         <f aca="false">IF(OR(G45="",C45=""),"",ROUND((G45-D45)/(D45-E45),2))</f>
         <v/>
       </c>
-      <c r="J45" s="26" t="str">
+      <c r="J45" s="32" t="str">
         <f aca="false">IF(I45="","",ROUND(I45*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K45" s="6"/>
-      <c r="L45" s="27"/>
+      <c r="L45" s="26"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="24"/>
+      <c r="A46" s="30"/>
       <c r="B46" s="6"/>
       <c r="C46" s="8" t="str">
         <f aca="false">IF(OR(D46="",E46="",D46=E46),"",IF(E46&lt;D46,"BUY","SELL"))</f>
@@ -2665,19 +3596,19 @@
         <f aca="false">IF(I46="","",IF(I46&gt;0,"WIN",IF(I46&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I46" s="25" t="str">
+      <c r="I46" s="31" t="str">
         <f aca="false">IF(OR(G46="",C46=""),"",ROUND((G46-D46)/(D46-E46),2))</f>
         <v/>
       </c>
-      <c r="J46" s="26" t="str">
+      <c r="J46" s="32" t="str">
         <f aca="false">IF(I46="","",ROUND(I46*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K46" s="6"/>
-      <c r="L46" s="27"/>
+      <c r="L46" s="26"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="24"/>
+      <c r="A47" s="30"/>
       <c r="B47" s="6"/>
       <c r="C47" s="8" t="str">
         <f aca="false">IF(OR(D47="",E47="",D47=E47),"",IF(E47&lt;D47,"BUY","SELL"))</f>
@@ -2694,19 +3625,19 @@
         <f aca="false">IF(I47="","",IF(I47&gt;0,"WIN",IF(I47&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I47" s="25" t="str">
+      <c r="I47" s="31" t="str">
         <f aca="false">IF(OR(G47="",C47=""),"",ROUND((G47-D47)/(D47-E47),2))</f>
         <v/>
       </c>
-      <c r="J47" s="26" t="str">
+      <c r="J47" s="32" t="str">
         <f aca="false">IF(I47="","",ROUND(I47*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K47" s="6"/>
-      <c r="L47" s="27"/>
+      <c r="L47" s="26"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="24"/>
+      <c r="A48" s="30"/>
       <c r="B48" s="6"/>
       <c r="C48" s="8" t="str">
         <f aca="false">IF(OR(D48="",E48="",D48=E48),"",IF(E48&lt;D48,"BUY","SELL"))</f>
@@ -2723,19 +3654,19 @@
         <f aca="false">IF(I48="","",IF(I48&gt;0,"WIN",IF(I48&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I48" s="25" t="str">
+      <c r="I48" s="31" t="str">
         <f aca="false">IF(OR(G48="",C48=""),"",ROUND((G48-D48)/(D48-E48),2))</f>
         <v/>
       </c>
-      <c r="J48" s="26" t="str">
+      <c r="J48" s="32" t="str">
         <f aca="false">IF(I48="","",ROUND(I48*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K48" s="6"/>
-      <c r="L48" s="27"/>
+      <c r="L48" s="26"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="24"/>
+      <c r="A49" s="30"/>
       <c r="B49" s="6"/>
       <c r="C49" s="8" t="str">
         <f aca="false">IF(OR(D49="",E49="",D49=E49),"",IF(E49&lt;D49,"BUY","SELL"))</f>
@@ -2752,19 +3683,19 @@
         <f aca="false">IF(I49="","",IF(I49&gt;0,"WIN",IF(I49&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I49" s="25" t="str">
+      <c r="I49" s="31" t="str">
         <f aca="false">IF(OR(G49="",C49=""),"",ROUND((G49-D49)/(D49-E49),2))</f>
         <v/>
       </c>
-      <c r="J49" s="26" t="str">
+      <c r="J49" s="32" t="str">
         <f aca="false">IF(I49="","",ROUND(I49*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K49" s="6"/>
-      <c r="L49" s="27"/>
+      <c r="L49" s="26"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="24"/>
+      <c r="A50" s="30"/>
       <c r="B50" s="6"/>
       <c r="C50" s="8" t="str">
         <f aca="false">IF(OR(D50="",E50="",D50=E50),"",IF(E50&lt;D50,"BUY","SELL"))</f>
@@ -2781,19 +3712,19 @@
         <f aca="false">IF(I50="","",IF(I50&gt;0,"WIN",IF(I50&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I50" s="25" t="str">
+      <c r="I50" s="31" t="str">
         <f aca="false">IF(OR(G50="",C50=""),"",ROUND((G50-D50)/(D50-E50),2))</f>
         <v/>
       </c>
-      <c r="J50" s="26" t="str">
+      <c r="J50" s="32" t="str">
         <f aca="false">IF(I50="","",ROUND(I50*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K50" s="6"/>
-      <c r="L50" s="27"/>
+      <c r="L50" s="26"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="24"/>
+      <c r="A51" s="30"/>
       <c r="B51" s="6"/>
       <c r="C51" s="8" t="str">
         <f aca="false">IF(OR(D51="",E51="",D51=E51),"",IF(E51&lt;D51,"BUY","SELL"))</f>
@@ -2810,19 +3741,19 @@
         <f aca="false">IF(I51="","",IF(I51&gt;0,"WIN",IF(I51&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I51" s="25" t="str">
+      <c r="I51" s="31" t="str">
         <f aca="false">IF(OR(G51="",C51=""),"",ROUND((G51-D51)/(D51-E51),2))</f>
         <v/>
       </c>
-      <c r="J51" s="26" t="str">
+      <c r="J51" s="32" t="str">
         <f aca="false">IF(I51="","",ROUND(I51*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K51" s="6"/>
-      <c r="L51" s="27"/>
+      <c r="L51" s="26"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="24"/>
+      <c r="A52" s="30"/>
       <c r="B52" s="6"/>
       <c r="C52" s="8" t="str">
         <f aca="false">IF(OR(D52="",E52="",D52=E52),"",IF(E52&lt;D52,"BUY","SELL"))</f>
@@ -2839,19 +3770,19 @@
         <f aca="false">IF(I52="","",IF(I52&gt;0,"WIN",IF(I52&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I52" s="25" t="str">
+      <c r="I52" s="31" t="str">
         <f aca="false">IF(OR(G52="",C52=""),"",ROUND((G52-D52)/(D52-E52),2))</f>
         <v/>
       </c>
-      <c r="J52" s="26" t="str">
+      <c r="J52" s="32" t="str">
         <f aca="false">IF(I52="","",ROUND(I52*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K52" s="6"/>
-      <c r="L52" s="27"/>
+      <c r="L52" s="26"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="24"/>
+      <c r="A53" s="30"/>
       <c r="B53" s="6"/>
       <c r="C53" s="8" t="str">
         <f aca="false">IF(OR(D53="",E53="",D53=E53),"",IF(E53&lt;D53,"BUY","SELL"))</f>
@@ -2868,19 +3799,19 @@
         <f aca="false">IF(I53="","",IF(I53&gt;0,"WIN",IF(I53&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I53" s="25" t="str">
+      <c r="I53" s="31" t="str">
         <f aca="false">IF(OR(G53="",C53=""),"",ROUND((G53-D53)/(D53-E53),2))</f>
         <v/>
       </c>
-      <c r="J53" s="26" t="str">
+      <c r="J53" s="32" t="str">
         <f aca="false">IF(I53="","",ROUND(I53*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K53" s="6"/>
-      <c r="L53" s="27"/>
+      <c r="L53" s="26"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="24"/>
+      <c r="A54" s="30"/>
       <c r="B54" s="6"/>
       <c r="C54" s="8" t="str">
         <f aca="false">IF(OR(D54="",E54="",D54=E54),"",IF(E54&lt;D54,"BUY","SELL"))</f>
@@ -2897,19 +3828,19 @@
         <f aca="false">IF(I54="","",IF(I54&gt;0,"WIN",IF(I54&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I54" s="25" t="str">
+      <c r="I54" s="31" t="str">
         <f aca="false">IF(OR(G54="",C54=""),"",ROUND((G54-D54)/(D54-E54),2))</f>
         <v/>
       </c>
-      <c r="J54" s="26" t="str">
+      <c r="J54" s="32" t="str">
         <f aca="false">IF(I54="","",ROUND(I54*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K54" s="6"/>
-      <c r="L54" s="27"/>
+      <c r="L54" s="26"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="24"/>
+      <c r="A55" s="30"/>
       <c r="B55" s="6"/>
       <c r="C55" s="8" t="str">
         <f aca="false">IF(OR(D55="",E55="",D55=E55),"",IF(E55&lt;D55,"BUY","SELL"))</f>
@@ -2926,19 +3857,19 @@
         <f aca="false">IF(I55="","",IF(I55&gt;0,"WIN",IF(I55&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I55" s="25" t="str">
+      <c r="I55" s="31" t="str">
         <f aca="false">IF(OR(G55="",C55=""),"",ROUND((G55-D55)/(D55-E55),2))</f>
         <v/>
       </c>
-      <c r="J55" s="26" t="str">
+      <c r="J55" s="32" t="str">
         <f aca="false">IF(I55="","",ROUND(I55*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K55" s="6"/>
-      <c r="L55" s="27"/>
+      <c r="L55" s="26"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="24"/>
+      <c r="A56" s="30"/>
       <c r="B56" s="6"/>
       <c r="C56" s="8" t="str">
         <f aca="false">IF(OR(D56="",E56="",D56=E56),"",IF(E56&lt;D56,"BUY","SELL"))</f>
@@ -2955,19 +3886,19 @@
         <f aca="false">IF(I56="","",IF(I56&gt;0,"WIN",IF(I56&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I56" s="25" t="str">
+      <c r="I56" s="31" t="str">
         <f aca="false">IF(OR(G56="",C56=""),"",ROUND((G56-D56)/(D56-E56),2))</f>
         <v/>
       </c>
-      <c r="J56" s="26" t="str">
+      <c r="J56" s="32" t="str">
         <f aca="false">IF(I56="","",ROUND(I56*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K56" s="6"/>
-      <c r="L56" s="27"/>
+      <c r="L56" s="26"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="24"/>
+      <c r="A57" s="30"/>
       <c r="B57" s="6"/>
       <c r="C57" s="8" t="str">
         <f aca="false">IF(OR(D57="",E57="",D57=E57),"",IF(E57&lt;D57,"BUY","SELL"))</f>
@@ -2984,19 +3915,19 @@
         <f aca="false">IF(I57="","",IF(I57&gt;0,"WIN",IF(I57&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I57" s="25" t="str">
+      <c r="I57" s="31" t="str">
         <f aca="false">IF(OR(G57="",C57=""),"",ROUND((G57-D57)/(D57-E57),2))</f>
         <v/>
       </c>
-      <c r="J57" s="26" t="str">
+      <c r="J57" s="32" t="str">
         <f aca="false">IF(I57="","",ROUND(I57*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K57" s="6"/>
-      <c r="L57" s="27"/>
+      <c r="L57" s="26"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="24"/>
+      <c r="A58" s="30"/>
       <c r="B58" s="6"/>
       <c r="C58" s="8" t="str">
         <f aca="false">IF(OR(D58="",E58="",D58=E58),"",IF(E58&lt;D58,"BUY","SELL"))</f>
@@ -3013,19 +3944,19 @@
         <f aca="false">IF(I58="","",IF(I58&gt;0,"WIN",IF(I58&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I58" s="25" t="str">
+      <c r="I58" s="31" t="str">
         <f aca="false">IF(OR(G58="",C58=""),"",ROUND((G58-D58)/(D58-E58),2))</f>
         <v/>
       </c>
-      <c r="J58" s="26" t="str">
+      <c r="J58" s="32" t="str">
         <f aca="false">IF(I58="","",ROUND(I58*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K58" s="6"/>
-      <c r="L58" s="27"/>
+      <c r="L58" s="26"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="24"/>
+      <c r="A59" s="30"/>
       <c r="B59" s="6"/>
       <c r="C59" s="8" t="str">
         <f aca="false">IF(OR(D59="",E59="",D59=E59),"",IF(E59&lt;D59,"BUY","SELL"))</f>
@@ -3042,19 +3973,19 @@
         <f aca="false">IF(I59="","",IF(I59&gt;0,"WIN",IF(I59&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I59" s="25" t="str">
+      <c r="I59" s="31" t="str">
         <f aca="false">IF(OR(G59="",C59=""),"",ROUND((G59-D59)/(D59-E59),2))</f>
         <v/>
       </c>
-      <c r="J59" s="26" t="str">
+      <c r="J59" s="32" t="str">
         <f aca="false">IF(I59="","",ROUND(I59*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K59" s="6"/>
-      <c r="L59" s="27"/>
+      <c r="L59" s="26"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="24"/>
+      <c r="A60" s="30"/>
       <c r="B60" s="6"/>
       <c r="C60" s="8" t="str">
         <f aca="false">IF(OR(D60="",E60="",D60=E60),"",IF(E60&lt;D60,"BUY","SELL"))</f>
@@ -3071,19 +4002,19 @@
         <f aca="false">IF(I60="","",IF(I60&gt;0,"WIN",IF(I60&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I60" s="25" t="str">
+      <c r="I60" s="31" t="str">
         <f aca="false">IF(OR(G60="",C60=""),"",ROUND((G60-D60)/(D60-E60),2))</f>
         <v/>
       </c>
-      <c r="J60" s="26" t="str">
+      <c r="J60" s="32" t="str">
         <f aca="false">IF(I60="","",ROUND(I60*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K60" s="6"/>
-      <c r="L60" s="27"/>
+      <c r="L60" s="26"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="24"/>
+      <c r="A61" s="30"/>
       <c r="B61" s="6"/>
       <c r="C61" s="8" t="str">
         <f aca="false">IF(OR(D61="",E61="",D61=E61),"",IF(E61&lt;D61,"BUY","SELL"))</f>
@@ -3100,19 +4031,19 @@
         <f aca="false">IF(I61="","",IF(I61&gt;0,"WIN",IF(I61&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I61" s="25" t="str">
+      <c r="I61" s="31" t="str">
         <f aca="false">IF(OR(G61="",C61=""),"",ROUND((G61-D61)/(D61-E61),2))</f>
         <v/>
       </c>
-      <c r="J61" s="26" t="str">
+      <c r="J61" s="32" t="str">
         <f aca="false">IF(I61="","",ROUND(I61*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K61" s="6"/>
-      <c r="L61" s="27"/>
+      <c r="L61" s="26"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="24"/>
+      <c r="A62" s="30"/>
       <c r="B62" s="6"/>
       <c r="C62" s="8" t="str">
         <f aca="false">IF(OR(D62="",E62="",D62=E62),"",IF(E62&lt;D62,"BUY","SELL"))</f>
@@ -3129,19 +4060,19 @@
         <f aca="false">IF(I62="","",IF(I62&gt;0,"WIN",IF(I62&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I62" s="25" t="str">
+      <c r="I62" s="31" t="str">
         <f aca="false">IF(OR(G62="",C62=""),"",ROUND((G62-D62)/(D62-E62),2))</f>
         <v/>
       </c>
-      <c r="J62" s="26" t="str">
+      <c r="J62" s="32" t="str">
         <f aca="false">IF(I62="","",ROUND(I62*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K62" s="6"/>
-      <c r="L62" s="27"/>
+      <c r="L62" s="26"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="24"/>
+      <c r="A63" s="30"/>
       <c r="B63" s="6"/>
       <c r="C63" s="8" t="str">
         <f aca="false">IF(OR(D63="",E63="",D63=E63),"",IF(E63&lt;D63,"BUY","SELL"))</f>
@@ -3158,19 +4089,19 @@
         <f aca="false">IF(I63="","",IF(I63&gt;0,"WIN",IF(I63&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I63" s="25" t="str">
+      <c r="I63" s="31" t="str">
         <f aca="false">IF(OR(G63="",C63=""),"",ROUND((G63-D63)/(D63-E63),2))</f>
         <v/>
       </c>
-      <c r="J63" s="26" t="str">
+      <c r="J63" s="32" t="str">
         <f aca="false">IF(I63="","",ROUND(I63*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K63" s="6"/>
-      <c r="L63" s="27"/>
+      <c r="L63" s="26"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="24"/>
+      <c r="A64" s="30"/>
       <c r="B64" s="6"/>
       <c r="C64" s="8" t="str">
         <f aca="false">IF(OR(D64="",E64="",D64=E64),"",IF(E64&lt;D64,"BUY","SELL"))</f>
@@ -3187,19 +4118,19 @@
         <f aca="false">IF(I64="","",IF(I64&gt;0,"WIN",IF(I64&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I64" s="25" t="str">
+      <c r="I64" s="31" t="str">
         <f aca="false">IF(OR(G64="",C64=""),"",ROUND((G64-D64)/(D64-E64),2))</f>
         <v/>
       </c>
-      <c r="J64" s="26" t="str">
+      <c r="J64" s="32" t="str">
         <f aca="false">IF(I64="","",ROUND(I64*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K64" s="6"/>
-      <c r="L64" s="27"/>
+      <c r="L64" s="26"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="24"/>
+      <c r="A65" s="30"/>
       <c r="B65" s="6"/>
       <c r="C65" s="8" t="str">
         <f aca="false">IF(OR(D65="",E65="",D65=E65),"",IF(E65&lt;D65,"BUY","SELL"))</f>
@@ -3216,19 +4147,19 @@
         <f aca="false">IF(I65="","",IF(I65&gt;0,"WIN",IF(I65&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I65" s="25" t="str">
+      <c r="I65" s="31" t="str">
         <f aca="false">IF(OR(G65="",C65=""),"",ROUND((G65-D65)/(D65-E65),2))</f>
         <v/>
       </c>
-      <c r="J65" s="26" t="str">
+      <c r="J65" s="32" t="str">
         <f aca="false">IF(I65="","",ROUND(I65*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K65" s="6"/>
-      <c r="L65" s="27"/>
+      <c r="L65" s="26"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="24"/>
+      <c r="A66" s="30"/>
       <c r="B66" s="6"/>
       <c r="C66" s="8" t="str">
         <f aca="false">IF(OR(D66="",E66="",D66=E66),"",IF(E66&lt;D66,"BUY","SELL"))</f>
@@ -3245,19 +4176,19 @@
         <f aca="false">IF(I66="","",IF(I66&gt;0,"WIN",IF(I66&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I66" s="25" t="str">
+      <c r="I66" s="31" t="str">
         <f aca="false">IF(OR(G66="",C66=""),"",ROUND((G66-D66)/(D66-E66),2))</f>
         <v/>
       </c>
-      <c r="J66" s="26" t="str">
+      <c r="J66" s="32" t="str">
         <f aca="false">IF(I66="","",ROUND(I66*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K66" s="6"/>
-      <c r="L66" s="27"/>
+      <c r="L66" s="26"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="24"/>
+      <c r="A67" s="30"/>
       <c r="B67" s="6"/>
       <c r="C67" s="8" t="str">
         <f aca="false">IF(OR(D67="",E67="",D67=E67),"",IF(E67&lt;D67,"BUY","SELL"))</f>
@@ -3274,19 +4205,19 @@
         <f aca="false">IF(I67="","",IF(I67&gt;0,"WIN",IF(I67&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I67" s="25" t="str">
+      <c r="I67" s="31" t="str">
         <f aca="false">IF(OR(G67="",C67=""),"",ROUND((G67-D67)/(D67-E67),2))</f>
         <v/>
       </c>
-      <c r="J67" s="26" t="str">
+      <c r="J67" s="32" t="str">
         <f aca="false">IF(I67="","",ROUND(I67*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K67" s="6"/>
-      <c r="L67" s="27"/>
+      <c r="L67" s="26"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="24"/>
+      <c r="A68" s="30"/>
       <c r="B68" s="6"/>
       <c r="C68" s="8" t="str">
         <f aca="false">IF(OR(D68="",E68="",D68=E68),"",IF(E68&lt;D68,"BUY","SELL"))</f>
@@ -3303,19 +4234,19 @@
         <f aca="false">IF(I68="","",IF(I68&gt;0,"WIN",IF(I68&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I68" s="25" t="str">
+      <c r="I68" s="31" t="str">
         <f aca="false">IF(OR(G68="",C68=""),"",ROUND((G68-D68)/(D68-E68),2))</f>
         <v/>
       </c>
-      <c r="J68" s="26" t="str">
+      <c r="J68" s="32" t="str">
         <f aca="false">IF(I68="","",ROUND(I68*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K68" s="6"/>
-      <c r="L68" s="27"/>
+      <c r="L68" s="26"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="24"/>
+      <c r="A69" s="30"/>
       <c r="B69" s="6"/>
       <c r="C69" s="8" t="str">
         <f aca="false">IF(OR(D69="",E69="",D69=E69),"",IF(E69&lt;D69,"BUY","SELL"))</f>
@@ -3332,19 +4263,19 @@
         <f aca="false">IF(I69="","",IF(I69&gt;0,"WIN",IF(I69&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I69" s="25" t="str">
+      <c r="I69" s="31" t="str">
         <f aca="false">IF(OR(G69="",C69=""),"",ROUND((G69-D69)/(D69-E69),2))</f>
         <v/>
       </c>
-      <c r="J69" s="26" t="str">
+      <c r="J69" s="32" t="str">
         <f aca="false">IF(I69="","",ROUND(I69*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K69" s="6"/>
-      <c r="L69" s="27"/>
+      <c r="L69" s="26"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="24"/>
+      <c r="A70" s="30"/>
       <c r="B70" s="6"/>
       <c r="C70" s="8" t="str">
         <f aca="false">IF(OR(D70="",E70="",D70=E70),"",IF(E70&lt;D70,"BUY","SELL"))</f>
@@ -3361,19 +4292,19 @@
         <f aca="false">IF(I70="","",IF(I70&gt;0,"WIN",IF(I70&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I70" s="25" t="str">
+      <c r="I70" s="31" t="str">
         <f aca="false">IF(OR(G70="",C70=""),"",ROUND((G70-D70)/(D70-E70),2))</f>
         <v/>
       </c>
-      <c r="J70" s="26" t="str">
+      <c r="J70" s="32" t="str">
         <f aca="false">IF(I70="","",ROUND(I70*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K70" s="6"/>
-      <c r="L70" s="27"/>
+      <c r="L70" s="26"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="24"/>
+      <c r="A71" s="30"/>
       <c r="B71" s="6"/>
       <c r="C71" s="8" t="str">
         <f aca="false">IF(OR(D71="",E71="",D71=E71),"",IF(E71&lt;D71,"BUY","SELL"))</f>
@@ -3390,19 +4321,19 @@
         <f aca="false">IF(I71="","",IF(I71&gt;0,"WIN",IF(I71&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I71" s="25" t="str">
+      <c r="I71" s="31" t="str">
         <f aca="false">IF(OR(G71="",C71=""),"",ROUND((G71-D71)/(D71-E71),2))</f>
         <v/>
       </c>
-      <c r="J71" s="26" t="str">
+      <c r="J71" s="32" t="str">
         <f aca="false">IF(I71="","",ROUND(I71*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K71" s="6"/>
-      <c r="L71" s="27"/>
+      <c r="L71" s="26"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="24"/>
+      <c r="A72" s="30"/>
       <c r="B72" s="6"/>
       <c r="C72" s="8" t="str">
         <f aca="false">IF(OR(D72="",E72="",D72=E72),"",IF(E72&lt;D72,"BUY","SELL"))</f>
@@ -3419,19 +4350,19 @@
         <f aca="false">IF(I72="","",IF(I72&gt;0,"WIN",IF(I72&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I72" s="25" t="str">
+      <c r="I72" s="31" t="str">
         <f aca="false">IF(OR(G72="",C72=""),"",ROUND((G72-D72)/(D72-E72),2))</f>
         <v/>
       </c>
-      <c r="J72" s="26" t="str">
+      <c r="J72" s="32" t="str">
         <f aca="false">IF(I72="","",ROUND(I72*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K72" s="6"/>
-      <c r="L72" s="27"/>
+      <c r="L72" s="26"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="24"/>
+      <c r="A73" s="30"/>
       <c r="B73" s="6"/>
       <c r="C73" s="8" t="str">
         <f aca="false">IF(OR(D73="",E73="",D73=E73),"",IF(E73&lt;D73,"BUY","SELL"))</f>
@@ -3448,19 +4379,19 @@
         <f aca="false">IF(I73="","",IF(I73&gt;0,"WIN",IF(I73&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I73" s="25" t="str">
+      <c r="I73" s="31" t="str">
         <f aca="false">IF(OR(G73="",C73=""),"",ROUND((G73-D73)/(D73-E73),2))</f>
         <v/>
       </c>
-      <c r="J73" s="26" t="str">
+      <c r="J73" s="32" t="str">
         <f aca="false">IF(I73="","",ROUND(I73*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K73" s="6"/>
-      <c r="L73" s="27"/>
+      <c r="L73" s="26"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="24"/>
+      <c r="A74" s="30"/>
       <c r="B74" s="6"/>
       <c r="C74" s="8" t="str">
         <f aca="false">IF(OR(D74="",E74="",D74=E74),"",IF(E74&lt;D74,"BUY","SELL"))</f>
@@ -3477,19 +4408,19 @@
         <f aca="false">IF(I74="","",IF(I74&gt;0,"WIN",IF(I74&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I74" s="25" t="str">
+      <c r="I74" s="31" t="str">
         <f aca="false">IF(OR(G74="",C74=""),"",ROUND((G74-D74)/(D74-E74),2))</f>
         <v/>
       </c>
-      <c r="J74" s="26" t="str">
+      <c r="J74" s="32" t="str">
         <f aca="false">IF(I74="","",ROUND(I74*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K74" s="6"/>
-      <c r="L74" s="27"/>
+      <c r="L74" s="26"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="24"/>
+      <c r="A75" s="30"/>
       <c r="B75" s="6"/>
       <c r="C75" s="8" t="str">
         <f aca="false">IF(OR(D75="",E75="",D75=E75),"",IF(E75&lt;D75,"BUY","SELL"))</f>
@@ -3506,19 +4437,19 @@
         <f aca="false">IF(I75="","",IF(I75&gt;0,"WIN",IF(I75&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I75" s="25" t="str">
+      <c r="I75" s="31" t="str">
         <f aca="false">IF(OR(G75="",C75=""),"",ROUND((G75-D75)/(D75-E75),2))</f>
         <v/>
       </c>
-      <c r="J75" s="26" t="str">
+      <c r="J75" s="32" t="str">
         <f aca="false">IF(I75="","",ROUND(I75*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K75" s="6"/>
-      <c r="L75" s="27"/>
+      <c r="L75" s="26"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="24"/>
+      <c r="A76" s="30"/>
       <c r="B76" s="6"/>
       <c r="C76" s="8" t="str">
         <f aca="false">IF(OR(D76="",E76="",D76=E76),"",IF(E76&lt;D76,"BUY","SELL"))</f>
@@ -3535,19 +4466,19 @@
         <f aca="false">IF(I76="","",IF(I76&gt;0,"WIN",IF(I76&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I76" s="25" t="str">
+      <c r="I76" s="31" t="str">
         <f aca="false">IF(OR(G76="",C76=""),"",ROUND((G76-D76)/(D76-E76),2))</f>
         <v/>
       </c>
-      <c r="J76" s="26" t="str">
+      <c r="J76" s="32" t="str">
         <f aca="false">IF(I76="","",ROUND(I76*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K76" s="6"/>
-      <c r="L76" s="27"/>
+      <c r="L76" s="26"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="24"/>
+      <c r="A77" s="30"/>
       <c r="B77" s="6"/>
       <c r="C77" s="8" t="str">
         <f aca="false">IF(OR(D77="",E77="",D77=E77),"",IF(E77&lt;D77,"BUY","SELL"))</f>
@@ -3564,19 +4495,19 @@
         <f aca="false">IF(I77="","",IF(I77&gt;0,"WIN",IF(I77&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I77" s="25" t="str">
+      <c r="I77" s="31" t="str">
         <f aca="false">IF(OR(G77="",C77=""),"",ROUND((G77-D77)/(D77-E77),2))</f>
         <v/>
       </c>
-      <c r="J77" s="26" t="str">
+      <c r="J77" s="32" t="str">
         <f aca="false">IF(I77="","",ROUND(I77*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K77" s="6"/>
-      <c r="L77" s="27"/>
+      <c r="L77" s="26"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="24"/>
+      <c r="A78" s="30"/>
       <c r="B78" s="6"/>
       <c r="C78" s="8" t="str">
         <f aca="false">IF(OR(D78="",E78="",D78=E78),"",IF(E78&lt;D78,"BUY","SELL"))</f>
@@ -3593,19 +4524,19 @@
         <f aca="false">IF(I78="","",IF(I78&gt;0,"WIN",IF(I78&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I78" s="25" t="str">
+      <c r="I78" s="31" t="str">
         <f aca="false">IF(OR(G78="",C78=""),"",ROUND((G78-D78)/(D78-E78),2))</f>
         <v/>
       </c>
-      <c r="J78" s="26" t="str">
+      <c r="J78" s="32" t="str">
         <f aca="false">IF(I78="","",ROUND(I78*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K78" s="6"/>
-      <c r="L78" s="27"/>
+      <c r="L78" s="26"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="24"/>
+      <c r="A79" s="30"/>
       <c r="B79" s="6"/>
       <c r="C79" s="8" t="str">
         <f aca="false">IF(OR(D79="",E79="",D79=E79),"",IF(E79&lt;D79,"BUY","SELL"))</f>
@@ -3622,19 +4553,19 @@
         <f aca="false">IF(I79="","",IF(I79&gt;0,"WIN",IF(I79&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I79" s="25" t="str">
+      <c r="I79" s="31" t="str">
         <f aca="false">IF(OR(G79="",C79=""),"",ROUND((G79-D79)/(D79-E79),2))</f>
         <v/>
       </c>
-      <c r="J79" s="26" t="str">
+      <c r="J79" s="32" t="str">
         <f aca="false">IF(I79="","",ROUND(I79*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K79" s="6"/>
-      <c r="L79" s="27"/>
+      <c r="L79" s="26"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="24"/>
+      <c r="A80" s="30"/>
       <c r="B80" s="6"/>
       <c r="C80" s="8" t="str">
         <f aca="false">IF(OR(D80="",E80="",D80=E80),"",IF(E80&lt;D80,"BUY","SELL"))</f>
@@ -3651,19 +4582,19 @@
         <f aca="false">IF(I80="","",IF(I80&gt;0,"WIN",IF(I80&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I80" s="25" t="str">
+      <c r="I80" s="31" t="str">
         <f aca="false">IF(OR(G80="",C80=""),"",ROUND((G80-D80)/(D80-E80),2))</f>
         <v/>
       </c>
-      <c r="J80" s="26" t="str">
+      <c r="J80" s="32" t="str">
         <f aca="false">IF(I80="","",ROUND(I80*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K80" s="6"/>
-      <c r="L80" s="27"/>
+      <c r="L80" s="26"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="24"/>
+      <c r="A81" s="30"/>
       <c r="B81" s="6"/>
       <c r="C81" s="8" t="str">
         <f aca="false">IF(OR(D81="",E81="",D81=E81),"",IF(E81&lt;D81,"BUY","SELL"))</f>
@@ -3680,19 +4611,19 @@
         <f aca="false">IF(I81="","",IF(I81&gt;0,"WIN",IF(I81&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I81" s="25" t="str">
+      <c r="I81" s="31" t="str">
         <f aca="false">IF(OR(G81="",C81=""),"",ROUND((G81-D81)/(D81-E81),2))</f>
         <v/>
       </c>
-      <c r="J81" s="26" t="str">
+      <c r="J81" s="32" t="str">
         <f aca="false">IF(I81="","",ROUND(I81*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K81" s="6"/>
-      <c r="L81" s="27"/>
+      <c r="L81" s="26"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="24"/>
+      <c r="A82" s="30"/>
       <c r="B82" s="6"/>
       <c r="C82" s="8" t="str">
         <f aca="false">IF(OR(D82="",E82="",D82=E82),"",IF(E82&lt;D82,"BUY","SELL"))</f>
@@ -3709,19 +4640,19 @@
         <f aca="false">IF(I82="","",IF(I82&gt;0,"WIN",IF(I82&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I82" s="25" t="str">
+      <c r="I82" s="31" t="str">
         <f aca="false">IF(OR(G82="",C82=""),"",ROUND((G82-D82)/(D82-E82),2))</f>
         <v/>
       </c>
-      <c r="J82" s="26" t="str">
+      <c r="J82" s="32" t="str">
         <f aca="false">IF(I82="","",ROUND(I82*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K82" s="6"/>
-      <c r="L82" s="27"/>
+      <c r="L82" s="26"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="24"/>
+      <c r="A83" s="30"/>
       <c r="B83" s="6"/>
       <c r="C83" s="8" t="str">
         <f aca="false">IF(OR(D83="",E83="",D83=E83),"",IF(E83&lt;D83,"BUY","SELL"))</f>
@@ -3738,19 +4669,19 @@
         <f aca="false">IF(I83="","",IF(I83&gt;0,"WIN",IF(I83&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I83" s="25" t="str">
+      <c r="I83" s="31" t="str">
         <f aca="false">IF(OR(G83="",C83=""),"",ROUND((G83-D83)/(D83-E83),2))</f>
         <v/>
       </c>
-      <c r="J83" s="26" t="str">
+      <c r="J83" s="32" t="str">
         <f aca="false">IF(I83="","",ROUND(I83*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K83" s="6"/>
-      <c r="L83" s="27"/>
+      <c r="L83" s="26"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="24"/>
+      <c r="A84" s="30"/>
       <c r="B84" s="6"/>
       <c r="C84" s="8" t="str">
         <f aca="false">IF(OR(D84="",E84="",D84=E84),"",IF(E84&lt;D84,"BUY","SELL"))</f>
@@ -3767,19 +4698,19 @@
         <f aca="false">IF(I84="","",IF(I84&gt;0,"WIN",IF(I84&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I84" s="25" t="str">
+      <c r="I84" s="31" t="str">
         <f aca="false">IF(OR(G84="",C84=""),"",ROUND((G84-D84)/(D84-E84),2))</f>
         <v/>
       </c>
-      <c r="J84" s="26" t="str">
+      <c r="J84" s="32" t="str">
         <f aca="false">IF(I84="","",ROUND(I84*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K84" s="6"/>
-      <c r="L84" s="27"/>
+      <c r="L84" s="26"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="24"/>
+      <c r="A85" s="30"/>
       <c r="B85" s="6"/>
       <c r="C85" s="8" t="str">
         <f aca="false">IF(OR(D85="",E85="",D85=E85),"",IF(E85&lt;D85,"BUY","SELL"))</f>
@@ -3796,19 +4727,19 @@
         <f aca="false">IF(I85="","",IF(I85&gt;0,"WIN",IF(I85&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I85" s="25" t="str">
+      <c r="I85" s="31" t="str">
         <f aca="false">IF(OR(G85="",C85=""),"",ROUND((G85-D85)/(D85-E85),2))</f>
         <v/>
       </c>
-      <c r="J85" s="26" t="str">
+      <c r="J85" s="32" t="str">
         <f aca="false">IF(I85="","",ROUND(I85*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K85" s="6"/>
-      <c r="L85" s="27"/>
+      <c r="L85" s="26"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="24"/>
+      <c r="A86" s="30"/>
       <c r="B86" s="6"/>
       <c r="C86" s="8" t="str">
         <f aca="false">IF(OR(D86="",E86="",D86=E86),"",IF(E86&lt;D86,"BUY","SELL"))</f>
@@ -3825,19 +4756,19 @@
         <f aca="false">IF(I86="","",IF(I86&gt;0,"WIN",IF(I86&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I86" s="25" t="str">
+      <c r="I86" s="31" t="str">
         <f aca="false">IF(OR(G86="",C86=""),"",ROUND((G86-D86)/(D86-E86),2))</f>
         <v/>
       </c>
-      <c r="J86" s="26" t="str">
+      <c r="J86" s="32" t="str">
         <f aca="false">IF(I86="","",ROUND(I86*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K86" s="6"/>
-      <c r="L86" s="27"/>
+      <c r="L86" s="26"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="24"/>
+      <c r="A87" s="30"/>
       <c r="B87" s="6"/>
       <c r="C87" s="8" t="str">
         <f aca="false">IF(OR(D87="",E87="",D87=E87),"",IF(E87&lt;D87,"BUY","SELL"))</f>
@@ -3854,19 +4785,19 @@
         <f aca="false">IF(I87="","",IF(I87&gt;0,"WIN",IF(I87&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I87" s="25" t="str">
+      <c r="I87" s="31" t="str">
         <f aca="false">IF(OR(G87="",C87=""),"",ROUND((G87-D87)/(D87-E87),2))</f>
         <v/>
       </c>
-      <c r="J87" s="26" t="str">
+      <c r="J87" s="32" t="str">
         <f aca="false">IF(I87="","",ROUND(I87*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K87" s="6"/>
-      <c r="L87" s="27"/>
+      <c r="L87" s="26"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="24"/>
+      <c r="A88" s="30"/>
       <c r="B88" s="6"/>
       <c r="C88" s="8" t="str">
         <f aca="false">IF(OR(D88="",E88="",D88=E88),"",IF(E88&lt;D88,"BUY","SELL"))</f>
@@ -3883,19 +4814,19 @@
         <f aca="false">IF(I88="","",IF(I88&gt;0,"WIN",IF(I88&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I88" s="25" t="str">
+      <c r="I88" s="31" t="str">
         <f aca="false">IF(OR(G88="",C88=""),"",ROUND((G88-D88)/(D88-E88),2))</f>
         <v/>
       </c>
-      <c r="J88" s="26" t="str">
+      <c r="J88" s="32" t="str">
         <f aca="false">IF(I88="","",ROUND(I88*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K88" s="6"/>
-      <c r="L88" s="27"/>
+      <c r="L88" s="26"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="24"/>
+      <c r="A89" s="30"/>
       <c r="B89" s="6"/>
       <c r="C89" s="8" t="str">
         <f aca="false">IF(OR(D89="",E89="",D89=E89),"",IF(E89&lt;D89,"BUY","SELL"))</f>
@@ -3912,19 +4843,19 @@
         <f aca="false">IF(I89="","",IF(I89&gt;0,"WIN",IF(I89&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I89" s="25" t="str">
+      <c r="I89" s="31" t="str">
         <f aca="false">IF(OR(G89="",C89=""),"",ROUND((G89-D89)/(D89-E89),2))</f>
         <v/>
       </c>
-      <c r="J89" s="26" t="str">
+      <c r="J89" s="32" t="str">
         <f aca="false">IF(I89="","",ROUND(I89*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K89" s="6"/>
-      <c r="L89" s="27"/>
+      <c r="L89" s="26"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="24"/>
+      <c r="A90" s="30"/>
       <c r="B90" s="6"/>
       <c r="C90" s="8" t="str">
         <f aca="false">IF(OR(D90="",E90="",D90=E90),"",IF(E90&lt;D90,"BUY","SELL"))</f>
@@ -3941,19 +4872,19 @@
         <f aca="false">IF(I90="","",IF(I90&gt;0,"WIN",IF(I90&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I90" s="25" t="str">
+      <c r="I90" s="31" t="str">
         <f aca="false">IF(OR(G90="",C90=""),"",ROUND((G90-D90)/(D90-E90),2))</f>
         <v/>
       </c>
-      <c r="J90" s="26" t="str">
+      <c r="J90" s="32" t="str">
         <f aca="false">IF(I90="","",ROUND(I90*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K90" s="6"/>
-      <c r="L90" s="27"/>
+      <c r="L90" s="26"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="24"/>
+      <c r="A91" s="30"/>
       <c r="B91" s="6"/>
       <c r="C91" s="8" t="str">
         <f aca="false">IF(OR(D91="",E91="",D91=E91),"",IF(E91&lt;D91,"BUY","SELL"))</f>
@@ -3970,19 +4901,19 @@
         <f aca="false">IF(I91="","",IF(I91&gt;0,"WIN",IF(I91&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I91" s="25" t="str">
+      <c r="I91" s="31" t="str">
         <f aca="false">IF(OR(G91="",C91=""),"",ROUND((G91-D91)/(D91-E91),2))</f>
         <v/>
       </c>
-      <c r="J91" s="26" t="str">
+      <c r="J91" s="32" t="str">
         <f aca="false">IF(I91="","",ROUND(I91*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K91" s="6"/>
-      <c r="L91" s="27"/>
+      <c r="L91" s="26"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="24"/>
+      <c r="A92" s="30"/>
       <c r="B92" s="6"/>
       <c r="C92" s="8" t="str">
         <f aca="false">IF(OR(D92="",E92="",D92=E92),"",IF(E92&lt;D92,"BUY","SELL"))</f>
@@ -3999,19 +4930,19 @@
         <f aca="false">IF(I92="","",IF(I92&gt;0,"WIN",IF(I92&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I92" s="25" t="str">
+      <c r="I92" s="31" t="str">
         <f aca="false">IF(OR(G92="",C92=""),"",ROUND((G92-D92)/(D92-E92),2))</f>
         <v/>
       </c>
-      <c r="J92" s="26" t="str">
+      <c r="J92" s="32" t="str">
         <f aca="false">IF(I92="","",ROUND(I92*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K92" s="6"/>
-      <c r="L92" s="27"/>
+      <c r="L92" s="26"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="24"/>
+      <c r="A93" s="30"/>
       <c r="B93" s="6"/>
       <c r="C93" s="8" t="str">
         <f aca="false">IF(OR(D93="",E93="",D93=E93),"",IF(E93&lt;D93,"BUY","SELL"))</f>
@@ -4028,19 +4959,19 @@
         <f aca="false">IF(I93="","",IF(I93&gt;0,"WIN",IF(I93&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I93" s="25" t="str">
+      <c r="I93" s="31" t="str">
         <f aca="false">IF(OR(G93="",C93=""),"",ROUND((G93-D93)/(D93-E93),2))</f>
         <v/>
       </c>
-      <c r="J93" s="26" t="str">
+      <c r="J93" s="32" t="str">
         <f aca="false">IF(I93="","",ROUND(I93*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K93" s="6"/>
-      <c r="L93" s="27"/>
+      <c r="L93" s="26"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="24"/>
+      <c r="A94" s="30"/>
       <c r="B94" s="6"/>
       <c r="C94" s="8" t="str">
         <f aca="false">IF(OR(D94="",E94="",D94=E94),"",IF(E94&lt;D94,"BUY","SELL"))</f>
@@ -4057,19 +4988,19 @@
         <f aca="false">IF(I94="","",IF(I94&gt;0,"WIN",IF(I94&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I94" s="25" t="str">
+      <c r="I94" s="31" t="str">
         <f aca="false">IF(OR(G94="",C94=""),"",ROUND((G94-D94)/(D94-E94),2))</f>
         <v/>
       </c>
-      <c r="J94" s="26" t="str">
+      <c r="J94" s="32" t="str">
         <f aca="false">IF(I94="","",ROUND(I94*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K94" s="6"/>
-      <c r="L94" s="27"/>
+      <c r="L94" s="26"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="24"/>
+      <c r="A95" s="30"/>
       <c r="B95" s="6"/>
       <c r="C95" s="8" t="str">
         <f aca="false">IF(OR(D95="",E95="",D95=E95),"",IF(E95&lt;D95,"BUY","SELL"))</f>
@@ -4086,19 +5017,19 @@
         <f aca="false">IF(I95="","",IF(I95&gt;0,"WIN",IF(I95&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I95" s="25" t="str">
+      <c r="I95" s="31" t="str">
         <f aca="false">IF(OR(G95="",C95=""),"",ROUND((G95-D95)/(D95-E95),2))</f>
         <v/>
       </c>
-      <c r="J95" s="26" t="str">
+      <c r="J95" s="32" t="str">
         <f aca="false">IF(I95="","",ROUND(I95*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K95" s="6"/>
-      <c r="L95" s="27"/>
+      <c r="L95" s="26"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="24"/>
+      <c r="A96" s="30"/>
       <c r="B96" s="6"/>
       <c r="C96" s="8" t="str">
         <f aca="false">IF(OR(D96="",E96="",D96=E96),"",IF(E96&lt;D96,"BUY","SELL"))</f>
@@ -4115,19 +5046,19 @@
         <f aca="false">IF(I96="","",IF(I96&gt;0,"WIN",IF(I96&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I96" s="25" t="str">
+      <c r="I96" s="31" t="str">
         <f aca="false">IF(OR(G96="",C96=""),"",ROUND((G96-D96)/(D96-E96),2))</f>
         <v/>
       </c>
-      <c r="J96" s="26" t="str">
+      <c r="J96" s="32" t="str">
         <f aca="false">IF(I96="","",ROUND(I96*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K96" s="6"/>
-      <c r="L96" s="27"/>
+      <c r="L96" s="26"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="24"/>
+      <c r="A97" s="30"/>
       <c r="B97" s="6"/>
       <c r="C97" s="8" t="str">
         <f aca="false">IF(OR(D97="",E97="",D97=E97),"",IF(E97&lt;D97,"BUY","SELL"))</f>
@@ -4144,19 +5075,19 @@
         <f aca="false">IF(I97="","",IF(I97&gt;0,"WIN",IF(I97&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I97" s="25" t="str">
+      <c r="I97" s="31" t="str">
         <f aca="false">IF(OR(G97="",C97=""),"",ROUND((G97-D97)/(D97-E97),2))</f>
         <v/>
       </c>
-      <c r="J97" s="26" t="str">
+      <c r="J97" s="32" t="str">
         <f aca="false">IF(I97="","",ROUND(I97*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K97" s="6"/>
-      <c r="L97" s="27"/>
+      <c r="L97" s="26"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="24"/>
+      <c r="A98" s="30"/>
       <c r="B98" s="6"/>
       <c r="C98" s="8" t="str">
         <f aca="false">IF(OR(D98="",E98="",D98=E98),"",IF(E98&lt;D98,"BUY","SELL"))</f>
@@ -4173,19 +5104,19 @@
         <f aca="false">IF(I98="","",IF(I98&gt;0,"WIN",IF(I98&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I98" s="25" t="str">
+      <c r="I98" s="31" t="str">
         <f aca="false">IF(OR(G98="",C98=""),"",ROUND((G98-D98)/(D98-E98),2))</f>
         <v/>
       </c>
-      <c r="J98" s="26" t="str">
+      <c r="J98" s="32" t="str">
         <f aca="false">IF(I98="","",ROUND(I98*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K98" s="6"/>
-      <c r="L98" s="27"/>
+      <c r="L98" s="26"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="24"/>
+      <c r="A99" s="30"/>
       <c r="B99" s="6"/>
       <c r="C99" s="8" t="str">
         <f aca="false">IF(OR(D99="",E99="",D99=E99),"",IF(E99&lt;D99,"BUY","SELL"))</f>
@@ -4202,19 +5133,19 @@
         <f aca="false">IF(I99="","",IF(I99&gt;0,"WIN",IF(I99&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I99" s="25" t="str">
+      <c r="I99" s="31" t="str">
         <f aca="false">IF(OR(G99="",C99=""),"",ROUND((G99-D99)/(D99-E99),2))</f>
         <v/>
       </c>
-      <c r="J99" s="26" t="str">
+      <c r="J99" s="32" t="str">
         <f aca="false">IF(I99="","",ROUND(I99*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K99" s="6"/>
-      <c r="L99" s="27"/>
+      <c r="L99" s="26"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="24"/>
+      <c r="A100" s="30"/>
       <c r="B100" s="6"/>
       <c r="C100" s="8" t="str">
         <f aca="false">IF(OR(D100="",E100="",D100=E100),"",IF(E100&lt;D100,"BUY","SELL"))</f>
@@ -4231,19 +5162,19 @@
         <f aca="false">IF(I100="","",IF(I100&gt;0,"WIN",IF(I100&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I100" s="25" t="str">
+      <c r="I100" s="31" t="str">
         <f aca="false">IF(OR(G100="",C100=""),"",ROUND((G100-D100)/(D100-E100),2))</f>
         <v/>
       </c>
-      <c r="J100" s="26" t="str">
+      <c r="J100" s="32" t="str">
         <f aca="false">IF(I100="","",ROUND(I100*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K100" s="6"/>
-      <c r="L100" s="27"/>
+      <c r="L100" s="26"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="24"/>
+      <c r="A101" s="30"/>
       <c r="B101" s="6"/>
       <c r="C101" s="8" t="str">
         <f aca="false">IF(OR(D101="",E101="",D101=E101),"",IF(E101&lt;D101,"BUY","SELL"))</f>
@@ -4260,19 +5191,19 @@
         <f aca="false">IF(I101="","",IF(I101&gt;0,"WIN",IF(I101&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I101" s="25" t="str">
+      <c r="I101" s="31" t="str">
         <f aca="false">IF(OR(G101="",C101=""),"",ROUND((G101-D101)/(D101-E101),2))</f>
         <v/>
       </c>
-      <c r="J101" s="26" t="str">
+      <c r="J101" s="32" t="str">
         <f aca="false">IF(I101="","",ROUND(I101*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K101" s="6"/>
-      <c r="L101" s="27"/>
+      <c r="L101" s="26"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="24"/>
+      <c r="A102" s="30"/>
       <c r="B102" s="6"/>
       <c r="C102" s="8" t="str">
         <f aca="false">IF(OR(D102="",E102="",D102=E102),"",IF(E102&lt;D102,"BUY","SELL"))</f>
@@ -4289,19 +5220,19 @@
         <f aca="false">IF(I102="","",IF(I102&gt;0,"WIN",IF(I102&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I102" s="25" t="str">
+      <c r="I102" s="31" t="str">
         <f aca="false">IF(OR(G102="",C102=""),"",ROUND((G102-D102)/(D102-E102),2))</f>
         <v/>
       </c>
-      <c r="J102" s="26" t="str">
+      <c r="J102" s="32" t="str">
         <f aca="false">IF(I102="","",ROUND(I102*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K102" s="6"/>
-      <c r="L102" s="27"/>
+      <c r="L102" s="26"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="24"/>
+      <c r="A103" s="30"/>
       <c r="B103" s="6"/>
       <c r="C103" s="8" t="str">
         <f aca="false">IF(OR(D103="",E103="",D103=E103),"",IF(E103&lt;D103,"BUY","SELL"))</f>
@@ -4318,19 +5249,19 @@
         <f aca="false">IF(I103="","",IF(I103&gt;0,"WIN",IF(I103&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I103" s="25" t="str">
+      <c r="I103" s="31" t="str">
         <f aca="false">IF(OR(G103="",C103=""),"",ROUND((G103-D103)/(D103-E103),2))</f>
         <v/>
       </c>
-      <c r="J103" s="26" t="str">
+      <c r="J103" s="32" t="str">
         <f aca="false">IF(I103="","",ROUND(I103*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K103" s="6"/>
-      <c r="L103" s="27"/>
+      <c r="L103" s="26"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="24"/>
+      <c r="A104" s="30"/>
       <c r="B104" s="6"/>
       <c r="C104" s="8" t="str">
         <f aca="false">IF(OR(D104="",E104="",D104=E104),"",IF(E104&lt;D104,"BUY","SELL"))</f>
@@ -4347,19 +5278,19 @@
         <f aca="false">IF(I104="","",IF(I104&gt;0,"WIN",IF(I104&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I104" s="25" t="str">
+      <c r="I104" s="31" t="str">
         <f aca="false">IF(OR(G104="",C104=""),"",ROUND((G104-D104)/(D104-E104),2))</f>
         <v/>
       </c>
-      <c r="J104" s="26" t="str">
+      <c r="J104" s="32" t="str">
         <f aca="false">IF(I104="","",ROUND(I104*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K104" s="6"/>
-      <c r="L104" s="27"/>
+      <c r="L104" s="26"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="24"/>
+      <c r="A105" s="30"/>
       <c r="B105" s="6"/>
       <c r="C105" s="8" t="str">
         <f aca="false">IF(OR(D105="",E105="",D105=E105),"",IF(E105&lt;D105,"BUY","SELL"))</f>
@@ -4376,19 +5307,19 @@
         <f aca="false">IF(I105="","",IF(I105&gt;0,"WIN",IF(I105&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I105" s="25" t="str">
+      <c r="I105" s="31" t="str">
         <f aca="false">IF(OR(G105="",C105=""),"",ROUND((G105-D105)/(D105-E105),2))</f>
         <v/>
       </c>
-      <c r="J105" s="26" t="str">
+      <c r="J105" s="32" t="str">
         <f aca="false">IF(I105="","",ROUND(I105*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K105" s="6"/>
-      <c r="L105" s="27"/>
+      <c r="L105" s="26"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="24"/>
+      <c r="A106" s="30"/>
       <c r="B106" s="6"/>
       <c r="C106" s="8" t="str">
         <f aca="false">IF(OR(D106="",E106="",D106=E106),"",IF(E106&lt;D106,"BUY","SELL"))</f>
@@ -4405,19 +5336,19 @@
         <f aca="false">IF(I106="","",IF(I106&gt;0,"WIN",IF(I106&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I106" s="25" t="str">
+      <c r="I106" s="31" t="str">
         <f aca="false">IF(OR(G106="",C106=""),"",ROUND((G106-D106)/(D106-E106),2))</f>
         <v/>
       </c>
-      <c r="J106" s="26" t="str">
+      <c r="J106" s="32" t="str">
         <f aca="false">IF(I106="","",ROUND(I106*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K106" s="6"/>
-      <c r="L106" s="27"/>
+      <c r="L106" s="26"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="24"/>
+      <c r="A107" s="30"/>
       <c r="B107" s="6"/>
       <c r="C107" s="8" t="str">
         <f aca="false">IF(OR(D107="",E107="",D107=E107),"",IF(E107&lt;D107,"BUY","SELL"))</f>
@@ -4434,19 +5365,19 @@
         <f aca="false">IF(I107="","",IF(I107&gt;0,"WIN",IF(I107&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I107" s="25" t="str">
+      <c r="I107" s="31" t="str">
         <f aca="false">IF(OR(G107="",C107=""),"",ROUND((G107-D107)/(D107-E107),2))</f>
         <v/>
       </c>
-      <c r="J107" s="26" t="str">
+      <c r="J107" s="32" t="str">
         <f aca="false">IF(I107="","",ROUND(I107*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K107" s="6"/>
-      <c r="L107" s="27"/>
+      <c r="L107" s="26"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="24"/>
+      <c r="A108" s="30"/>
       <c r="B108" s="6"/>
       <c r="C108" s="8" t="str">
         <f aca="false">IF(OR(D108="",E108="",D108=E108),"",IF(E108&lt;D108,"BUY","SELL"))</f>
@@ -4463,19 +5394,19 @@
         <f aca="false">IF(I108="","",IF(I108&gt;0,"WIN",IF(I108&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I108" s="25" t="str">
+      <c r="I108" s="31" t="str">
         <f aca="false">IF(OR(G108="",C108=""),"",ROUND((G108-D108)/(D108-E108),2))</f>
         <v/>
       </c>
-      <c r="J108" s="26" t="str">
+      <c r="J108" s="32" t="str">
         <f aca="false">IF(I108="","",ROUND(I108*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K108" s="6"/>
-      <c r="L108" s="27"/>
+      <c r="L108" s="26"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="24"/>
+      <c r="A109" s="30"/>
       <c r="B109" s="6"/>
       <c r="C109" s="8" t="str">
         <f aca="false">IF(OR(D109="",E109="",D109=E109),"",IF(E109&lt;D109,"BUY","SELL"))</f>
@@ -4492,19 +5423,19 @@
         <f aca="false">IF(I109="","",IF(I109&gt;0,"WIN",IF(I109&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I109" s="25" t="str">
+      <c r="I109" s="31" t="str">
         <f aca="false">IF(OR(G109="",C109=""),"",ROUND((G109-D109)/(D109-E109),2))</f>
         <v/>
       </c>
-      <c r="J109" s="26" t="str">
+      <c r="J109" s="32" t="str">
         <f aca="false">IF(I109="","",ROUND(I109*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K109" s="6"/>
-      <c r="L109" s="27"/>
+      <c r="L109" s="26"/>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="24"/>
+      <c r="A110" s="30"/>
       <c r="B110" s="6"/>
       <c r="C110" s="8" t="str">
         <f aca="false">IF(OR(D110="",E110="",D110=E110),"",IF(E110&lt;D110,"BUY","SELL"))</f>
@@ -4521,19 +5452,19 @@
         <f aca="false">IF(I110="","",IF(I110&gt;0,"WIN",IF(I110&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I110" s="25" t="str">
+      <c r="I110" s="31" t="str">
         <f aca="false">IF(OR(G110="",C110=""),"",ROUND((G110-D110)/(D110-E110),2))</f>
         <v/>
       </c>
-      <c r="J110" s="26" t="str">
+      <c r="J110" s="32" t="str">
         <f aca="false">IF(I110="","",ROUND(I110*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K110" s="6"/>
-      <c r="L110" s="27"/>
+      <c r="L110" s="26"/>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="24"/>
+      <c r="A111" s="30"/>
       <c r="B111" s="6"/>
       <c r="C111" s="8" t="str">
         <f aca="false">IF(OR(D111="",E111="",D111=E111),"",IF(E111&lt;D111,"BUY","SELL"))</f>
@@ -4550,19 +5481,19 @@
         <f aca="false">IF(I111="","",IF(I111&gt;0,"WIN",IF(I111&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I111" s="25" t="str">
+      <c r="I111" s="31" t="str">
         <f aca="false">IF(OR(G111="",C111=""),"",ROUND((G111-D111)/(D111-E111),2))</f>
         <v/>
       </c>
-      <c r="J111" s="26" t="str">
+      <c r="J111" s="32" t="str">
         <f aca="false">IF(I111="","",ROUND(I111*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K111" s="6"/>
-      <c r="L111" s="27"/>
+      <c r="L111" s="26"/>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="24"/>
+      <c r="A112" s="30"/>
       <c r="B112" s="6"/>
       <c r="C112" s="8" t="str">
         <f aca="false">IF(OR(D112="",E112="",D112=E112),"",IF(E112&lt;D112,"BUY","SELL"))</f>
@@ -4579,19 +5510,19 @@
         <f aca="false">IF(I112="","",IF(I112&gt;0,"WIN",IF(I112&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I112" s="25" t="str">
+      <c r="I112" s="31" t="str">
         <f aca="false">IF(OR(G112="",C112=""),"",ROUND((G112-D112)/(D112-E112),2))</f>
         <v/>
       </c>
-      <c r="J112" s="26" t="str">
+      <c r="J112" s="32" t="str">
         <f aca="false">IF(I112="","",ROUND(I112*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K112" s="6"/>
-      <c r="L112" s="27"/>
+      <c r="L112" s="26"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="24"/>
+      <c r="A113" s="30"/>
       <c r="B113" s="6"/>
       <c r="C113" s="8" t="str">
         <f aca="false">IF(OR(D113="",E113="",D113=E113),"",IF(E113&lt;D113,"BUY","SELL"))</f>
@@ -4608,19 +5539,19 @@
         <f aca="false">IF(I113="","",IF(I113&gt;0,"WIN",IF(I113&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I113" s="25" t="str">
+      <c r="I113" s="31" t="str">
         <f aca="false">IF(OR(G113="",C113=""),"",ROUND((G113-D113)/(D113-E113),2))</f>
         <v/>
       </c>
-      <c r="J113" s="26" t="str">
+      <c r="J113" s="32" t="str">
         <f aca="false">IF(I113="","",ROUND(I113*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K113" s="6"/>
-      <c r="L113" s="27"/>
+      <c r="L113" s="26"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="24"/>
+      <c r="A114" s="30"/>
       <c r="B114" s="6"/>
       <c r="C114" s="8" t="str">
         <f aca="false">IF(OR(D114="",E114="",D114=E114),"",IF(E114&lt;D114,"BUY","SELL"))</f>
@@ -4637,19 +5568,19 @@
         <f aca="false">IF(I114="","",IF(I114&gt;0,"WIN",IF(I114&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I114" s="25" t="str">
+      <c r="I114" s="31" t="str">
         <f aca="false">IF(OR(G114="",C114=""),"",ROUND((G114-D114)/(D114-E114),2))</f>
         <v/>
       </c>
-      <c r="J114" s="26" t="str">
+      <c r="J114" s="32" t="str">
         <f aca="false">IF(I114="","",ROUND(I114*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K114" s="6"/>
-      <c r="L114" s="27"/>
+      <c r="L114" s="26"/>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="24"/>
+      <c r="A115" s="30"/>
       <c r="B115" s="6"/>
       <c r="C115" s="8" t="str">
         <f aca="false">IF(OR(D115="",E115="",D115=E115),"",IF(E115&lt;D115,"BUY","SELL"))</f>
@@ -4666,19 +5597,19 @@
         <f aca="false">IF(I115="","",IF(I115&gt;0,"WIN",IF(I115&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I115" s="25" t="str">
+      <c r="I115" s="31" t="str">
         <f aca="false">IF(OR(G115="",C115=""),"",ROUND((G115-D115)/(D115-E115),2))</f>
         <v/>
       </c>
-      <c r="J115" s="26" t="str">
+      <c r="J115" s="32" t="str">
         <f aca="false">IF(I115="","",ROUND(I115*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K115" s="6"/>
-      <c r="L115" s="27"/>
+      <c r="L115" s="26"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="24"/>
+      <c r="A116" s="30"/>
       <c r="B116" s="6"/>
       <c r="C116" s="8" t="str">
         <f aca="false">IF(OR(D116="",E116="",D116=E116),"",IF(E116&lt;D116,"BUY","SELL"))</f>
@@ -4695,19 +5626,19 @@
         <f aca="false">IF(I116="","",IF(I116&gt;0,"WIN",IF(I116&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I116" s="25" t="str">
+      <c r="I116" s="31" t="str">
         <f aca="false">IF(OR(G116="",C116=""),"",ROUND((G116-D116)/(D116-E116),2))</f>
         <v/>
       </c>
-      <c r="J116" s="26" t="str">
+      <c r="J116" s="32" t="str">
         <f aca="false">IF(I116="","",ROUND(I116*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K116" s="6"/>
-      <c r="L116" s="27"/>
+      <c r="L116" s="26"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="24"/>
+      <c r="A117" s="30"/>
       <c r="B117" s="6"/>
       <c r="C117" s="8" t="str">
         <f aca="false">IF(OR(D117="",E117="",D117=E117),"",IF(E117&lt;D117,"BUY","SELL"))</f>
@@ -4724,19 +5655,19 @@
         <f aca="false">IF(I117="","",IF(I117&gt;0,"WIN",IF(I117&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I117" s="25" t="str">
+      <c r="I117" s="31" t="str">
         <f aca="false">IF(OR(G117="",C117=""),"",ROUND((G117-D117)/(D117-E117),2))</f>
         <v/>
       </c>
-      <c r="J117" s="26" t="str">
+      <c r="J117" s="32" t="str">
         <f aca="false">IF(I117="","",ROUND(I117*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K117" s="6"/>
-      <c r="L117" s="27"/>
+      <c r="L117" s="26"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="24"/>
+      <c r="A118" s="30"/>
       <c r="B118" s="6"/>
       <c r="C118" s="8" t="str">
         <f aca="false">IF(OR(D118="",E118="",D118=E118),"",IF(E118&lt;D118,"BUY","SELL"))</f>
@@ -4753,19 +5684,19 @@
         <f aca="false">IF(I118="","",IF(I118&gt;0,"WIN",IF(I118&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I118" s="25" t="str">
+      <c r="I118" s="31" t="str">
         <f aca="false">IF(OR(G118="",C118=""),"",ROUND((G118-D118)/(D118-E118),2))</f>
         <v/>
       </c>
-      <c r="J118" s="26" t="str">
+      <c r="J118" s="32" t="str">
         <f aca="false">IF(I118="","",ROUND(I118*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K118" s="6"/>
-      <c r="L118" s="27"/>
+      <c r="L118" s="26"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="24"/>
+      <c r="A119" s="30"/>
       <c r="B119" s="6"/>
       <c r="C119" s="8" t="str">
         <f aca="false">IF(OR(D119="",E119="",D119=E119),"",IF(E119&lt;D119,"BUY","SELL"))</f>
@@ -4782,19 +5713,19 @@
         <f aca="false">IF(I119="","",IF(I119&gt;0,"WIN",IF(I119&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I119" s="25" t="str">
+      <c r="I119" s="31" t="str">
         <f aca="false">IF(OR(G119="",C119=""),"",ROUND((G119-D119)/(D119-E119),2))</f>
         <v/>
       </c>
-      <c r="J119" s="26" t="str">
+      <c r="J119" s="32" t="str">
         <f aca="false">IF(I119="","",ROUND(I119*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K119" s="6"/>
-      <c r="L119" s="27"/>
+      <c r="L119" s="26"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="24"/>
+      <c r="A120" s="30"/>
       <c r="B120" s="6"/>
       <c r="C120" s="8" t="str">
         <f aca="false">IF(OR(D120="",E120="",D120=E120),"",IF(E120&lt;D120,"BUY","SELL"))</f>
@@ -4811,19 +5742,19 @@
         <f aca="false">IF(I120="","",IF(I120&gt;0,"WIN",IF(I120&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I120" s="25" t="str">
+      <c r="I120" s="31" t="str">
         <f aca="false">IF(OR(G120="",C120=""),"",ROUND((G120-D120)/(D120-E120),2))</f>
         <v/>
       </c>
-      <c r="J120" s="26" t="str">
+      <c r="J120" s="32" t="str">
         <f aca="false">IF(I120="","",ROUND(I120*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K120" s="6"/>
-      <c r="L120" s="27"/>
+      <c r="L120" s="26"/>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="24"/>
+      <c r="A121" s="30"/>
       <c r="B121" s="6"/>
       <c r="C121" s="8" t="str">
         <f aca="false">IF(OR(D121="",E121="",D121=E121),"",IF(E121&lt;D121,"BUY","SELL"))</f>
@@ -4840,19 +5771,19 @@
         <f aca="false">IF(I121="","",IF(I121&gt;0,"WIN",IF(I121&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I121" s="25" t="str">
+      <c r="I121" s="31" t="str">
         <f aca="false">IF(OR(G121="",C121=""),"",ROUND((G121-D121)/(D121-E121),2))</f>
         <v/>
       </c>
-      <c r="J121" s="26" t="str">
+      <c r="J121" s="32" t="str">
         <f aca="false">IF(I121="","",ROUND(I121*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K121" s="6"/>
-      <c r="L121" s="27"/>
+      <c r="L121" s="26"/>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="24"/>
+      <c r="A122" s="30"/>
       <c r="B122" s="6"/>
       <c r="C122" s="8" t="str">
         <f aca="false">IF(OR(D122="",E122="",D122=E122),"",IF(E122&lt;D122,"BUY","SELL"))</f>
@@ -4869,19 +5800,19 @@
         <f aca="false">IF(I122="","",IF(I122&gt;0,"WIN",IF(I122&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I122" s="25" t="str">
+      <c r="I122" s="31" t="str">
         <f aca="false">IF(OR(G122="",C122=""),"",ROUND((G122-D122)/(D122-E122),2))</f>
         <v/>
       </c>
-      <c r="J122" s="26" t="str">
+      <c r="J122" s="32" t="str">
         <f aca="false">IF(I122="","",ROUND(I122*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K122" s="6"/>
-      <c r="L122" s="27"/>
+      <c r="L122" s="26"/>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="24"/>
+      <c r="A123" s="30"/>
       <c r="B123" s="6"/>
       <c r="C123" s="8" t="str">
         <f aca="false">IF(OR(D123="",E123="",D123=E123),"",IF(E123&lt;D123,"BUY","SELL"))</f>
@@ -4898,19 +5829,19 @@
         <f aca="false">IF(I123="","",IF(I123&gt;0,"WIN",IF(I123&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I123" s="25" t="str">
+      <c r="I123" s="31" t="str">
         <f aca="false">IF(OR(G123="",C123=""),"",ROUND((G123-D123)/(D123-E123),2))</f>
         <v/>
       </c>
-      <c r="J123" s="26" t="str">
+      <c r="J123" s="32" t="str">
         <f aca="false">IF(I123="","",ROUND(I123*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K123" s="6"/>
-      <c r="L123" s="27"/>
+      <c r="L123" s="26"/>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="24"/>
+      <c r="A124" s="30"/>
       <c r="B124" s="6"/>
       <c r="C124" s="8" t="str">
         <f aca="false">IF(OR(D124="",E124="",D124=E124),"",IF(E124&lt;D124,"BUY","SELL"))</f>
@@ -4927,19 +5858,19 @@
         <f aca="false">IF(I124="","",IF(I124&gt;0,"WIN",IF(I124&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I124" s="25" t="str">
+      <c r="I124" s="31" t="str">
         <f aca="false">IF(OR(G124="",C124=""),"",ROUND((G124-D124)/(D124-E124),2))</f>
         <v/>
       </c>
-      <c r="J124" s="26" t="str">
+      <c r="J124" s="32" t="str">
         <f aca="false">IF(I124="","",ROUND(I124*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K124" s="6"/>
-      <c r="L124" s="27"/>
+      <c r="L124" s="26"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="24"/>
+      <c r="A125" s="30"/>
       <c r="B125" s="6"/>
       <c r="C125" s="8" t="str">
         <f aca="false">IF(OR(D125="",E125="",D125=E125),"",IF(E125&lt;D125,"BUY","SELL"))</f>
@@ -4956,19 +5887,19 @@
         <f aca="false">IF(I125="","",IF(I125&gt;0,"WIN",IF(I125&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I125" s="25" t="str">
+      <c r="I125" s="31" t="str">
         <f aca="false">IF(OR(G125="",C125=""),"",ROUND((G125-D125)/(D125-E125),2))</f>
         <v/>
       </c>
-      <c r="J125" s="26" t="str">
+      <c r="J125" s="32" t="str">
         <f aca="false">IF(I125="","",ROUND(I125*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K125" s="6"/>
-      <c r="L125" s="27"/>
+      <c r="L125" s="26"/>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="24"/>
+      <c r="A126" s="30"/>
       <c r="B126" s="6"/>
       <c r="C126" s="8" t="str">
         <f aca="false">IF(OR(D126="",E126="",D126=E126),"",IF(E126&lt;D126,"BUY","SELL"))</f>
@@ -4985,19 +5916,19 @@
         <f aca="false">IF(I126="","",IF(I126&gt;0,"WIN",IF(I126&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I126" s="25" t="str">
+      <c r="I126" s="31" t="str">
         <f aca="false">IF(OR(G126="",C126=""),"",ROUND((G126-D126)/(D126-E126),2))</f>
         <v/>
       </c>
-      <c r="J126" s="26" t="str">
+      <c r="J126" s="32" t="str">
         <f aca="false">IF(I126="","",ROUND(I126*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K126" s="6"/>
-      <c r="L126" s="27"/>
+      <c r="L126" s="26"/>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="24"/>
+      <c r="A127" s="30"/>
       <c r="B127" s="6"/>
       <c r="C127" s="8" t="str">
         <f aca="false">IF(OR(D127="",E127="",D127=E127),"",IF(E127&lt;D127,"BUY","SELL"))</f>
@@ -5014,19 +5945,19 @@
         <f aca="false">IF(I127="","",IF(I127&gt;0,"WIN",IF(I127&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I127" s="25" t="str">
+      <c r="I127" s="31" t="str">
         <f aca="false">IF(OR(G127="",C127=""),"",ROUND((G127-D127)/(D127-E127),2))</f>
         <v/>
       </c>
-      <c r="J127" s="26" t="str">
+      <c r="J127" s="32" t="str">
         <f aca="false">IF(I127="","",ROUND(I127*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K127" s="6"/>
-      <c r="L127" s="27"/>
+      <c r="L127" s="26"/>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="24"/>
+      <c r="A128" s="30"/>
       <c r="B128" s="6"/>
       <c r="C128" s="8" t="str">
         <f aca="false">IF(OR(D128="",E128="",D128=E128),"",IF(E128&lt;D128,"BUY","SELL"))</f>
@@ -5043,19 +5974,19 @@
         <f aca="false">IF(I128="","",IF(I128&gt;0,"WIN",IF(I128&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I128" s="25" t="str">
+      <c r="I128" s="31" t="str">
         <f aca="false">IF(OR(G128="",C128=""),"",ROUND((G128-D128)/(D128-E128),2))</f>
         <v/>
       </c>
-      <c r="J128" s="26" t="str">
+      <c r="J128" s="32" t="str">
         <f aca="false">IF(I128="","",ROUND(I128*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K128" s="6"/>
-      <c r="L128" s="27"/>
+      <c r="L128" s="26"/>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="24"/>
+      <c r="A129" s="30"/>
       <c r="B129" s="6"/>
       <c r="C129" s="8" t="str">
         <f aca="false">IF(OR(D129="",E129="",D129=E129),"",IF(E129&lt;D129,"BUY","SELL"))</f>
@@ -5072,19 +6003,19 @@
         <f aca="false">IF(I129="","",IF(I129&gt;0,"WIN",IF(I129&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I129" s="25" t="str">
+      <c r="I129" s="31" t="str">
         <f aca="false">IF(OR(G129="",C129=""),"",ROUND((G129-D129)/(D129-E129),2))</f>
         <v/>
       </c>
-      <c r="J129" s="26" t="str">
+      <c r="J129" s="32" t="str">
         <f aca="false">IF(I129="","",ROUND(I129*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K129" s="6"/>
-      <c r="L129" s="27"/>
+      <c r="L129" s="26"/>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="24"/>
+      <c r="A130" s="30"/>
       <c r="B130" s="6"/>
       <c r="C130" s="8" t="str">
         <f aca="false">IF(OR(D130="",E130="",D130=E130),"",IF(E130&lt;D130,"BUY","SELL"))</f>
@@ -5101,19 +6032,19 @@
         <f aca="false">IF(I130="","",IF(I130&gt;0,"WIN",IF(I130&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I130" s="25" t="str">
+      <c r="I130" s="31" t="str">
         <f aca="false">IF(OR(G130="",C130=""),"",ROUND((G130-D130)/(D130-E130),2))</f>
         <v/>
       </c>
-      <c r="J130" s="26" t="str">
+      <c r="J130" s="32" t="str">
         <f aca="false">IF(I130="","",ROUND(I130*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K130" s="6"/>
-      <c r="L130" s="27"/>
+      <c r="L130" s="26"/>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="24"/>
+      <c r="A131" s="30"/>
       <c r="B131" s="6"/>
       <c r="C131" s="8" t="str">
         <f aca="false">IF(OR(D131="",E131="",D131=E131),"",IF(E131&lt;D131,"BUY","SELL"))</f>
@@ -5130,19 +6061,19 @@
         <f aca="false">IF(I131="","",IF(I131&gt;0,"WIN",IF(I131&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I131" s="25" t="str">
+      <c r="I131" s="31" t="str">
         <f aca="false">IF(OR(G131="",C131=""),"",ROUND((G131-D131)/(D131-E131),2))</f>
         <v/>
       </c>
-      <c r="J131" s="26" t="str">
+      <c r="J131" s="32" t="str">
         <f aca="false">IF(I131="","",ROUND(I131*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K131" s="6"/>
-      <c r="L131" s="27"/>
+      <c r="L131" s="26"/>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="24"/>
+      <c r="A132" s="30"/>
       <c r="B132" s="6"/>
       <c r="C132" s="8" t="str">
         <f aca="false">IF(OR(D132="",E132="",D132=E132),"",IF(E132&lt;D132,"BUY","SELL"))</f>
@@ -5159,19 +6090,19 @@
         <f aca="false">IF(I132="","",IF(I132&gt;0,"WIN",IF(I132&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I132" s="25" t="str">
+      <c r="I132" s="31" t="str">
         <f aca="false">IF(OR(G132="",C132=""),"",ROUND((G132-D132)/(D132-E132),2))</f>
         <v/>
       </c>
-      <c r="J132" s="26" t="str">
+      <c r="J132" s="32" t="str">
         <f aca="false">IF(I132="","",ROUND(I132*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K132" s="6"/>
-      <c r="L132" s="27"/>
+      <c r="L132" s="26"/>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="24"/>
+      <c r="A133" s="30"/>
       <c r="B133" s="6"/>
       <c r="C133" s="8" t="str">
         <f aca="false">IF(OR(D133="",E133="",D133=E133),"",IF(E133&lt;D133,"BUY","SELL"))</f>
@@ -5188,19 +6119,19 @@
         <f aca="false">IF(I133="","",IF(I133&gt;0,"WIN",IF(I133&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I133" s="25" t="str">
+      <c r="I133" s="31" t="str">
         <f aca="false">IF(OR(G133="",C133=""),"",ROUND((G133-D133)/(D133-E133),2))</f>
         <v/>
       </c>
-      <c r="J133" s="26" t="str">
+      <c r="J133" s="32" t="str">
         <f aca="false">IF(I133="","",ROUND(I133*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K133" s="6"/>
-      <c r="L133" s="27"/>
+      <c r="L133" s="26"/>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="24"/>
+      <c r="A134" s="30"/>
       <c r="B134" s="6"/>
       <c r="C134" s="8" t="str">
         <f aca="false">IF(OR(D134="",E134="",D134=E134),"",IF(E134&lt;D134,"BUY","SELL"))</f>
@@ -5217,19 +6148,19 @@
         <f aca="false">IF(I134="","",IF(I134&gt;0,"WIN",IF(I134&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I134" s="25" t="str">
+      <c r="I134" s="31" t="str">
         <f aca="false">IF(OR(G134="",C134=""),"",ROUND((G134-D134)/(D134-E134),2))</f>
         <v/>
       </c>
-      <c r="J134" s="26" t="str">
+      <c r="J134" s="32" t="str">
         <f aca="false">IF(I134="","",ROUND(I134*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K134" s="6"/>
-      <c r="L134" s="27"/>
+      <c r="L134" s="26"/>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="24"/>
+      <c r="A135" s="30"/>
       <c r="B135" s="6"/>
       <c r="C135" s="8" t="str">
         <f aca="false">IF(OR(D135="",E135="",D135=E135),"",IF(E135&lt;D135,"BUY","SELL"))</f>
@@ -5246,19 +6177,19 @@
         <f aca="false">IF(I135="","",IF(I135&gt;0,"WIN",IF(I135&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I135" s="25" t="str">
+      <c r="I135" s="31" t="str">
         <f aca="false">IF(OR(G135="",C135=""),"",ROUND((G135-D135)/(D135-E135),2))</f>
         <v/>
       </c>
-      <c r="J135" s="26" t="str">
+      <c r="J135" s="32" t="str">
         <f aca="false">IF(I135="","",ROUND(I135*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K135" s="6"/>
-      <c r="L135" s="27"/>
+      <c r="L135" s="26"/>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="24"/>
+      <c r="A136" s="30"/>
       <c r="B136" s="6"/>
       <c r="C136" s="8" t="str">
         <f aca="false">IF(OR(D136="",E136="",D136=E136),"",IF(E136&lt;D136,"BUY","SELL"))</f>
@@ -5275,19 +6206,19 @@
         <f aca="false">IF(I136="","",IF(I136&gt;0,"WIN",IF(I136&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I136" s="25" t="str">
+      <c r="I136" s="31" t="str">
         <f aca="false">IF(OR(G136="",C136=""),"",ROUND((G136-D136)/(D136-E136),2))</f>
         <v/>
       </c>
-      <c r="J136" s="26" t="str">
+      <c r="J136" s="32" t="str">
         <f aca="false">IF(I136="","",ROUND(I136*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K136" s="6"/>
-      <c r="L136" s="27"/>
+      <c r="L136" s="26"/>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="24"/>
+      <c r="A137" s="30"/>
       <c r="B137" s="6"/>
       <c r="C137" s="8" t="str">
         <f aca="false">IF(OR(D137="",E137="",D137=E137),"",IF(E137&lt;D137,"BUY","SELL"))</f>
@@ -5304,19 +6235,19 @@
         <f aca="false">IF(I137="","",IF(I137&gt;0,"WIN",IF(I137&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I137" s="25" t="str">
+      <c r="I137" s="31" t="str">
         <f aca="false">IF(OR(G137="",C137=""),"",ROUND((G137-D137)/(D137-E137),2))</f>
         <v/>
       </c>
-      <c r="J137" s="26" t="str">
+      <c r="J137" s="32" t="str">
         <f aca="false">IF(I137="","",ROUND(I137*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K137" s="6"/>
-      <c r="L137" s="27"/>
+      <c r="L137" s="26"/>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="24"/>
+      <c r="A138" s="30"/>
       <c r="B138" s="6"/>
       <c r="C138" s="8" t="str">
         <f aca="false">IF(OR(D138="",E138="",D138=E138),"",IF(E138&lt;D138,"BUY","SELL"))</f>
@@ -5333,19 +6264,19 @@
         <f aca="false">IF(I138="","",IF(I138&gt;0,"WIN",IF(I138&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I138" s="25" t="str">
+      <c r="I138" s="31" t="str">
         <f aca="false">IF(OR(G138="",C138=""),"",ROUND((G138-D138)/(D138-E138),2))</f>
         <v/>
       </c>
-      <c r="J138" s="26" t="str">
+      <c r="J138" s="32" t="str">
         <f aca="false">IF(I138="","",ROUND(I138*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K138" s="6"/>
-      <c r="L138" s="27"/>
+      <c r="L138" s="26"/>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="24"/>
+      <c r="A139" s="30"/>
       <c r="B139" s="6"/>
       <c r="C139" s="8" t="str">
         <f aca="false">IF(OR(D139="",E139="",D139=E139),"",IF(E139&lt;D139,"BUY","SELL"))</f>
@@ -5362,19 +6293,19 @@
         <f aca="false">IF(I139="","",IF(I139&gt;0,"WIN",IF(I139&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I139" s="25" t="str">
+      <c r="I139" s="31" t="str">
         <f aca="false">IF(OR(G139="",C139=""),"",ROUND((G139-D139)/(D139-E139),2))</f>
         <v/>
       </c>
-      <c r="J139" s="26" t="str">
+      <c r="J139" s="32" t="str">
         <f aca="false">IF(I139="","",ROUND(I139*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K139" s="6"/>
-      <c r="L139" s="27"/>
+      <c r="L139" s="26"/>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="24"/>
+      <c r="A140" s="30"/>
       <c r="B140" s="6"/>
       <c r="C140" s="8" t="str">
         <f aca="false">IF(OR(D140="",E140="",D140=E140),"",IF(E140&lt;D140,"BUY","SELL"))</f>
@@ -5391,19 +6322,19 @@
         <f aca="false">IF(I140="","",IF(I140&gt;0,"WIN",IF(I140&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I140" s="25" t="str">
+      <c r="I140" s="31" t="str">
         <f aca="false">IF(OR(G140="",C140=""),"",ROUND((G140-D140)/(D140-E140),2))</f>
         <v/>
       </c>
-      <c r="J140" s="26" t="str">
+      <c r="J140" s="32" t="str">
         <f aca="false">IF(I140="","",ROUND(I140*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K140" s="6"/>
-      <c r="L140" s="27"/>
+      <c r="L140" s="26"/>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="24"/>
+      <c r="A141" s="30"/>
       <c r="B141" s="6"/>
       <c r="C141" s="8" t="str">
         <f aca="false">IF(OR(D141="",E141="",D141=E141),"",IF(E141&lt;D141,"BUY","SELL"))</f>
@@ -5420,19 +6351,19 @@
         <f aca="false">IF(I141="","",IF(I141&gt;0,"WIN",IF(I141&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I141" s="25" t="str">
+      <c r="I141" s="31" t="str">
         <f aca="false">IF(OR(G141="",C141=""),"",ROUND((G141-D141)/(D141-E141),2))</f>
         <v/>
       </c>
-      <c r="J141" s="26" t="str">
+      <c r="J141" s="32" t="str">
         <f aca="false">IF(I141="","",ROUND(I141*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K141" s="6"/>
-      <c r="L141" s="27"/>
+      <c r="L141" s="26"/>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="24"/>
+      <c r="A142" s="30"/>
       <c r="B142" s="6"/>
       <c r="C142" s="8" t="str">
         <f aca="false">IF(OR(D142="",E142="",D142=E142),"",IF(E142&lt;D142,"BUY","SELL"))</f>
@@ -5449,19 +6380,19 @@
         <f aca="false">IF(I142="","",IF(I142&gt;0,"WIN",IF(I142&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I142" s="25" t="str">
+      <c r="I142" s="31" t="str">
         <f aca="false">IF(OR(G142="",C142=""),"",ROUND((G142-D142)/(D142-E142),2))</f>
         <v/>
       </c>
-      <c r="J142" s="26" t="str">
+      <c r="J142" s="32" t="str">
         <f aca="false">IF(I142="","",ROUND(I142*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K142" s="6"/>
-      <c r="L142" s="27"/>
+      <c r="L142" s="26"/>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="24"/>
+      <c r="A143" s="30"/>
       <c r="B143" s="6"/>
       <c r="C143" s="8" t="str">
         <f aca="false">IF(OR(D143="",E143="",D143=E143),"",IF(E143&lt;D143,"BUY","SELL"))</f>
@@ -5478,19 +6409,19 @@
         <f aca="false">IF(I143="","",IF(I143&gt;0,"WIN",IF(I143&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I143" s="25" t="str">
+      <c r="I143" s="31" t="str">
         <f aca="false">IF(OR(G143="",C143=""),"",ROUND((G143-D143)/(D143-E143),2))</f>
         <v/>
       </c>
-      <c r="J143" s="26" t="str">
+      <c r="J143" s="32" t="str">
         <f aca="false">IF(I143="","",ROUND(I143*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K143" s="6"/>
-      <c r="L143" s="27"/>
+      <c r="L143" s="26"/>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="24"/>
+      <c r="A144" s="30"/>
       <c r="B144" s="6"/>
       <c r="C144" s="8" t="str">
         <f aca="false">IF(OR(D144="",E144="",D144=E144),"",IF(E144&lt;D144,"BUY","SELL"))</f>
@@ -5507,19 +6438,19 @@
         <f aca="false">IF(I144="","",IF(I144&gt;0,"WIN",IF(I144&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I144" s="25" t="str">
+      <c r="I144" s="31" t="str">
         <f aca="false">IF(OR(G144="",C144=""),"",ROUND((G144-D144)/(D144-E144),2))</f>
         <v/>
       </c>
-      <c r="J144" s="26" t="str">
+      <c r="J144" s="32" t="str">
         <f aca="false">IF(I144="","",ROUND(I144*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K144" s="6"/>
-      <c r="L144" s="27"/>
+      <c r="L144" s="26"/>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="24"/>
+      <c r="A145" s="30"/>
       <c r="B145" s="6"/>
       <c r="C145" s="8" t="str">
         <f aca="false">IF(OR(D145="",E145="",D145=E145),"",IF(E145&lt;D145,"BUY","SELL"))</f>
@@ -5536,19 +6467,19 @@
         <f aca="false">IF(I145="","",IF(I145&gt;0,"WIN",IF(I145&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I145" s="25" t="str">
+      <c r="I145" s="31" t="str">
         <f aca="false">IF(OR(G145="",C145=""),"",ROUND((G145-D145)/(D145-E145),2))</f>
         <v/>
       </c>
-      <c r="J145" s="26" t="str">
+      <c r="J145" s="32" t="str">
         <f aca="false">IF(I145="","",ROUND(I145*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K145" s="6"/>
-      <c r="L145" s="27"/>
+      <c r="L145" s="26"/>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="24"/>
+      <c r="A146" s="30"/>
       <c r="B146" s="6"/>
       <c r="C146" s="8" t="str">
         <f aca="false">IF(OR(D146="",E146="",D146=E146),"",IF(E146&lt;D146,"BUY","SELL"))</f>
@@ -5565,19 +6496,19 @@
         <f aca="false">IF(I146="","",IF(I146&gt;0,"WIN",IF(I146&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I146" s="25" t="str">
+      <c r="I146" s="31" t="str">
         <f aca="false">IF(OR(G146="",C146=""),"",ROUND((G146-D146)/(D146-E146),2))</f>
         <v/>
       </c>
-      <c r="J146" s="26" t="str">
+      <c r="J146" s="32" t="str">
         <f aca="false">IF(I146="","",ROUND(I146*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K146" s="6"/>
-      <c r="L146" s="27"/>
+      <c r="L146" s="26"/>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="24"/>
+      <c r="A147" s="30"/>
       <c r="B147" s="6"/>
       <c r="C147" s="8" t="str">
         <f aca="false">IF(OR(D147="",E147="",D147=E147),"",IF(E147&lt;D147,"BUY","SELL"))</f>
@@ -5594,19 +6525,19 @@
         <f aca="false">IF(I147="","",IF(I147&gt;0,"WIN",IF(I147&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I147" s="25" t="str">
+      <c r="I147" s="31" t="str">
         <f aca="false">IF(OR(G147="",C147=""),"",ROUND((G147-D147)/(D147-E147),2))</f>
         <v/>
       </c>
-      <c r="J147" s="26" t="str">
+      <c r="J147" s="32" t="str">
         <f aca="false">IF(I147="","",ROUND(I147*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K147" s="6"/>
-      <c r="L147" s="27"/>
+      <c r="L147" s="26"/>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="24"/>
+      <c r="A148" s="30"/>
       <c r="B148" s="6"/>
       <c r="C148" s="8" t="str">
         <f aca="false">IF(OR(D148="",E148="",D148=E148),"",IF(E148&lt;D148,"BUY","SELL"))</f>
@@ -5623,19 +6554,19 @@
         <f aca="false">IF(I148="","",IF(I148&gt;0,"WIN",IF(I148&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I148" s="25" t="str">
+      <c r="I148" s="31" t="str">
         <f aca="false">IF(OR(G148="",C148=""),"",ROUND((G148-D148)/(D148-E148),2))</f>
         <v/>
       </c>
-      <c r="J148" s="26" t="str">
+      <c r="J148" s="32" t="str">
         <f aca="false">IF(I148="","",ROUND(I148*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K148" s="6"/>
-      <c r="L148" s="27"/>
+      <c r="L148" s="26"/>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="24"/>
+      <c r="A149" s="30"/>
       <c r="B149" s="6"/>
       <c r="C149" s="8" t="str">
         <f aca="false">IF(OR(D149="",E149="",D149=E149),"",IF(E149&lt;D149,"BUY","SELL"))</f>
@@ -5652,19 +6583,19 @@
         <f aca="false">IF(I149="","",IF(I149&gt;0,"WIN",IF(I149&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I149" s="25" t="str">
+      <c r="I149" s="31" t="str">
         <f aca="false">IF(OR(G149="",C149=""),"",ROUND((G149-D149)/(D149-E149),2))</f>
         <v/>
       </c>
-      <c r="J149" s="26" t="str">
+      <c r="J149" s="32" t="str">
         <f aca="false">IF(I149="","",ROUND(I149*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K149" s="6"/>
-      <c r="L149" s="27"/>
+      <c r="L149" s="26"/>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="24"/>
+      <c r="A150" s="30"/>
       <c r="B150" s="6"/>
       <c r="C150" s="8" t="str">
         <f aca="false">IF(OR(D150="",E150="",D150=E150),"",IF(E150&lt;D150,"BUY","SELL"))</f>
@@ -5681,19 +6612,19 @@
         <f aca="false">IF(I150="","",IF(I150&gt;0,"WIN",IF(I150&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I150" s="25" t="str">
+      <c r="I150" s="31" t="str">
         <f aca="false">IF(OR(G150="",C150=""),"",ROUND((G150-D150)/(D150-E150),2))</f>
         <v/>
       </c>
-      <c r="J150" s="26" t="str">
+      <c r="J150" s="32" t="str">
         <f aca="false">IF(I150="","",ROUND(I150*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K150" s="6"/>
-      <c r="L150" s="27"/>
+      <c r="L150" s="26"/>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="24"/>
+      <c r="A151" s="30"/>
       <c r="B151" s="6"/>
       <c r="C151" s="8" t="str">
         <f aca="false">IF(OR(D151="",E151="",D151=E151),"",IF(E151&lt;D151,"BUY","SELL"))</f>
@@ -5710,19 +6641,19 @@
         <f aca="false">IF(I151="","",IF(I151&gt;0,"WIN",IF(I151&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I151" s="25" t="str">
+      <c r="I151" s="31" t="str">
         <f aca="false">IF(OR(G151="",C151=""),"",ROUND((G151-D151)/(D151-E151),2))</f>
         <v/>
       </c>
-      <c r="J151" s="26" t="str">
+      <c r="J151" s="32" t="str">
         <f aca="false">IF(I151="","",ROUND(I151*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K151" s="6"/>
-      <c r="L151" s="27"/>
+      <c r="L151" s="26"/>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="24"/>
+      <c r="A152" s="30"/>
       <c r="B152" s="6"/>
       <c r="C152" s="8" t="str">
         <f aca="false">IF(OR(D152="",E152="",D152=E152),"",IF(E152&lt;D152,"BUY","SELL"))</f>
@@ -5739,19 +6670,19 @@
         <f aca="false">IF(I152="","",IF(I152&gt;0,"WIN",IF(I152&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I152" s="25" t="str">
+      <c r="I152" s="31" t="str">
         <f aca="false">IF(OR(G152="",C152=""),"",ROUND((G152-D152)/(D152-E152),2))</f>
         <v/>
       </c>
-      <c r="J152" s="26" t="str">
+      <c r="J152" s="32" t="str">
         <f aca="false">IF(I152="","",ROUND(I152*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K152" s="6"/>
-      <c r="L152" s="27"/>
+      <c r="L152" s="26"/>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="24"/>
+      <c r="A153" s="30"/>
       <c r="B153" s="6"/>
       <c r="C153" s="8" t="str">
         <f aca="false">IF(OR(D153="",E153="",D153=E153),"",IF(E153&lt;D153,"BUY","SELL"))</f>
@@ -5768,19 +6699,19 @@
         <f aca="false">IF(I153="","",IF(I153&gt;0,"WIN",IF(I153&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I153" s="25" t="str">
+      <c r="I153" s="31" t="str">
         <f aca="false">IF(OR(G153="",C153=""),"",ROUND((G153-D153)/(D153-E153),2))</f>
         <v/>
       </c>
-      <c r="J153" s="26" t="str">
+      <c r="J153" s="32" t="str">
         <f aca="false">IF(I153="","",ROUND(I153*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K153" s="6"/>
-      <c r="L153" s="27"/>
+      <c r="L153" s="26"/>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="24"/>
+      <c r="A154" s="30"/>
       <c r="B154" s="6"/>
       <c r="C154" s="8" t="str">
         <f aca="false">IF(OR(D154="",E154="",D154=E154),"",IF(E154&lt;D154,"BUY","SELL"))</f>
@@ -5797,19 +6728,19 @@
         <f aca="false">IF(I154="","",IF(I154&gt;0,"WIN",IF(I154&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I154" s="25" t="str">
+      <c r="I154" s="31" t="str">
         <f aca="false">IF(OR(G154="",C154=""),"",ROUND((G154-D154)/(D154-E154),2))</f>
         <v/>
       </c>
-      <c r="J154" s="26" t="str">
+      <c r="J154" s="32" t="str">
         <f aca="false">IF(I154="","",ROUND(I154*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K154" s="6"/>
-      <c r="L154" s="27"/>
+      <c r="L154" s="26"/>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="24"/>
+      <c r="A155" s="30"/>
       <c r="B155" s="6"/>
       <c r="C155" s="8" t="str">
         <f aca="false">IF(OR(D155="",E155="",D155=E155),"",IF(E155&lt;D155,"BUY","SELL"))</f>
@@ -5826,19 +6757,19 @@
         <f aca="false">IF(I155="","",IF(I155&gt;0,"WIN",IF(I155&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I155" s="25" t="str">
+      <c r="I155" s="31" t="str">
         <f aca="false">IF(OR(G155="",C155=""),"",ROUND((G155-D155)/(D155-E155),2))</f>
         <v/>
       </c>
-      <c r="J155" s="26" t="str">
+      <c r="J155" s="32" t="str">
         <f aca="false">IF(I155="","",ROUND(I155*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K155" s="6"/>
-      <c r="L155" s="27"/>
+      <c r="L155" s="26"/>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="24"/>
+      <c r="A156" s="30"/>
       <c r="B156" s="6"/>
       <c r="C156" s="8" t="str">
         <f aca="false">IF(OR(D156="",E156="",D156=E156),"",IF(E156&lt;D156,"BUY","SELL"))</f>
@@ -5855,19 +6786,19 @@
         <f aca="false">IF(I156="","",IF(I156&gt;0,"WIN",IF(I156&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I156" s="25" t="str">
+      <c r="I156" s="31" t="str">
         <f aca="false">IF(OR(G156="",C156=""),"",ROUND((G156-D156)/(D156-E156),2))</f>
         <v/>
       </c>
-      <c r="J156" s="26" t="str">
+      <c r="J156" s="32" t="str">
         <f aca="false">IF(I156="","",ROUND(I156*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K156" s="6"/>
-      <c r="L156" s="27"/>
+      <c r="L156" s="26"/>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="24"/>
+      <c r="A157" s="30"/>
       <c r="B157" s="6"/>
       <c r="C157" s="8" t="str">
         <f aca="false">IF(OR(D157="",E157="",D157=E157),"",IF(E157&lt;D157,"BUY","SELL"))</f>
@@ -5884,19 +6815,19 @@
         <f aca="false">IF(I157="","",IF(I157&gt;0,"WIN",IF(I157&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I157" s="25" t="str">
+      <c r="I157" s="31" t="str">
         <f aca="false">IF(OR(G157="",C157=""),"",ROUND((G157-D157)/(D157-E157),2))</f>
         <v/>
       </c>
-      <c r="J157" s="26" t="str">
+      <c r="J157" s="32" t="str">
         <f aca="false">IF(I157="","",ROUND(I157*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K157" s="6"/>
-      <c r="L157" s="27"/>
+      <c r="L157" s="26"/>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="24"/>
+      <c r="A158" s="30"/>
       <c r="B158" s="6"/>
       <c r="C158" s="8" t="str">
         <f aca="false">IF(OR(D158="",E158="",D158=E158),"",IF(E158&lt;D158,"BUY","SELL"))</f>
@@ -5913,19 +6844,19 @@
         <f aca="false">IF(I158="","",IF(I158&gt;0,"WIN",IF(I158&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I158" s="25" t="str">
+      <c r="I158" s="31" t="str">
         <f aca="false">IF(OR(G158="",C158=""),"",ROUND((G158-D158)/(D158-E158),2))</f>
         <v/>
       </c>
-      <c r="J158" s="26" t="str">
+      <c r="J158" s="32" t="str">
         <f aca="false">IF(I158="","",ROUND(I158*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K158" s="6"/>
-      <c r="L158" s="27"/>
+      <c r="L158" s="26"/>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="24"/>
+      <c r="A159" s="30"/>
       <c r="B159" s="6"/>
       <c r="C159" s="8" t="str">
         <f aca="false">IF(OR(D159="",E159="",D159=E159),"",IF(E159&lt;D159,"BUY","SELL"))</f>
@@ -5942,19 +6873,19 @@
         <f aca="false">IF(I159="","",IF(I159&gt;0,"WIN",IF(I159&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I159" s="25" t="str">
+      <c r="I159" s="31" t="str">
         <f aca="false">IF(OR(G159="",C159=""),"",ROUND((G159-D159)/(D159-E159),2))</f>
         <v/>
       </c>
-      <c r="J159" s="26" t="str">
+      <c r="J159" s="32" t="str">
         <f aca="false">IF(I159="","",ROUND(I159*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K159" s="6"/>
-      <c r="L159" s="27"/>
+      <c r="L159" s="26"/>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="24"/>
+      <c r="A160" s="30"/>
       <c r="B160" s="6"/>
       <c r="C160" s="8" t="str">
         <f aca="false">IF(OR(D160="",E160="",D160=E160),"",IF(E160&lt;D160,"BUY","SELL"))</f>
@@ -5971,19 +6902,19 @@
         <f aca="false">IF(I160="","",IF(I160&gt;0,"WIN",IF(I160&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I160" s="25" t="str">
+      <c r="I160" s="31" t="str">
         <f aca="false">IF(OR(G160="",C160=""),"",ROUND((G160-D160)/(D160-E160),2))</f>
         <v/>
       </c>
-      <c r="J160" s="26" t="str">
+      <c r="J160" s="32" t="str">
         <f aca="false">IF(I160="","",ROUND(I160*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K160" s="6"/>
-      <c r="L160" s="27"/>
+      <c r="L160" s="26"/>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="24"/>
+      <c r="A161" s="30"/>
       <c r="B161" s="6"/>
       <c r="C161" s="8" t="str">
         <f aca="false">IF(OR(D161="",E161="",D161=E161),"",IF(E161&lt;D161,"BUY","SELL"))</f>
@@ -6000,19 +6931,19 @@
         <f aca="false">IF(I161="","",IF(I161&gt;0,"WIN",IF(I161&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I161" s="25" t="str">
+      <c r="I161" s="31" t="str">
         <f aca="false">IF(OR(G161="",C161=""),"",ROUND((G161-D161)/(D161-E161),2))</f>
         <v/>
       </c>
-      <c r="J161" s="26" t="str">
+      <c r="J161" s="32" t="str">
         <f aca="false">IF(I161="","",ROUND(I161*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K161" s="6"/>
-      <c r="L161" s="27"/>
+      <c r="L161" s="26"/>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="24"/>
+      <c r="A162" s="30"/>
       <c r="B162" s="6"/>
       <c r="C162" s="8" t="str">
         <f aca="false">IF(OR(D162="",E162="",D162=E162),"",IF(E162&lt;D162,"BUY","SELL"))</f>
@@ -6029,19 +6960,19 @@
         <f aca="false">IF(I162="","",IF(I162&gt;0,"WIN",IF(I162&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I162" s="25" t="str">
+      <c r="I162" s="31" t="str">
         <f aca="false">IF(OR(G162="",C162=""),"",ROUND((G162-D162)/(D162-E162),2))</f>
         <v/>
       </c>
-      <c r="J162" s="26" t="str">
+      <c r="J162" s="32" t="str">
         <f aca="false">IF(I162="","",ROUND(I162*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K162" s="6"/>
-      <c r="L162" s="27"/>
+      <c r="L162" s="26"/>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="24"/>
+      <c r="A163" s="30"/>
       <c r="B163" s="6"/>
       <c r="C163" s="8" t="str">
         <f aca="false">IF(OR(D163="",E163="",D163=E163),"",IF(E163&lt;D163,"BUY","SELL"))</f>
@@ -6058,19 +6989,19 @@
         <f aca="false">IF(I163="","",IF(I163&gt;0,"WIN",IF(I163&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I163" s="25" t="str">
+      <c r="I163" s="31" t="str">
         <f aca="false">IF(OR(G163="",C163=""),"",ROUND((G163-D163)/(D163-E163),2))</f>
         <v/>
       </c>
-      <c r="J163" s="26" t="str">
+      <c r="J163" s="32" t="str">
         <f aca="false">IF(I163="","",ROUND(I163*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K163" s="6"/>
-      <c r="L163" s="27"/>
+      <c r="L163" s="26"/>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="24"/>
+      <c r="A164" s="30"/>
       <c r="B164" s="6"/>
       <c r="C164" s="8" t="str">
         <f aca="false">IF(OR(D164="",E164="",D164=E164),"",IF(E164&lt;D164,"BUY","SELL"))</f>
@@ -6087,19 +7018,19 @@
         <f aca="false">IF(I164="","",IF(I164&gt;0,"WIN",IF(I164&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I164" s="25" t="str">
+      <c r="I164" s="31" t="str">
         <f aca="false">IF(OR(G164="",C164=""),"",ROUND((G164-D164)/(D164-E164),2))</f>
         <v/>
       </c>
-      <c r="J164" s="26" t="str">
+      <c r="J164" s="32" t="str">
         <f aca="false">IF(I164="","",ROUND(I164*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K164" s="6"/>
-      <c r="L164" s="27"/>
+      <c r="L164" s="26"/>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="24"/>
+      <c r="A165" s="30"/>
       <c r="B165" s="6"/>
       <c r="C165" s="8" t="str">
         <f aca="false">IF(OR(D165="",E165="",D165=E165),"",IF(E165&lt;D165,"BUY","SELL"))</f>
@@ -6116,19 +7047,19 @@
         <f aca="false">IF(I165="","",IF(I165&gt;0,"WIN",IF(I165&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I165" s="25" t="str">
+      <c r="I165" s="31" t="str">
         <f aca="false">IF(OR(G165="",C165=""),"",ROUND((G165-D165)/(D165-E165),2))</f>
         <v/>
       </c>
-      <c r="J165" s="26" t="str">
+      <c r="J165" s="32" t="str">
         <f aca="false">IF(I165="","",ROUND(I165*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K165" s="6"/>
-      <c r="L165" s="27"/>
+      <c r="L165" s="26"/>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="24"/>
+      <c r="A166" s="30"/>
       <c r="B166" s="6"/>
       <c r="C166" s="8" t="str">
         <f aca="false">IF(OR(D166="",E166="",D166=E166),"",IF(E166&lt;D166,"BUY","SELL"))</f>
@@ -6145,19 +7076,19 @@
         <f aca="false">IF(I166="","",IF(I166&gt;0,"WIN",IF(I166&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I166" s="25" t="str">
+      <c r="I166" s="31" t="str">
         <f aca="false">IF(OR(G166="",C166=""),"",ROUND((G166-D166)/(D166-E166),2))</f>
         <v/>
       </c>
-      <c r="J166" s="26" t="str">
+      <c r="J166" s="32" t="str">
         <f aca="false">IF(I166="","",ROUND(I166*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K166" s="6"/>
-      <c r="L166" s="27"/>
+      <c r="L166" s="26"/>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="24"/>
+      <c r="A167" s="30"/>
       <c r="B167" s="6"/>
       <c r="C167" s="8" t="str">
         <f aca="false">IF(OR(D167="",E167="",D167=E167),"",IF(E167&lt;D167,"BUY","SELL"))</f>
@@ -6174,19 +7105,19 @@
         <f aca="false">IF(I167="","",IF(I167&gt;0,"WIN",IF(I167&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I167" s="25" t="str">
+      <c r="I167" s="31" t="str">
         <f aca="false">IF(OR(G167="",C167=""),"",ROUND((G167-D167)/(D167-E167),2))</f>
         <v/>
       </c>
-      <c r="J167" s="26" t="str">
+      <c r="J167" s="32" t="str">
         <f aca="false">IF(I167="","",ROUND(I167*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K167" s="6"/>
-      <c r="L167" s="27"/>
+      <c r="L167" s="26"/>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="24"/>
+      <c r="A168" s="30"/>
       <c r="B168" s="6"/>
       <c r="C168" s="8" t="str">
         <f aca="false">IF(OR(D168="",E168="",D168=E168),"",IF(E168&lt;D168,"BUY","SELL"))</f>
@@ -6203,19 +7134,19 @@
         <f aca="false">IF(I168="","",IF(I168&gt;0,"WIN",IF(I168&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I168" s="25" t="str">
+      <c r="I168" s="31" t="str">
         <f aca="false">IF(OR(G168="",C168=""),"",ROUND((G168-D168)/(D168-E168),2))</f>
         <v/>
       </c>
-      <c r="J168" s="26" t="str">
+      <c r="J168" s="32" t="str">
         <f aca="false">IF(I168="","",ROUND(I168*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K168" s="6"/>
-      <c r="L168" s="27"/>
+      <c r="L168" s="26"/>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="24"/>
+      <c r="A169" s="30"/>
       <c r="B169" s="6"/>
       <c r="C169" s="8" t="str">
         <f aca="false">IF(OR(D169="",E169="",D169=E169),"",IF(E169&lt;D169,"BUY","SELL"))</f>
@@ -6232,19 +7163,19 @@
         <f aca="false">IF(I169="","",IF(I169&gt;0,"WIN",IF(I169&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I169" s="25" t="str">
+      <c r="I169" s="31" t="str">
         <f aca="false">IF(OR(G169="",C169=""),"",ROUND((G169-D169)/(D169-E169),2))</f>
         <v/>
       </c>
-      <c r="J169" s="26" t="str">
+      <c r="J169" s="32" t="str">
         <f aca="false">IF(I169="","",ROUND(I169*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K169" s="6"/>
-      <c r="L169" s="27"/>
+      <c r="L169" s="26"/>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="24"/>
+      <c r="A170" s="30"/>
       <c r="B170" s="6"/>
       <c r="C170" s="8" t="str">
         <f aca="false">IF(OR(D170="",E170="",D170=E170),"",IF(E170&lt;D170,"BUY","SELL"))</f>
@@ -6261,19 +7192,19 @@
         <f aca="false">IF(I170="","",IF(I170&gt;0,"WIN",IF(I170&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I170" s="25" t="str">
+      <c r="I170" s="31" t="str">
         <f aca="false">IF(OR(G170="",C170=""),"",ROUND((G170-D170)/(D170-E170),2))</f>
         <v/>
       </c>
-      <c r="J170" s="26" t="str">
+      <c r="J170" s="32" t="str">
         <f aca="false">IF(I170="","",ROUND(I170*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K170" s="6"/>
-      <c r="L170" s="27"/>
+      <c r="L170" s="26"/>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="24"/>
+      <c r="A171" s="30"/>
       <c r="B171" s="6"/>
       <c r="C171" s="8" t="str">
         <f aca="false">IF(OR(D171="",E171="",D171=E171),"",IF(E171&lt;D171,"BUY","SELL"))</f>
@@ -6290,19 +7221,19 @@
         <f aca="false">IF(I171="","",IF(I171&gt;0,"WIN",IF(I171&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I171" s="25" t="str">
+      <c r="I171" s="31" t="str">
         <f aca="false">IF(OR(G171="",C171=""),"",ROUND((G171-D171)/(D171-E171),2))</f>
         <v/>
       </c>
-      <c r="J171" s="26" t="str">
+      <c r="J171" s="32" t="str">
         <f aca="false">IF(I171="","",ROUND(I171*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K171" s="6"/>
-      <c r="L171" s="27"/>
+      <c r="L171" s="26"/>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="24"/>
+      <c r="A172" s="30"/>
       <c r="B172" s="6"/>
       <c r="C172" s="8" t="str">
         <f aca="false">IF(OR(D172="",E172="",D172=E172),"",IF(E172&lt;D172,"BUY","SELL"))</f>
@@ -6319,19 +7250,19 @@
         <f aca="false">IF(I172="","",IF(I172&gt;0,"WIN",IF(I172&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I172" s="25" t="str">
+      <c r="I172" s="31" t="str">
         <f aca="false">IF(OR(G172="",C172=""),"",ROUND((G172-D172)/(D172-E172),2))</f>
         <v/>
       </c>
-      <c r="J172" s="26" t="str">
+      <c r="J172" s="32" t="str">
         <f aca="false">IF(I172="","",ROUND(I172*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K172" s="6"/>
-      <c r="L172" s="27"/>
+      <c r="L172" s="26"/>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="24"/>
+      <c r="A173" s="30"/>
       <c r="B173" s="6"/>
       <c r="C173" s="8" t="str">
         <f aca="false">IF(OR(D173="",E173="",D173=E173),"",IF(E173&lt;D173,"BUY","SELL"))</f>
@@ -6348,19 +7279,19 @@
         <f aca="false">IF(I173="","",IF(I173&gt;0,"WIN",IF(I173&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I173" s="25" t="str">
+      <c r="I173" s="31" t="str">
         <f aca="false">IF(OR(G173="",C173=""),"",ROUND((G173-D173)/(D173-E173),2))</f>
         <v/>
       </c>
-      <c r="J173" s="26" t="str">
+      <c r="J173" s="32" t="str">
         <f aca="false">IF(I173="","",ROUND(I173*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K173" s="6"/>
-      <c r="L173" s="27"/>
+      <c r="L173" s="26"/>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="24"/>
+      <c r="A174" s="30"/>
       <c r="B174" s="6"/>
       <c r="C174" s="8" t="str">
         <f aca="false">IF(OR(D174="",E174="",D174=E174),"",IF(E174&lt;D174,"BUY","SELL"))</f>
@@ -6377,19 +7308,19 @@
         <f aca="false">IF(I174="","",IF(I174&gt;0,"WIN",IF(I174&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I174" s="25" t="str">
+      <c r="I174" s="31" t="str">
         <f aca="false">IF(OR(G174="",C174=""),"",ROUND((G174-D174)/(D174-E174),2))</f>
         <v/>
       </c>
-      <c r="J174" s="26" t="str">
+      <c r="J174" s="32" t="str">
         <f aca="false">IF(I174="","",ROUND(I174*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K174" s="6"/>
-      <c r="L174" s="27"/>
+      <c r="L174" s="26"/>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="24"/>
+      <c r="A175" s="30"/>
       <c r="B175" s="6"/>
       <c r="C175" s="8" t="str">
         <f aca="false">IF(OR(D175="",E175="",D175=E175),"",IF(E175&lt;D175,"BUY","SELL"))</f>
@@ -6406,19 +7337,19 @@
         <f aca="false">IF(I175="","",IF(I175&gt;0,"WIN",IF(I175&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I175" s="25" t="str">
+      <c r="I175" s="31" t="str">
         <f aca="false">IF(OR(G175="",C175=""),"",ROUND((G175-D175)/(D175-E175),2))</f>
         <v/>
       </c>
-      <c r="J175" s="26" t="str">
+      <c r="J175" s="32" t="str">
         <f aca="false">IF(I175="","",ROUND(I175*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K175" s="6"/>
-      <c r="L175" s="27"/>
+      <c r="L175" s="26"/>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="24"/>
+      <c r="A176" s="30"/>
       <c r="B176" s="6"/>
       <c r="C176" s="8" t="str">
         <f aca="false">IF(OR(D176="",E176="",D176=E176),"",IF(E176&lt;D176,"BUY","SELL"))</f>
@@ -6435,19 +7366,19 @@
         <f aca="false">IF(I176="","",IF(I176&gt;0,"WIN",IF(I176&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I176" s="25" t="str">
+      <c r="I176" s="31" t="str">
         <f aca="false">IF(OR(G176="",C176=""),"",ROUND((G176-D176)/(D176-E176),2))</f>
         <v/>
       </c>
-      <c r="J176" s="26" t="str">
+      <c r="J176" s="32" t="str">
         <f aca="false">IF(I176="","",ROUND(I176*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K176" s="6"/>
-      <c r="L176" s="27"/>
+      <c r="L176" s="26"/>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="24"/>
+      <c r="A177" s="30"/>
       <c r="B177" s="6"/>
       <c r="C177" s="8" t="str">
         <f aca="false">IF(OR(D177="",E177="",D177=E177),"",IF(E177&lt;D177,"BUY","SELL"))</f>
@@ -6464,19 +7395,19 @@
         <f aca="false">IF(I177="","",IF(I177&gt;0,"WIN",IF(I177&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I177" s="25" t="str">
+      <c r="I177" s="31" t="str">
         <f aca="false">IF(OR(G177="",C177=""),"",ROUND((G177-D177)/(D177-E177),2))</f>
         <v/>
       </c>
-      <c r="J177" s="26" t="str">
+      <c r="J177" s="32" t="str">
         <f aca="false">IF(I177="","",ROUND(I177*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K177" s="6"/>
-      <c r="L177" s="27"/>
+      <c r="L177" s="26"/>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="24"/>
+      <c r="A178" s="30"/>
       <c r="B178" s="6"/>
       <c r="C178" s="8" t="str">
         <f aca="false">IF(OR(D178="",E178="",D178=E178),"",IF(E178&lt;D178,"BUY","SELL"))</f>
@@ -6493,19 +7424,19 @@
         <f aca="false">IF(I178="","",IF(I178&gt;0,"WIN",IF(I178&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I178" s="25" t="str">
+      <c r="I178" s="31" t="str">
         <f aca="false">IF(OR(G178="",C178=""),"",ROUND((G178-D178)/(D178-E178),2))</f>
         <v/>
       </c>
-      <c r="J178" s="26" t="str">
+      <c r="J178" s="32" t="str">
         <f aca="false">IF(I178="","",ROUND(I178*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K178" s="6"/>
-      <c r="L178" s="27"/>
+      <c r="L178" s="26"/>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="24"/>
+      <c r="A179" s="30"/>
       <c r="B179" s="6"/>
       <c r="C179" s="8" t="str">
         <f aca="false">IF(OR(D179="",E179="",D179=E179),"",IF(E179&lt;D179,"BUY","SELL"))</f>
@@ -6522,19 +7453,19 @@
         <f aca="false">IF(I179="","",IF(I179&gt;0,"WIN",IF(I179&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I179" s="25" t="str">
+      <c r="I179" s="31" t="str">
         <f aca="false">IF(OR(G179="",C179=""),"",ROUND((G179-D179)/(D179-E179),2))</f>
         <v/>
       </c>
-      <c r="J179" s="26" t="str">
+      <c r="J179" s="32" t="str">
         <f aca="false">IF(I179="","",ROUND(I179*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K179" s="6"/>
-      <c r="L179" s="27"/>
+      <c r="L179" s="26"/>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="24"/>
+      <c r="A180" s="30"/>
       <c r="B180" s="6"/>
       <c r="C180" s="8" t="str">
         <f aca="false">IF(OR(D180="",E180="",D180=E180),"",IF(E180&lt;D180,"BUY","SELL"))</f>
@@ -6551,19 +7482,19 @@
         <f aca="false">IF(I180="","",IF(I180&gt;0,"WIN",IF(I180&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I180" s="25" t="str">
+      <c r="I180" s="31" t="str">
         <f aca="false">IF(OR(G180="",C180=""),"",ROUND((G180-D180)/(D180-E180),2))</f>
         <v/>
       </c>
-      <c r="J180" s="26" t="str">
+      <c r="J180" s="32" t="str">
         <f aca="false">IF(I180="","",ROUND(I180*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K180" s="6"/>
-      <c r="L180" s="27"/>
+      <c r="L180" s="26"/>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="24"/>
+      <c r="A181" s="30"/>
       <c r="B181" s="6"/>
       <c r="C181" s="8" t="str">
         <f aca="false">IF(OR(D181="",E181="",D181=E181),"",IF(E181&lt;D181,"BUY","SELL"))</f>
@@ -6580,19 +7511,19 @@
         <f aca="false">IF(I181="","",IF(I181&gt;0,"WIN",IF(I181&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I181" s="25" t="str">
+      <c r="I181" s="31" t="str">
         <f aca="false">IF(OR(G181="",C181=""),"",ROUND((G181-D181)/(D181-E181),2))</f>
         <v/>
       </c>
-      <c r="J181" s="26" t="str">
+      <c r="J181" s="32" t="str">
         <f aca="false">IF(I181="","",ROUND(I181*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K181" s="6"/>
-      <c r="L181" s="27"/>
+      <c r="L181" s="26"/>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="24"/>
+      <c r="A182" s="30"/>
       <c r="B182" s="6"/>
       <c r="C182" s="8" t="str">
         <f aca="false">IF(OR(D182="",E182="",D182=E182),"",IF(E182&lt;D182,"BUY","SELL"))</f>
@@ -6609,19 +7540,19 @@
         <f aca="false">IF(I182="","",IF(I182&gt;0,"WIN",IF(I182&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I182" s="25" t="str">
+      <c r="I182" s="31" t="str">
         <f aca="false">IF(OR(G182="",C182=""),"",ROUND((G182-D182)/(D182-E182),2))</f>
         <v/>
       </c>
-      <c r="J182" s="26" t="str">
+      <c r="J182" s="32" t="str">
         <f aca="false">IF(I182="","",ROUND(I182*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K182" s="6"/>
-      <c r="L182" s="27"/>
+      <c r="L182" s="26"/>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="24"/>
+      <c r="A183" s="30"/>
       <c r="B183" s="6"/>
       <c r="C183" s="8" t="str">
         <f aca="false">IF(OR(D183="",E183="",D183=E183),"",IF(E183&lt;D183,"BUY","SELL"))</f>
@@ -6638,19 +7569,19 @@
         <f aca="false">IF(I183="","",IF(I183&gt;0,"WIN",IF(I183&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I183" s="25" t="str">
+      <c r="I183" s="31" t="str">
         <f aca="false">IF(OR(G183="",C183=""),"",ROUND((G183-D183)/(D183-E183),2))</f>
         <v/>
       </c>
-      <c r="J183" s="26" t="str">
+      <c r="J183" s="32" t="str">
         <f aca="false">IF(I183="","",ROUND(I183*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K183" s="6"/>
-      <c r="L183" s="27"/>
+      <c r="L183" s="26"/>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="24"/>
+      <c r="A184" s="30"/>
       <c r="B184" s="6"/>
       <c r="C184" s="8" t="str">
         <f aca="false">IF(OR(D184="",E184="",D184=E184),"",IF(E184&lt;D184,"BUY","SELL"))</f>
@@ -6667,19 +7598,19 @@
         <f aca="false">IF(I184="","",IF(I184&gt;0,"WIN",IF(I184&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I184" s="25" t="str">
+      <c r="I184" s="31" t="str">
         <f aca="false">IF(OR(G184="",C184=""),"",ROUND((G184-D184)/(D184-E184),2))</f>
         <v/>
       </c>
-      <c r="J184" s="26" t="str">
+      <c r="J184" s="32" t="str">
         <f aca="false">IF(I184="","",ROUND(I184*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K184" s="6"/>
-      <c r="L184" s="27"/>
+      <c r="L184" s="26"/>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="24"/>
+      <c r="A185" s="30"/>
       <c r="B185" s="6"/>
       <c r="C185" s="8" t="str">
         <f aca="false">IF(OR(D185="",E185="",D185=E185),"",IF(E185&lt;D185,"BUY","SELL"))</f>
@@ -6696,19 +7627,19 @@
         <f aca="false">IF(I185="","",IF(I185&gt;0,"WIN",IF(I185&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I185" s="25" t="str">
+      <c r="I185" s="31" t="str">
         <f aca="false">IF(OR(G185="",C185=""),"",ROUND((G185-D185)/(D185-E185),2))</f>
         <v/>
       </c>
-      <c r="J185" s="26" t="str">
+      <c r="J185" s="32" t="str">
         <f aca="false">IF(I185="","",ROUND(I185*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K185" s="6"/>
-      <c r="L185" s="27"/>
+      <c r="L185" s="26"/>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="24"/>
+      <c r="A186" s="30"/>
       <c r="B186" s="6"/>
       <c r="C186" s="8" t="str">
         <f aca="false">IF(OR(D186="",E186="",D186=E186),"",IF(E186&lt;D186,"BUY","SELL"))</f>
@@ -6725,19 +7656,19 @@
         <f aca="false">IF(I186="","",IF(I186&gt;0,"WIN",IF(I186&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I186" s="25" t="str">
+      <c r="I186" s="31" t="str">
         <f aca="false">IF(OR(G186="",C186=""),"",ROUND((G186-D186)/(D186-E186),2))</f>
         <v/>
       </c>
-      <c r="J186" s="26" t="str">
+      <c r="J186" s="32" t="str">
         <f aca="false">IF(I186="","",ROUND(I186*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K186" s="6"/>
-      <c r="L186" s="27"/>
+      <c r="L186" s="26"/>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="24"/>
+      <c r="A187" s="30"/>
       <c r="B187" s="6"/>
       <c r="C187" s="8" t="str">
         <f aca="false">IF(OR(D187="",E187="",D187=E187),"",IF(E187&lt;D187,"BUY","SELL"))</f>
@@ -6754,19 +7685,19 @@
         <f aca="false">IF(I187="","",IF(I187&gt;0,"WIN",IF(I187&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I187" s="25" t="str">
+      <c r="I187" s="31" t="str">
         <f aca="false">IF(OR(G187="",C187=""),"",ROUND((G187-D187)/(D187-E187),2))</f>
         <v/>
       </c>
-      <c r="J187" s="26" t="str">
+      <c r="J187" s="32" t="str">
         <f aca="false">IF(I187="","",ROUND(I187*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K187" s="6"/>
-      <c r="L187" s="27"/>
+      <c r="L187" s="26"/>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="24"/>
+      <c r="A188" s="30"/>
       <c r="B188" s="6"/>
       <c r="C188" s="8" t="str">
         <f aca="false">IF(OR(D188="",E188="",D188=E188),"",IF(E188&lt;D188,"BUY","SELL"))</f>
@@ -6783,19 +7714,19 @@
         <f aca="false">IF(I188="","",IF(I188&gt;0,"WIN",IF(I188&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I188" s="25" t="str">
+      <c r="I188" s="31" t="str">
         <f aca="false">IF(OR(G188="",C188=""),"",ROUND((G188-D188)/(D188-E188),2))</f>
         <v/>
       </c>
-      <c r="J188" s="26" t="str">
+      <c r="J188" s="32" t="str">
         <f aca="false">IF(I188="","",ROUND(I188*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K188" s="6"/>
-      <c r="L188" s="27"/>
+      <c r="L188" s="26"/>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="24"/>
+      <c r="A189" s="30"/>
       <c r="B189" s="6"/>
       <c r="C189" s="8" t="str">
         <f aca="false">IF(OR(D189="",E189="",D189=E189),"",IF(E189&lt;D189,"BUY","SELL"))</f>
@@ -6812,19 +7743,19 @@
         <f aca="false">IF(I189="","",IF(I189&gt;0,"WIN",IF(I189&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I189" s="25" t="str">
+      <c r="I189" s="31" t="str">
         <f aca="false">IF(OR(G189="",C189=""),"",ROUND((G189-D189)/(D189-E189),2))</f>
         <v/>
       </c>
-      <c r="J189" s="26" t="str">
+      <c r="J189" s="32" t="str">
         <f aca="false">IF(I189="","",ROUND(I189*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K189" s="6"/>
-      <c r="L189" s="27"/>
+      <c r="L189" s="26"/>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="24"/>
+      <c r="A190" s="30"/>
       <c r="B190" s="6"/>
       <c r="C190" s="8" t="str">
         <f aca="false">IF(OR(D190="",E190="",D190=E190),"",IF(E190&lt;D190,"BUY","SELL"))</f>
@@ -6841,19 +7772,19 @@
         <f aca="false">IF(I190="","",IF(I190&gt;0,"WIN",IF(I190&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I190" s="25" t="str">
+      <c r="I190" s="31" t="str">
         <f aca="false">IF(OR(G190="",C190=""),"",ROUND((G190-D190)/(D190-E190),2))</f>
         <v/>
       </c>
-      <c r="J190" s="26" t="str">
+      <c r="J190" s="32" t="str">
         <f aca="false">IF(I190="","",ROUND(I190*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K190" s="6"/>
-      <c r="L190" s="27"/>
+      <c r="L190" s="26"/>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="24"/>
+      <c r="A191" s="30"/>
       <c r="B191" s="6"/>
       <c r="C191" s="8" t="str">
         <f aca="false">IF(OR(D191="",E191="",D191=E191),"",IF(E191&lt;D191,"BUY","SELL"))</f>
@@ -6870,19 +7801,19 @@
         <f aca="false">IF(I191="","",IF(I191&gt;0,"WIN",IF(I191&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I191" s="25" t="str">
+      <c r="I191" s="31" t="str">
         <f aca="false">IF(OR(G191="",C191=""),"",ROUND((G191-D191)/(D191-E191),2))</f>
         <v/>
       </c>
-      <c r="J191" s="26" t="str">
+      <c r="J191" s="32" t="str">
         <f aca="false">IF(I191="","",ROUND(I191*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K191" s="6"/>
-      <c r="L191" s="27"/>
+      <c r="L191" s="26"/>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="24"/>
+      <c r="A192" s="30"/>
       <c r="B192" s="6"/>
       <c r="C192" s="8" t="str">
         <f aca="false">IF(OR(D192="",E192="",D192=E192),"",IF(E192&lt;D192,"BUY","SELL"))</f>
@@ -6899,19 +7830,19 @@
         <f aca="false">IF(I192="","",IF(I192&gt;0,"WIN",IF(I192&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I192" s="25" t="str">
+      <c r="I192" s="31" t="str">
         <f aca="false">IF(OR(G192="",C192=""),"",ROUND((G192-D192)/(D192-E192),2))</f>
         <v/>
       </c>
-      <c r="J192" s="26" t="str">
+      <c r="J192" s="32" t="str">
         <f aca="false">IF(I192="","",ROUND(I192*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K192" s="6"/>
-      <c r="L192" s="27"/>
+      <c r="L192" s="26"/>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="24"/>
+      <c r="A193" s="30"/>
       <c r="B193" s="6"/>
       <c r="C193" s="8" t="str">
         <f aca="false">IF(OR(D193="",E193="",D193=E193),"",IF(E193&lt;D193,"BUY","SELL"))</f>
@@ -6928,19 +7859,19 @@
         <f aca="false">IF(I193="","",IF(I193&gt;0,"WIN",IF(I193&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I193" s="25" t="str">
+      <c r="I193" s="31" t="str">
         <f aca="false">IF(OR(G193="",C193=""),"",ROUND((G193-D193)/(D193-E193),2))</f>
         <v/>
       </c>
-      <c r="J193" s="26" t="str">
+      <c r="J193" s="32" t="str">
         <f aca="false">IF(I193="","",ROUND(I193*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K193" s="6"/>
-      <c r="L193" s="27"/>
+      <c r="L193" s="26"/>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="24"/>
+      <c r="A194" s="30"/>
       <c r="B194" s="6"/>
       <c r="C194" s="8" t="str">
         <f aca="false">IF(OR(D194="",E194="",D194=E194),"",IF(E194&lt;D194,"BUY","SELL"))</f>
@@ -6957,19 +7888,19 @@
         <f aca="false">IF(I194="","",IF(I194&gt;0,"WIN",IF(I194&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I194" s="25" t="str">
+      <c r="I194" s="31" t="str">
         <f aca="false">IF(OR(G194="",C194=""),"",ROUND((G194-D194)/(D194-E194),2))</f>
         <v/>
       </c>
-      <c r="J194" s="26" t="str">
+      <c r="J194" s="32" t="str">
         <f aca="false">IF(I194="","",ROUND(I194*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K194" s="6"/>
-      <c r="L194" s="27"/>
+      <c r="L194" s="26"/>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="24"/>
+      <c r="A195" s="30"/>
       <c r="B195" s="6"/>
       <c r="C195" s="8" t="str">
         <f aca="false">IF(OR(D195="",E195="",D195=E195),"",IF(E195&lt;D195,"BUY","SELL"))</f>
@@ -6986,19 +7917,19 @@
         <f aca="false">IF(I195="","",IF(I195&gt;0,"WIN",IF(I195&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I195" s="25" t="str">
+      <c r="I195" s="31" t="str">
         <f aca="false">IF(OR(G195="",C195=""),"",ROUND((G195-D195)/(D195-E195),2))</f>
         <v/>
       </c>
-      <c r="J195" s="26" t="str">
+      <c r="J195" s="32" t="str">
         <f aca="false">IF(I195="","",ROUND(I195*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K195" s="6"/>
-      <c r="L195" s="27"/>
+      <c r="L195" s="26"/>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="24"/>
+      <c r="A196" s="30"/>
       <c r="B196" s="6"/>
       <c r="C196" s="8" t="str">
         <f aca="false">IF(OR(D196="",E196="",D196=E196),"",IF(E196&lt;D196,"BUY","SELL"))</f>
@@ -7015,19 +7946,19 @@
         <f aca="false">IF(I196="","",IF(I196&gt;0,"WIN",IF(I196&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I196" s="25" t="str">
+      <c r="I196" s="31" t="str">
         <f aca="false">IF(OR(G196="",C196=""),"",ROUND((G196-D196)/(D196-E196),2))</f>
         <v/>
       </c>
-      <c r="J196" s="26" t="str">
+      <c r="J196" s="32" t="str">
         <f aca="false">IF(I196="","",ROUND(I196*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K196" s="6"/>
-      <c r="L196" s="27"/>
+      <c r="L196" s="26"/>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="24"/>
+      <c r="A197" s="30"/>
       <c r="B197" s="6"/>
       <c r="C197" s="8" t="str">
         <f aca="false">IF(OR(D197="",E197="",D197=E197),"",IF(E197&lt;D197,"BUY","SELL"))</f>
@@ -7044,19 +7975,19 @@
         <f aca="false">IF(I197="","",IF(I197&gt;0,"WIN",IF(I197&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I197" s="25" t="str">
+      <c r="I197" s="31" t="str">
         <f aca="false">IF(OR(G197="",C197=""),"",ROUND((G197-D197)/(D197-E197),2))</f>
         <v/>
       </c>
-      <c r="J197" s="26" t="str">
+      <c r="J197" s="32" t="str">
         <f aca="false">IF(I197="","",ROUND(I197*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K197" s="6"/>
-      <c r="L197" s="27"/>
+      <c r="L197" s="26"/>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="24"/>
+      <c r="A198" s="30"/>
       <c r="B198" s="6"/>
       <c r="C198" s="8" t="str">
         <f aca="false">IF(OR(D198="",E198="",D198=E198),"",IF(E198&lt;D198,"BUY","SELL"))</f>
@@ -7073,19 +8004,19 @@
         <f aca="false">IF(I198="","",IF(I198&gt;0,"WIN",IF(I198&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I198" s="25" t="str">
+      <c r="I198" s="31" t="str">
         <f aca="false">IF(OR(G198="",C198=""),"",ROUND((G198-D198)/(D198-E198),2))</f>
         <v/>
       </c>
-      <c r="J198" s="26" t="str">
+      <c r="J198" s="32" t="str">
         <f aca="false">IF(I198="","",ROUND(I198*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K198" s="6"/>
-      <c r="L198" s="27"/>
+      <c r="L198" s="26"/>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="24"/>
+      <c r="A199" s="30"/>
       <c r="B199" s="6"/>
       <c r="C199" s="8" t="str">
         <f aca="false">IF(OR(D199="",E199="",D199=E199),"",IF(E199&lt;D199,"BUY","SELL"))</f>
@@ -7102,19 +8033,19 @@
         <f aca="false">IF(I199="","",IF(I199&gt;0,"WIN",IF(I199&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I199" s="25" t="str">
+      <c r="I199" s="31" t="str">
         <f aca="false">IF(OR(G199="",C199=""),"",ROUND((G199-D199)/(D199-E199),2))</f>
         <v/>
       </c>
-      <c r="J199" s="26" t="str">
+      <c r="J199" s="32" t="str">
         <f aca="false">IF(I199="","",ROUND(I199*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K199" s="6"/>
-      <c r="L199" s="27"/>
+      <c r="L199" s="26"/>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="24"/>
+      <c r="A200" s="30"/>
       <c r="B200" s="6"/>
       <c r="C200" s="8" t="str">
         <f aca="false">IF(OR(D200="",E200="",D200=E200),"",IF(E200&lt;D200,"BUY","SELL"))</f>
@@ -7131,19 +8062,19 @@
         <f aca="false">IF(I200="","",IF(I200&gt;0,"WIN",IF(I200&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I200" s="25" t="str">
+      <c r="I200" s="31" t="str">
         <f aca="false">IF(OR(G200="",C200=""),"",ROUND((G200-D200)/(D200-E200),2))</f>
         <v/>
       </c>
-      <c r="J200" s="26" t="str">
+      <c r="J200" s="32" t="str">
         <f aca="false">IF(I200="","",ROUND(I200*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K200" s="6"/>
-      <c r="L200" s="27"/>
+      <c r="L200" s="26"/>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="24"/>
+      <c r="A201" s="30"/>
       <c r="B201" s="6"/>
       <c r="C201" s="8" t="str">
         <f aca="false">IF(OR(D201="",E201="",D201=E201),"",IF(E201&lt;D201,"BUY","SELL"))</f>
@@ -7160,19 +8091,19 @@
         <f aca="false">IF(I201="","",IF(I201&gt;0,"WIN",IF(I201&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I201" s="25" t="str">
+      <c r="I201" s="31" t="str">
         <f aca="false">IF(OR(G201="",C201=""),"",ROUND((G201-D201)/(D201-E201),2))</f>
         <v/>
       </c>
-      <c r="J201" s="26" t="str">
+      <c r="J201" s="32" t="str">
         <f aca="false">IF(I201="","",ROUND(I201*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K201" s="6"/>
-      <c r="L201" s="27"/>
+      <c r="L201" s="26"/>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="24"/>
+      <c r="A202" s="30"/>
       <c r="B202" s="6"/>
       <c r="C202" s="8" t="str">
         <f aca="false">IF(OR(D202="",E202="",D202=E202),"",IF(E202&lt;D202,"BUY","SELL"))</f>
@@ -7189,19 +8120,19 @@
         <f aca="false">IF(I202="","",IF(I202&gt;0,"WIN",IF(I202&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I202" s="25" t="str">
+      <c r="I202" s="31" t="str">
         <f aca="false">IF(OR(G202="",C202=""),"",ROUND((G202-D202)/(D202-E202),2))</f>
         <v/>
       </c>
-      <c r="J202" s="26" t="str">
+      <c r="J202" s="32" t="str">
         <f aca="false">IF(I202="","",ROUND(I202*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K202" s="6"/>
-      <c r="L202" s="27"/>
+      <c r="L202" s="26"/>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="24"/>
+      <c r="A203" s="30"/>
       <c r="B203" s="6"/>
       <c r="C203" s="8" t="str">
         <f aca="false">IF(OR(D203="",E203="",D203=E203),"",IF(E203&lt;D203,"BUY","SELL"))</f>
@@ -7218,19 +8149,19 @@
         <f aca="false">IF(I203="","",IF(I203&gt;0,"WIN",IF(I203&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I203" s="25" t="str">
+      <c r="I203" s="31" t="str">
         <f aca="false">IF(OR(G203="",C203=""),"",ROUND((G203-D203)/(D203-E203),2))</f>
         <v/>
       </c>
-      <c r="J203" s="26" t="str">
+      <c r="J203" s="32" t="str">
         <f aca="false">IF(I203="","",ROUND(I203*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K203" s="6"/>
-      <c r="L203" s="27"/>
+      <c r="L203" s="26"/>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="24"/>
+      <c r="A204" s="30"/>
       <c r="B204" s="6"/>
       <c r="C204" s="8" t="str">
         <f aca="false">IF(OR(D204="",E204="",D204=E204),"",IF(E204&lt;D204,"BUY","SELL"))</f>
@@ -7247,19 +8178,19 @@
         <f aca="false">IF(I204="","",IF(I204&gt;0,"WIN",IF(I204&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I204" s="25" t="str">
+      <c r="I204" s="31" t="str">
         <f aca="false">IF(OR(G204="",C204=""),"",ROUND((G204-D204)/(D204-E204),2))</f>
         <v/>
       </c>
-      <c r="J204" s="26" t="str">
+      <c r="J204" s="32" t="str">
         <f aca="false">IF(I204="","",ROUND(I204*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K204" s="6"/>
-      <c r="L204" s="27"/>
+      <c r="L204" s="26"/>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="24"/>
+      <c r="A205" s="30"/>
       <c r="B205" s="6"/>
       <c r="C205" s="8" t="str">
         <f aca="false">IF(OR(D205="",E205="",D205=E205),"",IF(E205&lt;D205,"BUY","SELL"))</f>
@@ -7276,19 +8207,19 @@
         <f aca="false">IF(I205="","",IF(I205&gt;0,"WIN",IF(I205&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I205" s="25" t="str">
+      <c r="I205" s="31" t="str">
         <f aca="false">IF(OR(G205="",C205=""),"",ROUND((G205-D205)/(D205-E205),2))</f>
         <v/>
       </c>
-      <c r="J205" s="26" t="str">
+      <c r="J205" s="32" t="str">
         <f aca="false">IF(I205="","",ROUND(I205*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K205" s="6"/>
-      <c r="L205" s="27"/>
+      <c r="L205" s="26"/>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="24"/>
+      <c r="A206" s="30"/>
       <c r="B206" s="6"/>
       <c r="C206" s="8" t="str">
         <f aca="false">IF(OR(D206="",E206="",D206=E206),"",IF(E206&lt;D206,"BUY","SELL"))</f>
@@ -7305,16 +8236,16 @@
         <f aca="false">IF(I206="","",IF(I206&gt;0,"WIN",IF(I206&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I206" s="25" t="str">
+      <c r="I206" s="31" t="str">
         <f aca="false">IF(OR(G206="",C206=""),"",ROUND((G206-D206)/(D206-E206),2))</f>
         <v/>
       </c>
-      <c r="J206" s="26" t="str">
+      <c r="J206" s="32" t="str">
         <f aca="false">IF(I206="","",ROUND(I206*$M$2*$M$3,2))</f>
         <v/>
       </c>
       <c r="K206" s="6"/>
-      <c r="L206" s="27"/>
+      <c r="L206" s="26"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H7:H206">
@@ -7345,7 +8276,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -7360,213 +8291,213 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="28" t="s">
-        <v>84</v>
-      </c>
-      <c r="B3" s="29" t="n">
+      <c r="A3" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3" s="34" t="n">
         <f aca="false">COUNT('Trade Log'!I7:I206)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="B4" s="29" t="n">
+      <c r="A4" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="B4" s="34" t="n">
         <f aca="false">COUNTIF('Trade Log'!H7:H206,"WIN")</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="28" t="s">
-        <v>86</v>
-      </c>
-      <c r="B5" s="29" t="n">
+      <c r="A5" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" s="34" t="n">
         <f aca="false">COUNTIF('Trade Log'!H7:H206,"LOSS")</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="B6" s="30" t="n">
+      <c r="A6" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="B6" s="35" t="n">
         <f aca="false">IFERROR(B4/B3,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="28" t="s">
-        <v>88</v>
-      </c>
-      <c r="B7" s="31" t="n">
+      <c r="A7" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" s="36" t="n">
         <f aca="false">SUM('Trade Log'!I7:I206)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="B8" s="31" t="n">
+      <c r="A8" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="B8" s="36" t="n">
         <f aca="false">IFERROR(B7/B3,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="B9" s="30" t="n">
+      <c r="A9" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="B9" s="35" t="n">
         <f aca="false">IFERROR(COUNTIF('Trade Log'!K7:K206,"Yes")/B3,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="B10" s="32" t="n">
+      <c r="A10" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="B10" s="37" t="n">
         <f aca="false">SUM('Trade Log'!J7:J206)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="B11" s="23" t="n">
+      <c r="A11" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="B11" s="29" t="n">
         <f aca="false">'Trade Log'!M4</f>
         <v>10000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="33" t="s">
-        <v>92</v>
+      <c r="A13" s="38" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="34" t="str">
+      <c r="A14" s="39" t="str">
         <f aca="false">IF(B3&lt;50,"Not enough trades yet: "&amp;B3&amp;" of 50. Keep going.",IF(B9&lt;0.9,"You broke the rules too often. The results don't count yet.",IF(B8&gt;=0.15,"Looks promising. Keep going to 100 trades to be sure.",IF(B8&lt;=0,"Not working as it is. Stop and review.","Too close to call. Keep going to 100 trades."))))</f>
         <v>Not enough trades yet: 0 of 50. Keep going.</v>
       </c>
-      <c r="B14" s="34"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="33" t="s">
-        <v>94</v>
+      <c r="A18" s="38" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="17" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B20" s="35" t="n">
+        <v>36</v>
+      </c>
+      <c r="B20" s="22" t="n">
         <f aca="false">COUNTIFS('Trade Log'!B7:B206,A20,'Trade Log'!I7:I206,"&gt;-99")</f>
         <v>0</v>
       </c>
-      <c r="C20" s="25" t="n">
+      <c r="C20" s="31" t="n">
         <f aca="false">SUMIF('Trade Log'!B7:B206,A20,'Trade Log'!I7:I206)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B21" s="35" t="n">
+        <v>56</v>
+      </c>
+      <c r="B21" s="22" t="n">
         <f aca="false">COUNTIFS('Trade Log'!B7:B206,A21,'Trade Log'!I7:I206,"&gt;-99")</f>
         <v>0</v>
       </c>
-      <c r="C21" s="25" t="n">
+      <c r="C21" s="31" t="n">
         <f aca="false">SUMIF('Trade Log'!B7:B206,A21,'Trade Log'!I7:I206)</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B22" s="35" t="n">
+        <v>58</v>
+      </c>
+      <c r="B22" s="22" t="n">
         <f aca="false">COUNTIFS('Trade Log'!B7:B206,A22,'Trade Log'!I7:I206,"&gt;-99")</f>
         <v>0</v>
       </c>
-      <c r="C22" s="25" t="n">
+      <c r="C22" s="31" t="n">
         <f aca="false">SUMIF('Trade Log'!B7:B206,A22,'Trade Log'!I7:I206)</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="B23" s="35" t="n">
+        <v>59</v>
+      </c>
+      <c r="B23" s="22" t="n">
         <f aca="false">COUNTIFS('Trade Log'!B7:B206,A23,'Trade Log'!I7:I206,"&gt;-99")</f>
         <v>0</v>
       </c>
-      <c r="C23" s="25" t="n">
+      <c r="C23" s="31" t="n">
         <f aca="false">SUMIF('Trade Log'!B7:B206,A23,'Trade Log'!I7:I206)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B24" s="35" t="n">
+        <v>61</v>
+      </c>
+      <c r="B24" s="22" t="n">
         <f aca="false">COUNTIFS('Trade Log'!B7:B206,A24,'Trade Log'!I7:I206,"&gt;-99")</f>
         <v>0</v>
       </c>
-      <c r="C24" s="25" t="n">
+      <c r="C24" s="31" t="n">
         <f aca="false">SUMIF('Trade Log'!B7:B206,A24,'Trade Log'!I7:I206)</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="B25" s="35" t="n">
+        <v>63</v>
+      </c>
+      <c r="B25" s="22" t="n">
         <f aca="false">COUNTIFS('Trade Log'!B7:B206,A25,'Trade Log'!I7:I206,"&gt;-99")</f>
         <v>0</v>
       </c>
-      <c r="C25" s="25" t="n">
+      <c r="C25" s="31" t="n">
         <f aca="false">SUMIF('Trade Log'!B7:B206,A25,'Trade Log'!I7:I206)</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B26" s="35" t="n">
+        <v>65</v>
+      </c>
+      <c r="B26" s="22" t="n">
         <f aca="false">COUNTIFS('Trade Log'!B7:B206,A26,'Trade Log'!I7:I206,"&gt;-99")</f>
         <v>0</v>
       </c>
-      <c r="C26" s="25" t="n">
+      <c r="C26" s="31" t="n">
         <f aca="false">SUMIF('Trade Log'!B7:B206,A26,'Trade Log'!I7:I206)</f>
         <v>0</v>
       </c>

--- a/KLR_Simple_Tracker.xlsx
+++ b/KLR_Simple_Tracker.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="118">
   <si>
     <t xml:space="preserve">MY TRADING RULES</t>
   </si>
@@ -317,6 +317,12 @@
     <t xml:space="preserve">Followed all rules?</t>
   </si>
   <si>
+    <t xml:space="preserve">Rejection candle at zone?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arrived very fast / stretched?</t>
+  </si>
+  <si>
     <t xml:space="preserve">HOW AM I DOING?</t>
   </si>
   <si>
@@ -348,6 +354,30 @@
   </si>
   <si>
     <t xml:space="preserve">Trades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO THESE MATTER FOR ME?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Condition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rejection candle: Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rejection candle: No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arrived very fast: Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arrived very fast: No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After 20+ trades in each row, compare Yes vs No. Higher average R = that condition helps you.</t>
   </si>
 </sst>
 </file>
@@ -560,7 +590,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -669,6 +699,10 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="173" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -719,6 +753,10 @@
     </xf>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1454,7 +1492,7 @@
         <v>68</v>
       </c>
       <c r="B27" s="10" t="n">
-        <f aca="false">'Trade Log'!$M$2*'Trade Log'!$M$3</f>
+        <f aca="false">'Trade Log'!$O$2*'Trade Log'!$O$3</f>
         <v>50</v>
       </c>
       <c r="D27" s="15" t="s">
@@ -2357,7 +2395,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M206"/>
+  <dimension ref="A1:O206"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -2369,8 +2407,10 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2379,10 +2419,10 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L2" s="11" t="s">
+      <c r="N2" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="M2" s="27" t="n">
+      <c r="O2" s="28" t="n">
         <v>10000</v>
       </c>
     </row>
@@ -2390,10 +2430,10 @@
       <c r="A3" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="N3" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="M3" s="28" t="n">
+      <c r="O3" s="29" t="n">
         <v>0.005</v>
       </c>
     </row>
@@ -2401,11 +2441,11 @@
       <c r="A4" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="N4" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="M4" s="29" t="n">
-        <f aca="false">M2+SUM(J7:J206)</f>
+      <c r="O4" s="30" t="n">
+        <f aca="false">O2+SUM(J7:J206)</f>
         <v>10000</v>
       </c>
     </row>
@@ -2444,11 +2484,17 @@
         <v>96</v>
       </c>
       <c r="L6" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="M6" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="N6" s="17" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="30"/>
+      <c r="A7" s="31"/>
       <c r="B7" s="6"/>
       <c r="C7" s="8" t="str">
         <f aca="false">IF(OR(D7="",E7="",D7=E7),"",IF(E7&lt;D7,"BUY","SELL"))</f>
@@ -2465,19 +2511,21 @@
         <f aca="false">IF(I7="","",IF(I7&gt;0,"WIN",IF(I7&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I7" s="31" t="str">
+      <c r="I7" s="32" t="str">
         <f aca="false">IF(OR(G7="",C7=""),"",ROUND((G7-D7)/(D7-E7),2))</f>
         <v/>
       </c>
-      <c r="J7" s="32" t="str">
-        <f aca="false">IF(I7="","",ROUND(I7*$M$2*$M$3,2))</f>
+      <c r="J7" s="33" t="str">
+        <f aca="false">IF(I7="","",ROUND(I7*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K7" s="6"/>
-      <c r="L7" s="26"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="26"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="30"/>
+      <c r="A8" s="31"/>
       <c r="B8" s="6"/>
       <c r="C8" s="8" t="str">
         <f aca="false">IF(OR(D8="",E8="",D8=E8),"",IF(E8&lt;D8,"BUY","SELL"))</f>
@@ -2494,19 +2542,21 @@
         <f aca="false">IF(I8="","",IF(I8&gt;0,"WIN",IF(I8&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I8" s="31" t="str">
+      <c r="I8" s="32" t="str">
         <f aca="false">IF(OR(G8="",C8=""),"",ROUND((G8-D8)/(D8-E8),2))</f>
         <v/>
       </c>
-      <c r="J8" s="32" t="str">
-        <f aca="false">IF(I8="","",ROUND(I8*$M$2*$M$3,2))</f>
+      <c r="J8" s="33" t="str">
+        <f aca="false">IF(I8="","",ROUND(I8*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K8" s="6"/>
-      <c r="L8" s="26"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="26"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="30"/>
+      <c r="A9" s="31"/>
       <c r="B9" s="6"/>
       <c r="C9" s="8" t="str">
         <f aca="false">IF(OR(D9="",E9="",D9=E9),"",IF(E9&lt;D9,"BUY","SELL"))</f>
@@ -2523,19 +2573,21 @@
         <f aca="false">IF(I9="","",IF(I9&gt;0,"WIN",IF(I9&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I9" s="31" t="str">
+      <c r="I9" s="32" t="str">
         <f aca="false">IF(OR(G9="",C9=""),"",ROUND((G9-D9)/(D9-E9),2))</f>
         <v/>
       </c>
-      <c r="J9" s="32" t="str">
-        <f aca="false">IF(I9="","",ROUND(I9*$M$2*$M$3,2))</f>
+      <c r="J9" s="33" t="str">
+        <f aca="false">IF(I9="","",ROUND(I9*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K9" s="6"/>
-      <c r="L9" s="26"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="26"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="30"/>
+      <c r="A10" s="31"/>
       <c r="B10" s="6"/>
       <c r="C10" s="8" t="str">
         <f aca="false">IF(OR(D10="",E10="",D10=E10),"",IF(E10&lt;D10,"BUY","SELL"))</f>
@@ -2552,19 +2604,21 @@
         <f aca="false">IF(I10="","",IF(I10&gt;0,"WIN",IF(I10&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I10" s="31" t="str">
+      <c r="I10" s="32" t="str">
         <f aca="false">IF(OR(G10="",C10=""),"",ROUND((G10-D10)/(D10-E10),2))</f>
         <v/>
       </c>
-      <c r="J10" s="32" t="str">
-        <f aca="false">IF(I10="","",ROUND(I10*$M$2*$M$3,2))</f>
+      <c r="J10" s="33" t="str">
+        <f aca="false">IF(I10="","",ROUND(I10*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K10" s="6"/>
-      <c r="L10" s="26"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="26"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="30"/>
+      <c r="A11" s="31"/>
       <c r="B11" s="6"/>
       <c r="C11" s="8" t="str">
         <f aca="false">IF(OR(D11="",E11="",D11=E11),"",IF(E11&lt;D11,"BUY","SELL"))</f>
@@ -2581,19 +2635,21 @@
         <f aca="false">IF(I11="","",IF(I11&gt;0,"WIN",IF(I11&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I11" s="31" t="str">
+      <c r="I11" s="32" t="str">
         <f aca="false">IF(OR(G11="",C11=""),"",ROUND((G11-D11)/(D11-E11),2))</f>
         <v/>
       </c>
-      <c r="J11" s="32" t="str">
-        <f aca="false">IF(I11="","",ROUND(I11*$M$2*$M$3,2))</f>
+      <c r="J11" s="33" t="str">
+        <f aca="false">IF(I11="","",ROUND(I11*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K11" s="6"/>
-      <c r="L11" s="26"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="26"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="30"/>
+      <c r="A12" s="31"/>
       <c r="B12" s="6"/>
       <c r="C12" s="8" t="str">
         <f aca="false">IF(OR(D12="",E12="",D12=E12),"",IF(E12&lt;D12,"BUY","SELL"))</f>
@@ -2610,19 +2666,21 @@
         <f aca="false">IF(I12="","",IF(I12&gt;0,"WIN",IF(I12&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I12" s="31" t="str">
+      <c r="I12" s="32" t="str">
         <f aca="false">IF(OR(G12="",C12=""),"",ROUND((G12-D12)/(D12-E12),2))</f>
         <v/>
       </c>
-      <c r="J12" s="32" t="str">
-        <f aca="false">IF(I12="","",ROUND(I12*$M$2*$M$3,2))</f>
+      <c r="J12" s="33" t="str">
+        <f aca="false">IF(I12="","",ROUND(I12*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K12" s="6"/>
-      <c r="L12" s="26"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="26"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="30"/>
+      <c r="A13" s="31"/>
       <c r="B13" s="6"/>
       <c r="C13" s="8" t="str">
         <f aca="false">IF(OR(D13="",E13="",D13=E13),"",IF(E13&lt;D13,"BUY","SELL"))</f>
@@ -2639,19 +2697,21 @@
         <f aca="false">IF(I13="","",IF(I13&gt;0,"WIN",IF(I13&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I13" s="31" t="str">
+      <c r="I13" s="32" t="str">
         <f aca="false">IF(OR(G13="",C13=""),"",ROUND((G13-D13)/(D13-E13),2))</f>
         <v/>
       </c>
-      <c r="J13" s="32" t="str">
-        <f aca="false">IF(I13="","",ROUND(I13*$M$2*$M$3,2))</f>
+      <c r="J13" s="33" t="str">
+        <f aca="false">IF(I13="","",ROUND(I13*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K13" s="6"/>
-      <c r="L13" s="26"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="26"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="30"/>
+      <c r="A14" s="31"/>
       <c r="B14" s="6"/>
       <c r="C14" s="8" t="str">
         <f aca="false">IF(OR(D14="",E14="",D14=E14),"",IF(E14&lt;D14,"BUY","SELL"))</f>
@@ -2668,19 +2728,21 @@
         <f aca="false">IF(I14="","",IF(I14&gt;0,"WIN",IF(I14&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I14" s="31" t="str">
+      <c r="I14" s="32" t="str">
         <f aca="false">IF(OR(G14="",C14=""),"",ROUND((G14-D14)/(D14-E14),2))</f>
         <v/>
       </c>
-      <c r="J14" s="32" t="str">
-        <f aca="false">IF(I14="","",ROUND(I14*$M$2*$M$3,2))</f>
+      <c r="J14" s="33" t="str">
+        <f aca="false">IF(I14="","",ROUND(I14*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K14" s="6"/>
-      <c r="L14" s="26"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="26"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="30"/>
+      <c r="A15" s="31"/>
       <c r="B15" s="6"/>
       <c r="C15" s="8" t="str">
         <f aca="false">IF(OR(D15="",E15="",D15=E15),"",IF(E15&lt;D15,"BUY","SELL"))</f>
@@ -2697,19 +2759,21 @@
         <f aca="false">IF(I15="","",IF(I15&gt;0,"WIN",IF(I15&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I15" s="31" t="str">
+      <c r="I15" s="32" t="str">
         <f aca="false">IF(OR(G15="",C15=""),"",ROUND((G15-D15)/(D15-E15),2))</f>
         <v/>
       </c>
-      <c r="J15" s="32" t="str">
-        <f aca="false">IF(I15="","",ROUND(I15*$M$2*$M$3,2))</f>
+      <c r="J15" s="33" t="str">
+        <f aca="false">IF(I15="","",ROUND(I15*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K15" s="6"/>
-      <c r="L15" s="26"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="26"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="30"/>
+      <c r="A16" s="31"/>
       <c r="B16" s="6"/>
       <c r="C16" s="8" t="str">
         <f aca="false">IF(OR(D16="",E16="",D16=E16),"",IF(E16&lt;D16,"BUY","SELL"))</f>
@@ -2726,19 +2790,21 @@
         <f aca="false">IF(I16="","",IF(I16&gt;0,"WIN",IF(I16&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I16" s="31" t="str">
+      <c r="I16" s="32" t="str">
         <f aca="false">IF(OR(G16="",C16=""),"",ROUND((G16-D16)/(D16-E16),2))</f>
         <v/>
       </c>
-      <c r="J16" s="32" t="str">
-        <f aca="false">IF(I16="","",ROUND(I16*$M$2*$M$3,2))</f>
+      <c r="J16" s="33" t="str">
+        <f aca="false">IF(I16="","",ROUND(I16*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K16" s="6"/>
-      <c r="L16" s="26"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="26"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="30"/>
+      <c r="A17" s="31"/>
       <c r="B17" s="6"/>
       <c r="C17" s="8" t="str">
         <f aca="false">IF(OR(D17="",E17="",D17=E17),"",IF(E17&lt;D17,"BUY","SELL"))</f>
@@ -2755,19 +2821,21 @@
         <f aca="false">IF(I17="","",IF(I17&gt;0,"WIN",IF(I17&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I17" s="31" t="str">
+      <c r="I17" s="32" t="str">
         <f aca="false">IF(OR(G17="",C17=""),"",ROUND((G17-D17)/(D17-E17),2))</f>
         <v/>
       </c>
-      <c r="J17" s="32" t="str">
-        <f aca="false">IF(I17="","",ROUND(I17*$M$2*$M$3,2))</f>
+      <c r="J17" s="33" t="str">
+        <f aca="false">IF(I17="","",ROUND(I17*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K17" s="6"/>
-      <c r="L17" s="26"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="26"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="30"/>
+      <c r="A18" s="31"/>
       <c r="B18" s="6"/>
       <c r="C18" s="8" t="str">
         <f aca="false">IF(OR(D18="",E18="",D18=E18),"",IF(E18&lt;D18,"BUY","SELL"))</f>
@@ -2784,19 +2852,21 @@
         <f aca="false">IF(I18="","",IF(I18&gt;0,"WIN",IF(I18&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I18" s="31" t="str">
+      <c r="I18" s="32" t="str">
         <f aca="false">IF(OR(G18="",C18=""),"",ROUND((G18-D18)/(D18-E18),2))</f>
         <v/>
       </c>
-      <c r="J18" s="32" t="str">
-        <f aca="false">IF(I18="","",ROUND(I18*$M$2*$M$3,2))</f>
+      <c r="J18" s="33" t="str">
+        <f aca="false">IF(I18="","",ROUND(I18*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K18" s="6"/>
-      <c r="L18" s="26"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="26"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="30"/>
+      <c r="A19" s="31"/>
       <c r="B19" s="6"/>
       <c r="C19" s="8" t="str">
         <f aca="false">IF(OR(D19="",E19="",D19=E19),"",IF(E19&lt;D19,"BUY","SELL"))</f>
@@ -2813,19 +2883,21 @@
         <f aca="false">IF(I19="","",IF(I19&gt;0,"WIN",IF(I19&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I19" s="31" t="str">
+      <c r="I19" s="32" t="str">
         <f aca="false">IF(OR(G19="",C19=""),"",ROUND((G19-D19)/(D19-E19),2))</f>
         <v/>
       </c>
-      <c r="J19" s="32" t="str">
-        <f aca="false">IF(I19="","",ROUND(I19*$M$2*$M$3,2))</f>
+      <c r="J19" s="33" t="str">
+        <f aca="false">IF(I19="","",ROUND(I19*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K19" s="6"/>
-      <c r="L19" s="26"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="26"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="30"/>
+      <c r="A20" s="31"/>
       <c r="B20" s="6"/>
       <c r="C20" s="8" t="str">
         <f aca="false">IF(OR(D20="",E20="",D20=E20),"",IF(E20&lt;D20,"BUY","SELL"))</f>
@@ -2842,19 +2914,21 @@
         <f aca="false">IF(I20="","",IF(I20&gt;0,"WIN",IF(I20&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I20" s="31" t="str">
+      <c r="I20" s="32" t="str">
         <f aca="false">IF(OR(G20="",C20=""),"",ROUND((G20-D20)/(D20-E20),2))</f>
         <v/>
       </c>
-      <c r="J20" s="32" t="str">
-        <f aca="false">IF(I20="","",ROUND(I20*$M$2*$M$3,2))</f>
+      <c r="J20" s="33" t="str">
+        <f aca="false">IF(I20="","",ROUND(I20*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K20" s="6"/>
-      <c r="L20" s="26"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="26"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="30"/>
+      <c r="A21" s="31"/>
       <c r="B21" s="6"/>
       <c r="C21" s="8" t="str">
         <f aca="false">IF(OR(D21="",E21="",D21=E21),"",IF(E21&lt;D21,"BUY","SELL"))</f>
@@ -2871,19 +2945,21 @@
         <f aca="false">IF(I21="","",IF(I21&gt;0,"WIN",IF(I21&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I21" s="31" t="str">
+      <c r="I21" s="32" t="str">
         <f aca="false">IF(OR(G21="",C21=""),"",ROUND((G21-D21)/(D21-E21),2))</f>
         <v/>
       </c>
-      <c r="J21" s="32" t="str">
-        <f aca="false">IF(I21="","",ROUND(I21*$M$2*$M$3,2))</f>
+      <c r="J21" s="33" t="str">
+        <f aca="false">IF(I21="","",ROUND(I21*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K21" s="6"/>
-      <c r="L21" s="26"/>
+      <c r="L21" s="6"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="26"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="30"/>
+      <c r="A22" s="31"/>
       <c r="B22" s="6"/>
       <c r="C22" s="8" t="str">
         <f aca="false">IF(OR(D22="",E22="",D22=E22),"",IF(E22&lt;D22,"BUY","SELL"))</f>
@@ -2900,19 +2976,21 @@
         <f aca="false">IF(I22="","",IF(I22&gt;0,"WIN",IF(I22&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I22" s="31" t="str">
+      <c r="I22" s="32" t="str">
         <f aca="false">IF(OR(G22="",C22=""),"",ROUND((G22-D22)/(D22-E22),2))</f>
         <v/>
       </c>
-      <c r="J22" s="32" t="str">
-        <f aca="false">IF(I22="","",ROUND(I22*$M$2*$M$3,2))</f>
+      <c r="J22" s="33" t="str">
+        <f aca="false">IF(I22="","",ROUND(I22*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K22" s="6"/>
-      <c r="L22" s="26"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="26"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="30"/>
+      <c r="A23" s="31"/>
       <c r="B23" s="6"/>
       <c r="C23" s="8" t="str">
         <f aca="false">IF(OR(D23="",E23="",D23=E23),"",IF(E23&lt;D23,"BUY","SELL"))</f>
@@ -2929,19 +3007,21 @@
         <f aca="false">IF(I23="","",IF(I23&gt;0,"WIN",IF(I23&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I23" s="31" t="str">
+      <c r="I23" s="32" t="str">
         <f aca="false">IF(OR(G23="",C23=""),"",ROUND((G23-D23)/(D23-E23),2))</f>
         <v/>
       </c>
-      <c r="J23" s="32" t="str">
-        <f aca="false">IF(I23="","",ROUND(I23*$M$2*$M$3,2))</f>
+      <c r="J23" s="33" t="str">
+        <f aca="false">IF(I23="","",ROUND(I23*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K23" s="6"/>
-      <c r="L23" s="26"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="26"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="30"/>
+      <c r="A24" s="31"/>
       <c r="B24" s="6"/>
       <c r="C24" s="8" t="str">
         <f aca="false">IF(OR(D24="",E24="",D24=E24),"",IF(E24&lt;D24,"BUY","SELL"))</f>
@@ -2958,19 +3038,21 @@
         <f aca="false">IF(I24="","",IF(I24&gt;0,"WIN",IF(I24&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I24" s="31" t="str">
+      <c r="I24" s="32" t="str">
         <f aca="false">IF(OR(G24="",C24=""),"",ROUND((G24-D24)/(D24-E24),2))</f>
         <v/>
       </c>
-      <c r="J24" s="32" t="str">
-        <f aca="false">IF(I24="","",ROUND(I24*$M$2*$M$3,2))</f>
+      <c r="J24" s="33" t="str">
+        <f aca="false">IF(I24="","",ROUND(I24*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K24" s="6"/>
-      <c r="L24" s="26"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
+      <c r="N24" s="26"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="30"/>
+      <c r="A25" s="31"/>
       <c r="B25" s="6"/>
       <c r="C25" s="8" t="str">
         <f aca="false">IF(OR(D25="",E25="",D25=E25),"",IF(E25&lt;D25,"BUY","SELL"))</f>
@@ -2987,19 +3069,21 @@
         <f aca="false">IF(I25="","",IF(I25&gt;0,"WIN",IF(I25&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I25" s="31" t="str">
+      <c r="I25" s="32" t="str">
         <f aca="false">IF(OR(G25="",C25=""),"",ROUND((G25-D25)/(D25-E25),2))</f>
         <v/>
       </c>
-      <c r="J25" s="32" t="str">
-        <f aca="false">IF(I25="","",ROUND(I25*$M$2*$M$3,2))</f>
+      <c r="J25" s="33" t="str">
+        <f aca="false">IF(I25="","",ROUND(I25*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K25" s="6"/>
-      <c r="L25" s="26"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="26"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="30"/>
+      <c r="A26" s="31"/>
       <c r="B26" s="6"/>
       <c r="C26" s="8" t="str">
         <f aca="false">IF(OR(D26="",E26="",D26=E26),"",IF(E26&lt;D26,"BUY","SELL"))</f>
@@ -3016,19 +3100,21 @@
         <f aca="false">IF(I26="","",IF(I26&gt;0,"WIN",IF(I26&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I26" s="31" t="str">
+      <c r="I26" s="32" t="str">
         <f aca="false">IF(OR(G26="",C26=""),"",ROUND((G26-D26)/(D26-E26),2))</f>
         <v/>
       </c>
-      <c r="J26" s="32" t="str">
-        <f aca="false">IF(I26="","",ROUND(I26*$M$2*$M$3,2))</f>
+      <c r="J26" s="33" t="str">
+        <f aca="false">IF(I26="","",ROUND(I26*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K26" s="6"/>
-      <c r="L26" s="26"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
+      <c r="N26" s="26"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="30"/>
+      <c r="A27" s="31"/>
       <c r="B27" s="6"/>
       <c r="C27" s="8" t="str">
         <f aca="false">IF(OR(D27="",E27="",D27=E27),"",IF(E27&lt;D27,"BUY","SELL"))</f>
@@ -3045,19 +3131,21 @@
         <f aca="false">IF(I27="","",IF(I27&gt;0,"WIN",IF(I27&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I27" s="31" t="str">
+      <c r="I27" s="32" t="str">
         <f aca="false">IF(OR(G27="",C27=""),"",ROUND((G27-D27)/(D27-E27),2))</f>
         <v/>
       </c>
-      <c r="J27" s="32" t="str">
-        <f aca="false">IF(I27="","",ROUND(I27*$M$2*$M$3,2))</f>
+      <c r="J27" s="33" t="str">
+        <f aca="false">IF(I27="","",ROUND(I27*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K27" s="6"/>
-      <c r="L27" s="26"/>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6"/>
+      <c r="N27" s="26"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="30"/>
+      <c r="A28" s="31"/>
       <c r="B28" s="6"/>
       <c r="C28" s="8" t="str">
         <f aca="false">IF(OR(D28="",E28="",D28=E28),"",IF(E28&lt;D28,"BUY","SELL"))</f>
@@ -3074,19 +3162,21 @@
         <f aca="false">IF(I28="","",IF(I28&gt;0,"WIN",IF(I28&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I28" s="31" t="str">
+      <c r="I28" s="32" t="str">
         <f aca="false">IF(OR(G28="",C28=""),"",ROUND((G28-D28)/(D28-E28),2))</f>
         <v/>
       </c>
-      <c r="J28" s="32" t="str">
-        <f aca="false">IF(I28="","",ROUND(I28*$M$2*$M$3,2))</f>
+      <c r="J28" s="33" t="str">
+        <f aca="false">IF(I28="","",ROUND(I28*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K28" s="6"/>
-      <c r="L28" s="26"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="6"/>
+      <c r="N28" s="26"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="30"/>
+      <c r="A29" s="31"/>
       <c r="B29" s="6"/>
       <c r="C29" s="8" t="str">
         <f aca="false">IF(OR(D29="",E29="",D29=E29),"",IF(E29&lt;D29,"BUY","SELL"))</f>
@@ -3103,19 +3193,21 @@
         <f aca="false">IF(I29="","",IF(I29&gt;0,"WIN",IF(I29&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I29" s="31" t="str">
+      <c r="I29" s="32" t="str">
         <f aca="false">IF(OR(G29="",C29=""),"",ROUND((G29-D29)/(D29-E29),2))</f>
         <v/>
       </c>
-      <c r="J29" s="32" t="str">
-        <f aca="false">IF(I29="","",ROUND(I29*$M$2*$M$3,2))</f>
+      <c r="J29" s="33" t="str">
+        <f aca="false">IF(I29="","",ROUND(I29*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K29" s="6"/>
-      <c r="L29" s="26"/>
+      <c r="L29" s="6"/>
+      <c r="M29" s="6"/>
+      <c r="N29" s="26"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="30"/>
+      <c r="A30" s="31"/>
       <c r="B30" s="6"/>
       <c r="C30" s="8" t="str">
         <f aca="false">IF(OR(D30="",E30="",D30=E30),"",IF(E30&lt;D30,"BUY","SELL"))</f>
@@ -3132,19 +3224,21 @@
         <f aca="false">IF(I30="","",IF(I30&gt;0,"WIN",IF(I30&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I30" s="31" t="str">
+      <c r="I30" s="32" t="str">
         <f aca="false">IF(OR(G30="",C30=""),"",ROUND((G30-D30)/(D30-E30),2))</f>
         <v/>
       </c>
-      <c r="J30" s="32" t="str">
-        <f aca="false">IF(I30="","",ROUND(I30*$M$2*$M$3,2))</f>
+      <c r="J30" s="33" t="str">
+        <f aca="false">IF(I30="","",ROUND(I30*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K30" s="6"/>
-      <c r="L30" s="26"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="6"/>
+      <c r="N30" s="26"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="30"/>
+      <c r="A31" s="31"/>
       <c r="B31" s="6"/>
       <c r="C31" s="8" t="str">
         <f aca="false">IF(OR(D31="",E31="",D31=E31),"",IF(E31&lt;D31,"BUY","SELL"))</f>
@@ -3161,19 +3255,21 @@
         <f aca="false">IF(I31="","",IF(I31&gt;0,"WIN",IF(I31&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I31" s="31" t="str">
+      <c r="I31" s="32" t="str">
         <f aca="false">IF(OR(G31="",C31=""),"",ROUND((G31-D31)/(D31-E31),2))</f>
         <v/>
       </c>
-      <c r="J31" s="32" t="str">
-        <f aca="false">IF(I31="","",ROUND(I31*$M$2*$M$3,2))</f>
+      <c r="J31" s="33" t="str">
+        <f aca="false">IF(I31="","",ROUND(I31*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K31" s="6"/>
-      <c r="L31" s="26"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="26"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="30"/>
+      <c r="A32" s="31"/>
       <c r="B32" s="6"/>
       <c r="C32" s="8" t="str">
         <f aca="false">IF(OR(D32="",E32="",D32=E32),"",IF(E32&lt;D32,"BUY","SELL"))</f>
@@ -3190,19 +3286,21 @@
         <f aca="false">IF(I32="","",IF(I32&gt;0,"WIN",IF(I32&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I32" s="31" t="str">
+      <c r="I32" s="32" t="str">
         <f aca="false">IF(OR(G32="",C32=""),"",ROUND((G32-D32)/(D32-E32),2))</f>
         <v/>
       </c>
-      <c r="J32" s="32" t="str">
-        <f aca="false">IF(I32="","",ROUND(I32*$M$2*$M$3,2))</f>
+      <c r="J32" s="33" t="str">
+        <f aca="false">IF(I32="","",ROUND(I32*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K32" s="6"/>
-      <c r="L32" s="26"/>
+      <c r="L32" s="6"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="26"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="30"/>
+      <c r="A33" s="31"/>
       <c r="B33" s="6"/>
       <c r="C33" s="8" t="str">
         <f aca="false">IF(OR(D33="",E33="",D33=E33),"",IF(E33&lt;D33,"BUY","SELL"))</f>
@@ -3219,19 +3317,21 @@
         <f aca="false">IF(I33="","",IF(I33&gt;0,"WIN",IF(I33&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I33" s="31" t="str">
+      <c r="I33" s="32" t="str">
         <f aca="false">IF(OR(G33="",C33=""),"",ROUND((G33-D33)/(D33-E33),2))</f>
         <v/>
       </c>
-      <c r="J33" s="32" t="str">
-        <f aca="false">IF(I33="","",ROUND(I33*$M$2*$M$3,2))</f>
+      <c r="J33" s="33" t="str">
+        <f aca="false">IF(I33="","",ROUND(I33*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K33" s="6"/>
-      <c r="L33" s="26"/>
+      <c r="L33" s="6"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="26"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="30"/>
+      <c r="A34" s="31"/>
       <c r="B34" s="6"/>
       <c r="C34" s="8" t="str">
         <f aca="false">IF(OR(D34="",E34="",D34=E34),"",IF(E34&lt;D34,"BUY","SELL"))</f>
@@ -3248,19 +3348,21 @@
         <f aca="false">IF(I34="","",IF(I34&gt;0,"WIN",IF(I34&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I34" s="31" t="str">
+      <c r="I34" s="32" t="str">
         <f aca="false">IF(OR(G34="",C34=""),"",ROUND((G34-D34)/(D34-E34),2))</f>
         <v/>
       </c>
-      <c r="J34" s="32" t="str">
-        <f aca="false">IF(I34="","",ROUND(I34*$M$2*$M$3,2))</f>
+      <c r="J34" s="33" t="str">
+        <f aca="false">IF(I34="","",ROUND(I34*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K34" s="6"/>
-      <c r="L34" s="26"/>
+      <c r="L34" s="6"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="26"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="30"/>
+      <c r="A35" s="31"/>
       <c r="B35" s="6"/>
       <c r="C35" s="8" t="str">
         <f aca="false">IF(OR(D35="",E35="",D35=E35),"",IF(E35&lt;D35,"BUY","SELL"))</f>
@@ -3277,19 +3379,21 @@
         <f aca="false">IF(I35="","",IF(I35&gt;0,"WIN",IF(I35&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I35" s="31" t="str">
+      <c r="I35" s="32" t="str">
         <f aca="false">IF(OR(G35="",C35=""),"",ROUND((G35-D35)/(D35-E35),2))</f>
         <v/>
       </c>
-      <c r="J35" s="32" t="str">
-        <f aca="false">IF(I35="","",ROUND(I35*$M$2*$M$3,2))</f>
+      <c r="J35" s="33" t="str">
+        <f aca="false">IF(I35="","",ROUND(I35*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K35" s="6"/>
-      <c r="L35" s="26"/>
+      <c r="L35" s="6"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="26"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="30"/>
+      <c r="A36" s="31"/>
       <c r="B36" s="6"/>
       <c r="C36" s="8" t="str">
         <f aca="false">IF(OR(D36="",E36="",D36=E36),"",IF(E36&lt;D36,"BUY","SELL"))</f>
@@ -3306,19 +3410,21 @@
         <f aca="false">IF(I36="","",IF(I36&gt;0,"WIN",IF(I36&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I36" s="31" t="str">
+      <c r="I36" s="32" t="str">
         <f aca="false">IF(OR(G36="",C36=""),"",ROUND((G36-D36)/(D36-E36),2))</f>
         <v/>
       </c>
-      <c r="J36" s="32" t="str">
-        <f aca="false">IF(I36="","",ROUND(I36*$M$2*$M$3,2))</f>
+      <c r="J36" s="33" t="str">
+        <f aca="false">IF(I36="","",ROUND(I36*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K36" s="6"/>
-      <c r="L36" s="26"/>
+      <c r="L36" s="6"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="26"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="30"/>
+      <c r="A37" s="31"/>
       <c r="B37" s="6"/>
       <c r="C37" s="8" t="str">
         <f aca="false">IF(OR(D37="",E37="",D37=E37),"",IF(E37&lt;D37,"BUY","SELL"))</f>
@@ -3335,19 +3441,21 @@
         <f aca="false">IF(I37="","",IF(I37&gt;0,"WIN",IF(I37&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I37" s="31" t="str">
+      <c r="I37" s="32" t="str">
         <f aca="false">IF(OR(G37="",C37=""),"",ROUND((G37-D37)/(D37-E37),2))</f>
         <v/>
       </c>
-      <c r="J37" s="32" t="str">
-        <f aca="false">IF(I37="","",ROUND(I37*$M$2*$M$3,2))</f>
+      <c r="J37" s="33" t="str">
+        <f aca="false">IF(I37="","",ROUND(I37*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K37" s="6"/>
-      <c r="L37" s="26"/>
+      <c r="L37" s="6"/>
+      <c r="M37" s="6"/>
+      <c r="N37" s="26"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="30"/>
+      <c r="A38" s="31"/>
       <c r="B38" s="6"/>
       <c r="C38" s="8" t="str">
         <f aca="false">IF(OR(D38="",E38="",D38=E38),"",IF(E38&lt;D38,"BUY","SELL"))</f>
@@ -3364,19 +3472,21 @@
         <f aca="false">IF(I38="","",IF(I38&gt;0,"WIN",IF(I38&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I38" s="31" t="str">
+      <c r="I38" s="32" t="str">
         <f aca="false">IF(OR(G38="",C38=""),"",ROUND((G38-D38)/(D38-E38),2))</f>
         <v/>
       </c>
-      <c r="J38" s="32" t="str">
-        <f aca="false">IF(I38="","",ROUND(I38*$M$2*$M$3,2))</f>
+      <c r="J38" s="33" t="str">
+        <f aca="false">IF(I38="","",ROUND(I38*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K38" s="6"/>
-      <c r="L38" s="26"/>
+      <c r="L38" s="6"/>
+      <c r="M38" s="6"/>
+      <c r="N38" s="26"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="30"/>
+      <c r="A39" s="31"/>
       <c r="B39" s="6"/>
       <c r="C39" s="8" t="str">
         <f aca="false">IF(OR(D39="",E39="",D39=E39),"",IF(E39&lt;D39,"BUY","SELL"))</f>
@@ -3393,19 +3503,21 @@
         <f aca="false">IF(I39="","",IF(I39&gt;0,"WIN",IF(I39&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I39" s="31" t="str">
+      <c r="I39" s="32" t="str">
         <f aca="false">IF(OR(G39="",C39=""),"",ROUND((G39-D39)/(D39-E39),2))</f>
         <v/>
       </c>
-      <c r="J39" s="32" t="str">
-        <f aca="false">IF(I39="","",ROUND(I39*$M$2*$M$3,2))</f>
+      <c r="J39" s="33" t="str">
+        <f aca="false">IF(I39="","",ROUND(I39*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K39" s="6"/>
-      <c r="L39" s="26"/>
+      <c r="L39" s="6"/>
+      <c r="M39" s="6"/>
+      <c r="N39" s="26"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="30"/>
+      <c r="A40" s="31"/>
       <c r="B40" s="6"/>
       <c r="C40" s="8" t="str">
         <f aca="false">IF(OR(D40="",E40="",D40=E40),"",IF(E40&lt;D40,"BUY","SELL"))</f>
@@ -3422,19 +3534,21 @@
         <f aca="false">IF(I40="","",IF(I40&gt;0,"WIN",IF(I40&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I40" s="31" t="str">
+      <c r="I40" s="32" t="str">
         <f aca="false">IF(OR(G40="",C40=""),"",ROUND((G40-D40)/(D40-E40),2))</f>
         <v/>
       </c>
-      <c r="J40" s="32" t="str">
-        <f aca="false">IF(I40="","",ROUND(I40*$M$2*$M$3,2))</f>
+      <c r="J40" s="33" t="str">
+        <f aca="false">IF(I40="","",ROUND(I40*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K40" s="6"/>
-      <c r="L40" s="26"/>
+      <c r="L40" s="6"/>
+      <c r="M40" s="6"/>
+      <c r="N40" s="26"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="30"/>
+      <c r="A41" s="31"/>
       <c r="B41" s="6"/>
       <c r="C41" s="8" t="str">
         <f aca="false">IF(OR(D41="",E41="",D41=E41),"",IF(E41&lt;D41,"BUY","SELL"))</f>
@@ -3451,19 +3565,21 @@
         <f aca="false">IF(I41="","",IF(I41&gt;0,"WIN",IF(I41&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I41" s="31" t="str">
+      <c r="I41" s="32" t="str">
         <f aca="false">IF(OR(G41="",C41=""),"",ROUND((G41-D41)/(D41-E41),2))</f>
         <v/>
       </c>
-      <c r="J41" s="32" t="str">
-        <f aca="false">IF(I41="","",ROUND(I41*$M$2*$M$3,2))</f>
+      <c r="J41" s="33" t="str">
+        <f aca="false">IF(I41="","",ROUND(I41*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K41" s="6"/>
-      <c r="L41" s="26"/>
+      <c r="L41" s="6"/>
+      <c r="M41" s="6"/>
+      <c r="N41" s="26"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="30"/>
+      <c r="A42" s="31"/>
       <c r="B42" s="6"/>
       <c r="C42" s="8" t="str">
         <f aca="false">IF(OR(D42="",E42="",D42=E42),"",IF(E42&lt;D42,"BUY","SELL"))</f>
@@ -3480,19 +3596,21 @@
         <f aca="false">IF(I42="","",IF(I42&gt;0,"WIN",IF(I42&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I42" s="31" t="str">
+      <c r="I42" s="32" t="str">
         <f aca="false">IF(OR(G42="",C42=""),"",ROUND((G42-D42)/(D42-E42),2))</f>
         <v/>
       </c>
-      <c r="J42" s="32" t="str">
-        <f aca="false">IF(I42="","",ROUND(I42*$M$2*$M$3,2))</f>
+      <c r="J42" s="33" t="str">
+        <f aca="false">IF(I42="","",ROUND(I42*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K42" s="6"/>
-      <c r="L42" s="26"/>
+      <c r="L42" s="6"/>
+      <c r="M42" s="6"/>
+      <c r="N42" s="26"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="30"/>
+      <c r="A43" s="31"/>
       <c r="B43" s="6"/>
       <c r="C43" s="8" t="str">
         <f aca="false">IF(OR(D43="",E43="",D43=E43),"",IF(E43&lt;D43,"BUY","SELL"))</f>
@@ -3509,19 +3627,21 @@
         <f aca="false">IF(I43="","",IF(I43&gt;0,"WIN",IF(I43&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I43" s="31" t="str">
+      <c r="I43" s="32" t="str">
         <f aca="false">IF(OR(G43="",C43=""),"",ROUND((G43-D43)/(D43-E43),2))</f>
         <v/>
       </c>
-      <c r="J43" s="32" t="str">
-        <f aca="false">IF(I43="","",ROUND(I43*$M$2*$M$3,2))</f>
+      <c r="J43" s="33" t="str">
+        <f aca="false">IF(I43="","",ROUND(I43*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K43" s="6"/>
-      <c r="L43" s="26"/>
+      <c r="L43" s="6"/>
+      <c r="M43" s="6"/>
+      <c r="N43" s="26"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="30"/>
+      <c r="A44" s="31"/>
       <c r="B44" s="6"/>
       <c r="C44" s="8" t="str">
         <f aca="false">IF(OR(D44="",E44="",D44=E44),"",IF(E44&lt;D44,"BUY","SELL"))</f>
@@ -3538,19 +3658,21 @@
         <f aca="false">IF(I44="","",IF(I44&gt;0,"WIN",IF(I44&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I44" s="31" t="str">
+      <c r="I44" s="32" t="str">
         <f aca="false">IF(OR(G44="",C44=""),"",ROUND((G44-D44)/(D44-E44),2))</f>
         <v/>
       </c>
-      <c r="J44" s="32" t="str">
-        <f aca="false">IF(I44="","",ROUND(I44*$M$2*$M$3,2))</f>
+      <c r="J44" s="33" t="str">
+        <f aca="false">IF(I44="","",ROUND(I44*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K44" s="6"/>
-      <c r="L44" s="26"/>
+      <c r="L44" s="6"/>
+      <c r="M44" s="6"/>
+      <c r="N44" s="26"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="30"/>
+      <c r="A45" s="31"/>
       <c r="B45" s="6"/>
       <c r="C45" s="8" t="str">
         <f aca="false">IF(OR(D45="",E45="",D45=E45),"",IF(E45&lt;D45,"BUY","SELL"))</f>
@@ -3567,19 +3689,21 @@
         <f aca="false">IF(I45="","",IF(I45&gt;0,"WIN",IF(I45&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I45" s="31" t="str">
+      <c r="I45" s="32" t="str">
         <f aca="false">IF(OR(G45="",C45=""),"",ROUND((G45-D45)/(D45-E45),2))</f>
         <v/>
       </c>
-      <c r="J45" s="32" t="str">
-        <f aca="false">IF(I45="","",ROUND(I45*$M$2*$M$3,2))</f>
+      <c r="J45" s="33" t="str">
+        <f aca="false">IF(I45="","",ROUND(I45*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K45" s="6"/>
-      <c r="L45" s="26"/>
+      <c r="L45" s="6"/>
+      <c r="M45" s="6"/>
+      <c r="N45" s="26"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="30"/>
+      <c r="A46" s="31"/>
       <c r="B46" s="6"/>
       <c r="C46" s="8" t="str">
         <f aca="false">IF(OR(D46="",E46="",D46=E46),"",IF(E46&lt;D46,"BUY","SELL"))</f>
@@ -3596,19 +3720,21 @@
         <f aca="false">IF(I46="","",IF(I46&gt;0,"WIN",IF(I46&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I46" s="31" t="str">
+      <c r="I46" s="32" t="str">
         <f aca="false">IF(OR(G46="",C46=""),"",ROUND((G46-D46)/(D46-E46),2))</f>
         <v/>
       </c>
-      <c r="J46" s="32" t="str">
-        <f aca="false">IF(I46="","",ROUND(I46*$M$2*$M$3,2))</f>
+      <c r="J46" s="33" t="str">
+        <f aca="false">IF(I46="","",ROUND(I46*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K46" s="6"/>
-      <c r="L46" s="26"/>
+      <c r="L46" s="6"/>
+      <c r="M46" s="6"/>
+      <c r="N46" s="26"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="30"/>
+      <c r="A47" s="31"/>
       <c r="B47" s="6"/>
       <c r="C47" s="8" t="str">
         <f aca="false">IF(OR(D47="",E47="",D47=E47),"",IF(E47&lt;D47,"BUY","SELL"))</f>
@@ -3625,19 +3751,21 @@
         <f aca="false">IF(I47="","",IF(I47&gt;0,"WIN",IF(I47&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I47" s="31" t="str">
+      <c r="I47" s="32" t="str">
         <f aca="false">IF(OR(G47="",C47=""),"",ROUND((G47-D47)/(D47-E47),2))</f>
         <v/>
       </c>
-      <c r="J47" s="32" t="str">
-        <f aca="false">IF(I47="","",ROUND(I47*$M$2*$M$3,2))</f>
+      <c r="J47" s="33" t="str">
+        <f aca="false">IF(I47="","",ROUND(I47*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K47" s="6"/>
-      <c r="L47" s="26"/>
+      <c r="L47" s="6"/>
+      <c r="M47" s="6"/>
+      <c r="N47" s="26"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="30"/>
+      <c r="A48" s="31"/>
       <c r="B48" s="6"/>
       <c r="C48" s="8" t="str">
         <f aca="false">IF(OR(D48="",E48="",D48=E48),"",IF(E48&lt;D48,"BUY","SELL"))</f>
@@ -3654,19 +3782,21 @@
         <f aca="false">IF(I48="","",IF(I48&gt;0,"WIN",IF(I48&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I48" s="31" t="str">
+      <c r="I48" s="32" t="str">
         <f aca="false">IF(OR(G48="",C48=""),"",ROUND((G48-D48)/(D48-E48),2))</f>
         <v/>
       </c>
-      <c r="J48" s="32" t="str">
-        <f aca="false">IF(I48="","",ROUND(I48*$M$2*$M$3,2))</f>
+      <c r="J48" s="33" t="str">
+        <f aca="false">IF(I48="","",ROUND(I48*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K48" s="6"/>
-      <c r="L48" s="26"/>
+      <c r="L48" s="6"/>
+      <c r="M48" s="6"/>
+      <c r="N48" s="26"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="30"/>
+      <c r="A49" s="31"/>
       <c r="B49" s="6"/>
       <c r="C49" s="8" t="str">
         <f aca="false">IF(OR(D49="",E49="",D49=E49),"",IF(E49&lt;D49,"BUY","SELL"))</f>
@@ -3683,19 +3813,21 @@
         <f aca="false">IF(I49="","",IF(I49&gt;0,"WIN",IF(I49&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I49" s="31" t="str">
+      <c r="I49" s="32" t="str">
         <f aca="false">IF(OR(G49="",C49=""),"",ROUND((G49-D49)/(D49-E49),2))</f>
         <v/>
       </c>
-      <c r="J49" s="32" t="str">
-        <f aca="false">IF(I49="","",ROUND(I49*$M$2*$M$3,2))</f>
+      <c r="J49" s="33" t="str">
+        <f aca="false">IF(I49="","",ROUND(I49*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K49" s="6"/>
-      <c r="L49" s="26"/>
+      <c r="L49" s="6"/>
+      <c r="M49" s="6"/>
+      <c r="N49" s="26"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="30"/>
+      <c r="A50" s="31"/>
       <c r="B50" s="6"/>
       <c r="C50" s="8" t="str">
         <f aca="false">IF(OR(D50="",E50="",D50=E50),"",IF(E50&lt;D50,"BUY","SELL"))</f>
@@ -3712,19 +3844,21 @@
         <f aca="false">IF(I50="","",IF(I50&gt;0,"WIN",IF(I50&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I50" s="31" t="str">
+      <c r="I50" s="32" t="str">
         <f aca="false">IF(OR(G50="",C50=""),"",ROUND((G50-D50)/(D50-E50),2))</f>
         <v/>
       </c>
-      <c r="J50" s="32" t="str">
-        <f aca="false">IF(I50="","",ROUND(I50*$M$2*$M$3,2))</f>
+      <c r="J50" s="33" t="str">
+        <f aca="false">IF(I50="","",ROUND(I50*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K50" s="6"/>
-      <c r="L50" s="26"/>
+      <c r="L50" s="6"/>
+      <c r="M50" s="6"/>
+      <c r="N50" s="26"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="30"/>
+      <c r="A51" s="31"/>
       <c r="B51" s="6"/>
       <c r="C51" s="8" t="str">
         <f aca="false">IF(OR(D51="",E51="",D51=E51),"",IF(E51&lt;D51,"BUY","SELL"))</f>
@@ -3741,19 +3875,21 @@
         <f aca="false">IF(I51="","",IF(I51&gt;0,"WIN",IF(I51&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I51" s="31" t="str">
+      <c r="I51" s="32" t="str">
         <f aca="false">IF(OR(G51="",C51=""),"",ROUND((G51-D51)/(D51-E51),2))</f>
         <v/>
       </c>
-      <c r="J51" s="32" t="str">
-        <f aca="false">IF(I51="","",ROUND(I51*$M$2*$M$3,2))</f>
+      <c r="J51" s="33" t="str">
+        <f aca="false">IF(I51="","",ROUND(I51*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K51" s="6"/>
-      <c r="L51" s="26"/>
+      <c r="L51" s="6"/>
+      <c r="M51" s="6"/>
+      <c r="N51" s="26"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="30"/>
+      <c r="A52" s="31"/>
       <c r="B52" s="6"/>
       <c r="C52" s="8" t="str">
         <f aca="false">IF(OR(D52="",E52="",D52=E52),"",IF(E52&lt;D52,"BUY","SELL"))</f>
@@ -3770,19 +3906,21 @@
         <f aca="false">IF(I52="","",IF(I52&gt;0,"WIN",IF(I52&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I52" s="31" t="str">
+      <c r="I52" s="32" t="str">
         <f aca="false">IF(OR(G52="",C52=""),"",ROUND((G52-D52)/(D52-E52),2))</f>
         <v/>
       </c>
-      <c r="J52" s="32" t="str">
-        <f aca="false">IF(I52="","",ROUND(I52*$M$2*$M$3,2))</f>
+      <c r="J52" s="33" t="str">
+        <f aca="false">IF(I52="","",ROUND(I52*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K52" s="6"/>
-      <c r="L52" s="26"/>
+      <c r="L52" s="6"/>
+      <c r="M52" s="6"/>
+      <c r="N52" s="26"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="30"/>
+      <c r="A53" s="31"/>
       <c r="B53" s="6"/>
       <c r="C53" s="8" t="str">
         <f aca="false">IF(OR(D53="",E53="",D53=E53),"",IF(E53&lt;D53,"BUY","SELL"))</f>
@@ -3799,19 +3937,21 @@
         <f aca="false">IF(I53="","",IF(I53&gt;0,"WIN",IF(I53&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I53" s="31" t="str">
+      <c r="I53" s="32" t="str">
         <f aca="false">IF(OR(G53="",C53=""),"",ROUND((G53-D53)/(D53-E53),2))</f>
         <v/>
       </c>
-      <c r="J53" s="32" t="str">
-        <f aca="false">IF(I53="","",ROUND(I53*$M$2*$M$3,2))</f>
+      <c r="J53" s="33" t="str">
+        <f aca="false">IF(I53="","",ROUND(I53*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K53" s="6"/>
-      <c r="L53" s="26"/>
+      <c r="L53" s="6"/>
+      <c r="M53" s="6"/>
+      <c r="N53" s="26"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="30"/>
+      <c r="A54" s="31"/>
       <c r="B54" s="6"/>
       <c r="C54" s="8" t="str">
         <f aca="false">IF(OR(D54="",E54="",D54=E54),"",IF(E54&lt;D54,"BUY","SELL"))</f>
@@ -3828,19 +3968,21 @@
         <f aca="false">IF(I54="","",IF(I54&gt;0,"WIN",IF(I54&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I54" s="31" t="str">
+      <c r="I54" s="32" t="str">
         <f aca="false">IF(OR(G54="",C54=""),"",ROUND((G54-D54)/(D54-E54),2))</f>
         <v/>
       </c>
-      <c r="J54" s="32" t="str">
-        <f aca="false">IF(I54="","",ROUND(I54*$M$2*$M$3,2))</f>
+      <c r="J54" s="33" t="str">
+        <f aca="false">IF(I54="","",ROUND(I54*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K54" s="6"/>
-      <c r="L54" s="26"/>
+      <c r="L54" s="6"/>
+      <c r="M54" s="6"/>
+      <c r="N54" s="26"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="30"/>
+      <c r="A55" s="31"/>
       <c r="B55" s="6"/>
       <c r="C55" s="8" t="str">
         <f aca="false">IF(OR(D55="",E55="",D55=E55),"",IF(E55&lt;D55,"BUY","SELL"))</f>
@@ -3857,19 +3999,21 @@
         <f aca="false">IF(I55="","",IF(I55&gt;0,"WIN",IF(I55&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I55" s="31" t="str">
+      <c r="I55" s="32" t="str">
         <f aca="false">IF(OR(G55="",C55=""),"",ROUND((G55-D55)/(D55-E55),2))</f>
         <v/>
       </c>
-      <c r="J55" s="32" t="str">
-        <f aca="false">IF(I55="","",ROUND(I55*$M$2*$M$3,2))</f>
+      <c r="J55" s="33" t="str">
+        <f aca="false">IF(I55="","",ROUND(I55*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K55" s="6"/>
-      <c r="L55" s="26"/>
+      <c r="L55" s="6"/>
+      <c r="M55" s="6"/>
+      <c r="N55" s="26"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="30"/>
+      <c r="A56" s="31"/>
       <c r="B56" s="6"/>
       <c r="C56" s="8" t="str">
         <f aca="false">IF(OR(D56="",E56="",D56=E56),"",IF(E56&lt;D56,"BUY","SELL"))</f>
@@ -3886,19 +4030,21 @@
         <f aca="false">IF(I56="","",IF(I56&gt;0,"WIN",IF(I56&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I56" s="31" t="str">
+      <c r="I56" s="32" t="str">
         <f aca="false">IF(OR(G56="",C56=""),"",ROUND((G56-D56)/(D56-E56),2))</f>
         <v/>
       </c>
-      <c r="J56" s="32" t="str">
-        <f aca="false">IF(I56="","",ROUND(I56*$M$2*$M$3,2))</f>
+      <c r="J56" s="33" t="str">
+        <f aca="false">IF(I56="","",ROUND(I56*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K56" s="6"/>
-      <c r="L56" s="26"/>
+      <c r="L56" s="6"/>
+      <c r="M56" s="6"/>
+      <c r="N56" s="26"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="30"/>
+      <c r="A57" s="31"/>
       <c r="B57" s="6"/>
       <c r="C57" s="8" t="str">
         <f aca="false">IF(OR(D57="",E57="",D57=E57),"",IF(E57&lt;D57,"BUY","SELL"))</f>
@@ -3915,19 +4061,21 @@
         <f aca="false">IF(I57="","",IF(I57&gt;0,"WIN",IF(I57&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I57" s="31" t="str">
+      <c r="I57" s="32" t="str">
         <f aca="false">IF(OR(G57="",C57=""),"",ROUND((G57-D57)/(D57-E57),2))</f>
         <v/>
       </c>
-      <c r="J57" s="32" t="str">
-        <f aca="false">IF(I57="","",ROUND(I57*$M$2*$M$3,2))</f>
+      <c r="J57" s="33" t="str">
+        <f aca="false">IF(I57="","",ROUND(I57*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K57" s="6"/>
-      <c r="L57" s="26"/>
+      <c r="L57" s="6"/>
+      <c r="M57" s="6"/>
+      <c r="N57" s="26"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="30"/>
+      <c r="A58" s="31"/>
       <c r="B58" s="6"/>
       <c r="C58" s="8" t="str">
         <f aca="false">IF(OR(D58="",E58="",D58=E58),"",IF(E58&lt;D58,"BUY","SELL"))</f>
@@ -3944,19 +4092,21 @@
         <f aca="false">IF(I58="","",IF(I58&gt;0,"WIN",IF(I58&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I58" s="31" t="str">
+      <c r="I58" s="32" t="str">
         <f aca="false">IF(OR(G58="",C58=""),"",ROUND((G58-D58)/(D58-E58),2))</f>
         <v/>
       </c>
-      <c r="J58" s="32" t="str">
-        <f aca="false">IF(I58="","",ROUND(I58*$M$2*$M$3,2))</f>
+      <c r="J58" s="33" t="str">
+        <f aca="false">IF(I58="","",ROUND(I58*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K58" s="6"/>
-      <c r="L58" s="26"/>
+      <c r="L58" s="6"/>
+      <c r="M58" s="6"/>
+      <c r="N58" s="26"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="30"/>
+      <c r="A59" s="31"/>
       <c r="B59" s="6"/>
       <c r="C59" s="8" t="str">
         <f aca="false">IF(OR(D59="",E59="",D59=E59),"",IF(E59&lt;D59,"BUY","SELL"))</f>
@@ -3973,19 +4123,21 @@
         <f aca="false">IF(I59="","",IF(I59&gt;0,"WIN",IF(I59&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I59" s="31" t="str">
+      <c r="I59" s="32" t="str">
         <f aca="false">IF(OR(G59="",C59=""),"",ROUND((G59-D59)/(D59-E59),2))</f>
         <v/>
       </c>
-      <c r="J59" s="32" t="str">
-        <f aca="false">IF(I59="","",ROUND(I59*$M$2*$M$3,2))</f>
+      <c r="J59" s="33" t="str">
+        <f aca="false">IF(I59="","",ROUND(I59*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K59" s="6"/>
-      <c r="L59" s="26"/>
+      <c r="L59" s="6"/>
+      <c r="M59" s="6"/>
+      <c r="N59" s="26"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="30"/>
+      <c r="A60" s="31"/>
       <c r="B60" s="6"/>
       <c r="C60" s="8" t="str">
         <f aca="false">IF(OR(D60="",E60="",D60=E60),"",IF(E60&lt;D60,"BUY","SELL"))</f>
@@ -4002,19 +4154,21 @@
         <f aca="false">IF(I60="","",IF(I60&gt;0,"WIN",IF(I60&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I60" s="31" t="str">
+      <c r="I60" s="32" t="str">
         <f aca="false">IF(OR(G60="",C60=""),"",ROUND((G60-D60)/(D60-E60),2))</f>
         <v/>
       </c>
-      <c r="J60" s="32" t="str">
-        <f aca="false">IF(I60="","",ROUND(I60*$M$2*$M$3,2))</f>
+      <c r="J60" s="33" t="str">
+        <f aca="false">IF(I60="","",ROUND(I60*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K60" s="6"/>
-      <c r="L60" s="26"/>
+      <c r="L60" s="6"/>
+      <c r="M60" s="6"/>
+      <c r="N60" s="26"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="30"/>
+      <c r="A61" s="31"/>
       <c r="B61" s="6"/>
       <c r="C61" s="8" t="str">
         <f aca="false">IF(OR(D61="",E61="",D61=E61),"",IF(E61&lt;D61,"BUY","SELL"))</f>
@@ -4031,19 +4185,21 @@
         <f aca="false">IF(I61="","",IF(I61&gt;0,"WIN",IF(I61&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I61" s="31" t="str">
+      <c r="I61" s="32" t="str">
         <f aca="false">IF(OR(G61="",C61=""),"",ROUND((G61-D61)/(D61-E61),2))</f>
         <v/>
       </c>
-      <c r="J61" s="32" t="str">
-        <f aca="false">IF(I61="","",ROUND(I61*$M$2*$M$3,2))</f>
+      <c r="J61" s="33" t="str">
+        <f aca="false">IF(I61="","",ROUND(I61*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K61" s="6"/>
-      <c r="L61" s="26"/>
+      <c r="L61" s="6"/>
+      <c r="M61" s="6"/>
+      <c r="N61" s="26"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="30"/>
+      <c r="A62" s="31"/>
       <c r="B62" s="6"/>
       <c r="C62" s="8" t="str">
         <f aca="false">IF(OR(D62="",E62="",D62=E62),"",IF(E62&lt;D62,"BUY","SELL"))</f>
@@ -4060,19 +4216,21 @@
         <f aca="false">IF(I62="","",IF(I62&gt;0,"WIN",IF(I62&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I62" s="31" t="str">
+      <c r="I62" s="32" t="str">
         <f aca="false">IF(OR(G62="",C62=""),"",ROUND((G62-D62)/(D62-E62),2))</f>
         <v/>
       </c>
-      <c r="J62" s="32" t="str">
-        <f aca="false">IF(I62="","",ROUND(I62*$M$2*$M$3,2))</f>
+      <c r="J62" s="33" t="str">
+        <f aca="false">IF(I62="","",ROUND(I62*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K62" s="6"/>
-      <c r="L62" s="26"/>
+      <c r="L62" s="6"/>
+      <c r="M62" s="6"/>
+      <c r="N62" s="26"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="30"/>
+      <c r="A63" s="31"/>
       <c r="B63" s="6"/>
       <c r="C63" s="8" t="str">
         <f aca="false">IF(OR(D63="",E63="",D63=E63),"",IF(E63&lt;D63,"BUY","SELL"))</f>
@@ -4089,19 +4247,21 @@
         <f aca="false">IF(I63="","",IF(I63&gt;0,"WIN",IF(I63&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I63" s="31" t="str">
+      <c r="I63" s="32" t="str">
         <f aca="false">IF(OR(G63="",C63=""),"",ROUND((G63-D63)/(D63-E63),2))</f>
         <v/>
       </c>
-      <c r="J63" s="32" t="str">
-        <f aca="false">IF(I63="","",ROUND(I63*$M$2*$M$3,2))</f>
+      <c r="J63" s="33" t="str">
+        <f aca="false">IF(I63="","",ROUND(I63*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K63" s="6"/>
-      <c r="L63" s="26"/>
+      <c r="L63" s="6"/>
+      <c r="M63" s="6"/>
+      <c r="N63" s="26"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="30"/>
+      <c r="A64" s="31"/>
       <c r="B64" s="6"/>
       <c r="C64" s="8" t="str">
         <f aca="false">IF(OR(D64="",E64="",D64=E64),"",IF(E64&lt;D64,"BUY","SELL"))</f>
@@ -4118,19 +4278,21 @@
         <f aca="false">IF(I64="","",IF(I64&gt;0,"WIN",IF(I64&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I64" s="31" t="str">
+      <c r="I64" s="32" t="str">
         <f aca="false">IF(OR(G64="",C64=""),"",ROUND((G64-D64)/(D64-E64),2))</f>
         <v/>
       </c>
-      <c r="J64" s="32" t="str">
-        <f aca="false">IF(I64="","",ROUND(I64*$M$2*$M$3,2))</f>
+      <c r="J64" s="33" t="str">
+        <f aca="false">IF(I64="","",ROUND(I64*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K64" s="6"/>
-      <c r="L64" s="26"/>
+      <c r="L64" s="6"/>
+      <c r="M64" s="6"/>
+      <c r="N64" s="26"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="30"/>
+      <c r="A65" s="31"/>
       <c r="B65" s="6"/>
       <c r="C65" s="8" t="str">
         <f aca="false">IF(OR(D65="",E65="",D65=E65),"",IF(E65&lt;D65,"BUY","SELL"))</f>
@@ -4147,19 +4309,21 @@
         <f aca="false">IF(I65="","",IF(I65&gt;0,"WIN",IF(I65&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I65" s="31" t="str">
+      <c r="I65" s="32" t="str">
         <f aca="false">IF(OR(G65="",C65=""),"",ROUND((G65-D65)/(D65-E65),2))</f>
         <v/>
       </c>
-      <c r="J65" s="32" t="str">
-        <f aca="false">IF(I65="","",ROUND(I65*$M$2*$M$3,2))</f>
+      <c r="J65" s="33" t="str">
+        <f aca="false">IF(I65="","",ROUND(I65*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K65" s="6"/>
-      <c r="L65" s="26"/>
+      <c r="L65" s="6"/>
+      <c r="M65" s="6"/>
+      <c r="N65" s="26"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="30"/>
+      <c r="A66" s="31"/>
       <c r="B66" s="6"/>
       <c r="C66" s="8" t="str">
         <f aca="false">IF(OR(D66="",E66="",D66=E66),"",IF(E66&lt;D66,"BUY","SELL"))</f>
@@ -4176,19 +4340,21 @@
         <f aca="false">IF(I66="","",IF(I66&gt;0,"WIN",IF(I66&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I66" s="31" t="str">
+      <c r="I66" s="32" t="str">
         <f aca="false">IF(OR(G66="",C66=""),"",ROUND((G66-D66)/(D66-E66),2))</f>
         <v/>
       </c>
-      <c r="J66" s="32" t="str">
-        <f aca="false">IF(I66="","",ROUND(I66*$M$2*$M$3,2))</f>
+      <c r="J66" s="33" t="str">
+        <f aca="false">IF(I66="","",ROUND(I66*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K66" s="6"/>
-      <c r="L66" s="26"/>
+      <c r="L66" s="6"/>
+      <c r="M66" s="6"/>
+      <c r="N66" s="26"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="30"/>
+      <c r="A67" s="31"/>
       <c r="B67" s="6"/>
       <c r="C67" s="8" t="str">
         <f aca="false">IF(OR(D67="",E67="",D67=E67),"",IF(E67&lt;D67,"BUY","SELL"))</f>
@@ -4205,19 +4371,21 @@
         <f aca="false">IF(I67="","",IF(I67&gt;0,"WIN",IF(I67&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I67" s="31" t="str">
+      <c r="I67" s="32" t="str">
         <f aca="false">IF(OR(G67="",C67=""),"",ROUND((G67-D67)/(D67-E67),2))</f>
         <v/>
       </c>
-      <c r="J67" s="32" t="str">
-        <f aca="false">IF(I67="","",ROUND(I67*$M$2*$M$3,2))</f>
+      <c r="J67" s="33" t="str">
+        <f aca="false">IF(I67="","",ROUND(I67*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K67" s="6"/>
-      <c r="L67" s="26"/>
+      <c r="L67" s="6"/>
+      <c r="M67" s="6"/>
+      <c r="N67" s="26"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="30"/>
+      <c r="A68" s="31"/>
       <c r="B68" s="6"/>
       <c r="C68" s="8" t="str">
         <f aca="false">IF(OR(D68="",E68="",D68=E68),"",IF(E68&lt;D68,"BUY","SELL"))</f>
@@ -4234,19 +4402,21 @@
         <f aca="false">IF(I68="","",IF(I68&gt;0,"WIN",IF(I68&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I68" s="31" t="str">
+      <c r="I68" s="32" t="str">
         <f aca="false">IF(OR(G68="",C68=""),"",ROUND((G68-D68)/(D68-E68),2))</f>
         <v/>
       </c>
-      <c r="J68" s="32" t="str">
-        <f aca="false">IF(I68="","",ROUND(I68*$M$2*$M$3,2))</f>
+      <c r="J68" s="33" t="str">
+        <f aca="false">IF(I68="","",ROUND(I68*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K68" s="6"/>
-      <c r="L68" s="26"/>
+      <c r="L68" s="6"/>
+      <c r="M68" s="6"/>
+      <c r="N68" s="26"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="30"/>
+      <c r="A69" s="31"/>
       <c r="B69" s="6"/>
       <c r="C69" s="8" t="str">
         <f aca="false">IF(OR(D69="",E69="",D69=E69),"",IF(E69&lt;D69,"BUY","SELL"))</f>
@@ -4263,19 +4433,21 @@
         <f aca="false">IF(I69="","",IF(I69&gt;0,"WIN",IF(I69&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I69" s="31" t="str">
+      <c r="I69" s="32" t="str">
         <f aca="false">IF(OR(G69="",C69=""),"",ROUND((G69-D69)/(D69-E69),2))</f>
         <v/>
       </c>
-      <c r="J69" s="32" t="str">
-        <f aca="false">IF(I69="","",ROUND(I69*$M$2*$M$3,2))</f>
+      <c r="J69" s="33" t="str">
+        <f aca="false">IF(I69="","",ROUND(I69*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K69" s="6"/>
-      <c r="L69" s="26"/>
+      <c r="L69" s="6"/>
+      <c r="M69" s="6"/>
+      <c r="N69" s="26"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="30"/>
+      <c r="A70" s="31"/>
       <c r="B70" s="6"/>
       <c r="C70" s="8" t="str">
         <f aca="false">IF(OR(D70="",E70="",D70=E70),"",IF(E70&lt;D70,"BUY","SELL"))</f>
@@ -4292,19 +4464,21 @@
         <f aca="false">IF(I70="","",IF(I70&gt;0,"WIN",IF(I70&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I70" s="31" t="str">
+      <c r="I70" s="32" t="str">
         <f aca="false">IF(OR(G70="",C70=""),"",ROUND((G70-D70)/(D70-E70),2))</f>
         <v/>
       </c>
-      <c r="J70" s="32" t="str">
-        <f aca="false">IF(I70="","",ROUND(I70*$M$2*$M$3,2))</f>
+      <c r="J70" s="33" t="str">
+        <f aca="false">IF(I70="","",ROUND(I70*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K70" s="6"/>
-      <c r="L70" s="26"/>
+      <c r="L70" s="6"/>
+      <c r="M70" s="6"/>
+      <c r="N70" s="26"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="30"/>
+      <c r="A71" s="31"/>
       <c r="B71" s="6"/>
       <c r="C71" s="8" t="str">
         <f aca="false">IF(OR(D71="",E71="",D71=E71),"",IF(E71&lt;D71,"BUY","SELL"))</f>
@@ -4321,19 +4495,21 @@
         <f aca="false">IF(I71="","",IF(I71&gt;0,"WIN",IF(I71&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I71" s="31" t="str">
+      <c r="I71" s="32" t="str">
         <f aca="false">IF(OR(G71="",C71=""),"",ROUND((G71-D71)/(D71-E71),2))</f>
         <v/>
       </c>
-      <c r="J71" s="32" t="str">
-        <f aca="false">IF(I71="","",ROUND(I71*$M$2*$M$3,2))</f>
+      <c r="J71" s="33" t="str">
+        <f aca="false">IF(I71="","",ROUND(I71*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K71" s="6"/>
-      <c r="L71" s="26"/>
+      <c r="L71" s="6"/>
+      <c r="M71" s="6"/>
+      <c r="N71" s="26"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="30"/>
+      <c r="A72" s="31"/>
       <c r="B72" s="6"/>
       <c r="C72" s="8" t="str">
         <f aca="false">IF(OR(D72="",E72="",D72=E72),"",IF(E72&lt;D72,"BUY","SELL"))</f>
@@ -4350,19 +4526,21 @@
         <f aca="false">IF(I72="","",IF(I72&gt;0,"WIN",IF(I72&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I72" s="31" t="str">
+      <c r="I72" s="32" t="str">
         <f aca="false">IF(OR(G72="",C72=""),"",ROUND((G72-D72)/(D72-E72),2))</f>
         <v/>
       </c>
-      <c r="J72" s="32" t="str">
-        <f aca="false">IF(I72="","",ROUND(I72*$M$2*$M$3,2))</f>
+      <c r="J72" s="33" t="str">
+        <f aca="false">IF(I72="","",ROUND(I72*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K72" s="6"/>
-      <c r="L72" s="26"/>
+      <c r="L72" s="6"/>
+      <c r="M72" s="6"/>
+      <c r="N72" s="26"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="30"/>
+      <c r="A73" s="31"/>
       <c r="B73" s="6"/>
       <c r="C73" s="8" t="str">
         <f aca="false">IF(OR(D73="",E73="",D73=E73),"",IF(E73&lt;D73,"BUY","SELL"))</f>
@@ -4379,19 +4557,21 @@
         <f aca="false">IF(I73="","",IF(I73&gt;0,"WIN",IF(I73&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I73" s="31" t="str">
+      <c r="I73" s="32" t="str">
         <f aca="false">IF(OR(G73="",C73=""),"",ROUND((G73-D73)/(D73-E73),2))</f>
         <v/>
       </c>
-      <c r="J73" s="32" t="str">
-        <f aca="false">IF(I73="","",ROUND(I73*$M$2*$M$3,2))</f>
+      <c r="J73" s="33" t="str">
+        <f aca="false">IF(I73="","",ROUND(I73*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K73" s="6"/>
-      <c r="L73" s="26"/>
+      <c r="L73" s="6"/>
+      <c r="M73" s="6"/>
+      <c r="N73" s="26"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="30"/>
+      <c r="A74" s="31"/>
       <c r="B74" s="6"/>
       <c r="C74" s="8" t="str">
         <f aca="false">IF(OR(D74="",E74="",D74=E74),"",IF(E74&lt;D74,"BUY","SELL"))</f>
@@ -4408,19 +4588,21 @@
         <f aca="false">IF(I74="","",IF(I74&gt;0,"WIN",IF(I74&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I74" s="31" t="str">
+      <c r="I74" s="32" t="str">
         <f aca="false">IF(OR(G74="",C74=""),"",ROUND((G74-D74)/(D74-E74),2))</f>
         <v/>
       </c>
-      <c r="J74" s="32" t="str">
-        <f aca="false">IF(I74="","",ROUND(I74*$M$2*$M$3,2))</f>
+      <c r="J74" s="33" t="str">
+        <f aca="false">IF(I74="","",ROUND(I74*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K74" s="6"/>
-      <c r="L74" s="26"/>
+      <c r="L74" s="6"/>
+      <c r="M74" s="6"/>
+      <c r="N74" s="26"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="30"/>
+      <c r="A75" s="31"/>
       <c r="B75" s="6"/>
       <c r="C75" s="8" t="str">
         <f aca="false">IF(OR(D75="",E75="",D75=E75),"",IF(E75&lt;D75,"BUY","SELL"))</f>
@@ -4437,19 +4619,21 @@
         <f aca="false">IF(I75="","",IF(I75&gt;0,"WIN",IF(I75&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I75" s="31" t="str">
+      <c r="I75" s="32" t="str">
         <f aca="false">IF(OR(G75="",C75=""),"",ROUND((G75-D75)/(D75-E75),2))</f>
         <v/>
       </c>
-      <c r="J75" s="32" t="str">
-        <f aca="false">IF(I75="","",ROUND(I75*$M$2*$M$3,2))</f>
+      <c r="J75" s="33" t="str">
+        <f aca="false">IF(I75="","",ROUND(I75*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K75" s="6"/>
-      <c r="L75" s="26"/>
+      <c r="L75" s="6"/>
+      <c r="M75" s="6"/>
+      <c r="N75" s="26"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="30"/>
+      <c r="A76" s="31"/>
       <c r="B76" s="6"/>
       <c r="C76" s="8" t="str">
         <f aca="false">IF(OR(D76="",E76="",D76=E76),"",IF(E76&lt;D76,"BUY","SELL"))</f>
@@ -4466,19 +4650,21 @@
         <f aca="false">IF(I76="","",IF(I76&gt;0,"WIN",IF(I76&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I76" s="31" t="str">
+      <c r="I76" s="32" t="str">
         <f aca="false">IF(OR(G76="",C76=""),"",ROUND((G76-D76)/(D76-E76),2))</f>
         <v/>
       </c>
-      <c r="J76" s="32" t="str">
-        <f aca="false">IF(I76="","",ROUND(I76*$M$2*$M$3,2))</f>
+      <c r="J76" s="33" t="str">
+        <f aca="false">IF(I76="","",ROUND(I76*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K76" s="6"/>
-      <c r="L76" s="26"/>
+      <c r="L76" s="6"/>
+      <c r="M76" s="6"/>
+      <c r="N76" s="26"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="30"/>
+      <c r="A77" s="31"/>
       <c r="B77" s="6"/>
       <c r="C77" s="8" t="str">
         <f aca="false">IF(OR(D77="",E77="",D77=E77),"",IF(E77&lt;D77,"BUY","SELL"))</f>
@@ -4495,19 +4681,21 @@
         <f aca="false">IF(I77="","",IF(I77&gt;0,"WIN",IF(I77&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I77" s="31" t="str">
+      <c r="I77" s="32" t="str">
         <f aca="false">IF(OR(G77="",C77=""),"",ROUND((G77-D77)/(D77-E77),2))</f>
         <v/>
       </c>
-      <c r="J77" s="32" t="str">
-        <f aca="false">IF(I77="","",ROUND(I77*$M$2*$M$3,2))</f>
+      <c r="J77" s="33" t="str">
+        <f aca="false">IF(I77="","",ROUND(I77*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K77" s="6"/>
-      <c r="L77" s="26"/>
+      <c r="L77" s="6"/>
+      <c r="M77" s="6"/>
+      <c r="N77" s="26"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="30"/>
+      <c r="A78" s="31"/>
       <c r="B78" s="6"/>
       <c r="C78" s="8" t="str">
         <f aca="false">IF(OR(D78="",E78="",D78=E78),"",IF(E78&lt;D78,"BUY","SELL"))</f>
@@ -4524,19 +4712,21 @@
         <f aca="false">IF(I78="","",IF(I78&gt;0,"WIN",IF(I78&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I78" s="31" t="str">
+      <c r="I78" s="32" t="str">
         <f aca="false">IF(OR(G78="",C78=""),"",ROUND((G78-D78)/(D78-E78),2))</f>
         <v/>
       </c>
-      <c r="J78" s="32" t="str">
-        <f aca="false">IF(I78="","",ROUND(I78*$M$2*$M$3,2))</f>
+      <c r="J78" s="33" t="str">
+        <f aca="false">IF(I78="","",ROUND(I78*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K78" s="6"/>
-      <c r="L78" s="26"/>
+      <c r="L78" s="6"/>
+      <c r="M78" s="6"/>
+      <c r="N78" s="26"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="30"/>
+      <c r="A79" s="31"/>
       <c r="B79" s="6"/>
       <c r="C79" s="8" t="str">
         <f aca="false">IF(OR(D79="",E79="",D79=E79),"",IF(E79&lt;D79,"BUY","SELL"))</f>
@@ -4553,19 +4743,21 @@
         <f aca="false">IF(I79="","",IF(I79&gt;0,"WIN",IF(I79&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I79" s="31" t="str">
+      <c r="I79" s="32" t="str">
         <f aca="false">IF(OR(G79="",C79=""),"",ROUND((G79-D79)/(D79-E79),2))</f>
         <v/>
       </c>
-      <c r="J79" s="32" t="str">
-        <f aca="false">IF(I79="","",ROUND(I79*$M$2*$M$3,2))</f>
+      <c r="J79" s="33" t="str">
+        <f aca="false">IF(I79="","",ROUND(I79*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K79" s="6"/>
-      <c r="L79" s="26"/>
+      <c r="L79" s="6"/>
+      <c r="M79" s="6"/>
+      <c r="N79" s="26"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="30"/>
+      <c r="A80" s="31"/>
       <c r="B80" s="6"/>
       <c r="C80" s="8" t="str">
         <f aca="false">IF(OR(D80="",E80="",D80=E80),"",IF(E80&lt;D80,"BUY","SELL"))</f>
@@ -4582,19 +4774,21 @@
         <f aca="false">IF(I80="","",IF(I80&gt;0,"WIN",IF(I80&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I80" s="31" t="str">
+      <c r="I80" s="32" t="str">
         <f aca="false">IF(OR(G80="",C80=""),"",ROUND((G80-D80)/(D80-E80),2))</f>
         <v/>
       </c>
-      <c r="J80" s="32" t="str">
-        <f aca="false">IF(I80="","",ROUND(I80*$M$2*$M$3,2))</f>
+      <c r="J80" s="33" t="str">
+        <f aca="false">IF(I80="","",ROUND(I80*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K80" s="6"/>
-      <c r="L80" s="26"/>
+      <c r="L80" s="6"/>
+      <c r="M80" s="6"/>
+      <c r="N80" s="26"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="30"/>
+      <c r="A81" s="31"/>
       <c r="B81" s="6"/>
       <c r="C81" s="8" t="str">
         <f aca="false">IF(OR(D81="",E81="",D81=E81),"",IF(E81&lt;D81,"BUY","SELL"))</f>
@@ -4611,19 +4805,21 @@
         <f aca="false">IF(I81="","",IF(I81&gt;0,"WIN",IF(I81&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I81" s="31" t="str">
+      <c r="I81" s="32" t="str">
         <f aca="false">IF(OR(G81="",C81=""),"",ROUND((G81-D81)/(D81-E81),2))</f>
         <v/>
       </c>
-      <c r="J81" s="32" t="str">
-        <f aca="false">IF(I81="","",ROUND(I81*$M$2*$M$3,2))</f>
+      <c r="J81" s="33" t="str">
+        <f aca="false">IF(I81="","",ROUND(I81*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K81" s="6"/>
-      <c r="L81" s="26"/>
+      <c r="L81" s="6"/>
+      <c r="M81" s="6"/>
+      <c r="N81" s="26"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="30"/>
+      <c r="A82" s="31"/>
       <c r="B82" s="6"/>
       <c r="C82" s="8" t="str">
         <f aca="false">IF(OR(D82="",E82="",D82=E82),"",IF(E82&lt;D82,"BUY","SELL"))</f>
@@ -4640,19 +4836,21 @@
         <f aca="false">IF(I82="","",IF(I82&gt;0,"WIN",IF(I82&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I82" s="31" t="str">
+      <c r="I82" s="32" t="str">
         <f aca="false">IF(OR(G82="",C82=""),"",ROUND((G82-D82)/(D82-E82),2))</f>
         <v/>
       </c>
-      <c r="J82" s="32" t="str">
-        <f aca="false">IF(I82="","",ROUND(I82*$M$2*$M$3,2))</f>
+      <c r="J82" s="33" t="str">
+        <f aca="false">IF(I82="","",ROUND(I82*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K82" s="6"/>
-      <c r="L82" s="26"/>
+      <c r="L82" s="6"/>
+      <c r="M82" s="6"/>
+      <c r="N82" s="26"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="30"/>
+      <c r="A83" s="31"/>
       <c r="B83" s="6"/>
       <c r="C83" s="8" t="str">
         <f aca="false">IF(OR(D83="",E83="",D83=E83),"",IF(E83&lt;D83,"BUY","SELL"))</f>
@@ -4669,19 +4867,21 @@
         <f aca="false">IF(I83="","",IF(I83&gt;0,"WIN",IF(I83&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I83" s="31" t="str">
+      <c r="I83" s="32" t="str">
         <f aca="false">IF(OR(G83="",C83=""),"",ROUND((G83-D83)/(D83-E83),2))</f>
         <v/>
       </c>
-      <c r="J83" s="32" t="str">
-        <f aca="false">IF(I83="","",ROUND(I83*$M$2*$M$3,2))</f>
+      <c r="J83" s="33" t="str">
+        <f aca="false">IF(I83="","",ROUND(I83*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K83" s="6"/>
-      <c r="L83" s="26"/>
+      <c r="L83" s="6"/>
+      <c r="M83" s="6"/>
+      <c r="N83" s="26"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="30"/>
+      <c r="A84" s="31"/>
       <c r="B84" s="6"/>
       <c r="C84" s="8" t="str">
         <f aca="false">IF(OR(D84="",E84="",D84=E84),"",IF(E84&lt;D84,"BUY","SELL"))</f>
@@ -4698,19 +4898,21 @@
         <f aca="false">IF(I84="","",IF(I84&gt;0,"WIN",IF(I84&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I84" s="31" t="str">
+      <c r="I84" s="32" t="str">
         <f aca="false">IF(OR(G84="",C84=""),"",ROUND((G84-D84)/(D84-E84),2))</f>
         <v/>
       </c>
-      <c r="J84" s="32" t="str">
-        <f aca="false">IF(I84="","",ROUND(I84*$M$2*$M$3,2))</f>
+      <c r="J84" s="33" t="str">
+        <f aca="false">IF(I84="","",ROUND(I84*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K84" s="6"/>
-      <c r="L84" s="26"/>
+      <c r="L84" s="6"/>
+      <c r="M84" s="6"/>
+      <c r="N84" s="26"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="30"/>
+      <c r="A85" s="31"/>
       <c r="B85" s="6"/>
       <c r="C85" s="8" t="str">
         <f aca="false">IF(OR(D85="",E85="",D85=E85),"",IF(E85&lt;D85,"BUY","SELL"))</f>
@@ -4727,19 +4929,21 @@
         <f aca="false">IF(I85="","",IF(I85&gt;0,"WIN",IF(I85&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I85" s="31" t="str">
+      <c r="I85" s="32" t="str">
         <f aca="false">IF(OR(G85="",C85=""),"",ROUND((G85-D85)/(D85-E85),2))</f>
         <v/>
       </c>
-      <c r="J85" s="32" t="str">
-        <f aca="false">IF(I85="","",ROUND(I85*$M$2*$M$3,2))</f>
+      <c r="J85" s="33" t="str">
+        <f aca="false">IF(I85="","",ROUND(I85*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K85" s="6"/>
-      <c r="L85" s="26"/>
+      <c r="L85" s="6"/>
+      <c r="M85" s="6"/>
+      <c r="N85" s="26"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="30"/>
+      <c r="A86" s="31"/>
       <c r="B86" s="6"/>
       <c r="C86" s="8" t="str">
         <f aca="false">IF(OR(D86="",E86="",D86=E86),"",IF(E86&lt;D86,"BUY","SELL"))</f>
@@ -4756,19 +4960,21 @@
         <f aca="false">IF(I86="","",IF(I86&gt;0,"WIN",IF(I86&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I86" s="31" t="str">
+      <c r="I86" s="32" t="str">
         <f aca="false">IF(OR(G86="",C86=""),"",ROUND((G86-D86)/(D86-E86),2))</f>
         <v/>
       </c>
-      <c r="J86" s="32" t="str">
-        <f aca="false">IF(I86="","",ROUND(I86*$M$2*$M$3,2))</f>
+      <c r="J86" s="33" t="str">
+        <f aca="false">IF(I86="","",ROUND(I86*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K86" s="6"/>
-      <c r="L86" s="26"/>
+      <c r="L86" s="6"/>
+      <c r="M86" s="6"/>
+      <c r="N86" s="26"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="30"/>
+      <c r="A87" s="31"/>
       <c r="B87" s="6"/>
       <c r="C87" s="8" t="str">
         <f aca="false">IF(OR(D87="",E87="",D87=E87),"",IF(E87&lt;D87,"BUY","SELL"))</f>
@@ -4785,19 +4991,21 @@
         <f aca="false">IF(I87="","",IF(I87&gt;0,"WIN",IF(I87&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I87" s="31" t="str">
+      <c r="I87" s="32" t="str">
         <f aca="false">IF(OR(G87="",C87=""),"",ROUND((G87-D87)/(D87-E87),2))</f>
         <v/>
       </c>
-      <c r="J87" s="32" t="str">
-        <f aca="false">IF(I87="","",ROUND(I87*$M$2*$M$3,2))</f>
+      <c r="J87" s="33" t="str">
+        <f aca="false">IF(I87="","",ROUND(I87*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K87" s="6"/>
-      <c r="L87" s="26"/>
+      <c r="L87" s="6"/>
+      <c r="M87" s="6"/>
+      <c r="N87" s="26"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="30"/>
+      <c r="A88" s="31"/>
       <c r="B88" s="6"/>
       <c r="C88" s="8" t="str">
         <f aca="false">IF(OR(D88="",E88="",D88=E88),"",IF(E88&lt;D88,"BUY","SELL"))</f>
@@ -4814,19 +5022,21 @@
         <f aca="false">IF(I88="","",IF(I88&gt;0,"WIN",IF(I88&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I88" s="31" t="str">
+      <c r="I88" s="32" t="str">
         <f aca="false">IF(OR(G88="",C88=""),"",ROUND((G88-D88)/(D88-E88),2))</f>
         <v/>
       </c>
-      <c r="J88" s="32" t="str">
-        <f aca="false">IF(I88="","",ROUND(I88*$M$2*$M$3,2))</f>
+      <c r="J88" s="33" t="str">
+        <f aca="false">IF(I88="","",ROUND(I88*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K88" s="6"/>
-      <c r="L88" s="26"/>
+      <c r="L88" s="6"/>
+      <c r="M88" s="6"/>
+      <c r="N88" s="26"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="30"/>
+      <c r="A89" s="31"/>
       <c r="B89" s="6"/>
       <c r="C89" s="8" t="str">
         <f aca="false">IF(OR(D89="",E89="",D89=E89),"",IF(E89&lt;D89,"BUY","SELL"))</f>
@@ -4843,19 +5053,21 @@
         <f aca="false">IF(I89="","",IF(I89&gt;0,"WIN",IF(I89&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I89" s="31" t="str">
+      <c r="I89" s="32" t="str">
         <f aca="false">IF(OR(G89="",C89=""),"",ROUND((G89-D89)/(D89-E89),2))</f>
         <v/>
       </c>
-      <c r="J89" s="32" t="str">
-        <f aca="false">IF(I89="","",ROUND(I89*$M$2*$M$3,2))</f>
+      <c r="J89" s="33" t="str">
+        <f aca="false">IF(I89="","",ROUND(I89*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K89" s="6"/>
-      <c r="L89" s="26"/>
+      <c r="L89" s="6"/>
+      <c r="M89" s="6"/>
+      <c r="N89" s="26"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="30"/>
+      <c r="A90" s="31"/>
       <c r="B90" s="6"/>
       <c r="C90" s="8" t="str">
         <f aca="false">IF(OR(D90="",E90="",D90=E90),"",IF(E90&lt;D90,"BUY","SELL"))</f>
@@ -4872,19 +5084,21 @@
         <f aca="false">IF(I90="","",IF(I90&gt;0,"WIN",IF(I90&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I90" s="31" t="str">
+      <c r="I90" s="32" t="str">
         <f aca="false">IF(OR(G90="",C90=""),"",ROUND((G90-D90)/(D90-E90),2))</f>
         <v/>
       </c>
-      <c r="J90" s="32" t="str">
-        <f aca="false">IF(I90="","",ROUND(I90*$M$2*$M$3,2))</f>
+      <c r="J90" s="33" t="str">
+        <f aca="false">IF(I90="","",ROUND(I90*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K90" s="6"/>
-      <c r="L90" s="26"/>
+      <c r="L90" s="6"/>
+      <c r="M90" s="6"/>
+      <c r="N90" s="26"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="30"/>
+      <c r="A91" s="31"/>
       <c r="B91" s="6"/>
       <c r="C91" s="8" t="str">
         <f aca="false">IF(OR(D91="",E91="",D91=E91),"",IF(E91&lt;D91,"BUY","SELL"))</f>
@@ -4901,19 +5115,21 @@
         <f aca="false">IF(I91="","",IF(I91&gt;0,"WIN",IF(I91&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I91" s="31" t="str">
+      <c r="I91" s="32" t="str">
         <f aca="false">IF(OR(G91="",C91=""),"",ROUND((G91-D91)/(D91-E91),2))</f>
         <v/>
       </c>
-      <c r="J91" s="32" t="str">
-        <f aca="false">IF(I91="","",ROUND(I91*$M$2*$M$3,2))</f>
+      <c r="J91" s="33" t="str">
+        <f aca="false">IF(I91="","",ROUND(I91*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K91" s="6"/>
-      <c r="L91" s="26"/>
+      <c r="L91" s="6"/>
+      <c r="M91" s="6"/>
+      <c r="N91" s="26"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="30"/>
+      <c r="A92" s="31"/>
       <c r="B92" s="6"/>
       <c r="C92" s="8" t="str">
         <f aca="false">IF(OR(D92="",E92="",D92=E92),"",IF(E92&lt;D92,"BUY","SELL"))</f>
@@ -4930,19 +5146,21 @@
         <f aca="false">IF(I92="","",IF(I92&gt;0,"WIN",IF(I92&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I92" s="31" t="str">
+      <c r="I92" s="32" t="str">
         <f aca="false">IF(OR(G92="",C92=""),"",ROUND((G92-D92)/(D92-E92),2))</f>
         <v/>
       </c>
-      <c r="J92" s="32" t="str">
-        <f aca="false">IF(I92="","",ROUND(I92*$M$2*$M$3,2))</f>
+      <c r="J92" s="33" t="str">
+        <f aca="false">IF(I92="","",ROUND(I92*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K92" s="6"/>
-      <c r="L92" s="26"/>
+      <c r="L92" s="6"/>
+      <c r="M92" s="6"/>
+      <c r="N92" s="26"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="30"/>
+      <c r="A93" s="31"/>
       <c r="B93" s="6"/>
       <c r="C93" s="8" t="str">
         <f aca="false">IF(OR(D93="",E93="",D93=E93),"",IF(E93&lt;D93,"BUY","SELL"))</f>
@@ -4959,19 +5177,21 @@
         <f aca="false">IF(I93="","",IF(I93&gt;0,"WIN",IF(I93&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I93" s="31" t="str">
+      <c r="I93" s="32" t="str">
         <f aca="false">IF(OR(G93="",C93=""),"",ROUND((G93-D93)/(D93-E93),2))</f>
         <v/>
       </c>
-      <c r="J93" s="32" t="str">
-        <f aca="false">IF(I93="","",ROUND(I93*$M$2*$M$3,2))</f>
+      <c r="J93" s="33" t="str">
+        <f aca="false">IF(I93="","",ROUND(I93*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K93" s="6"/>
-      <c r="L93" s="26"/>
+      <c r="L93" s="6"/>
+      <c r="M93" s="6"/>
+      <c r="N93" s="26"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="30"/>
+      <c r="A94" s="31"/>
       <c r="B94" s="6"/>
       <c r="C94" s="8" t="str">
         <f aca="false">IF(OR(D94="",E94="",D94=E94),"",IF(E94&lt;D94,"BUY","SELL"))</f>
@@ -4988,19 +5208,21 @@
         <f aca="false">IF(I94="","",IF(I94&gt;0,"WIN",IF(I94&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I94" s="31" t="str">
+      <c r="I94" s="32" t="str">
         <f aca="false">IF(OR(G94="",C94=""),"",ROUND((G94-D94)/(D94-E94),2))</f>
         <v/>
       </c>
-      <c r="J94" s="32" t="str">
-        <f aca="false">IF(I94="","",ROUND(I94*$M$2*$M$3,2))</f>
+      <c r="J94" s="33" t="str">
+        <f aca="false">IF(I94="","",ROUND(I94*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K94" s="6"/>
-      <c r="L94" s="26"/>
+      <c r="L94" s="6"/>
+      <c r="M94" s="6"/>
+      <c r="N94" s="26"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="30"/>
+      <c r="A95" s="31"/>
       <c r="B95" s="6"/>
       <c r="C95" s="8" t="str">
         <f aca="false">IF(OR(D95="",E95="",D95=E95),"",IF(E95&lt;D95,"BUY","SELL"))</f>
@@ -5017,19 +5239,21 @@
         <f aca="false">IF(I95="","",IF(I95&gt;0,"WIN",IF(I95&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I95" s="31" t="str">
+      <c r="I95" s="32" t="str">
         <f aca="false">IF(OR(G95="",C95=""),"",ROUND((G95-D95)/(D95-E95),2))</f>
         <v/>
       </c>
-      <c r="J95" s="32" t="str">
-        <f aca="false">IF(I95="","",ROUND(I95*$M$2*$M$3,2))</f>
+      <c r="J95" s="33" t="str">
+        <f aca="false">IF(I95="","",ROUND(I95*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K95" s="6"/>
-      <c r="L95" s="26"/>
+      <c r="L95" s="6"/>
+      <c r="M95" s="6"/>
+      <c r="N95" s="26"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="30"/>
+      <c r="A96" s="31"/>
       <c r="B96" s="6"/>
       <c r="C96" s="8" t="str">
         <f aca="false">IF(OR(D96="",E96="",D96=E96),"",IF(E96&lt;D96,"BUY","SELL"))</f>
@@ -5046,19 +5270,21 @@
         <f aca="false">IF(I96="","",IF(I96&gt;0,"WIN",IF(I96&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I96" s="31" t="str">
+      <c r="I96" s="32" t="str">
         <f aca="false">IF(OR(G96="",C96=""),"",ROUND((G96-D96)/(D96-E96),2))</f>
         <v/>
       </c>
-      <c r="J96" s="32" t="str">
-        <f aca="false">IF(I96="","",ROUND(I96*$M$2*$M$3,2))</f>
+      <c r="J96" s="33" t="str">
+        <f aca="false">IF(I96="","",ROUND(I96*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K96" s="6"/>
-      <c r="L96" s="26"/>
+      <c r="L96" s="6"/>
+      <c r="M96" s="6"/>
+      <c r="N96" s="26"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="30"/>
+      <c r="A97" s="31"/>
       <c r="B97" s="6"/>
       <c r="C97" s="8" t="str">
         <f aca="false">IF(OR(D97="",E97="",D97=E97),"",IF(E97&lt;D97,"BUY","SELL"))</f>
@@ -5075,19 +5301,21 @@
         <f aca="false">IF(I97="","",IF(I97&gt;0,"WIN",IF(I97&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I97" s="31" t="str">
+      <c r="I97" s="32" t="str">
         <f aca="false">IF(OR(G97="",C97=""),"",ROUND((G97-D97)/(D97-E97),2))</f>
         <v/>
       </c>
-      <c r="J97" s="32" t="str">
-        <f aca="false">IF(I97="","",ROUND(I97*$M$2*$M$3,2))</f>
+      <c r="J97" s="33" t="str">
+        <f aca="false">IF(I97="","",ROUND(I97*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K97" s="6"/>
-      <c r="L97" s="26"/>
+      <c r="L97" s="6"/>
+      <c r="M97" s="6"/>
+      <c r="N97" s="26"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="30"/>
+      <c r="A98" s="31"/>
       <c r="B98" s="6"/>
       <c r="C98" s="8" t="str">
         <f aca="false">IF(OR(D98="",E98="",D98=E98),"",IF(E98&lt;D98,"BUY","SELL"))</f>
@@ -5104,19 +5332,21 @@
         <f aca="false">IF(I98="","",IF(I98&gt;0,"WIN",IF(I98&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I98" s="31" t="str">
+      <c r="I98" s="32" t="str">
         <f aca="false">IF(OR(G98="",C98=""),"",ROUND((G98-D98)/(D98-E98),2))</f>
         <v/>
       </c>
-      <c r="J98" s="32" t="str">
-        <f aca="false">IF(I98="","",ROUND(I98*$M$2*$M$3,2))</f>
+      <c r="J98" s="33" t="str">
+        <f aca="false">IF(I98="","",ROUND(I98*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K98" s="6"/>
-      <c r="L98" s="26"/>
+      <c r="L98" s="6"/>
+      <c r="M98" s="6"/>
+      <c r="N98" s="26"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="30"/>
+      <c r="A99" s="31"/>
       <c r="B99" s="6"/>
       <c r="C99" s="8" t="str">
         <f aca="false">IF(OR(D99="",E99="",D99=E99),"",IF(E99&lt;D99,"BUY","SELL"))</f>
@@ -5133,19 +5363,21 @@
         <f aca="false">IF(I99="","",IF(I99&gt;0,"WIN",IF(I99&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I99" s="31" t="str">
+      <c r="I99" s="32" t="str">
         <f aca="false">IF(OR(G99="",C99=""),"",ROUND((G99-D99)/(D99-E99),2))</f>
         <v/>
       </c>
-      <c r="J99" s="32" t="str">
-        <f aca="false">IF(I99="","",ROUND(I99*$M$2*$M$3,2))</f>
+      <c r="J99" s="33" t="str">
+        <f aca="false">IF(I99="","",ROUND(I99*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K99" s="6"/>
-      <c r="L99" s="26"/>
+      <c r="L99" s="6"/>
+      <c r="M99" s="6"/>
+      <c r="N99" s="26"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="30"/>
+      <c r="A100" s="31"/>
       <c r="B100" s="6"/>
       <c r="C100" s="8" t="str">
         <f aca="false">IF(OR(D100="",E100="",D100=E100),"",IF(E100&lt;D100,"BUY","SELL"))</f>
@@ -5162,19 +5394,21 @@
         <f aca="false">IF(I100="","",IF(I100&gt;0,"WIN",IF(I100&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I100" s="31" t="str">
+      <c r="I100" s="32" t="str">
         <f aca="false">IF(OR(G100="",C100=""),"",ROUND((G100-D100)/(D100-E100),2))</f>
         <v/>
       </c>
-      <c r="J100" s="32" t="str">
-        <f aca="false">IF(I100="","",ROUND(I100*$M$2*$M$3,2))</f>
+      <c r="J100" s="33" t="str">
+        <f aca="false">IF(I100="","",ROUND(I100*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K100" s="6"/>
-      <c r="L100" s="26"/>
+      <c r="L100" s="6"/>
+      <c r="M100" s="6"/>
+      <c r="N100" s="26"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="30"/>
+      <c r="A101" s="31"/>
       <c r="B101" s="6"/>
       <c r="C101" s="8" t="str">
         <f aca="false">IF(OR(D101="",E101="",D101=E101),"",IF(E101&lt;D101,"BUY","SELL"))</f>
@@ -5191,19 +5425,21 @@
         <f aca="false">IF(I101="","",IF(I101&gt;0,"WIN",IF(I101&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I101" s="31" t="str">
+      <c r="I101" s="32" t="str">
         <f aca="false">IF(OR(G101="",C101=""),"",ROUND((G101-D101)/(D101-E101),2))</f>
         <v/>
       </c>
-      <c r="J101" s="32" t="str">
-        <f aca="false">IF(I101="","",ROUND(I101*$M$2*$M$3,2))</f>
+      <c r="J101" s="33" t="str">
+        <f aca="false">IF(I101="","",ROUND(I101*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K101" s="6"/>
-      <c r="L101" s="26"/>
+      <c r="L101" s="6"/>
+      <c r="M101" s="6"/>
+      <c r="N101" s="26"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="30"/>
+      <c r="A102" s="31"/>
       <c r="B102" s="6"/>
       <c r="C102" s="8" t="str">
         <f aca="false">IF(OR(D102="",E102="",D102=E102),"",IF(E102&lt;D102,"BUY","SELL"))</f>
@@ -5220,19 +5456,21 @@
         <f aca="false">IF(I102="","",IF(I102&gt;0,"WIN",IF(I102&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I102" s="31" t="str">
+      <c r="I102" s="32" t="str">
         <f aca="false">IF(OR(G102="",C102=""),"",ROUND((G102-D102)/(D102-E102),2))</f>
         <v/>
       </c>
-      <c r="J102" s="32" t="str">
-        <f aca="false">IF(I102="","",ROUND(I102*$M$2*$M$3,2))</f>
+      <c r="J102" s="33" t="str">
+        <f aca="false">IF(I102="","",ROUND(I102*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K102" s="6"/>
-      <c r="L102" s="26"/>
+      <c r="L102" s="6"/>
+      <c r="M102" s="6"/>
+      <c r="N102" s="26"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="30"/>
+      <c r="A103" s="31"/>
       <c r="B103" s="6"/>
       <c r="C103" s="8" t="str">
         <f aca="false">IF(OR(D103="",E103="",D103=E103),"",IF(E103&lt;D103,"BUY","SELL"))</f>
@@ -5249,19 +5487,21 @@
         <f aca="false">IF(I103="","",IF(I103&gt;0,"WIN",IF(I103&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I103" s="31" t="str">
+      <c r="I103" s="32" t="str">
         <f aca="false">IF(OR(G103="",C103=""),"",ROUND((G103-D103)/(D103-E103),2))</f>
         <v/>
       </c>
-      <c r="J103" s="32" t="str">
-        <f aca="false">IF(I103="","",ROUND(I103*$M$2*$M$3,2))</f>
+      <c r="J103" s="33" t="str">
+        <f aca="false">IF(I103="","",ROUND(I103*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K103" s="6"/>
-      <c r="L103" s="26"/>
+      <c r="L103" s="6"/>
+      <c r="M103" s="6"/>
+      <c r="N103" s="26"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="30"/>
+      <c r="A104" s="31"/>
       <c r="B104" s="6"/>
       <c r="C104" s="8" t="str">
         <f aca="false">IF(OR(D104="",E104="",D104=E104),"",IF(E104&lt;D104,"BUY","SELL"))</f>
@@ -5278,19 +5518,21 @@
         <f aca="false">IF(I104="","",IF(I104&gt;0,"WIN",IF(I104&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I104" s="31" t="str">
+      <c r="I104" s="32" t="str">
         <f aca="false">IF(OR(G104="",C104=""),"",ROUND((G104-D104)/(D104-E104),2))</f>
         <v/>
       </c>
-      <c r="J104" s="32" t="str">
-        <f aca="false">IF(I104="","",ROUND(I104*$M$2*$M$3,2))</f>
+      <c r="J104" s="33" t="str">
+        <f aca="false">IF(I104="","",ROUND(I104*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K104" s="6"/>
-      <c r="L104" s="26"/>
+      <c r="L104" s="6"/>
+      <c r="M104" s="6"/>
+      <c r="N104" s="26"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="30"/>
+      <c r="A105" s="31"/>
       <c r="B105" s="6"/>
       <c r="C105" s="8" t="str">
         <f aca="false">IF(OR(D105="",E105="",D105=E105),"",IF(E105&lt;D105,"BUY","SELL"))</f>
@@ -5307,19 +5549,21 @@
         <f aca="false">IF(I105="","",IF(I105&gt;0,"WIN",IF(I105&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I105" s="31" t="str">
+      <c r="I105" s="32" t="str">
         <f aca="false">IF(OR(G105="",C105=""),"",ROUND((G105-D105)/(D105-E105),2))</f>
         <v/>
       </c>
-      <c r="J105" s="32" t="str">
-        <f aca="false">IF(I105="","",ROUND(I105*$M$2*$M$3,2))</f>
+      <c r="J105" s="33" t="str">
+        <f aca="false">IF(I105="","",ROUND(I105*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K105" s="6"/>
-      <c r="L105" s="26"/>
+      <c r="L105" s="6"/>
+      <c r="M105" s="6"/>
+      <c r="N105" s="26"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="30"/>
+      <c r="A106" s="31"/>
       <c r="B106" s="6"/>
       <c r="C106" s="8" t="str">
         <f aca="false">IF(OR(D106="",E106="",D106=E106),"",IF(E106&lt;D106,"BUY","SELL"))</f>
@@ -5336,19 +5580,21 @@
         <f aca="false">IF(I106="","",IF(I106&gt;0,"WIN",IF(I106&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I106" s="31" t="str">
+      <c r="I106" s="32" t="str">
         <f aca="false">IF(OR(G106="",C106=""),"",ROUND((G106-D106)/(D106-E106),2))</f>
         <v/>
       </c>
-      <c r="J106" s="32" t="str">
-        <f aca="false">IF(I106="","",ROUND(I106*$M$2*$M$3,2))</f>
+      <c r="J106" s="33" t="str">
+        <f aca="false">IF(I106="","",ROUND(I106*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K106" s="6"/>
-      <c r="L106" s="26"/>
+      <c r="L106" s="6"/>
+      <c r="M106" s="6"/>
+      <c r="N106" s="26"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="30"/>
+      <c r="A107" s="31"/>
       <c r="B107" s="6"/>
       <c r="C107" s="8" t="str">
         <f aca="false">IF(OR(D107="",E107="",D107=E107),"",IF(E107&lt;D107,"BUY","SELL"))</f>
@@ -5365,19 +5611,21 @@
         <f aca="false">IF(I107="","",IF(I107&gt;0,"WIN",IF(I107&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I107" s="31" t="str">
+      <c r="I107" s="32" t="str">
         <f aca="false">IF(OR(G107="",C107=""),"",ROUND((G107-D107)/(D107-E107),2))</f>
         <v/>
       </c>
-      <c r="J107" s="32" t="str">
-        <f aca="false">IF(I107="","",ROUND(I107*$M$2*$M$3,2))</f>
+      <c r="J107" s="33" t="str">
+        <f aca="false">IF(I107="","",ROUND(I107*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K107" s="6"/>
-      <c r="L107" s="26"/>
+      <c r="L107" s="6"/>
+      <c r="M107" s="6"/>
+      <c r="N107" s="26"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="30"/>
+      <c r="A108" s="31"/>
       <c r="B108" s="6"/>
       <c r="C108" s="8" t="str">
         <f aca="false">IF(OR(D108="",E108="",D108=E108),"",IF(E108&lt;D108,"BUY","SELL"))</f>
@@ -5394,19 +5642,21 @@
         <f aca="false">IF(I108="","",IF(I108&gt;0,"WIN",IF(I108&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I108" s="31" t="str">
+      <c r="I108" s="32" t="str">
         <f aca="false">IF(OR(G108="",C108=""),"",ROUND((G108-D108)/(D108-E108),2))</f>
         <v/>
       </c>
-      <c r="J108" s="32" t="str">
-        <f aca="false">IF(I108="","",ROUND(I108*$M$2*$M$3,2))</f>
+      <c r="J108" s="33" t="str">
+        <f aca="false">IF(I108="","",ROUND(I108*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K108" s="6"/>
-      <c r="L108" s="26"/>
+      <c r="L108" s="6"/>
+      <c r="M108" s="6"/>
+      <c r="N108" s="26"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="30"/>
+      <c r="A109" s="31"/>
       <c r="B109" s="6"/>
       <c r="C109" s="8" t="str">
         <f aca="false">IF(OR(D109="",E109="",D109=E109),"",IF(E109&lt;D109,"BUY","SELL"))</f>
@@ -5423,19 +5673,21 @@
         <f aca="false">IF(I109="","",IF(I109&gt;0,"WIN",IF(I109&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I109" s="31" t="str">
+      <c r="I109" s="32" t="str">
         <f aca="false">IF(OR(G109="",C109=""),"",ROUND((G109-D109)/(D109-E109),2))</f>
         <v/>
       </c>
-      <c r="J109" s="32" t="str">
-        <f aca="false">IF(I109="","",ROUND(I109*$M$2*$M$3,2))</f>
+      <c r="J109" s="33" t="str">
+        <f aca="false">IF(I109="","",ROUND(I109*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K109" s="6"/>
-      <c r="L109" s="26"/>
+      <c r="L109" s="6"/>
+      <c r="M109" s="6"/>
+      <c r="N109" s="26"/>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="30"/>
+      <c r="A110" s="31"/>
       <c r="B110" s="6"/>
       <c r="C110" s="8" t="str">
         <f aca="false">IF(OR(D110="",E110="",D110=E110),"",IF(E110&lt;D110,"BUY","SELL"))</f>
@@ -5452,19 +5704,21 @@
         <f aca="false">IF(I110="","",IF(I110&gt;0,"WIN",IF(I110&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I110" s="31" t="str">
+      <c r="I110" s="32" t="str">
         <f aca="false">IF(OR(G110="",C110=""),"",ROUND((G110-D110)/(D110-E110),2))</f>
         <v/>
       </c>
-      <c r="J110" s="32" t="str">
-        <f aca="false">IF(I110="","",ROUND(I110*$M$2*$M$3,2))</f>
+      <c r="J110" s="33" t="str">
+        <f aca="false">IF(I110="","",ROUND(I110*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K110" s="6"/>
-      <c r="L110" s="26"/>
+      <c r="L110" s="6"/>
+      <c r="M110" s="6"/>
+      <c r="N110" s="26"/>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="30"/>
+      <c r="A111" s="31"/>
       <c r="B111" s="6"/>
       <c r="C111" s="8" t="str">
         <f aca="false">IF(OR(D111="",E111="",D111=E111),"",IF(E111&lt;D111,"BUY","SELL"))</f>
@@ -5481,19 +5735,21 @@
         <f aca="false">IF(I111="","",IF(I111&gt;0,"WIN",IF(I111&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I111" s="31" t="str">
+      <c r="I111" s="32" t="str">
         <f aca="false">IF(OR(G111="",C111=""),"",ROUND((G111-D111)/(D111-E111),2))</f>
         <v/>
       </c>
-      <c r="J111" s="32" t="str">
-        <f aca="false">IF(I111="","",ROUND(I111*$M$2*$M$3,2))</f>
+      <c r="J111" s="33" t="str">
+        <f aca="false">IF(I111="","",ROUND(I111*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K111" s="6"/>
-      <c r="L111" s="26"/>
+      <c r="L111" s="6"/>
+      <c r="M111" s="6"/>
+      <c r="N111" s="26"/>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="30"/>
+      <c r="A112" s="31"/>
       <c r="B112" s="6"/>
       <c r="C112" s="8" t="str">
         <f aca="false">IF(OR(D112="",E112="",D112=E112),"",IF(E112&lt;D112,"BUY","SELL"))</f>
@@ -5510,19 +5766,21 @@
         <f aca="false">IF(I112="","",IF(I112&gt;0,"WIN",IF(I112&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I112" s="31" t="str">
+      <c r="I112" s="32" t="str">
         <f aca="false">IF(OR(G112="",C112=""),"",ROUND((G112-D112)/(D112-E112),2))</f>
         <v/>
       </c>
-      <c r="J112" s="32" t="str">
-        <f aca="false">IF(I112="","",ROUND(I112*$M$2*$M$3,2))</f>
+      <c r="J112" s="33" t="str">
+        <f aca="false">IF(I112="","",ROUND(I112*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K112" s="6"/>
-      <c r="L112" s="26"/>
+      <c r="L112" s="6"/>
+      <c r="M112" s="6"/>
+      <c r="N112" s="26"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="30"/>
+      <c r="A113" s="31"/>
       <c r="B113" s="6"/>
       <c r="C113" s="8" t="str">
         <f aca="false">IF(OR(D113="",E113="",D113=E113),"",IF(E113&lt;D113,"BUY","SELL"))</f>
@@ -5539,19 +5797,21 @@
         <f aca="false">IF(I113="","",IF(I113&gt;0,"WIN",IF(I113&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I113" s="31" t="str">
+      <c r="I113" s="32" t="str">
         <f aca="false">IF(OR(G113="",C113=""),"",ROUND((G113-D113)/(D113-E113),2))</f>
         <v/>
       </c>
-      <c r="J113" s="32" t="str">
-        <f aca="false">IF(I113="","",ROUND(I113*$M$2*$M$3,2))</f>
+      <c r="J113" s="33" t="str">
+        <f aca="false">IF(I113="","",ROUND(I113*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K113" s="6"/>
-      <c r="L113" s="26"/>
+      <c r="L113" s="6"/>
+      <c r="M113" s="6"/>
+      <c r="N113" s="26"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="30"/>
+      <c r="A114" s="31"/>
       <c r="B114" s="6"/>
       <c r="C114" s="8" t="str">
         <f aca="false">IF(OR(D114="",E114="",D114=E114),"",IF(E114&lt;D114,"BUY","SELL"))</f>
@@ -5568,19 +5828,21 @@
         <f aca="false">IF(I114="","",IF(I114&gt;0,"WIN",IF(I114&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I114" s="31" t="str">
+      <c r="I114" s="32" t="str">
         <f aca="false">IF(OR(G114="",C114=""),"",ROUND((G114-D114)/(D114-E114),2))</f>
         <v/>
       </c>
-      <c r="J114" s="32" t="str">
-        <f aca="false">IF(I114="","",ROUND(I114*$M$2*$M$3,2))</f>
+      <c r="J114" s="33" t="str">
+        <f aca="false">IF(I114="","",ROUND(I114*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K114" s="6"/>
-      <c r="L114" s="26"/>
+      <c r="L114" s="6"/>
+      <c r="M114" s="6"/>
+      <c r="N114" s="26"/>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="30"/>
+      <c r="A115" s="31"/>
       <c r="B115" s="6"/>
       <c r="C115" s="8" t="str">
         <f aca="false">IF(OR(D115="",E115="",D115=E115),"",IF(E115&lt;D115,"BUY","SELL"))</f>
@@ -5597,19 +5859,21 @@
         <f aca="false">IF(I115="","",IF(I115&gt;0,"WIN",IF(I115&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I115" s="31" t="str">
+      <c r="I115" s="32" t="str">
         <f aca="false">IF(OR(G115="",C115=""),"",ROUND((G115-D115)/(D115-E115),2))</f>
         <v/>
       </c>
-      <c r="J115" s="32" t="str">
-        <f aca="false">IF(I115="","",ROUND(I115*$M$2*$M$3,2))</f>
+      <c r="J115" s="33" t="str">
+        <f aca="false">IF(I115="","",ROUND(I115*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K115" s="6"/>
-      <c r="L115" s="26"/>
+      <c r="L115" s="6"/>
+      <c r="M115" s="6"/>
+      <c r="N115" s="26"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="30"/>
+      <c r="A116" s="31"/>
       <c r="B116" s="6"/>
       <c r="C116" s="8" t="str">
         <f aca="false">IF(OR(D116="",E116="",D116=E116),"",IF(E116&lt;D116,"BUY","SELL"))</f>
@@ -5626,19 +5890,21 @@
         <f aca="false">IF(I116="","",IF(I116&gt;0,"WIN",IF(I116&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I116" s="31" t="str">
+      <c r="I116" s="32" t="str">
         <f aca="false">IF(OR(G116="",C116=""),"",ROUND((G116-D116)/(D116-E116),2))</f>
         <v/>
       </c>
-      <c r="J116" s="32" t="str">
-        <f aca="false">IF(I116="","",ROUND(I116*$M$2*$M$3,2))</f>
+      <c r="J116" s="33" t="str">
+        <f aca="false">IF(I116="","",ROUND(I116*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K116" s="6"/>
-      <c r="L116" s="26"/>
+      <c r="L116" s="6"/>
+      <c r="M116" s="6"/>
+      <c r="N116" s="26"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="30"/>
+      <c r="A117" s="31"/>
       <c r="B117" s="6"/>
       <c r="C117" s="8" t="str">
         <f aca="false">IF(OR(D117="",E117="",D117=E117),"",IF(E117&lt;D117,"BUY","SELL"))</f>
@@ -5655,19 +5921,21 @@
         <f aca="false">IF(I117="","",IF(I117&gt;0,"WIN",IF(I117&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I117" s="31" t="str">
+      <c r="I117" s="32" t="str">
         <f aca="false">IF(OR(G117="",C117=""),"",ROUND((G117-D117)/(D117-E117),2))</f>
         <v/>
       </c>
-      <c r="J117" s="32" t="str">
-        <f aca="false">IF(I117="","",ROUND(I117*$M$2*$M$3,2))</f>
+      <c r="J117" s="33" t="str">
+        <f aca="false">IF(I117="","",ROUND(I117*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K117" s="6"/>
-      <c r="L117" s="26"/>
+      <c r="L117" s="6"/>
+      <c r="M117" s="6"/>
+      <c r="N117" s="26"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="30"/>
+      <c r="A118" s="31"/>
       <c r="B118" s="6"/>
       <c r="C118" s="8" t="str">
         <f aca="false">IF(OR(D118="",E118="",D118=E118),"",IF(E118&lt;D118,"BUY","SELL"))</f>
@@ -5684,19 +5952,21 @@
         <f aca="false">IF(I118="","",IF(I118&gt;0,"WIN",IF(I118&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I118" s="31" t="str">
+      <c r="I118" s="32" t="str">
         <f aca="false">IF(OR(G118="",C118=""),"",ROUND((G118-D118)/(D118-E118),2))</f>
         <v/>
       </c>
-      <c r="J118" s="32" t="str">
-        <f aca="false">IF(I118="","",ROUND(I118*$M$2*$M$3,2))</f>
+      <c r="J118" s="33" t="str">
+        <f aca="false">IF(I118="","",ROUND(I118*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K118" s="6"/>
-      <c r="L118" s="26"/>
+      <c r="L118" s="6"/>
+      <c r="M118" s="6"/>
+      <c r="N118" s="26"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="30"/>
+      <c r="A119" s="31"/>
       <c r="B119" s="6"/>
       <c r="C119" s="8" t="str">
         <f aca="false">IF(OR(D119="",E119="",D119=E119),"",IF(E119&lt;D119,"BUY","SELL"))</f>
@@ -5713,19 +5983,21 @@
         <f aca="false">IF(I119="","",IF(I119&gt;0,"WIN",IF(I119&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I119" s="31" t="str">
+      <c r="I119" s="32" t="str">
         <f aca="false">IF(OR(G119="",C119=""),"",ROUND((G119-D119)/(D119-E119),2))</f>
         <v/>
       </c>
-      <c r="J119" s="32" t="str">
-        <f aca="false">IF(I119="","",ROUND(I119*$M$2*$M$3,2))</f>
+      <c r="J119" s="33" t="str">
+        <f aca="false">IF(I119="","",ROUND(I119*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K119" s="6"/>
-      <c r="L119" s="26"/>
+      <c r="L119" s="6"/>
+      <c r="M119" s="6"/>
+      <c r="N119" s="26"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="30"/>
+      <c r="A120" s="31"/>
       <c r="B120" s="6"/>
       <c r="C120" s="8" t="str">
         <f aca="false">IF(OR(D120="",E120="",D120=E120),"",IF(E120&lt;D120,"BUY","SELL"))</f>
@@ -5742,19 +6014,21 @@
         <f aca="false">IF(I120="","",IF(I120&gt;0,"WIN",IF(I120&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I120" s="31" t="str">
+      <c r="I120" s="32" t="str">
         <f aca="false">IF(OR(G120="",C120=""),"",ROUND((G120-D120)/(D120-E120),2))</f>
         <v/>
       </c>
-      <c r="J120" s="32" t="str">
-        <f aca="false">IF(I120="","",ROUND(I120*$M$2*$M$3,2))</f>
+      <c r="J120" s="33" t="str">
+        <f aca="false">IF(I120="","",ROUND(I120*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K120" s="6"/>
-      <c r="L120" s="26"/>
+      <c r="L120" s="6"/>
+      <c r="M120" s="6"/>
+      <c r="N120" s="26"/>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="30"/>
+      <c r="A121" s="31"/>
       <c r="B121" s="6"/>
       <c r="C121" s="8" t="str">
         <f aca="false">IF(OR(D121="",E121="",D121=E121),"",IF(E121&lt;D121,"BUY","SELL"))</f>
@@ -5771,19 +6045,21 @@
         <f aca="false">IF(I121="","",IF(I121&gt;0,"WIN",IF(I121&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I121" s="31" t="str">
+      <c r="I121" s="32" t="str">
         <f aca="false">IF(OR(G121="",C121=""),"",ROUND((G121-D121)/(D121-E121),2))</f>
         <v/>
       </c>
-      <c r="J121" s="32" t="str">
-        <f aca="false">IF(I121="","",ROUND(I121*$M$2*$M$3,2))</f>
+      <c r="J121" s="33" t="str">
+        <f aca="false">IF(I121="","",ROUND(I121*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K121" s="6"/>
-      <c r="L121" s="26"/>
+      <c r="L121" s="6"/>
+      <c r="M121" s="6"/>
+      <c r="N121" s="26"/>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="30"/>
+      <c r="A122" s="31"/>
       <c r="B122" s="6"/>
       <c r="C122" s="8" t="str">
         <f aca="false">IF(OR(D122="",E122="",D122=E122),"",IF(E122&lt;D122,"BUY","SELL"))</f>
@@ -5800,19 +6076,21 @@
         <f aca="false">IF(I122="","",IF(I122&gt;0,"WIN",IF(I122&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I122" s="31" t="str">
+      <c r="I122" s="32" t="str">
         <f aca="false">IF(OR(G122="",C122=""),"",ROUND((G122-D122)/(D122-E122),2))</f>
         <v/>
       </c>
-      <c r="J122" s="32" t="str">
-        <f aca="false">IF(I122="","",ROUND(I122*$M$2*$M$3,2))</f>
+      <c r="J122" s="33" t="str">
+        <f aca="false">IF(I122="","",ROUND(I122*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K122" s="6"/>
-      <c r="L122" s="26"/>
+      <c r="L122" s="6"/>
+      <c r="M122" s="6"/>
+      <c r="N122" s="26"/>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="30"/>
+      <c r="A123" s="31"/>
       <c r="B123" s="6"/>
       <c r="C123" s="8" t="str">
         <f aca="false">IF(OR(D123="",E123="",D123=E123),"",IF(E123&lt;D123,"BUY","SELL"))</f>
@@ -5829,19 +6107,21 @@
         <f aca="false">IF(I123="","",IF(I123&gt;0,"WIN",IF(I123&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I123" s="31" t="str">
+      <c r="I123" s="32" t="str">
         <f aca="false">IF(OR(G123="",C123=""),"",ROUND((G123-D123)/(D123-E123),2))</f>
         <v/>
       </c>
-      <c r="J123" s="32" t="str">
-        <f aca="false">IF(I123="","",ROUND(I123*$M$2*$M$3,2))</f>
+      <c r="J123" s="33" t="str">
+        <f aca="false">IF(I123="","",ROUND(I123*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K123" s="6"/>
-      <c r="L123" s="26"/>
+      <c r="L123" s="6"/>
+      <c r="M123" s="6"/>
+      <c r="N123" s="26"/>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="30"/>
+      <c r="A124" s="31"/>
       <c r="B124" s="6"/>
       <c r="C124" s="8" t="str">
         <f aca="false">IF(OR(D124="",E124="",D124=E124),"",IF(E124&lt;D124,"BUY","SELL"))</f>
@@ -5858,19 +6138,21 @@
         <f aca="false">IF(I124="","",IF(I124&gt;0,"WIN",IF(I124&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I124" s="31" t="str">
+      <c r="I124" s="32" t="str">
         <f aca="false">IF(OR(G124="",C124=""),"",ROUND((G124-D124)/(D124-E124),2))</f>
         <v/>
       </c>
-      <c r="J124" s="32" t="str">
-        <f aca="false">IF(I124="","",ROUND(I124*$M$2*$M$3,2))</f>
+      <c r="J124" s="33" t="str">
+        <f aca="false">IF(I124="","",ROUND(I124*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K124" s="6"/>
-      <c r="L124" s="26"/>
+      <c r="L124" s="6"/>
+      <c r="M124" s="6"/>
+      <c r="N124" s="26"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="30"/>
+      <c r="A125" s="31"/>
       <c r="B125" s="6"/>
       <c r="C125" s="8" t="str">
         <f aca="false">IF(OR(D125="",E125="",D125=E125),"",IF(E125&lt;D125,"BUY","SELL"))</f>
@@ -5887,19 +6169,21 @@
         <f aca="false">IF(I125="","",IF(I125&gt;0,"WIN",IF(I125&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I125" s="31" t="str">
+      <c r="I125" s="32" t="str">
         <f aca="false">IF(OR(G125="",C125=""),"",ROUND((G125-D125)/(D125-E125),2))</f>
         <v/>
       </c>
-      <c r="J125" s="32" t="str">
-        <f aca="false">IF(I125="","",ROUND(I125*$M$2*$M$3,2))</f>
+      <c r="J125" s="33" t="str">
+        <f aca="false">IF(I125="","",ROUND(I125*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K125" s="6"/>
-      <c r="L125" s="26"/>
+      <c r="L125" s="6"/>
+      <c r="M125" s="6"/>
+      <c r="N125" s="26"/>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="30"/>
+      <c r="A126" s="31"/>
       <c r="B126" s="6"/>
       <c r="C126" s="8" t="str">
         <f aca="false">IF(OR(D126="",E126="",D126=E126),"",IF(E126&lt;D126,"BUY","SELL"))</f>
@@ -5916,19 +6200,21 @@
         <f aca="false">IF(I126="","",IF(I126&gt;0,"WIN",IF(I126&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I126" s="31" t="str">
+      <c r="I126" s="32" t="str">
         <f aca="false">IF(OR(G126="",C126=""),"",ROUND((G126-D126)/(D126-E126),2))</f>
         <v/>
       </c>
-      <c r="J126" s="32" t="str">
-        <f aca="false">IF(I126="","",ROUND(I126*$M$2*$M$3,2))</f>
+      <c r="J126" s="33" t="str">
+        <f aca="false">IF(I126="","",ROUND(I126*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K126" s="6"/>
-      <c r="L126" s="26"/>
+      <c r="L126" s="6"/>
+      <c r="M126" s="6"/>
+      <c r="N126" s="26"/>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="30"/>
+      <c r="A127" s="31"/>
       <c r="B127" s="6"/>
       <c r="C127" s="8" t="str">
         <f aca="false">IF(OR(D127="",E127="",D127=E127),"",IF(E127&lt;D127,"BUY","SELL"))</f>
@@ -5945,19 +6231,21 @@
         <f aca="false">IF(I127="","",IF(I127&gt;0,"WIN",IF(I127&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I127" s="31" t="str">
+      <c r="I127" s="32" t="str">
         <f aca="false">IF(OR(G127="",C127=""),"",ROUND((G127-D127)/(D127-E127),2))</f>
         <v/>
       </c>
-      <c r="J127" s="32" t="str">
-        <f aca="false">IF(I127="","",ROUND(I127*$M$2*$M$3,2))</f>
+      <c r="J127" s="33" t="str">
+        <f aca="false">IF(I127="","",ROUND(I127*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K127" s="6"/>
-      <c r="L127" s="26"/>
+      <c r="L127" s="6"/>
+      <c r="M127" s="6"/>
+      <c r="N127" s="26"/>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="30"/>
+      <c r="A128" s="31"/>
       <c r="B128" s="6"/>
       <c r="C128" s="8" t="str">
         <f aca="false">IF(OR(D128="",E128="",D128=E128),"",IF(E128&lt;D128,"BUY","SELL"))</f>
@@ -5974,19 +6262,21 @@
         <f aca="false">IF(I128="","",IF(I128&gt;0,"WIN",IF(I128&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I128" s="31" t="str">
+      <c r="I128" s="32" t="str">
         <f aca="false">IF(OR(G128="",C128=""),"",ROUND((G128-D128)/(D128-E128),2))</f>
         <v/>
       </c>
-      <c r="J128" s="32" t="str">
-        <f aca="false">IF(I128="","",ROUND(I128*$M$2*$M$3,2))</f>
+      <c r="J128" s="33" t="str">
+        <f aca="false">IF(I128="","",ROUND(I128*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K128" s="6"/>
-      <c r="L128" s="26"/>
+      <c r="L128" s="6"/>
+      <c r="M128" s="6"/>
+      <c r="N128" s="26"/>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="30"/>
+      <c r="A129" s="31"/>
       <c r="B129" s="6"/>
       <c r="C129" s="8" t="str">
         <f aca="false">IF(OR(D129="",E129="",D129=E129),"",IF(E129&lt;D129,"BUY","SELL"))</f>
@@ -6003,19 +6293,21 @@
         <f aca="false">IF(I129="","",IF(I129&gt;0,"WIN",IF(I129&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I129" s="31" t="str">
+      <c r="I129" s="32" t="str">
         <f aca="false">IF(OR(G129="",C129=""),"",ROUND((G129-D129)/(D129-E129),2))</f>
         <v/>
       </c>
-      <c r="J129" s="32" t="str">
-        <f aca="false">IF(I129="","",ROUND(I129*$M$2*$M$3,2))</f>
+      <c r="J129" s="33" t="str">
+        <f aca="false">IF(I129="","",ROUND(I129*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K129" s="6"/>
-      <c r="L129" s="26"/>
+      <c r="L129" s="6"/>
+      <c r="M129" s="6"/>
+      <c r="N129" s="26"/>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="30"/>
+      <c r="A130" s="31"/>
       <c r="B130" s="6"/>
       <c r="C130" s="8" t="str">
         <f aca="false">IF(OR(D130="",E130="",D130=E130),"",IF(E130&lt;D130,"BUY","SELL"))</f>
@@ -6032,19 +6324,21 @@
         <f aca="false">IF(I130="","",IF(I130&gt;0,"WIN",IF(I130&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I130" s="31" t="str">
+      <c r="I130" s="32" t="str">
         <f aca="false">IF(OR(G130="",C130=""),"",ROUND((G130-D130)/(D130-E130),2))</f>
         <v/>
       </c>
-      <c r="J130" s="32" t="str">
-        <f aca="false">IF(I130="","",ROUND(I130*$M$2*$M$3,2))</f>
+      <c r="J130" s="33" t="str">
+        <f aca="false">IF(I130="","",ROUND(I130*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K130" s="6"/>
-      <c r="L130" s="26"/>
+      <c r="L130" s="6"/>
+      <c r="M130" s="6"/>
+      <c r="N130" s="26"/>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="30"/>
+      <c r="A131" s="31"/>
       <c r="B131" s="6"/>
       <c r="C131" s="8" t="str">
         <f aca="false">IF(OR(D131="",E131="",D131=E131),"",IF(E131&lt;D131,"BUY","SELL"))</f>
@@ -6061,19 +6355,21 @@
         <f aca="false">IF(I131="","",IF(I131&gt;0,"WIN",IF(I131&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I131" s="31" t="str">
+      <c r="I131" s="32" t="str">
         <f aca="false">IF(OR(G131="",C131=""),"",ROUND((G131-D131)/(D131-E131),2))</f>
         <v/>
       </c>
-      <c r="J131" s="32" t="str">
-        <f aca="false">IF(I131="","",ROUND(I131*$M$2*$M$3,2))</f>
+      <c r="J131" s="33" t="str">
+        <f aca="false">IF(I131="","",ROUND(I131*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K131" s="6"/>
-      <c r="L131" s="26"/>
+      <c r="L131" s="6"/>
+      <c r="M131" s="6"/>
+      <c r="N131" s="26"/>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="30"/>
+      <c r="A132" s="31"/>
       <c r="B132" s="6"/>
       <c r="C132" s="8" t="str">
         <f aca="false">IF(OR(D132="",E132="",D132=E132),"",IF(E132&lt;D132,"BUY","SELL"))</f>
@@ -6090,19 +6386,21 @@
         <f aca="false">IF(I132="","",IF(I132&gt;0,"WIN",IF(I132&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I132" s="31" t="str">
+      <c r="I132" s="32" t="str">
         <f aca="false">IF(OR(G132="",C132=""),"",ROUND((G132-D132)/(D132-E132),2))</f>
         <v/>
       </c>
-      <c r="J132" s="32" t="str">
-        <f aca="false">IF(I132="","",ROUND(I132*$M$2*$M$3,2))</f>
+      <c r="J132" s="33" t="str">
+        <f aca="false">IF(I132="","",ROUND(I132*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K132" s="6"/>
-      <c r="L132" s="26"/>
+      <c r="L132" s="6"/>
+      <c r="M132" s="6"/>
+      <c r="N132" s="26"/>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="30"/>
+      <c r="A133" s="31"/>
       <c r="B133" s="6"/>
       <c r="C133" s="8" t="str">
         <f aca="false">IF(OR(D133="",E133="",D133=E133),"",IF(E133&lt;D133,"BUY","SELL"))</f>
@@ -6119,19 +6417,21 @@
         <f aca="false">IF(I133="","",IF(I133&gt;0,"WIN",IF(I133&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I133" s="31" t="str">
+      <c r="I133" s="32" t="str">
         <f aca="false">IF(OR(G133="",C133=""),"",ROUND((G133-D133)/(D133-E133),2))</f>
         <v/>
       </c>
-      <c r="J133" s="32" t="str">
-        <f aca="false">IF(I133="","",ROUND(I133*$M$2*$M$3,2))</f>
+      <c r="J133" s="33" t="str">
+        <f aca="false">IF(I133="","",ROUND(I133*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K133" s="6"/>
-      <c r="L133" s="26"/>
+      <c r="L133" s="6"/>
+      <c r="M133" s="6"/>
+      <c r="N133" s="26"/>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="30"/>
+      <c r="A134" s="31"/>
       <c r="B134" s="6"/>
       <c r="C134" s="8" t="str">
         <f aca="false">IF(OR(D134="",E134="",D134=E134),"",IF(E134&lt;D134,"BUY","SELL"))</f>
@@ -6148,19 +6448,21 @@
         <f aca="false">IF(I134="","",IF(I134&gt;0,"WIN",IF(I134&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I134" s="31" t="str">
+      <c r="I134" s="32" t="str">
         <f aca="false">IF(OR(G134="",C134=""),"",ROUND((G134-D134)/(D134-E134),2))</f>
         <v/>
       </c>
-      <c r="J134" s="32" t="str">
-        <f aca="false">IF(I134="","",ROUND(I134*$M$2*$M$3,2))</f>
+      <c r="J134" s="33" t="str">
+        <f aca="false">IF(I134="","",ROUND(I134*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K134" s="6"/>
-      <c r="L134" s="26"/>
+      <c r="L134" s="6"/>
+      <c r="M134" s="6"/>
+      <c r="N134" s="26"/>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="30"/>
+      <c r="A135" s="31"/>
       <c r="B135" s="6"/>
       <c r="C135" s="8" t="str">
         <f aca="false">IF(OR(D135="",E135="",D135=E135),"",IF(E135&lt;D135,"BUY","SELL"))</f>
@@ -6177,19 +6479,21 @@
         <f aca="false">IF(I135="","",IF(I135&gt;0,"WIN",IF(I135&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I135" s="31" t="str">
+      <c r="I135" s="32" t="str">
         <f aca="false">IF(OR(G135="",C135=""),"",ROUND((G135-D135)/(D135-E135),2))</f>
         <v/>
       </c>
-      <c r="J135" s="32" t="str">
-        <f aca="false">IF(I135="","",ROUND(I135*$M$2*$M$3,2))</f>
+      <c r="J135" s="33" t="str">
+        <f aca="false">IF(I135="","",ROUND(I135*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K135" s="6"/>
-      <c r="L135" s="26"/>
+      <c r="L135" s="6"/>
+      <c r="M135" s="6"/>
+      <c r="N135" s="26"/>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="30"/>
+      <c r="A136" s="31"/>
       <c r="B136" s="6"/>
       <c r="C136" s="8" t="str">
         <f aca="false">IF(OR(D136="",E136="",D136=E136),"",IF(E136&lt;D136,"BUY","SELL"))</f>
@@ -6206,19 +6510,21 @@
         <f aca="false">IF(I136="","",IF(I136&gt;0,"WIN",IF(I136&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I136" s="31" t="str">
+      <c r="I136" s="32" t="str">
         <f aca="false">IF(OR(G136="",C136=""),"",ROUND((G136-D136)/(D136-E136),2))</f>
         <v/>
       </c>
-      <c r="J136" s="32" t="str">
-        <f aca="false">IF(I136="","",ROUND(I136*$M$2*$M$3,2))</f>
+      <c r="J136" s="33" t="str">
+        <f aca="false">IF(I136="","",ROUND(I136*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K136" s="6"/>
-      <c r="L136" s="26"/>
+      <c r="L136" s="6"/>
+      <c r="M136" s="6"/>
+      <c r="N136" s="26"/>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="30"/>
+      <c r="A137" s="31"/>
       <c r="B137" s="6"/>
       <c r="C137" s="8" t="str">
         <f aca="false">IF(OR(D137="",E137="",D137=E137),"",IF(E137&lt;D137,"BUY","SELL"))</f>
@@ -6235,19 +6541,21 @@
         <f aca="false">IF(I137="","",IF(I137&gt;0,"WIN",IF(I137&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I137" s="31" t="str">
+      <c r="I137" s="32" t="str">
         <f aca="false">IF(OR(G137="",C137=""),"",ROUND((G137-D137)/(D137-E137),2))</f>
         <v/>
       </c>
-      <c r="J137" s="32" t="str">
-        <f aca="false">IF(I137="","",ROUND(I137*$M$2*$M$3,2))</f>
+      <c r="J137" s="33" t="str">
+        <f aca="false">IF(I137="","",ROUND(I137*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K137" s="6"/>
-      <c r="L137" s="26"/>
+      <c r="L137" s="6"/>
+      <c r="M137" s="6"/>
+      <c r="N137" s="26"/>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="30"/>
+      <c r="A138" s="31"/>
       <c r="B138" s="6"/>
       <c r="C138" s="8" t="str">
         <f aca="false">IF(OR(D138="",E138="",D138=E138),"",IF(E138&lt;D138,"BUY","SELL"))</f>
@@ -6264,19 +6572,21 @@
         <f aca="false">IF(I138="","",IF(I138&gt;0,"WIN",IF(I138&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I138" s="31" t="str">
+      <c r="I138" s="32" t="str">
         <f aca="false">IF(OR(G138="",C138=""),"",ROUND((G138-D138)/(D138-E138),2))</f>
         <v/>
       </c>
-      <c r="J138" s="32" t="str">
-        <f aca="false">IF(I138="","",ROUND(I138*$M$2*$M$3,2))</f>
+      <c r="J138" s="33" t="str">
+        <f aca="false">IF(I138="","",ROUND(I138*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K138" s="6"/>
-      <c r="L138" s="26"/>
+      <c r="L138" s="6"/>
+      <c r="M138" s="6"/>
+      <c r="N138" s="26"/>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="30"/>
+      <c r="A139" s="31"/>
       <c r="B139" s="6"/>
       <c r="C139" s="8" t="str">
         <f aca="false">IF(OR(D139="",E139="",D139=E139),"",IF(E139&lt;D139,"BUY","SELL"))</f>
@@ -6293,19 +6603,21 @@
         <f aca="false">IF(I139="","",IF(I139&gt;0,"WIN",IF(I139&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I139" s="31" t="str">
+      <c r="I139" s="32" t="str">
         <f aca="false">IF(OR(G139="",C139=""),"",ROUND((G139-D139)/(D139-E139),2))</f>
         <v/>
       </c>
-      <c r="J139" s="32" t="str">
-        <f aca="false">IF(I139="","",ROUND(I139*$M$2*$M$3,2))</f>
+      <c r="J139" s="33" t="str">
+        <f aca="false">IF(I139="","",ROUND(I139*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K139" s="6"/>
-      <c r="L139" s="26"/>
+      <c r="L139" s="6"/>
+      <c r="M139" s="6"/>
+      <c r="N139" s="26"/>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="30"/>
+      <c r="A140" s="31"/>
       <c r="B140" s="6"/>
       <c r="C140" s="8" t="str">
         <f aca="false">IF(OR(D140="",E140="",D140=E140),"",IF(E140&lt;D140,"BUY","SELL"))</f>
@@ -6322,19 +6634,21 @@
         <f aca="false">IF(I140="","",IF(I140&gt;0,"WIN",IF(I140&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I140" s="31" t="str">
+      <c r="I140" s="32" t="str">
         <f aca="false">IF(OR(G140="",C140=""),"",ROUND((G140-D140)/(D140-E140),2))</f>
         <v/>
       </c>
-      <c r="J140" s="32" t="str">
-        <f aca="false">IF(I140="","",ROUND(I140*$M$2*$M$3,2))</f>
+      <c r="J140" s="33" t="str">
+        <f aca="false">IF(I140="","",ROUND(I140*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K140" s="6"/>
-      <c r="L140" s="26"/>
+      <c r="L140" s="6"/>
+      <c r="M140" s="6"/>
+      <c r="N140" s="26"/>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="30"/>
+      <c r="A141" s="31"/>
       <c r="B141" s="6"/>
       <c r="C141" s="8" t="str">
         <f aca="false">IF(OR(D141="",E141="",D141=E141),"",IF(E141&lt;D141,"BUY","SELL"))</f>
@@ -6351,19 +6665,21 @@
         <f aca="false">IF(I141="","",IF(I141&gt;0,"WIN",IF(I141&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I141" s="31" t="str">
+      <c r="I141" s="32" t="str">
         <f aca="false">IF(OR(G141="",C141=""),"",ROUND((G141-D141)/(D141-E141),2))</f>
         <v/>
       </c>
-      <c r="J141" s="32" t="str">
-        <f aca="false">IF(I141="","",ROUND(I141*$M$2*$M$3,2))</f>
+      <c r="J141" s="33" t="str">
+        <f aca="false">IF(I141="","",ROUND(I141*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K141" s="6"/>
-      <c r="L141" s="26"/>
+      <c r="L141" s="6"/>
+      <c r="M141" s="6"/>
+      <c r="N141" s="26"/>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="30"/>
+      <c r="A142" s="31"/>
       <c r="B142" s="6"/>
       <c r="C142" s="8" t="str">
         <f aca="false">IF(OR(D142="",E142="",D142=E142),"",IF(E142&lt;D142,"BUY","SELL"))</f>
@@ -6380,19 +6696,21 @@
         <f aca="false">IF(I142="","",IF(I142&gt;0,"WIN",IF(I142&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I142" s="31" t="str">
+      <c r="I142" s="32" t="str">
         <f aca="false">IF(OR(G142="",C142=""),"",ROUND((G142-D142)/(D142-E142),2))</f>
         <v/>
       </c>
-      <c r="J142" s="32" t="str">
-        <f aca="false">IF(I142="","",ROUND(I142*$M$2*$M$3,2))</f>
+      <c r="J142" s="33" t="str">
+        <f aca="false">IF(I142="","",ROUND(I142*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K142" s="6"/>
-      <c r="L142" s="26"/>
+      <c r="L142" s="6"/>
+      <c r="M142" s="6"/>
+      <c r="N142" s="26"/>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="30"/>
+      <c r="A143" s="31"/>
       <c r="B143" s="6"/>
       <c r="C143" s="8" t="str">
         <f aca="false">IF(OR(D143="",E143="",D143=E143),"",IF(E143&lt;D143,"BUY","SELL"))</f>
@@ -6409,19 +6727,21 @@
         <f aca="false">IF(I143="","",IF(I143&gt;0,"WIN",IF(I143&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I143" s="31" t="str">
+      <c r="I143" s="32" t="str">
         <f aca="false">IF(OR(G143="",C143=""),"",ROUND((G143-D143)/(D143-E143),2))</f>
         <v/>
       </c>
-      <c r="J143" s="32" t="str">
-        <f aca="false">IF(I143="","",ROUND(I143*$M$2*$M$3,2))</f>
+      <c r="J143" s="33" t="str">
+        <f aca="false">IF(I143="","",ROUND(I143*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K143" s="6"/>
-      <c r="L143" s="26"/>
+      <c r="L143" s="6"/>
+      <c r="M143" s="6"/>
+      <c r="N143" s="26"/>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="30"/>
+      <c r="A144" s="31"/>
       <c r="B144" s="6"/>
       <c r="C144" s="8" t="str">
         <f aca="false">IF(OR(D144="",E144="",D144=E144),"",IF(E144&lt;D144,"BUY","SELL"))</f>
@@ -6438,19 +6758,21 @@
         <f aca="false">IF(I144="","",IF(I144&gt;0,"WIN",IF(I144&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I144" s="31" t="str">
+      <c r="I144" s="32" t="str">
         <f aca="false">IF(OR(G144="",C144=""),"",ROUND((G144-D144)/(D144-E144),2))</f>
         <v/>
       </c>
-      <c r="J144" s="32" t="str">
-        <f aca="false">IF(I144="","",ROUND(I144*$M$2*$M$3,2))</f>
+      <c r="J144" s="33" t="str">
+        <f aca="false">IF(I144="","",ROUND(I144*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K144" s="6"/>
-      <c r="L144" s="26"/>
+      <c r="L144" s="6"/>
+      <c r="M144" s="6"/>
+      <c r="N144" s="26"/>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="30"/>
+      <c r="A145" s="31"/>
       <c r="B145" s="6"/>
       <c r="C145" s="8" t="str">
         <f aca="false">IF(OR(D145="",E145="",D145=E145),"",IF(E145&lt;D145,"BUY","SELL"))</f>
@@ -6467,19 +6789,21 @@
         <f aca="false">IF(I145="","",IF(I145&gt;0,"WIN",IF(I145&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I145" s="31" t="str">
+      <c r="I145" s="32" t="str">
         <f aca="false">IF(OR(G145="",C145=""),"",ROUND((G145-D145)/(D145-E145),2))</f>
         <v/>
       </c>
-      <c r="J145" s="32" t="str">
-        <f aca="false">IF(I145="","",ROUND(I145*$M$2*$M$3,2))</f>
+      <c r="J145" s="33" t="str">
+        <f aca="false">IF(I145="","",ROUND(I145*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K145" s="6"/>
-      <c r="L145" s="26"/>
+      <c r="L145" s="6"/>
+      <c r="M145" s="6"/>
+      <c r="N145" s="26"/>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="30"/>
+      <c r="A146" s="31"/>
       <c r="B146" s="6"/>
       <c r="C146" s="8" t="str">
         <f aca="false">IF(OR(D146="",E146="",D146=E146),"",IF(E146&lt;D146,"BUY","SELL"))</f>
@@ -6496,19 +6820,21 @@
         <f aca="false">IF(I146="","",IF(I146&gt;0,"WIN",IF(I146&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I146" s="31" t="str">
+      <c r="I146" s="32" t="str">
         <f aca="false">IF(OR(G146="",C146=""),"",ROUND((G146-D146)/(D146-E146),2))</f>
         <v/>
       </c>
-      <c r="J146" s="32" t="str">
-        <f aca="false">IF(I146="","",ROUND(I146*$M$2*$M$3,2))</f>
+      <c r="J146" s="33" t="str">
+        <f aca="false">IF(I146="","",ROUND(I146*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K146" s="6"/>
-      <c r="L146" s="26"/>
+      <c r="L146" s="6"/>
+      <c r="M146" s="6"/>
+      <c r="N146" s="26"/>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="30"/>
+      <c r="A147" s="31"/>
       <c r="B147" s="6"/>
       <c r="C147" s="8" t="str">
         <f aca="false">IF(OR(D147="",E147="",D147=E147),"",IF(E147&lt;D147,"BUY","SELL"))</f>
@@ -6525,19 +6851,21 @@
         <f aca="false">IF(I147="","",IF(I147&gt;0,"WIN",IF(I147&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I147" s="31" t="str">
+      <c r="I147" s="32" t="str">
         <f aca="false">IF(OR(G147="",C147=""),"",ROUND((G147-D147)/(D147-E147),2))</f>
         <v/>
       </c>
-      <c r="J147" s="32" t="str">
-        <f aca="false">IF(I147="","",ROUND(I147*$M$2*$M$3,2))</f>
+      <c r="J147" s="33" t="str">
+        <f aca="false">IF(I147="","",ROUND(I147*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K147" s="6"/>
-      <c r="L147" s="26"/>
+      <c r="L147" s="6"/>
+      <c r="M147" s="6"/>
+      <c r="N147" s="26"/>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="30"/>
+      <c r="A148" s="31"/>
       <c r="B148" s="6"/>
       <c r="C148" s="8" t="str">
         <f aca="false">IF(OR(D148="",E148="",D148=E148),"",IF(E148&lt;D148,"BUY","SELL"))</f>
@@ -6554,19 +6882,21 @@
         <f aca="false">IF(I148="","",IF(I148&gt;0,"WIN",IF(I148&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I148" s="31" t="str">
+      <c r="I148" s="32" t="str">
         <f aca="false">IF(OR(G148="",C148=""),"",ROUND((G148-D148)/(D148-E148),2))</f>
         <v/>
       </c>
-      <c r="J148" s="32" t="str">
-        <f aca="false">IF(I148="","",ROUND(I148*$M$2*$M$3,2))</f>
+      <c r="J148" s="33" t="str">
+        <f aca="false">IF(I148="","",ROUND(I148*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K148" s="6"/>
-      <c r="L148" s="26"/>
+      <c r="L148" s="6"/>
+      <c r="M148" s="6"/>
+      <c r="N148" s="26"/>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="30"/>
+      <c r="A149" s="31"/>
       <c r="B149" s="6"/>
       <c r="C149" s="8" t="str">
         <f aca="false">IF(OR(D149="",E149="",D149=E149),"",IF(E149&lt;D149,"BUY","SELL"))</f>
@@ -6583,19 +6913,21 @@
         <f aca="false">IF(I149="","",IF(I149&gt;0,"WIN",IF(I149&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I149" s="31" t="str">
+      <c r="I149" s="32" t="str">
         <f aca="false">IF(OR(G149="",C149=""),"",ROUND((G149-D149)/(D149-E149),2))</f>
         <v/>
       </c>
-      <c r="J149" s="32" t="str">
-        <f aca="false">IF(I149="","",ROUND(I149*$M$2*$M$3,2))</f>
+      <c r="J149" s="33" t="str">
+        <f aca="false">IF(I149="","",ROUND(I149*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K149" s="6"/>
-      <c r="L149" s="26"/>
+      <c r="L149" s="6"/>
+      <c r="M149" s="6"/>
+      <c r="N149" s="26"/>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="30"/>
+      <c r="A150" s="31"/>
       <c r="B150" s="6"/>
       <c r="C150" s="8" t="str">
         <f aca="false">IF(OR(D150="",E150="",D150=E150),"",IF(E150&lt;D150,"BUY","SELL"))</f>
@@ -6612,19 +6944,21 @@
         <f aca="false">IF(I150="","",IF(I150&gt;0,"WIN",IF(I150&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I150" s="31" t="str">
+      <c r="I150" s="32" t="str">
         <f aca="false">IF(OR(G150="",C150=""),"",ROUND((G150-D150)/(D150-E150),2))</f>
         <v/>
       </c>
-      <c r="J150" s="32" t="str">
-        <f aca="false">IF(I150="","",ROUND(I150*$M$2*$M$3,2))</f>
+      <c r="J150" s="33" t="str">
+        <f aca="false">IF(I150="","",ROUND(I150*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K150" s="6"/>
-      <c r="L150" s="26"/>
+      <c r="L150" s="6"/>
+      <c r="M150" s="6"/>
+      <c r="N150" s="26"/>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="30"/>
+      <c r="A151" s="31"/>
       <c r="B151" s="6"/>
       <c r="C151" s="8" t="str">
         <f aca="false">IF(OR(D151="",E151="",D151=E151),"",IF(E151&lt;D151,"BUY","SELL"))</f>
@@ -6641,19 +6975,21 @@
         <f aca="false">IF(I151="","",IF(I151&gt;0,"WIN",IF(I151&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I151" s="31" t="str">
+      <c r="I151" s="32" t="str">
         <f aca="false">IF(OR(G151="",C151=""),"",ROUND((G151-D151)/(D151-E151),2))</f>
         <v/>
       </c>
-      <c r="J151" s="32" t="str">
-        <f aca="false">IF(I151="","",ROUND(I151*$M$2*$M$3,2))</f>
+      <c r="J151" s="33" t="str">
+        <f aca="false">IF(I151="","",ROUND(I151*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K151" s="6"/>
-      <c r="L151" s="26"/>
+      <c r="L151" s="6"/>
+      <c r="M151" s="6"/>
+      <c r="N151" s="26"/>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="30"/>
+      <c r="A152" s="31"/>
       <c r="B152" s="6"/>
       <c r="C152" s="8" t="str">
         <f aca="false">IF(OR(D152="",E152="",D152=E152),"",IF(E152&lt;D152,"BUY","SELL"))</f>
@@ -6670,19 +7006,21 @@
         <f aca="false">IF(I152="","",IF(I152&gt;0,"WIN",IF(I152&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I152" s="31" t="str">
+      <c r="I152" s="32" t="str">
         <f aca="false">IF(OR(G152="",C152=""),"",ROUND((G152-D152)/(D152-E152),2))</f>
         <v/>
       </c>
-      <c r="J152" s="32" t="str">
-        <f aca="false">IF(I152="","",ROUND(I152*$M$2*$M$3,2))</f>
+      <c r="J152" s="33" t="str">
+        <f aca="false">IF(I152="","",ROUND(I152*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K152" s="6"/>
-      <c r="L152" s="26"/>
+      <c r="L152" s="6"/>
+      <c r="M152" s="6"/>
+      <c r="N152" s="26"/>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="30"/>
+      <c r="A153" s="31"/>
       <c r="B153" s="6"/>
       <c r="C153" s="8" t="str">
         <f aca="false">IF(OR(D153="",E153="",D153=E153),"",IF(E153&lt;D153,"BUY","SELL"))</f>
@@ -6699,19 +7037,21 @@
         <f aca="false">IF(I153="","",IF(I153&gt;0,"WIN",IF(I153&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I153" s="31" t="str">
+      <c r="I153" s="32" t="str">
         <f aca="false">IF(OR(G153="",C153=""),"",ROUND((G153-D153)/(D153-E153),2))</f>
         <v/>
       </c>
-      <c r="J153" s="32" t="str">
-        <f aca="false">IF(I153="","",ROUND(I153*$M$2*$M$3,2))</f>
+      <c r="J153" s="33" t="str">
+        <f aca="false">IF(I153="","",ROUND(I153*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K153" s="6"/>
-      <c r="L153" s="26"/>
+      <c r="L153" s="6"/>
+      <c r="M153" s="6"/>
+      <c r="N153" s="26"/>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="30"/>
+      <c r="A154" s="31"/>
       <c r="B154" s="6"/>
       <c r="C154" s="8" t="str">
         <f aca="false">IF(OR(D154="",E154="",D154=E154),"",IF(E154&lt;D154,"BUY","SELL"))</f>
@@ -6728,19 +7068,21 @@
         <f aca="false">IF(I154="","",IF(I154&gt;0,"WIN",IF(I154&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I154" s="31" t="str">
+      <c r="I154" s="32" t="str">
         <f aca="false">IF(OR(G154="",C154=""),"",ROUND((G154-D154)/(D154-E154),2))</f>
         <v/>
       </c>
-      <c r="J154" s="32" t="str">
-        <f aca="false">IF(I154="","",ROUND(I154*$M$2*$M$3,2))</f>
+      <c r="J154" s="33" t="str">
+        <f aca="false">IF(I154="","",ROUND(I154*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K154" s="6"/>
-      <c r="L154" s="26"/>
+      <c r="L154" s="6"/>
+      <c r="M154" s="6"/>
+      <c r="N154" s="26"/>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="30"/>
+      <c r="A155" s="31"/>
       <c r="B155" s="6"/>
       <c r="C155" s="8" t="str">
         <f aca="false">IF(OR(D155="",E155="",D155=E155),"",IF(E155&lt;D155,"BUY","SELL"))</f>
@@ -6757,19 +7099,21 @@
         <f aca="false">IF(I155="","",IF(I155&gt;0,"WIN",IF(I155&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I155" s="31" t="str">
+      <c r="I155" s="32" t="str">
         <f aca="false">IF(OR(G155="",C155=""),"",ROUND((G155-D155)/(D155-E155),2))</f>
         <v/>
       </c>
-      <c r="J155" s="32" t="str">
-        <f aca="false">IF(I155="","",ROUND(I155*$M$2*$M$3,2))</f>
+      <c r="J155" s="33" t="str">
+        <f aca="false">IF(I155="","",ROUND(I155*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K155" s="6"/>
-      <c r="L155" s="26"/>
+      <c r="L155" s="6"/>
+      <c r="M155" s="6"/>
+      <c r="N155" s="26"/>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="30"/>
+      <c r="A156" s="31"/>
       <c r="B156" s="6"/>
       <c r="C156" s="8" t="str">
         <f aca="false">IF(OR(D156="",E156="",D156=E156),"",IF(E156&lt;D156,"BUY","SELL"))</f>
@@ -6786,19 +7130,21 @@
         <f aca="false">IF(I156="","",IF(I156&gt;0,"WIN",IF(I156&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I156" s="31" t="str">
+      <c r="I156" s="32" t="str">
         <f aca="false">IF(OR(G156="",C156=""),"",ROUND((G156-D156)/(D156-E156),2))</f>
         <v/>
       </c>
-      <c r="J156" s="32" t="str">
-        <f aca="false">IF(I156="","",ROUND(I156*$M$2*$M$3,2))</f>
+      <c r="J156" s="33" t="str">
+        <f aca="false">IF(I156="","",ROUND(I156*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K156" s="6"/>
-      <c r="L156" s="26"/>
+      <c r="L156" s="6"/>
+      <c r="M156" s="6"/>
+      <c r="N156" s="26"/>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="30"/>
+      <c r="A157" s="31"/>
       <c r="B157" s="6"/>
       <c r="C157" s="8" t="str">
         <f aca="false">IF(OR(D157="",E157="",D157=E157),"",IF(E157&lt;D157,"BUY","SELL"))</f>
@@ -6815,19 +7161,21 @@
         <f aca="false">IF(I157="","",IF(I157&gt;0,"WIN",IF(I157&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I157" s="31" t="str">
+      <c r="I157" s="32" t="str">
         <f aca="false">IF(OR(G157="",C157=""),"",ROUND((G157-D157)/(D157-E157),2))</f>
         <v/>
       </c>
-      <c r="J157" s="32" t="str">
-        <f aca="false">IF(I157="","",ROUND(I157*$M$2*$M$3,2))</f>
+      <c r="J157" s="33" t="str">
+        <f aca="false">IF(I157="","",ROUND(I157*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K157" s="6"/>
-      <c r="L157" s="26"/>
+      <c r="L157" s="6"/>
+      <c r="M157" s="6"/>
+      <c r="N157" s="26"/>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="30"/>
+      <c r="A158" s="31"/>
       <c r="B158" s="6"/>
       <c r="C158" s="8" t="str">
         <f aca="false">IF(OR(D158="",E158="",D158=E158),"",IF(E158&lt;D158,"BUY","SELL"))</f>
@@ -6844,19 +7192,21 @@
         <f aca="false">IF(I158="","",IF(I158&gt;0,"WIN",IF(I158&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I158" s="31" t="str">
+      <c r="I158" s="32" t="str">
         <f aca="false">IF(OR(G158="",C158=""),"",ROUND((G158-D158)/(D158-E158),2))</f>
         <v/>
       </c>
-      <c r="J158" s="32" t="str">
-        <f aca="false">IF(I158="","",ROUND(I158*$M$2*$M$3,2))</f>
+      <c r="J158" s="33" t="str">
+        <f aca="false">IF(I158="","",ROUND(I158*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K158" s="6"/>
-      <c r="L158" s="26"/>
+      <c r="L158" s="6"/>
+      <c r="M158" s="6"/>
+      <c r="N158" s="26"/>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="30"/>
+      <c r="A159" s="31"/>
       <c r="B159" s="6"/>
       <c r="C159" s="8" t="str">
         <f aca="false">IF(OR(D159="",E159="",D159=E159),"",IF(E159&lt;D159,"BUY","SELL"))</f>
@@ -6873,19 +7223,21 @@
         <f aca="false">IF(I159="","",IF(I159&gt;0,"WIN",IF(I159&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I159" s="31" t="str">
+      <c r="I159" s="32" t="str">
         <f aca="false">IF(OR(G159="",C159=""),"",ROUND((G159-D159)/(D159-E159),2))</f>
         <v/>
       </c>
-      <c r="J159" s="32" t="str">
-        <f aca="false">IF(I159="","",ROUND(I159*$M$2*$M$3,2))</f>
+      <c r="J159" s="33" t="str">
+        <f aca="false">IF(I159="","",ROUND(I159*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K159" s="6"/>
-      <c r="L159" s="26"/>
+      <c r="L159" s="6"/>
+      <c r="M159" s="6"/>
+      <c r="N159" s="26"/>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="30"/>
+      <c r="A160" s="31"/>
       <c r="B160" s="6"/>
       <c r="C160" s="8" t="str">
         <f aca="false">IF(OR(D160="",E160="",D160=E160),"",IF(E160&lt;D160,"BUY","SELL"))</f>
@@ -6902,19 +7254,21 @@
         <f aca="false">IF(I160="","",IF(I160&gt;0,"WIN",IF(I160&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I160" s="31" t="str">
+      <c r="I160" s="32" t="str">
         <f aca="false">IF(OR(G160="",C160=""),"",ROUND((G160-D160)/(D160-E160),2))</f>
         <v/>
       </c>
-      <c r="J160" s="32" t="str">
-        <f aca="false">IF(I160="","",ROUND(I160*$M$2*$M$3,2))</f>
+      <c r="J160" s="33" t="str">
+        <f aca="false">IF(I160="","",ROUND(I160*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K160" s="6"/>
-      <c r="L160" s="26"/>
+      <c r="L160" s="6"/>
+      <c r="M160" s="6"/>
+      <c r="N160" s="26"/>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="30"/>
+      <c r="A161" s="31"/>
       <c r="B161" s="6"/>
       <c r="C161" s="8" t="str">
         <f aca="false">IF(OR(D161="",E161="",D161=E161),"",IF(E161&lt;D161,"BUY","SELL"))</f>
@@ -6931,19 +7285,21 @@
         <f aca="false">IF(I161="","",IF(I161&gt;0,"WIN",IF(I161&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I161" s="31" t="str">
+      <c r="I161" s="32" t="str">
         <f aca="false">IF(OR(G161="",C161=""),"",ROUND((G161-D161)/(D161-E161),2))</f>
         <v/>
       </c>
-      <c r="J161" s="32" t="str">
-        <f aca="false">IF(I161="","",ROUND(I161*$M$2*$M$3,2))</f>
+      <c r="J161" s="33" t="str">
+        <f aca="false">IF(I161="","",ROUND(I161*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K161" s="6"/>
-      <c r="L161" s="26"/>
+      <c r="L161" s="6"/>
+      <c r="M161" s="6"/>
+      <c r="N161" s="26"/>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="30"/>
+      <c r="A162" s="31"/>
       <c r="B162" s="6"/>
       <c r="C162" s="8" t="str">
         <f aca="false">IF(OR(D162="",E162="",D162=E162),"",IF(E162&lt;D162,"BUY","SELL"))</f>
@@ -6960,19 +7316,21 @@
         <f aca="false">IF(I162="","",IF(I162&gt;0,"WIN",IF(I162&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I162" s="31" t="str">
+      <c r="I162" s="32" t="str">
         <f aca="false">IF(OR(G162="",C162=""),"",ROUND((G162-D162)/(D162-E162),2))</f>
         <v/>
       </c>
-      <c r="J162" s="32" t="str">
-        <f aca="false">IF(I162="","",ROUND(I162*$M$2*$M$3,2))</f>
+      <c r="J162" s="33" t="str">
+        <f aca="false">IF(I162="","",ROUND(I162*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K162" s="6"/>
-      <c r="L162" s="26"/>
+      <c r="L162" s="6"/>
+      <c r="M162" s="6"/>
+      <c r="N162" s="26"/>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="30"/>
+      <c r="A163" s="31"/>
       <c r="B163" s="6"/>
       <c r="C163" s="8" t="str">
         <f aca="false">IF(OR(D163="",E163="",D163=E163),"",IF(E163&lt;D163,"BUY","SELL"))</f>
@@ -6989,19 +7347,21 @@
         <f aca="false">IF(I163="","",IF(I163&gt;0,"WIN",IF(I163&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I163" s="31" t="str">
+      <c r="I163" s="32" t="str">
         <f aca="false">IF(OR(G163="",C163=""),"",ROUND((G163-D163)/(D163-E163),2))</f>
         <v/>
       </c>
-      <c r="J163" s="32" t="str">
-        <f aca="false">IF(I163="","",ROUND(I163*$M$2*$M$3,2))</f>
+      <c r="J163" s="33" t="str">
+        <f aca="false">IF(I163="","",ROUND(I163*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K163" s="6"/>
-      <c r="L163" s="26"/>
+      <c r="L163" s="6"/>
+      <c r="M163" s="6"/>
+      <c r="N163" s="26"/>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="30"/>
+      <c r="A164" s="31"/>
       <c r="B164" s="6"/>
       <c r="C164" s="8" t="str">
         <f aca="false">IF(OR(D164="",E164="",D164=E164),"",IF(E164&lt;D164,"BUY","SELL"))</f>
@@ -7018,19 +7378,21 @@
         <f aca="false">IF(I164="","",IF(I164&gt;0,"WIN",IF(I164&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I164" s="31" t="str">
+      <c r="I164" s="32" t="str">
         <f aca="false">IF(OR(G164="",C164=""),"",ROUND((G164-D164)/(D164-E164),2))</f>
         <v/>
       </c>
-      <c r="J164" s="32" t="str">
-        <f aca="false">IF(I164="","",ROUND(I164*$M$2*$M$3,2))</f>
+      <c r="J164" s="33" t="str">
+        <f aca="false">IF(I164="","",ROUND(I164*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K164" s="6"/>
-      <c r="L164" s="26"/>
+      <c r="L164" s="6"/>
+      <c r="M164" s="6"/>
+      <c r="N164" s="26"/>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="30"/>
+      <c r="A165" s="31"/>
       <c r="B165" s="6"/>
       <c r="C165" s="8" t="str">
         <f aca="false">IF(OR(D165="",E165="",D165=E165),"",IF(E165&lt;D165,"BUY","SELL"))</f>
@@ -7047,19 +7409,21 @@
         <f aca="false">IF(I165="","",IF(I165&gt;0,"WIN",IF(I165&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I165" s="31" t="str">
+      <c r="I165" s="32" t="str">
         <f aca="false">IF(OR(G165="",C165=""),"",ROUND((G165-D165)/(D165-E165),2))</f>
         <v/>
       </c>
-      <c r="J165" s="32" t="str">
-        <f aca="false">IF(I165="","",ROUND(I165*$M$2*$M$3,2))</f>
+      <c r="J165" s="33" t="str">
+        <f aca="false">IF(I165="","",ROUND(I165*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K165" s="6"/>
-      <c r="L165" s="26"/>
+      <c r="L165" s="6"/>
+      <c r="M165" s="6"/>
+      <c r="N165" s="26"/>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="30"/>
+      <c r="A166" s="31"/>
       <c r="B166" s="6"/>
       <c r="C166" s="8" t="str">
         <f aca="false">IF(OR(D166="",E166="",D166=E166),"",IF(E166&lt;D166,"BUY","SELL"))</f>
@@ -7076,19 +7440,21 @@
         <f aca="false">IF(I166="","",IF(I166&gt;0,"WIN",IF(I166&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I166" s="31" t="str">
+      <c r="I166" s="32" t="str">
         <f aca="false">IF(OR(G166="",C166=""),"",ROUND((G166-D166)/(D166-E166),2))</f>
         <v/>
       </c>
-      <c r="J166" s="32" t="str">
-        <f aca="false">IF(I166="","",ROUND(I166*$M$2*$M$3,2))</f>
+      <c r="J166" s="33" t="str">
+        <f aca="false">IF(I166="","",ROUND(I166*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K166" s="6"/>
-      <c r="L166" s="26"/>
+      <c r="L166" s="6"/>
+      <c r="M166" s="6"/>
+      <c r="N166" s="26"/>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="30"/>
+      <c r="A167" s="31"/>
       <c r="B167" s="6"/>
       <c r="C167" s="8" t="str">
         <f aca="false">IF(OR(D167="",E167="",D167=E167),"",IF(E167&lt;D167,"BUY","SELL"))</f>
@@ -7105,19 +7471,21 @@
         <f aca="false">IF(I167="","",IF(I167&gt;0,"WIN",IF(I167&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I167" s="31" t="str">
+      <c r="I167" s="32" t="str">
         <f aca="false">IF(OR(G167="",C167=""),"",ROUND((G167-D167)/(D167-E167),2))</f>
         <v/>
       </c>
-      <c r="J167" s="32" t="str">
-        <f aca="false">IF(I167="","",ROUND(I167*$M$2*$M$3,2))</f>
+      <c r="J167" s="33" t="str">
+        <f aca="false">IF(I167="","",ROUND(I167*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K167" s="6"/>
-      <c r="L167" s="26"/>
+      <c r="L167" s="6"/>
+      <c r="M167" s="6"/>
+      <c r="N167" s="26"/>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="30"/>
+      <c r="A168" s="31"/>
       <c r="B168" s="6"/>
       <c r="C168" s="8" t="str">
         <f aca="false">IF(OR(D168="",E168="",D168=E168),"",IF(E168&lt;D168,"BUY","SELL"))</f>
@@ -7134,19 +7502,21 @@
         <f aca="false">IF(I168="","",IF(I168&gt;0,"WIN",IF(I168&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I168" s="31" t="str">
+      <c r="I168" s="32" t="str">
         <f aca="false">IF(OR(G168="",C168=""),"",ROUND((G168-D168)/(D168-E168),2))</f>
         <v/>
       </c>
-      <c r="J168" s="32" t="str">
-        <f aca="false">IF(I168="","",ROUND(I168*$M$2*$M$3,2))</f>
+      <c r="J168" s="33" t="str">
+        <f aca="false">IF(I168="","",ROUND(I168*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K168" s="6"/>
-      <c r="L168" s="26"/>
+      <c r="L168" s="6"/>
+      <c r="M168" s="6"/>
+      <c r="N168" s="26"/>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="30"/>
+      <c r="A169" s="31"/>
       <c r="B169" s="6"/>
       <c r="C169" s="8" t="str">
         <f aca="false">IF(OR(D169="",E169="",D169=E169),"",IF(E169&lt;D169,"BUY","SELL"))</f>
@@ -7163,19 +7533,21 @@
         <f aca="false">IF(I169="","",IF(I169&gt;0,"WIN",IF(I169&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I169" s="31" t="str">
+      <c r="I169" s="32" t="str">
         <f aca="false">IF(OR(G169="",C169=""),"",ROUND((G169-D169)/(D169-E169),2))</f>
         <v/>
       </c>
-      <c r="J169" s="32" t="str">
-        <f aca="false">IF(I169="","",ROUND(I169*$M$2*$M$3,2))</f>
+      <c r="J169" s="33" t="str">
+        <f aca="false">IF(I169="","",ROUND(I169*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K169" s="6"/>
-      <c r="L169" s="26"/>
+      <c r="L169" s="6"/>
+      <c r="M169" s="6"/>
+      <c r="N169" s="26"/>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="30"/>
+      <c r="A170" s="31"/>
       <c r="B170" s="6"/>
       <c r="C170" s="8" t="str">
         <f aca="false">IF(OR(D170="",E170="",D170=E170),"",IF(E170&lt;D170,"BUY","SELL"))</f>
@@ -7192,19 +7564,21 @@
         <f aca="false">IF(I170="","",IF(I170&gt;0,"WIN",IF(I170&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I170" s="31" t="str">
+      <c r="I170" s="32" t="str">
         <f aca="false">IF(OR(G170="",C170=""),"",ROUND((G170-D170)/(D170-E170),2))</f>
         <v/>
       </c>
-      <c r="J170" s="32" t="str">
-        <f aca="false">IF(I170="","",ROUND(I170*$M$2*$M$3,2))</f>
+      <c r="J170" s="33" t="str">
+        <f aca="false">IF(I170="","",ROUND(I170*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K170" s="6"/>
-      <c r="L170" s="26"/>
+      <c r="L170" s="6"/>
+      <c r="M170" s="6"/>
+      <c r="N170" s="26"/>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="30"/>
+      <c r="A171" s="31"/>
       <c r="B171" s="6"/>
       <c r="C171" s="8" t="str">
         <f aca="false">IF(OR(D171="",E171="",D171=E171),"",IF(E171&lt;D171,"BUY","SELL"))</f>
@@ -7221,19 +7595,21 @@
         <f aca="false">IF(I171="","",IF(I171&gt;0,"WIN",IF(I171&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I171" s="31" t="str">
+      <c r="I171" s="32" t="str">
         <f aca="false">IF(OR(G171="",C171=""),"",ROUND((G171-D171)/(D171-E171),2))</f>
         <v/>
       </c>
-      <c r="J171" s="32" t="str">
-        <f aca="false">IF(I171="","",ROUND(I171*$M$2*$M$3,2))</f>
+      <c r="J171" s="33" t="str">
+        <f aca="false">IF(I171="","",ROUND(I171*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K171" s="6"/>
-      <c r="L171" s="26"/>
+      <c r="L171" s="6"/>
+      <c r="M171" s="6"/>
+      <c r="N171" s="26"/>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="30"/>
+      <c r="A172" s="31"/>
       <c r="B172" s="6"/>
       <c r="C172" s="8" t="str">
         <f aca="false">IF(OR(D172="",E172="",D172=E172),"",IF(E172&lt;D172,"BUY","SELL"))</f>
@@ -7250,19 +7626,21 @@
         <f aca="false">IF(I172="","",IF(I172&gt;0,"WIN",IF(I172&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I172" s="31" t="str">
+      <c r="I172" s="32" t="str">
         <f aca="false">IF(OR(G172="",C172=""),"",ROUND((G172-D172)/(D172-E172),2))</f>
         <v/>
       </c>
-      <c r="J172" s="32" t="str">
-        <f aca="false">IF(I172="","",ROUND(I172*$M$2*$M$3,2))</f>
+      <c r="J172" s="33" t="str">
+        <f aca="false">IF(I172="","",ROUND(I172*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K172" s="6"/>
-      <c r="L172" s="26"/>
+      <c r="L172" s="6"/>
+      <c r="M172" s="6"/>
+      <c r="N172" s="26"/>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="30"/>
+      <c r="A173" s="31"/>
       <c r="B173" s="6"/>
       <c r="C173" s="8" t="str">
         <f aca="false">IF(OR(D173="",E173="",D173=E173),"",IF(E173&lt;D173,"BUY","SELL"))</f>
@@ -7279,19 +7657,21 @@
         <f aca="false">IF(I173="","",IF(I173&gt;0,"WIN",IF(I173&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I173" s="31" t="str">
+      <c r="I173" s="32" t="str">
         <f aca="false">IF(OR(G173="",C173=""),"",ROUND((G173-D173)/(D173-E173),2))</f>
         <v/>
       </c>
-      <c r="J173" s="32" t="str">
-        <f aca="false">IF(I173="","",ROUND(I173*$M$2*$M$3,2))</f>
+      <c r="J173" s="33" t="str">
+        <f aca="false">IF(I173="","",ROUND(I173*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K173" s="6"/>
-      <c r="L173" s="26"/>
+      <c r="L173" s="6"/>
+      <c r="M173" s="6"/>
+      <c r="N173" s="26"/>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="30"/>
+      <c r="A174" s="31"/>
       <c r="B174" s="6"/>
       <c r="C174" s="8" t="str">
         <f aca="false">IF(OR(D174="",E174="",D174=E174),"",IF(E174&lt;D174,"BUY","SELL"))</f>
@@ -7308,19 +7688,21 @@
         <f aca="false">IF(I174="","",IF(I174&gt;0,"WIN",IF(I174&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I174" s="31" t="str">
+      <c r="I174" s="32" t="str">
         <f aca="false">IF(OR(G174="",C174=""),"",ROUND((G174-D174)/(D174-E174),2))</f>
         <v/>
       </c>
-      <c r="J174" s="32" t="str">
-        <f aca="false">IF(I174="","",ROUND(I174*$M$2*$M$3,2))</f>
+      <c r="J174" s="33" t="str">
+        <f aca="false">IF(I174="","",ROUND(I174*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K174" s="6"/>
-      <c r="L174" s="26"/>
+      <c r="L174" s="6"/>
+      <c r="M174" s="6"/>
+      <c r="N174" s="26"/>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="30"/>
+      <c r="A175" s="31"/>
       <c r="B175" s="6"/>
       <c r="C175" s="8" t="str">
         <f aca="false">IF(OR(D175="",E175="",D175=E175),"",IF(E175&lt;D175,"BUY","SELL"))</f>
@@ -7337,19 +7719,21 @@
         <f aca="false">IF(I175="","",IF(I175&gt;0,"WIN",IF(I175&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I175" s="31" t="str">
+      <c r="I175" s="32" t="str">
         <f aca="false">IF(OR(G175="",C175=""),"",ROUND((G175-D175)/(D175-E175),2))</f>
         <v/>
       </c>
-      <c r="J175" s="32" t="str">
-        <f aca="false">IF(I175="","",ROUND(I175*$M$2*$M$3,2))</f>
+      <c r="J175" s="33" t="str">
+        <f aca="false">IF(I175="","",ROUND(I175*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K175" s="6"/>
-      <c r="L175" s="26"/>
+      <c r="L175" s="6"/>
+      <c r="M175" s="6"/>
+      <c r="N175" s="26"/>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="30"/>
+      <c r="A176" s="31"/>
       <c r="B176" s="6"/>
       <c r="C176" s="8" t="str">
         <f aca="false">IF(OR(D176="",E176="",D176=E176),"",IF(E176&lt;D176,"BUY","SELL"))</f>
@@ -7366,19 +7750,21 @@
         <f aca="false">IF(I176="","",IF(I176&gt;0,"WIN",IF(I176&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I176" s="31" t="str">
+      <c r="I176" s="32" t="str">
         <f aca="false">IF(OR(G176="",C176=""),"",ROUND((G176-D176)/(D176-E176),2))</f>
         <v/>
       </c>
-      <c r="J176" s="32" t="str">
-        <f aca="false">IF(I176="","",ROUND(I176*$M$2*$M$3,2))</f>
+      <c r="J176" s="33" t="str">
+        <f aca="false">IF(I176="","",ROUND(I176*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K176" s="6"/>
-      <c r="L176" s="26"/>
+      <c r="L176" s="6"/>
+      <c r="M176" s="6"/>
+      <c r="N176" s="26"/>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="30"/>
+      <c r="A177" s="31"/>
       <c r="B177" s="6"/>
       <c r="C177" s="8" t="str">
         <f aca="false">IF(OR(D177="",E177="",D177=E177),"",IF(E177&lt;D177,"BUY","SELL"))</f>
@@ -7395,19 +7781,21 @@
         <f aca="false">IF(I177="","",IF(I177&gt;0,"WIN",IF(I177&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I177" s="31" t="str">
+      <c r="I177" s="32" t="str">
         <f aca="false">IF(OR(G177="",C177=""),"",ROUND((G177-D177)/(D177-E177),2))</f>
         <v/>
       </c>
-      <c r="J177" s="32" t="str">
-        <f aca="false">IF(I177="","",ROUND(I177*$M$2*$M$3,2))</f>
+      <c r="J177" s="33" t="str">
+        <f aca="false">IF(I177="","",ROUND(I177*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K177" s="6"/>
-      <c r="L177" s="26"/>
+      <c r="L177" s="6"/>
+      <c r="M177" s="6"/>
+      <c r="N177" s="26"/>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="30"/>
+      <c r="A178" s="31"/>
       <c r="B178" s="6"/>
       <c r="C178" s="8" t="str">
         <f aca="false">IF(OR(D178="",E178="",D178=E178),"",IF(E178&lt;D178,"BUY","SELL"))</f>
@@ -7424,19 +7812,21 @@
         <f aca="false">IF(I178="","",IF(I178&gt;0,"WIN",IF(I178&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I178" s="31" t="str">
+      <c r="I178" s="32" t="str">
         <f aca="false">IF(OR(G178="",C178=""),"",ROUND((G178-D178)/(D178-E178),2))</f>
         <v/>
       </c>
-      <c r="J178" s="32" t="str">
-        <f aca="false">IF(I178="","",ROUND(I178*$M$2*$M$3,2))</f>
+      <c r="J178" s="33" t="str">
+        <f aca="false">IF(I178="","",ROUND(I178*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K178" s="6"/>
-      <c r="L178" s="26"/>
+      <c r="L178" s="6"/>
+      <c r="M178" s="6"/>
+      <c r="N178" s="26"/>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="30"/>
+      <c r="A179" s="31"/>
       <c r="B179" s="6"/>
       <c r="C179" s="8" t="str">
         <f aca="false">IF(OR(D179="",E179="",D179=E179),"",IF(E179&lt;D179,"BUY","SELL"))</f>
@@ -7453,19 +7843,21 @@
         <f aca="false">IF(I179="","",IF(I179&gt;0,"WIN",IF(I179&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I179" s="31" t="str">
+      <c r="I179" s="32" t="str">
         <f aca="false">IF(OR(G179="",C179=""),"",ROUND((G179-D179)/(D179-E179),2))</f>
         <v/>
       </c>
-      <c r="J179" s="32" t="str">
-        <f aca="false">IF(I179="","",ROUND(I179*$M$2*$M$3,2))</f>
+      <c r="J179" s="33" t="str">
+        <f aca="false">IF(I179="","",ROUND(I179*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K179" s="6"/>
-      <c r="L179" s="26"/>
+      <c r="L179" s="6"/>
+      <c r="M179" s="6"/>
+      <c r="N179" s="26"/>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="30"/>
+      <c r="A180" s="31"/>
       <c r="B180" s="6"/>
       <c r="C180" s="8" t="str">
         <f aca="false">IF(OR(D180="",E180="",D180=E180),"",IF(E180&lt;D180,"BUY","SELL"))</f>
@@ -7482,19 +7874,21 @@
         <f aca="false">IF(I180="","",IF(I180&gt;0,"WIN",IF(I180&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I180" s="31" t="str">
+      <c r="I180" s="32" t="str">
         <f aca="false">IF(OR(G180="",C180=""),"",ROUND((G180-D180)/(D180-E180),2))</f>
         <v/>
       </c>
-      <c r="J180" s="32" t="str">
-        <f aca="false">IF(I180="","",ROUND(I180*$M$2*$M$3,2))</f>
+      <c r="J180" s="33" t="str">
+        <f aca="false">IF(I180="","",ROUND(I180*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K180" s="6"/>
-      <c r="L180" s="26"/>
+      <c r="L180" s="6"/>
+      <c r="M180" s="6"/>
+      <c r="N180" s="26"/>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="30"/>
+      <c r="A181" s="31"/>
       <c r="B181" s="6"/>
       <c r="C181" s="8" t="str">
         <f aca="false">IF(OR(D181="",E181="",D181=E181),"",IF(E181&lt;D181,"BUY","SELL"))</f>
@@ -7511,19 +7905,21 @@
         <f aca="false">IF(I181="","",IF(I181&gt;0,"WIN",IF(I181&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I181" s="31" t="str">
+      <c r="I181" s="32" t="str">
         <f aca="false">IF(OR(G181="",C181=""),"",ROUND((G181-D181)/(D181-E181),2))</f>
         <v/>
       </c>
-      <c r="J181" s="32" t="str">
-        <f aca="false">IF(I181="","",ROUND(I181*$M$2*$M$3,2))</f>
+      <c r="J181" s="33" t="str">
+        <f aca="false">IF(I181="","",ROUND(I181*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K181" s="6"/>
-      <c r="L181" s="26"/>
+      <c r="L181" s="6"/>
+      <c r="M181" s="6"/>
+      <c r="N181" s="26"/>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="30"/>
+      <c r="A182" s="31"/>
       <c r="B182" s="6"/>
       <c r="C182" s="8" t="str">
         <f aca="false">IF(OR(D182="",E182="",D182=E182),"",IF(E182&lt;D182,"BUY","SELL"))</f>
@@ -7540,19 +7936,21 @@
         <f aca="false">IF(I182="","",IF(I182&gt;0,"WIN",IF(I182&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I182" s="31" t="str">
+      <c r="I182" s="32" t="str">
         <f aca="false">IF(OR(G182="",C182=""),"",ROUND((G182-D182)/(D182-E182),2))</f>
         <v/>
       </c>
-      <c r="J182" s="32" t="str">
-        <f aca="false">IF(I182="","",ROUND(I182*$M$2*$M$3,2))</f>
+      <c r="J182" s="33" t="str">
+        <f aca="false">IF(I182="","",ROUND(I182*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K182" s="6"/>
-      <c r="L182" s="26"/>
+      <c r="L182" s="6"/>
+      <c r="M182" s="6"/>
+      <c r="N182" s="26"/>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="30"/>
+      <c r="A183" s="31"/>
       <c r="B183" s="6"/>
       <c r="C183" s="8" t="str">
         <f aca="false">IF(OR(D183="",E183="",D183=E183),"",IF(E183&lt;D183,"BUY","SELL"))</f>
@@ -7569,19 +7967,21 @@
         <f aca="false">IF(I183="","",IF(I183&gt;0,"WIN",IF(I183&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I183" s="31" t="str">
+      <c r="I183" s="32" t="str">
         <f aca="false">IF(OR(G183="",C183=""),"",ROUND((G183-D183)/(D183-E183),2))</f>
         <v/>
       </c>
-      <c r="J183" s="32" t="str">
-        <f aca="false">IF(I183="","",ROUND(I183*$M$2*$M$3,2))</f>
+      <c r="J183" s="33" t="str">
+        <f aca="false">IF(I183="","",ROUND(I183*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K183" s="6"/>
-      <c r="L183" s="26"/>
+      <c r="L183" s="6"/>
+      <c r="M183" s="6"/>
+      <c r="N183" s="26"/>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="30"/>
+      <c r="A184" s="31"/>
       <c r="B184" s="6"/>
       <c r="C184" s="8" t="str">
         <f aca="false">IF(OR(D184="",E184="",D184=E184),"",IF(E184&lt;D184,"BUY","SELL"))</f>
@@ -7598,19 +7998,21 @@
         <f aca="false">IF(I184="","",IF(I184&gt;0,"WIN",IF(I184&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I184" s="31" t="str">
+      <c r="I184" s="32" t="str">
         <f aca="false">IF(OR(G184="",C184=""),"",ROUND((G184-D184)/(D184-E184),2))</f>
         <v/>
       </c>
-      <c r="J184" s="32" t="str">
-        <f aca="false">IF(I184="","",ROUND(I184*$M$2*$M$3,2))</f>
+      <c r="J184" s="33" t="str">
+        <f aca="false">IF(I184="","",ROUND(I184*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K184" s="6"/>
-      <c r="L184" s="26"/>
+      <c r="L184" s="6"/>
+      <c r="M184" s="6"/>
+      <c r="N184" s="26"/>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="30"/>
+      <c r="A185" s="31"/>
       <c r="B185" s="6"/>
       <c r="C185" s="8" t="str">
         <f aca="false">IF(OR(D185="",E185="",D185=E185),"",IF(E185&lt;D185,"BUY","SELL"))</f>
@@ -7627,19 +8029,21 @@
         <f aca="false">IF(I185="","",IF(I185&gt;0,"WIN",IF(I185&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I185" s="31" t="str">
+      <c r="I185" s="32" t="str">
         <f aca="false">IF(OR(G185="",C185=""),"",ROUND((G185-D185)/(D185-E185),2))</f>
         <v/>
       </c>
-      <c r="J185" s="32" t="str">
-        <f aca="false">IF(I185="","",ROUND(I185*$M$2*$M$3,2))</f>
+      <c r="J185" s="33" t="str">
+        <f aca="false">IF(I185="","",ROUND(I185*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K185" s="6"/>
-      <c r="L185" s="26"/>
+      <c r="L185" s="6"/>
+      <c r="M185" s="6"/>
+      <c r="N185" s="26"/>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="30"/>
+      <c r="A186" s="31"/>
       <c r="B186" s="6"/>
       <c r="C186" s="8" t="str">
         <f aca="false">IF(OR(D186="",E186="",D186=E186),"",IF(E186&lt;D186,"BUY","SELL"))</f>
@@ -7656,19 +8060,21 @@
         <f aca="false">IF(I186="","",IF(I186&gt;0,"WIN",IF(I186&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I186" s="31" t="str">
+      <c r="I186" s="32" t="str">
         <f aca="false">IF(OR(G186="",C186=""),"",ROUND((G186-D186)/(D186-E186),2))</f>
         <v/>
       </c>
-      <c r="J186" s="32" t="str">
-        <f aca="false">IF(I186="","",ROUND(I186*$M$2*$M$3,2))</f>
+      <c r="J186" s="33" t="str">
+        <f aca="false">IF(I186="","",ROUND(I186*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K186" s="6"/>
-      <c r="L186" s="26"/>
+      <c r="L186" s="6"/>
+      <c r="M186" s="6"/>
+      <c r="N186" s="26"/>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="30"/>
+      <c r="A187" s="31"/>
       <c r="B187" s="6"/>
       <c r="C187" s="8" t="str">
         <f aca="false">IF(OR(D187="",E187="",D187=E187),"",IF(E187&lt;D187,"BUY","SELL"))</f>
@@ -7685,19 +8091,21 @@
         <f aca="false">IF(I187="","",IF(I187&gt;0,"WIN",IF(I187&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I187" s="31" t="str">
+      <c r="I187" s="32" t="str">
         <f aca="false">IF(OR(G187="",C187=""),"",ROUND((G187-D187)/(D187-E187),2))</f>
         <v/>
       </c>
-      <c r="J187" s="32" t="str">
-        <f aca="false">IF(I187="","",ROUND(I187*$M$2*$M$3,2))</f>
+      <c r="J187" s="33" t="str">
+        <f aca="false">IF(I187="","",ROUND(I187*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K187" s="6"/>
-      <c r="L187" s="26"/>
+      <c r="L187" s="6"/>
+      <c r="M187" s="6"/>
+      <c r="N187" s="26"/>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="30"/>
+      <c r="A188" s="31"/>
       <c r="B188" s="6"/>
       <c r="C188" s="8" t="str">
         <f aca="false">IF(OR(D188="",E188="",D188=E188),"",IF(E188&lt;D188,"BUY","SELL"))</f>
@@ -7714,19 +8122,21 @@
         <f aca="false">IF(I188="","",IF(I188&gt;0,"WIN",IF(I188&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I188" s="31" t="str">
+      <c r="I188" s="32" t="str">
         <f aca="false">IF(OR(G188="",C188=""),"",ROUND((G188-D188)/(D188-E188),2))</f>
         <v/>
       </c>
-      <c r="J188" s="32" t="str">
-        <f aca="false">IF(I188="","",ROUND(I188*$M$2*$M$3,2))</f>
+      <c r="J188" s="33" t="str">
+        <f aca="false">IF(I188="","",ROUND(I188*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K188" s="6"/>
-      <c r="L188" s="26"/>
+      <c r="L188" s="6"/>
+      <c r="M188" s="6"/>
+      <c r="N188" s="26"/>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="30"/>
+      <c r="A189" s="31"/>
       <c r="B189" s="6"/>
       <c r="C189" s="8" t="str">
         <f aca="false">IF(OR(D189="",E189="",D189=E189),"",IF(E189&lt;D189,"BUY","SELL"))</f>
@@ -7743,19 +8153,21 @@
         <f aca="false">IF(I189="","",IF(I189&gt;0,"WIN",IF(I189&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I189" s="31" t="str">
+      <c r="I189" s="32" t="str">
         <f aca="false">IF(OR(G189="",C189=""),"",ROUND((G189-D189)/(D189-E189),2))</f>
         <v/>
       </c>
-      <c r="J189" s="32" t="str">
-        <f aca="false">IF(I189="","",ROUND(I189*$M$2*$M$3,2))</f>
+      <c r="J189" s="33" t="str">
+        <f aca="false">IF(I189="","",ROUND(I189*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K189" s="6"/>
-      <c r="L189" s="26"/>
+      <c r="L189" s="6"/>
+      <c r="M189" s="6"/>
+      <c r="N189" s="26"/>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="30"/>
+      <c r="A190" s="31"/>
       <c r="B190" s="6"/>
       <c r="C190" s="8" t="str">
         <f aca="false">IF(OR(D190="",E190="",D190=E190),"",IF(E190&lt;D190,"BUY","SELL"))</f>
@@ -7772,19 +8184,21 @@
         <f aca="false">IF(I190="","",IF(I190&gt;0,"WIN",IF(I190&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I190" s="31" t="str">
+      <c r="I190" s="32" t="str">
         <f aca="false">IF(OR(G190="",C190=""),"",ROUND((G190-D190)/(D190-E190),2))</f>
         <v/>
       </c>
-      <c r="J190" s="32" t="str">
-        <f aca="false">IF(I190="","",ROUND(I190*$M$2*$M$3,2))</f>
+      <c r="J190" s="33" t="str">
+        <f aca="false">IF(I190="","",ROUND(I190*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K190" s="6"/>
-      <c r="L190" s="26"/>
+      <c r="L190" s="6"/>
+      <c r="M190" s="6"/>
+      <c r="N190" s="26"/>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="30"/>
+      <c r="A191" s="31"/>
       <c r="B191" s="6"/>
       <c r="C191" s="8" t="str">
         <f aca="false">IF(OR(D191="",E191="",D191=E191),"",IF(E191&lt;D191,"BUY","SELL"))</f>
@@ -7801,19 +8215,21 @@
         <f aca="false">IF(I191="","",IF(I191&gt;0,"WIN",IF(I191&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I191" s="31" t="str">
+      <c r="I191" s="32" t="str">
         <f aca="false">IF(OR(G191="",C191=""),"",ROUND((G191-D191)/(D191-E191),2))</f>
         <v/>
       </c>
-      <c r="J191" s="32" t="str">
-        <f aca="false">IF(I191="","",ROUND(I191*$M$2*$M$3,2))</f>
+      <c r="J191" s="33" t="str">
+        <f aca="false">IF(I191="","",ROUND(I191*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K191" s="6"/>
-      <c r="L191" s="26"/>
+      <c r="L191" s="6"/>
+      <c r="M191" s="6"/>
+      <c r="N191" s="26"/>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="30"/>
+      <c r="A192" s="31"/>
       <c r="B192" s="6"/>
       <c r="C192" s="8" t="str">
         <f aca="false">IF(OR(D192="",E192="",D192=E192),"",IF(E192&lt;D192,"BUY","SELL"))</f>
@@ -7830,19 +8246,21 @@
         <f aca="false">IF(I192="","",IF(I192&gt;0,"WIN",IF(I192&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I192" s="31" t="str">
+      <c r="I192" s="32" t="str">
         <f aca="false">IF(OR(G192="",C192=""),"",ROUND((G192-D192)/(D192-E192),2))</f>
         <v/>
       </c>
-      <c r="J192" s="32" t="str">
-        <f aca="false">IF(I192="","",ROUND(I192*$M$2*$M$3,2))</f>
+      <c r="J192" s="33" t="str">
+        <f aca="false">IF(I192="","",ROUND(I192*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K192" s="6"/>
-      <c r="L192" s="26"/>
+      <c r="L192" s="6"/>
+      <c r="M192" s="6"/>
+      <c r="N192" s="26"/>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="30"/>
+      <c r="A193" s="31"/>
       <c r="B193" s="6"/>
       <c r="C193" s="8" t="str">
         <f aca="false">IF(OR(D193="",E193="",D193=E193),"",IF(E193&lt;D193,"BUY","SELL"))</f>
@@ -7859,19 +8277,21 @@
         <f aca="false">IF(I193="","",IF(I193&gt;0,"WIN",IF(I193&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I193" s="31" t="str">
+      <c r="I193" s="32" t="str">
         <f aca="false">IF(OR(G193="",C193=""),"",ROUND((G193-D193)/(D193-E193),2))</f>
         <v/>
       </c>
-      <c r="J193" s="32" t="str">
-        <f aca="false">IF(I193="","",ROUND(I193*$M$2*$M$3,2))</f>
+      <c r="J193" s="33" t="str">
+        <f aca="false">IF(I193="","",ROUND(I193*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K193" s="6"/>
-      <c r="L193" s="26"/>
+      <c r="L193" s="6"/>
+      <c r="M193" s="6"/>
+      <c r="N193" s="26"/>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="30"/>
+      <c r="A194" s="31"/>
       <c r="B194" s="6"/>
       <c r="C194" s="8" t="str">
         <f aca="false">IF(OR(D194="",E194="",D194=E194),"",IF(E194&lt;D194,"BUY","SELL"))</f>
@@ -7888,19 +8308,21 @@
         <f aca="false">IF(I194="","",IF(I194&gt;0,"WIN",IF(I194&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I194" s="31" t="str">
+      <c r="I194" s="32" t="str">
         <f aca="false">IF(OR(G194="",C194=""),"",ROUND((G194-D194)/(D194-E194),2))</f>
         <v/>
       </c>
-      <c r="J194" s="32" t="str">
-        <f aca="false">IF(I194="","",ROUND(I194*$M$2*$M$3,2))</f>
+      <c r="J194" s="33" t="str">
+        <f aca="false">IF(I194="","",ROUND(I194*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K194" s="6"/>
-      <c r="L194" s="26"/>
+      <c r="L194" s="6"/>
+      <c r="M194" s="6"/>
+      <c r="N194" s="26"/>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="30"/>
+      <c r="A195" s="31"/>
       <c r="B195" s="6"/>
       <c r="C195" s="8" t="str">
         <f aca="false">IF(OR(D195="",E195="",D195=E195),"",IF(E195&lt;D195,"BUY","SELL"))</f>
@@ -7917,19 +8339,21 @@
         <f aca="false">IF(I195="","",IF(I195&gt;0,"WIN",IF(I195&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I195" s="31" t="str">
+      <c r="I195" s="32" t="str">
         <f aca="false">IF(OR(G195="",C195=""),"",ROUND((G195-D195)/(D195-E195),2))</f>
         <v/>
       </c>
-      <c r="J195" s="32" t="str">
-        <f aca="false">IF(I195="","",ROUND(I195*$M$2*$M$3,2))</f>
+      <c r="J195" s="33" t="str">
+        <f aca="false">IF(I195="","",ROUND(I195*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K195" s="6"/>
-      <c r="L195" s="26"/>
+      <c r="L195" s="6"/>
+      <c r="M195" s="6"/>
+      <c r="N195" s="26"/>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="30"/>
+      <c r="A196" s="31"/>
       <c r="B196" s="6"/>
       <c r="C196" s="8" t="str">
         <f aca="false">IF(OR(D196="",E196="",D196=E196),"",IF(E196&lt;D196,"BUY","SELL"))</f>
@@ -7946,19 +8370,21 @@
         <f aca="false">IF(I196="","",IF(I196&gt;0,"WIN",IF(I196&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I196" s="31" t="str">
+      <c r="I196" s="32" t="str">
         <f aca="false">IF(OR(G196="",C196=""),"",ROUND((G196-D196)/(D196-E196),2))</f>
         <v/>
       </c>
-      <c r="J196" s="32" t="str">
-        <f aca="false">IF(I196="","",ROUND(I196*$M$2*$M$3,2))</f>
+      <c r="J196" s="33" t="str">
+        <f aca="false">IF(I196="","",ROUND(I196*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K196" s="6"/>
-      <c r="L196" s="26"/>
+      <c r="L196" s="6"/>
+      <c r="M196" s="6"/>
+      <c r="N196" s="26"/>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="30"/>
+      <c r="A197" s="31"/>
       <c r="B197" s="6"/>
       <c r="C197" s="8" t="str">
         <f aca="false">IF(OR(D197="",E197="",D197=E197),"",IF(E197&lt;D197,"BUY","SELL"))</f>
@@ -7975,19 +8401,21 @@
         <f aca="false">IF(I197="","",IF(I197&gt;0,"WIN",IF(I197&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I197" s="31" t="str">
+      <c r="I197" s="32" t="str">
         <f aca="false">IF(OR(G197="",C197=""),"",ROUND((G197-D197)/(D197-E197),2))</f>
         <v/>
       </c>
-      <c r="J197" s="32" t="str">
-        <f aca="false">IF(I197="","",ROUND(I197*$M$2*$M$3,2))</f>
+      <c r="J197" s="33" t="str">
+        <f aca="false">IF(I197="","",ROUND(I197*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K197" s="6"/>
-      <c r="L197" s="26"/>
+      <c r="L197" s="6"/>
+      <c r="M197" s="6"/>
+      <c r="N197" s="26"/>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="30"/>
+      <c r="A198" s="31"/>
       <c r="B198" s="6"/>
       <c r="C198" s="8" t="str">
         <f aca="false">IF(OR(D198="",E198="",D198=E198),"",IF(E198&lt;D198,"BUY","SELL"))</f>
@@ -8004,19 +8432,21 @@
         <f aca="false">IF(I198="","",IF(I198&gt;0,"WIN",IF(I198&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I198" s="31" t="str">
+      <c r="I198" s="32" t="str">
         <f aca="false">IF(OR(G198="",C198=""),"",ROUND((G198-D198)/(D198-E198),2))</f>
         <v/>
       </c>
-      <c r="J198" s="32" t="str">
-        <f aca="false">IF(I198="","",ROUND(I198*$M$2*$M$3,2))</f>
+      <c r="J198" s="33" t="str">
+        <f aca="false">IF(I198="","",ROUND(I198*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K198" s="6"/>
-      <c r="L198" s="26"/>
+      <c r="L198" s="6"/>
+      <c r="M198" s="6"/>
+      <c r="N198" s="26"/>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="30"/>
+      <c r="A199" s="31"/>
       <c r="B199" s="6"/>
       <c r="C199" s="8" t="str">
         <f aca="false">IF(OR(D199="",E199="",D199=E199),"",IF(E199&lt;D199,"BUY","SELL"))</f>
@@ -8033,19 +8463,21 @@
         <f aca="false">IF(I199="","",IF(I199&gt;0,"WIN",IF(I199&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I199" s="31" t="str">
+      <c r="I199" s="32" t="str">
         <f aca="false">IF(OR(G199="",C199=""),"",ROUND((G199-D199)/(D199-E199),2))</f>
         <v/>
       </c>
-      <c r="J199" s="32" t="str">
-        <f aca="false">IF(I199="","",ROUND(I199*$M$2*$M$3,2))</f>
+      <c r="J199" s="33" t="str">
+        <f aca="false">IF(I199="","",ROUND(I199*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K199" s="6"/>
-      <c r="L199" s="26"/>
+      <c r="L199" s="6"/>
+      <c r="M199" s="6"/>
+      <c r="N199" s="26"/>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="30"/>
+      <c r="A200" s="31"/>
       <c r="B200" s="6"/>
       <c r="C200" s="8" t="str">
         <f aca="false">IF(OR(D200="",E200="",D200=E200),"",IF(E200&lt;D200,"BUY","SELL"))</f>
@@ -8062,19 +8494,21 @@
         <f aca="false">IF(I200="","",IF(I200&gt;0,"WIN",IF(I200&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I200" s="31" t="str">
+      <c r="I200" s="32" t="str">
         <f aca="false">IF(OR(G200="",C200=""),"",ROUND((G200-D200)/(D200-E200),2))</f>
         <v/>
       </c>
-      <c r="J200" s="32" t="str">
-        <f aca="false">IF(I200="","",ROUND(I200*$M$2*$M$3,2))</f>
+      <c r="J200" s="33" t="str">
+        <f aca="false">IF(I200="","",ROUND(I200*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K200" s="6"/>
-      <c r="L200" s="26"/>
+      <c r="L200" s="6"/>
+      <c r="M200" s="6"/>
+      <c r="N200" s="26"/>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="30"/>
+      <c r="A201" s="31"/>
       <c r="B201" s="6"/>
       <c r="C201" s="8" t="str">
         <f aca="false">IF(OR(D201="",E201="",D201=E201),"",IF(E201&lt;D201,"BUY","SELL"))</f>
@@ -8091,19 +8525,21 @@
         <f aca="false">IF(I201="","",IF(I201&gt;0,"WIN",IF(I201&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I201" s="31" t="str">
+      <c r="I201" s="32" t="str">
         <f aca="false">IF(OR(G201="",C201=""),"",ROUND((G201-D201)/(D201-E201),2))</f>
         <v/>
       </c>
-      <c r="J201" s="32" t="str">
-        <f aca="false">IF(I201="","",ROUND(I201*$M$2*$M$3,2))</f>
+      <c r="J201" s="33" t="str">
+        <f aca="false">IF(I201="","",ROUND(I201*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K201" s="6"/>
-      <c r="L201" s="26"/>
+      <c r="L201" s="6"/>
+      <c r="M201" s="6"/>
+      <c r="N201" s="26"/>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="30"/>
+      <c r="A202" s="31"/>
       <c r="B202" s="6"/>
       <c r="C202" s="8" t="str">
         <f aca="false">IF(OR(D202="",E202="",D202=E202),"",IF(E202&lt;D202,"BUY","SELL"))</f>
@@ -8120,19 +8556,21 @@
         <f aca="false">IF(I202="","",IF(I202&gt;0,"WIN",IF(I202&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I202" s="31" t="str">
+      <c r="I202" s="32" t="str">
         <f aca="false">IF(OR(G202="",C202=""),"",ROUND((G202-D202)/(D202-E202),2))</f>
         <v/>
       </c>
-      <c r="J202" s="32" t="str">
-        <f aca="false">IF(I202="","",ROUND(I202*$M$2*$M$3,2))</f>
+      <c r="J202" s="33" t="str">
+        <f aca="false">IF(I202="","",ROUND(I202*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K202" s="6"/>
-      <c r="L202" s="26"/>
+      <c r="L202" s="6"/>
+      <c r="M202" s="6"/>
+      <c r="N202" s="26"/>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="30"/>
+      <c r="A203" s="31"/>
       <c r="B203" s="6"/>
       <c r="C203" s="8" t="str">
         <f aca="false">IF(OR(D203="",E203="",D203=E203),"",IF(E203&lt;D203,"BUY","SELL"))</f>
@@ -8149,19 +8587,21 @@
         <f aca="false">IF(I203="","",IF(I203&gt;0,"WIN",IF(I203&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I203" s="31" t="str">
+      <c r="I203" s="32" t="str">
         <f aca="false">IF(OR(G203="",C203=""),"",ROUND((G203-D203)/(D203-E203),2))</f>
         <v/>
       </c>
-      <c r="J203" s="32" t="str">
-        <f aca="false">IF(I203="","",ROUND(I203*$M$2*$M$3,2))</f>
+      <c r="J203" s="33" t="str">
+        <f aca="false">IF(I203="","",ROUND(I203*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K203" s="6"/>
-      <c r="L203" s="26"/>
+      <c r="L203" s="6"/>
+      <c r="M203" s="6"/>
+      <c r="N203" s="26"/>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="30"/>
+      <c r="A204" s="31"/>
       <c r="B204" s="6"/>
       <c r="C204" s="8" t="str">
         <f aca="false">IF(OR(D204="",E204="",D204=E204),"",IF(E204&lt;D204,"BUY","SELL"))</f>
@@ -8178,19 +8618,21 @@
         <f aca="false">IF(I204="","",IF(I204&gt;0,"WIN",IF(I204&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I204" s="31" t="str">
+      <c r="I204" s="32" t="str">
         <f aca="false">IF(OR(G204="",C204=""),"",ROUND((G204-D204)/(D204-E204),2))</f>
         <v/>
       </c>
-      <c r="J204" s="32" t="str">
-        <f aca="false">IF(I204="","",ROUND(I204*$M$2*$M$3,2))</f>
+      <c r="J204" s="33" t="str">
+        <f aca="false">IF(I204="","",ROUND(I204*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K204" s="6"/>
-      <c r="L204" s="26"/>
+      <c r="L204" s="6"/>
+      <c r="M204" s="6"/>
+      <c r="N204" s="26"/>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="30"/>
+      <c r="A205" s="31"/>
       <c r="B205" s="6"/>
       <c r="C205" s="8" t="str">
         <f aca="false">IF(OR(D205="",E205="",D205=E205),"",IF(E205&lt;D205,"BUY","SELL"))</f>
@@ -8207,19 +8649,21 @@
         <f aca="false">IF(I205="","",IF(I205&gt;0,"WIN",IF(I205&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I205" s="31" t="str">
+      <c r="I205" s="32" t="str">
         <f aca="false">IF(OR(G205="",C205=""),"",ROUND((G205-D205)/(D205-E205),2))</f>
         <v/>
       </c>
-      <c r="J205" s="32" t="str">
-        <f aca="false">IF(I205="","",ROUND(I205*$M$2*$M$3,2))</f>
+      <c r="J205" s="33" t="str">
+        <f aca="false">IF(I205="","",ROUND(I205*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K205" s="6"/>
-      <c r="L205" s="26"/>
+      <c r="L205" s="6"/>
+      <c r="M205" s="6"/>
+      <c r="N205" s="26"/>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="30"/>
+      <c r="A206" s="31"/>
       <c r="B206" s="6"/>
       <c r="C206" s="8" t="str">
         <f aca="false">IF(OR(D206="",E206="",D206=E206),"",IF(E206&lt;D206,"BUY","SELL"))</f>
@@ -8236,16 +8680,18 @@
         <f aca="false">IF(I206="","",IF(I206&gt;0,"WIN",IF(I206&lt;0,"LOSS","BE")))</f>
         <v/>
       </c>
-      <c r="I206" s="31" t="str">
+      <c r="I206" s="32" t="str">
         <f aca="false">IF(OR(G206="",C206=""),"",ROUND((G206-D206)/(D206-E206),2))</f>
         <v/>
       </c>
-      <c r="J206" s="32" t="str">
-        <f aca="false">IF(I206="","",ROUND(I206*$M$2*$M$3,2))</f>
+      <c r="J206" s="33" t="str">
+        <f aca="false">IF(I206="","",ROUND(I206*$O$2*$O$3,2))</f>
         <v/>
       </c>
       <c r="K206" s="6"/>
-      <c r="L206" s="26"/>
+      <c r="L206" s="6"/>
+      <c r="M206" s="6"/>
+      <c r="N206" s="26"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H7:H206">
@@ -8261,7 +8707,7 @@
       <formula1>Calculator!$D$19:$D$25</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K7:K206" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K7:M206" type="list">
       <formula1>"Yes,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -8281,123 +8727,123 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="33" t="s">
-        <v>98</v>
-      </c>
-      <c r="B3" s="34" t="n">
+      <c r="A3" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="B3" s="35" t="n">
         <f aca="false">COUNT('Trade Log'!I7:I206)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="33" t="s">
-        <v>99</v>
-      </c>
-      <c r="B4" s="34" t="n">
+      <c r="A4" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="B4" s="35" t="n">
         <f aca="false">COUNTIF('Trade Log'!H7:H206,"WIN")</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="33" t="s">
-        <v>100</v>
-      </c>
-      <c r="B5" s="34" t="n">
+      <c r="A5" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="B5" s="35" t="n">
         <f aca="false">COUNTIF('Trade Log'!H7:H206,"LOSS")</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="33" t="s">
+      <c r="A6" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="B6" s="35" t="n">
+      <c r="B6" s="36" t="n">
         <f aca="false">IFERROR(B4/B3,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="33" t="s">
+      <c r="A7" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="B7" s="36" t="n">
+      <c r="B7" s="37" t="n">
         <f aca="false">SUM('Trade Log'!I7:I206)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="33" t="s">
-        <v>101</v>
-      </c>
-      <c r="B8" s="36" t="n">
+      <c r="A8" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" s="37" t="n">
         <f aca="false">IFERROR(B7/B3,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="33" t="s">
-        <v>102</v>
-      </c>
-      <c r="B9" s="35" t="n">
+      <c r="A9" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="B9" s="36" t="n">
         <f aca="false">IFERROR(COUNTIF('Trade Log'!K7:K206,"Yes")/B3,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="33" t="s">
-        <v>103</v>
-      </c>
-      <c r="B10" s="37" t="n">
+      <c r="A10" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="B10" s="38" t="n">
         <f aca="false">SUM('Trade Log'!J7:J206)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="33" t="s">
+      <c r="A11" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="B11" s="29" t="n">
-        <f aca="false">'Trade Log'!M4</f>
+      <c r="B11" s="30" t="n">
+        <f aca="false">'Trade Log'!O4</f>
         <v>10000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="38" t="s">
-        <v>104</v>
+      <c r="A13" s="39" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="39" t="str">
+      <c r="A14" s="40" t="str">
         <f aca="false">IF(B3&lt;50,"Not enough trades yet: "&amp;B3&amp;" of 50. Keep going.",IF(B9&lt;0.9,"You broke the rules too often. The results don't count yet.",IF(B8&gt;=0.15,"Looks promising. Keep going to 100 trades to be sure.",IF(B8&lt;=0,"Not working as it is. Stop and review.","Too close to call. Keep going to 100 trades."))))</f>
         <v>Not enough trades yet: 0 of 50. Keep going.</v>
       </c>
-      <c r="B14" s="39"/>
-      <c r="C14" s="39"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
+      <c r="B14" s="40"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="38" t="s">
-        <v>106</v>
+      <c r="A18" s="39" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8405,7 +8851,7 @@
         <v>35</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C19" s="17" t="s">
         <v>80</v>
@@ -8419,7 +8865,7 @@
         <f aca="false">COUNTIFS('Trade Log'!B7:B206,A20,'Trade Log'!I7:I206,"&gt;-99")</f>
         <v>0</v>
       </c>
-      <c r="C20" s="31" t="n">
+      <c r="C20" s="32" t="n">
         <f aca="false">SUMIF('Trade Log'!B7:B206,A20,'Trade Log'!I7:I206)</f>
         <v>0</v>
       </c>
@@ -8432,7 +8878,7 @@
         <f aca="false">COUNTIFS('Trade Log'!B7:B206,A21,'Trade Log'!I7:I206,"&gt;-99")</f>
         <v>0</v>
       </c>
-      <c r="C21" s="31" t="n">
+      <c r="C21" s="32" t="n">
         <f aca="false">SUMIF('Trade Log'!B7:B206,A21,'Trade Log'!I7:I206)</f>
         <v>0</v>
       </c>
@@ -8445,7 +8891,7 @@
         <f aca="false">COUNTIFS('Trade Log'!B7:B206,A22,'Trade Log'!I7:I206,"&gt;-99")</f>
         <v>0</v>
       </c>
-      <c r="C22" s="31" t="n">
+      <c r="C22" s="32" t="n">
         <f aca="false">SUMIF('Trade Log'!B7:B206,A22,'Trade Log'!I7:I206)</f>
         <v>0</v>
       </c>
@@ -8458,7 +8904,7 @@
         <f aca="false">COUNTIFS('Trade Log'!B7:B206,A23,'Trade Log'!I7:I206,"&gt;-99")</f>
         <v>0</v>
       </c>
-      <c r="C23" s="31" t="n">
+      <c r="C23" s="32" t="n">
         <f aca="false">SUMIF('Trade Log'!B7:B206,A23,'Trade Log'!I7:I206)</f>
         <v>0</v>
       </c>
@@ -8471,7 +8917,7 @@
         <f aca="false">COUNTIFS('Trade Log'!B7:B206,A24,'Trade Log'!I7:I206,"&gt;-99")</f>
         <v>0</v>
       </c>
-      <c r="C24" s="31" t="n">
+      <c r="C24" s="32" t="n">
         <f aca="false">SUMIF('Trade Log'!B7:B206,A24,'Trade Log'!I7:I206)</f>
         <v>0</v>
       </c>
@@ -8484,7 +8930,7 @@
         <f aca="false">COUNTIFS('Trade Log'!B7:B206,A25,'Trade Log'!I7:I206,"&gt;-99")</f>
         <v>0</v>
       </c>
-      <c r="C25" s="31" t="n">
+      <c r="C25" s="32" t="n">
         <f aca="false">SUMIF('Trade Log'!B7:B206,A25,'Trade Log'!I7:I206)</f>
         <v>0</v>
       </c>
@@ -8497,9 +8943,101 @@
         <f aca="false">COUNTIFS('Trade Log'!B7:B206,A26,'Trade Log'!I7:I206,"&gt;-99")</f>
         <v>0</v>
       </c>
-      <c r="C26" s="31" t="n">
+      <c r="C26" s="32" t="n">
         <f aca="false">SUMIF('Trade Log'!B7:B206,A26,'Trade Log'!I7:I206)</f>
         <v>0</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="39" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="B31" s="22" t="n">
+        <f aca="false">COUNTIFS('Trade Log'!L7:L206,"Yes",'Trade Log'!I7:I206,"&gt;-99")</f>
+        <v>0</v>
+      </c>
+      <c r="C31" s="23" t="n">
+        <f aca="false">IFERROR(COUNTIFS('Trade Log'!L7:L206,"Yes",'Trade Log'!H7:H206,"WIN")/B31,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D31" s="32" t="n">
+        <f aca="false">IFERROR(AVERAGEIFS('Trade Log'!I7:I206,'Trade Log'!L7:L206,"Yes"),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="41" t="s">
+        <v>114</v>
+      </c>
+      <c r="B32" s="22" t="n">
+        <f aca="false">COUNTIFS('Trade Log'!L7:L206,"No",'Trade Log'!I7:I206,"&gt;-99")</f>
+        <v>0</v>
+      </c>
+      <c r="C32" s="23" t="n">
+        <f aca="false">IFERROR(COUNTIFS('Trade Log'!L7:L206,"No",'Trade Log'!H7:H206,"WIN")/B32,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D32" s="32" t="n">
+        <f aca="false">IFERROR(AVERAGEIFS('Trade Log'!I7:I206,'Trade Log'!L7:L206,"No"),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="B33" s="22" t="n">
+        <f aca="false">COUNTIFS('Trade Log'!M7:M206,"Yes",'Trade Log'!I7:I206,"&gt;-99")</f>
+        <v>0</v>
+      </c>
+      <c r="C33" s="23" t="n">
+        <f aca="false">IFERROR(COUNTIFS('Trade Log'!M7:M206,"Yes",'Trade Log'!H7:H206,"WIN")/B33,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D33" s="32" t="n">
+        <f aca="false">IFERROR(AVERAGEIFS('Trade Log'!I7:I206,'Trade Log'!M7:M206,"Yes"),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="B34" s="22" t="n">
+        <f aca="false">COUNTIFS('Trade Log'!M7:M206,"No",'Trade Log'!I7:I206,"&gt;-99")</f>
+        <v>0</v>
+      </c>
+      <c r="C34" s="23" t="n">
+        <f aca="false">IFERROR(COUNTIFS('Trade Log'!M7:M206,"No",'Trade Log'!H7:H206,"WIN")/B34,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D34" s="32" t="n">
+        <f aca="false">IFERROR(AVERAGEIFS('Trade Log'!I7:I206,'Trade Log'!M7:M206,"No"),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="15" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
